--- a/IM/202606_Service_Count_Report.xlsx
+++ b/IM/202606_Service_Count_Report.xlsx
@@ -11,14 +11,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Report'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$AA$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$AA$98</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="301">
   <si>
     <t>服務次數統計表        篩選月份：202606</t>
   </si>
@@ -122,27 +122,252 @@
     <t>TJ22</t>
   </si>
   <si>
+    <t>劉柏均</t>
+  </si>
+  <si>
+    <t>2026-06-02</t>
+  </si>
+  <si>
+    <t>10:00:00</t>
+  </si>
+  <si>
+    <t>10:22:00</t>
+  </si>
+  <si>
+    <t>T252000054</t>
+  </si>
+  <si>
+    <t>eS-2520AC 彩色複合機</t>
+  </si>
+  <si>
+    <t>MFP商品</t>
+  </si>
+  <si>
+    <t xml:space="preserve">佳諾金屬有限公司 </t>
+  </si>
+  <si>
+    <t>新北市永和區中和路343號17樓</t>
+  </si>
+  <si>
+    <t>服務</t>
+  </si>
+  <si>
+    <t>O</t>
+  </si>
+  <si>
+    <t>Pm</t>
+  </si>
+  <si>
+    <t>09:20:00</t>
+  </si>
+  <si>
+    <t>09:45:00</t>
+  </si>
+  <si>
+    <t>T252000089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">漢庭營造股份有限公司 </t>
+  </si>
+  <si>
+    <t>新北市中和區新興街9號2樓</t>
+  </si>
+  <si>
+    <t>中和</t>
+  </si>
+  <si>
+    <t>抄表</t>
+  </si>
+  <si>
+    <t>16:00:00</t>
+  </si>
+  <si>
+    <t>16:24:00</t>
+  </si>
+  <si>
+    <t>T252000150</t>
+  </si>
+  <si>
+    <t>台北市士林區延平北路5段257巷2弄1號</t>
+  </si>
+  <si>
+    <t>士林</t>
+  </si>
+  <si>
+    <t>2026-06-03</t>
+  </si>
+  <si>
+    <t>09:03:00</t>
+  </si>
+  <si>
+    <t>09:27:00</t>
+  </si>
+  <si>
+    <t>T302800001</t>
+  </si>
+  <si>
+    <t>eS-3028A 黑白複合機</t>
+  </si>
+  <si>
+    <t>財團法人台北國際社區青年育樂活動中心基金會</t>
+  </si>
+  <si>
+    <t>台北市士林區天玉街26-1號</t>
+  </si>
+  <si>
+    <t>天玉街</t>
+  </si>
+  <si>
+    <t>10:30:00</t>
+  </si>
+  <si>
+    <t>10:53:00</t>
+  </si>
+  <si>
+    <t>T352800006</t>
+  </si>
+  <si>
+    <t>eS-3528A 黑白複合機</t>
+  </si>
+  <si>
+    <t xml:space="preserve">中原造像股份有限公司 </t>
+  </si>
+  <si>
+    <t>新北市中和區建康路130號7樓-11</t>
+  </si>
+  <si>
+    <t>15:50:00</t>
+  </si>
+  <si>
+    <t>16:25:00</t>
+  </si>
+  <si>
+    <t>11:05:00</t>
+  </si>
+  <si>
+    <t>11:40:00</t>
+  </si>
+  <si>
+    <t>T352800007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">中康彩色印刷事業股份有限公司 </t>
+  </si>
+  <si>
+    <t>新北市中和區建二路56號</t>
+  </si>
+  <si>
+    <t>16:40:00</t>
+  </si>
+  <si>
+    <t>17:15:00</t>
+  </si>
+  <si>
+    <t>Pm 清定著積碳</t>
+  </si>
+  <si>
+    <t>14:00:00</t>
+  </si>
+  <si>
+    <t>15:15:00</t>
+  </si>
+  <si>
+    <t>THILF02442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">萊爾富國際股份有限公司 </t>
+  </si>
+  <si>
+    <t>新北市八里區商港路46.48號</t>
+  </si>
+  <si>
+    <t>北縣商港店</t>
+  </si>
+  <si>
+    <t>裝潢撤機</t>
+  </si>
+  <si>
+    <t>10:20:00</t>
+  </si>
+  <si>
+    <t>10:41:00</t>
+  </si>
+  <si>
+    <t>THILF04184</t>
+  </si>
+  <si>
+    <t>新北市三重區大仁街52號</t>
+  </si>
+  <si>
+    <t>三重今大店</t>
+  </si>
+  <si>
+    <t>PMQ2 EDC</t>
+  </si>
+  <si>
+    <t>09:47:00</t>
+  </si>
+  <si>
+    <t>10:10:00</t>
+  </si>
+  <si>
+    <t>THILF04804</t>
+  </si>
+  <si>
+    <t>新北市三重區國隆路19、21、23號</t>
+  </si>
+  <si>
+    <t>三重國隆店</t>
+  </si>
+  <si>
+    <t>2026-05-28</t>
+  </si>
+  <si>
+    <t>11:19:00</t>
+  </si>
+  <si>
+    <t>THILF0D024</t>
+  </si>
+  <si>
+    <t>新北市三重區三民街100,102號</t>
+  </si>
+  <si>
+    <t>三重三民店</t>
+  </si>
+  <si>
     <t>吳宗鴻</t>
   </si>
   <si>
+    <t>09:30:00</t>
+  </si>
+  <si>
+    <t>10:59:00</t>
+  </si>
+  <si>
+    <t>T252000025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">品興營造股份有限公司 </t>
+  </si>
+  <si>
+    <t>新北市泰山區莊田路與信華三街交叉口(華固一莊)</t>
+  </si>
+  <si>
+    <t>華固一莊</t>
+  </si>
+  <si>
+    <t>PM抄表</t>
+  </si>
+  <si>
     <t>2026-06-01</t>
   </si>
   <si>
-    <t>15:15:00</t>
-  </si>
-  <si>
     <t>15:30:00</t>
   </si>
   <si>
     <t>T252000125</t>
   </si>
   <si>
-    <t>eS-2520AC 彩色複合機</t>
-  </si>
-  <si>
-    <t>MFP商品</t>
-  </si>
-  <si>
     <t>合作金庫商業銀行股份有限公司林口文化分行</t>
   </si>
   <si>
@@ -152,16 +377,19 @@
     <t>林口文化2F放款部</t>
   </si>
   <si>
-    <t>服務</t>
-  </si>
-  <si>
-    <t>O</t>
-  </si>
-  <si>
-    <t>PM抄表</t>
-  </si>
-  <si>
-    <t>抄表</t>
+    <t>11:25:00</t>
+  </si>
+  <si>
+    <t>11:44:00</t>
+  </si>
+  <si>
+    <t>T252000153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">德森精密有限公司 </t>
+  </si>
+  <si>
+    <t>新北市林口區文化北路1段60巷108號3樓</t>
   </si>
   <si>
     <t>14:45:00</t>
@@ -185,6 +413,36 @@
     <t>林口長庚分行</t>
   </si>
   <si>
+    <t>12:15:00</t>
+  </si>
+  <si>
+    <t>12:34:00</t>
+  </si>
+  <si>
+    <t>T301800172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">智基科技開發股份有限公司 </t>
+  </si>
+  <si>
+    <t>新北市淡水區中山路123號3樓(淡水分校)</t>
+  </si>
+  <si>
+    <t>淡水</t>
+  </si>
+  <si>
+    <t>10:48:00</t>
+  </si>
+  <si>
+    <t>T302800006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">信宇顧問有限公司 </t>
+  </si>
+  <si>
+    <t>新北市淡水區民族路50巷46號3樓</t>
+  </si>
+  <si>
     <t>14:20:00</t>
   </si>
   <si>
@@ -192,15 +450,51 @@
   </si>
   <si>
     <t>T302800131</t>
-  </si>
-  <si>
-    <t>eS-3028A 黑白複合機</t>
   </si>
   <si>
     <t>PM抄表
 送黑色碳粉 1</t>
   </si>
   <si>
+    <t>11:00:00</t>
+  </si>
+  <si>
+    <t>12:11:00</t>
+  </si>
+  <si>
+    <t>T351500137</t>
+  </si>
+  <si>
+    <t>eS-3515AC 彩色複合機</t>
+  </si>
+  <si>
+    <t>華南永昌綜合証券股份有限公司-淡水?</t>
+  </si>
+  <si>
+    <t>新北市淡水區中正路28號4樓(淡水)</t>
+  </si>
+  <si>
+    <t>12:00:00</t>
+  </si>
+  <si>
+    <t>12:58:00</t>
+  </si>
+  <si>
+    <t>T352500149</t>
+  </si>
+  <si>
+    <t>eS-3525AC 彩色複合機</t>
+  </si>
+  <si>
+    <t xml:space="preserve">東南旅行社股份有限公司 </t>
+  </si>
+  <si>
+    <t>桃園市蘆竹區忠孝東路17之3號(南崁分公司</t>
+  </si>
+  <si>
+    <t>南崁分公司</t>
+  </si>
+  <si>
     <t>15:31:00</t>
   </si>
   <si>
@@ -219,9 +513,106 @@
     <t>林口文化1F營業部</t>
   </si>
   <si>
+    <t>THILF02322</t>
+  </si>
+  <si>
+    <t>桃園市蘆竹區大華街69-1、69-2號</t>
+  </si>
+  <si>
+    <t>蘆竹大華店</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PMQ2 EDC
+</t>
+  </si>
+  <si>
+    <t>15:14:00</t>
+  </si>
+  <si>
+    <t>裝潢撤機完工</t>
+  </si>
+  <si>
+    <t>14:50:00</t>
+  </si>
+  <si>
+    <t>15:10:00</t>
+  </si>
+  <si>
+    <t>THILF03556</t>
+  </si>
+  <si>
+    <t>桃園市蘆竹區大竹北路180號</t>
+  </si>
+  <si>
+    <t>桃縣蘆華店</t>
+  </si>
+  <si>
+    <t>13:10:00</t>
+  </si>
+  <si>
+    <t>13:38:00</t>
+  </si>
+  <si>
+    <t>THILF03880</t>
+  </si>
+  <si>
+    <t>桃園市蘆竹區富國路二段2號</t>
+  </si>
+  <si>
+    <t>桃縣富竹店</t>
+  </si>
+  <si>
+    <t>14:34:00</t>
+  </si>
+  <si>
+    <t>THILF04289</t>
+  </si>
+  <si>
+    <t>桃園市蘆竹區中興路118號</t>
+  </si>
+  <si>
+    <t>蘆竹六股埤</t>
+  </si>
+  <si>
     <t>湯家瑋</t>
   </si>
   <si>
+    <t>T252000086</t>
+  </si>
+  <si>
+    <t>新北市三重區仁義街79巷旁工地</t>
+  </si>
+  <si>
+    <t>華固慕川</t>
+  </si>
+  <si>
+    <t>pm</t>
+  </si>
+  <si>
+    <t>T252000113</t>
+  </si>
+  <si>
+    <t>新北市三重區仁義街與元信一街交叉口</t>
+  </si>
+  <si>
+    <t>華固織幸</t>
+  </si>
+  <si>
+    <t>T252000136</t>
+  </si>
+  <si>
+    <t>新北市三重區德厚街76號7樓</t>
+  </si>
+  <si>
+    <t>三重</t>
+  </si>
+  <si>
+    <t>14:05:00</t>
+  </si>
+  <si>
+    <t>發票</t>
+  </si>
+  <si>
     <t>12:30:00</t>
   </si>
   <si>
@@ -240,7 +631,31 @@
     <t>異地備援泰山</t>
   </si>
   <si>
-    <t>pm</t>
+    <t>08:30:00</t>
+  </si>
+  <si>
+    <t>09:00:00</t>
+  </si>
+  <si>
+    <t>T302800007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">財團法人台灣省私立台灣盲人重建院 </t>
+  </si>
+  <si>
+    <t>新北市新莊區中正路384號3樓</t>
+  </si>
+  <si>
+    <t>3F</t>
+  </si>
+  <si>
+    <t>T302800008</t>
+  </si>
+  <si>
+    <t>新北市新莊區中正路384號4樓</t>
+  </si>
+  <si>
+    <t>4F</t>
   </si>
   <si>
     <t>16:10:00</t>
@@ -267,9 +682,6 @@
     <t>11:30:00</t>
   </si>
   <si>
-    <t>12:00:00</t>
-  </si>
-  <si>
     <t>T302800053</t>
   </si>
   <si>
@@ -279,9 +691,6 @@
     <t>業務部辦公室</t>
   </si>
   <si>
-    <t>11:00:00</t>
-  </si>
-  <si>
     <t>T302800152</t>
   </si>
   <si>
@@ -291,12 +700,6 @@
     <t>營管部</t>
   </si>
   <si>
-    <t>10:00:00</t>
-  </si>
-  <si>
-    <t>10:30:00</t>
-  </si>
-  <si>
     <t>T302800153</t>
   </si>
   <si>
@@ -306,12 +709,6 @@
     <t>走道</t>
   </si>
   <si>
-    <t>08:30:00</t>
-  </si>
-  <si>
-    <t>09:00:00</t>
-  </si>
-  <si>
     <t>T302800154</t>
   </si>
   <si>
@@ -321,9 +718,6 @@
     <t>櫃台2</t>
   </si>
   <si>
-    <t>09:30:00</t>
-  </si>
-  <si>
     <t>T302800155</t>
   </si>
   <si>
@@ -342,12 +736,24 @@
     <t>工程部1</t>
   </si>
   <si>
+    <t>T351800045</t>
+  </si>
+  <si>
+    <t>eS-3518A 黑白複合機</t>
+  </si>
+  <si>
+    <t xml:space="preserve">台灣善美的股份有限公司 </t>
+  </si>
+  <si>
+    <t>新北市五股區五工六路35號1樓(五股生鮮物流)</t>
+  </si>
+  <si>
+    <t>五股生鮮物流</t>
+  </si>
+  <si>
     <t>T351800082</t>
   </si>
   <si>
-    <t>eS-3518A 黑白複合機</t>
-  </si>
-  <si>
     <t>新北市新莊區中正路651-5號10樓(櫃台1)</t>
   </si>
   <si>
@@ -366,7 +772,64 @@
     <t>13:30:00</t>
   </si>
   <si>
-    <t>14:00:00</t>
+    <t>T352500148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">宏偉營造股份有限公司 </t>
+  </si>
+  <si>
+    <t>新北市三重區光復路1段61巷26號2樓</t>
+  </si>
+  <si>
+    <t>T352800011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">全聯實業股份有限公司 </t>
+  </si>
+  <si>
+    <t>新北市蘆洲區水湳街74號2樓</t>
+  </si>
+  <si>
+    <t>蘆洲北二處</t>
+  </si>
+  <si>
+    <t>T352800029</t>
+  </si>
+  <si>
+    <t>新北市五股區五工六路35號4樓(五股)</t>
+  </si>
+  <si>
+    <t>五股4樓</t>
+  </si>
+  <si>
+    <t>T352800030</t>
+  </si>
+  <si>
+    <t>新北市五股區五工六路35號1樓(五股檢品)</t>
+  </si>
+  <si>
+    <t>五股檢品</t>
+  </si>
+  <si>
+    <t>更換 OD OD刮 回刮 上下熱 取送分輪</t>
+  </si>
+  <si>
+    <t>T352800031</t>
+  </si>
+  <si>
+    <t>新北市五股區工商路128號1樓(五股DC廠工商運輸)</t>
+  </si>
+  <si>
+    <t>五股DC廠工商運輸</t>
+  </si>
+  <si>
+    <t>T352800032</t>
+  </si>
+  <si>
+    <t>新北市五股區五工六路35號1樓(五股運輸)</t>
+  </si>
+  <si>
+    <t>五股運輸</t>
   </si>
   <si>
     <t>T451800027</t>
@@ -381,9 +844,6 @@
     <t>台北客服4F申裝查核處(黑)</t>
   </si>
   <si>
-    <t>15:50:00</t>
-  </si>
-  <si>
     <t>T452800031</t>
   </si>
   <si>
@@ -399,18 +859,12 @@
     <t>台北客服4樓-2LJ15(黑)</t>
   </si>
   <si>
-    <t>15:10:00</t>
-  </si>
-  <si>
     <t>T452800069</t>
   </si>
   <si>
     <t>台北客服4樓-2LJ6(黑)</t>
   </si>
   <si>
-    <t>14:50:00</t>
-  </si>
-  <si>
     <t>T452800070</t>
   </si>
   <si>
@@ -424,6 +878,60 @@
   </si>
   <si>
     <t>台北客服4樓中(黑)</t>
+  </si>
+  <si>
+    <t>狄澤洋</t>
+  </si>
+  <si>
+    <t>15:20:00</t>
+  </si>
+  <si>
+    <t>15:33:00</t>
+  </si>
+  <si>
+    <t>THILF03551</t>
+  </si>
+  <si>
+    <t>新北市板橋區永豐街51-1.51-2號一樓全部</t>
+  </si>
+  <si>
+    <t>板橋板豐店</t>
+  </si>
+  <si>
+    <t>THILF04406</t>
+  </si>
+  <si>
+    <t>新北市板橋區貴興路89號、91號一樓</t>
+  </si>
+  <si>
+    <t>板橋稚暉店</t>
+  </si>
+  <si>
+    <t>PMQ2 EDC SC7</t>
+  </si>
+  <si>
+    <t>14:25:00</t>
+  </si>
+  <si>
+    <t>THILF05451</t>
+  </si>
+  <si>
+    <t>新北市板橋區懷仁街17、19、21號一樓</t>
+  </si>
+  <si>
+    <t>板橋懷仁店</t>
+  </si>
+  <si>
+    <t>一般件</t>
+  </si>
+  <si>
+    <t>其他</t>
+  </si>
+  <si>
+    <t>維修</t>
+  </si>
+  <si>
+    <t>票券紙無效票未撕除，排除後測試正常</t>
   </si>
   <si>
     <t>合計</t>
@@ -840,7 +1348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AB37"/>
+  <dimension ref="A1:AB98"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="true" style="0"/>
@@ -996,7 +1504,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="7">
-        <v>2026060125</v>
+        <v>2026060376</v>
       </c>
       <c r="C3" s="7">
         <v>1</v>
@@ -1031,21 +1539,19 @@
       <c r="M3" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="N3" s="8" t="s">
+      <c r="N3" s="8"/>
+      <c r="O3" s="7" t="s">
         <v>39</v>
-      </c>
-      <c r="O3" s="7" t="s">
-        <v>40</v>
       </c>
       <c r="P3" s="7"/>
       <c r="Q3" s="7">
-        <v>2375</v>
+        <v>1440</v>
       </c>
       <c r="R3" s="7">
-        <v>129731</v>
+        <v>18943</v>
       </c>
       <c r="S3" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="T3" s="7"/>
       <c r="U3" s="7"/>
@@ -1054,17 +1560,21 @@
       <c r="X3" s="7"/>
       <c r="Y3" s="7"/>
       <c r="Z3" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="AA3" s="7"/>
-      <c r="AB3" s="7"/>
+        <v>41</v>
+      </c>
+      <c r="AA3" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB3" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="1:28">
       <c r="A4" s="3">
         <v>2</v>
       </c>
       <c r="B4" s="3">
-        <v>2026060126</v>
+        <v>2026060340</v>
       </c>
       <c r="C4" s="3">
         <v>1</v>
@@ -1079,13 +1589,13 @@
         <v>31</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>35</v>
@@ -1094,23 +1604,23 @@
         <v>36</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="P4" s="3"/>
       <c r="Q4" s="3">
-        <v>2375</v>
+        <v>4424</v>
       </c>
       <c r="R4" s="3">
-        <v>129731</v>
+        <v>19026</v>
       </c>
       <c r="S4" s="3"/>
       <c r="T4" s="3"/>
@@ -1119,18 +1629,20 @@
       <c r="W4" s="3"/>
       <c r="X4" s="3"/>
       <c r="Y4" s="3"/>
-      <c r="Z4" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="AA4" s="3"/>
-      <c r="AB4" s="3"/>
+      <c r="Z4" s="6"/>
+      <c r="AA4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB4" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:28">
       <c r="A5" s="7">
         <v>3</v>
       </c>
       <c r="B5" s="7">
-        <v>2026060107</v>
+        <v>2026060555</v>
       </c>
       <c r="C5" s="7">
         <v>1</v>
@@ -1145,58 +1657,60 @@
         <v>31</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H5" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L5" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="I5" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="L5" s="8" t="s">
+      <c r="M5" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="N5" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="O5" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="M5" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="N5" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="O5" s="7" t="s">
-        <v>40</v>
-      </c>
       <c r="P5" s="7"/>
-      <c r="Q5" s="7"/>
+      <c r="Q5" s="7">
+        <v>2719</v>
+      </c>
       <c r="R5" s="7">
-        <v>313246</v>
-      </c>
-      <c r="S5" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>1717</v>
+      </c>
+      <c r="S5" s="7"/>
       <c r="T5" s="7"/>
       <c r="U5" s="7"/>
       <c r="V5" s="7"/>
       <c r="W5" s="7"/>
       <c r="X5" s="7"/>
       <c r="Y5" s="7"/>
-      <c r="Z5" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="AA5" s="7"/>
-      <c r="AB5" s="7"/>
+      <c r="Z5" s="8"/>
+      <c r="AA5" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB5" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:28">
       <c r="A6" s="3">
         <v>4</v>
       </c>
       <c r="B6" s="3">
-        <v>2026060108</v>
+        <v>2026060623</v>
       </c>
       <c r="C6" s="3">
         <v>1</v>
@@ -1208,39 +1722,39 @@
         <v>30</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="K6" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L6" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="M6" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="N6" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="O6" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="M6" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="N6" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="O6" s="3" t="s">
-        <v>43</v>
       </c>
       <c r="P6" s="3"/>
       <c r="Q6" s="3"/>
       <c r="R6" s="3">
-        <v>313246</v>
+        <v>83977</v>
       </c>
       <c r="S6" s="3"/>
       <c r="T6" s="3"/>
@@ -1249,18 +1763,20 @@
       <c r="W6" s="3"/>
       <c r="X6" s="3"/>
       <c r="Y6" s="3"/>
-      <c r="Z6" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="AA6" s="3"/>
-      <c r="AB6" s="3"/>
+      <c r="Z6" s="6"/>
+      <c r="AA6" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB6" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:28">
       <c r="A7" s="7">
         <v>5</v>
       </c>
       <c r="B7" s="7">
-        <v>2026060110</v>
+        <v>2026060404</v>
       </c>
       <c r="C7" s="7">
         <v>1</v>
@@ -1275,58 +1791,56 @@
         <v>31</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="K7" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L7" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="M7" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="N7" s="8"/>
+      <c r="O7" s="7" t="s">
         <v>48</v>
-      </c>
-      <c r="M7" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="N7" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="O7" s="7" t="s">
-        <v>40</v>
       </c>
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
       <c r="R7" s="7">
-        <v>113426</v>
-      </c>
-      <c r="S7" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>142473</v>
+      </c>
+      <c r="S7" s="7"/>
       <c r="T7" s="7"/>
       <c r="U7" s="7"/>
       <c r="V7" s="7"/>
       <c r="W7" s="7"/>
       <c r="X7" s="7"/>
       <c r="Y7" s="7"/>
-      <c r="Z7" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="AA7" s="7"/>
-      <c r="AB7" s="7"/>
+      <c r="Z7" s="8"/>
+      <c r="AA7" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB7" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="1:28">
       <c r="A8" s="3">
         <v>6</v>
       </c>
       <c r="B8" s="3">
-        <v>2026060111</v>
+        <v>2026060855</v>
       </c>
       <c r="C8" s="3">
         <v>1</v>
@@ -1338,41 +1852,41 @@
         <v>30</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="M8" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="N8" s="6" t="s">
-        <v>50</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="N8" s="6"/>
       <c r="O8" s="3" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
       <c r="R8" s="3">
-        <v>113426</v>
-      </c>
-      <c r="S8" s="3"/>
+        <v>142511</v>
+      </c>
+      <c r="S8" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T8" s="3"/>
       <c r="U8" s="3"/>
       <c r="V8" s="3"/>
@@ -1380,17 +1894,21 @@
       <c r="X8" s="3"/>
       <c r="Y8" s="3"/>
       <c r="Z8" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="AA8" s="3"/>
-      <c r="AB8" s="3"/>
+        <v>41</v>
+      </c>
+      <c r="AA8" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB8" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="1:28">
       <c r="A9" s="7">
         <v>7</v>
       </c>
       <c r="B9" s="7">
-        <v>2026060127</v>
+        <v>2026060391</v>
       </c>
       <c r="C9" s="7">
         <v>1</v>
@@ -1405,58 +1923,56 @@
         <v>31</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K9" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="M9" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="N9" s="8" t="s">
-        <v>61</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="N9" s="8"/>
       <c r="O9" s="7" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="P9" s="7"/>
       <c r="Q9" s="7"/>
       <c r="R9" s="7">
-        <v>212738</v>
-      </c>
-      <c r="S9" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>255338</v>
+      </c>
+      <c r="S9" s="7"/>
       <c r="T9" s="7"/>
       <c r="U9" s="7"/>
       <c r="V9" s="7"/>
       <c r="W9" s="7"/>
       <c r="X9" s="7"/>
       <c r="Y9" s="7"/>
-      <c r="Z9" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="AA9" s="7"/>
-      <c r="AB9" s="7"/>
+      <c r="Z9" s="8"/>
+      <c r="AA9" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB9" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:28">
       <c r="A10" s="3">
         <v>8</v>
       </c>
       <c r="B10" s="3">
-        <v>2026060128</v>
+        <v>2026060865</v>
       </c>
       <c r="C10" s="3">
         <v>1</v>
@@ -1468,41 +1984,41 @@
         <v>30</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="M10" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="N10" s="6" t="s">
-        <v>61</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="N10" s="6"/>
       <c r="O10" s="3" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
       <c r="R10" s="3">
-        <v>212738</v>
-      </c>
-      <c r="S10" s="3"/>
+        <v>255417</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T10" s="3"/>
       <c r="U10" s="3"/>
       <c r="V10" s="3"/>
@@ -1510,17 +2026,21 @@
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
       <c r="Z10" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="AA10" s="3"/>
-      <c r="AB10" s="3"/>
+        <v>77</v>
+      </c>
+      <c r="AA10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB10" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="1:28">
       <c r="A11" s="7">
         <v>9</v>
       </c>
       <c r="B11" s="7">
-        <v>2026060063</v>
+        <v>2026060464</v>
       </c>
       <c r="C11" s="7">
         <v>1</v>
@@ -1529,57 +2049,53 @@
         <v>29</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="J11" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="K11" s="7" t="s">
-        <v>36</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
       <c r="L11" s="8" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="M11" s="8" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="N11" s="8" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="O11" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P11" s="7"/>
       <c r="Q11" s="7"/>
       <c r="R11" s="7">
-        <v>2818</v>
-      </c>
-      <c r="S11" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S11" s="7"/>
       <c r="T11" s="7"/>
-      <c r="U11" s="7"/>
+      <c r="U11" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="V11" s="7"/>
       <c r="W11" s="7"/>
       <c r="X11" s="7"/>
       <c r="Y11" s="7"/>
       <c r="Z11" s="8" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="AA11" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB11" s="7">
         <v>1</v>
@@ -1590,7 +2106,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="3">
-        <v>2026060064</v>
+        <v>2026060669</v>
       </c>
       <c r="C12" s="3">
         <v>1</v>
@@ -1599,64 +2115,66 @@
         <v>29</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>36</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
       <c r="L12" s="6" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
       <c r="R12" s="3">
-        <v>2818</v>
-      </c>
-      <c r="S12" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T12" s="3"/>
       <c r="U12" s="3"/>
       <c r="V12" s="3"/>
       <c r="W12" s="3"/>
       <c r="X12" s="3"/>
-      <c r="Y12" s="3"/>
+      <c r="Y12" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="Z12" s="6" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="AA12" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB12" s="3"/>
+        <v>40</v>
+      </c>
+      <c r="AB12" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:28">
       <c r="A13" s="7">
         <v>11</v>
       </c>
       <c r="B13" s="7">
-        <v>2026060146</v>
+        <v>2026060656</v>
       </c>
       <c r="C13" s="7">
         <v>1</v>
@@ -1665,57 +2183,55 @@
         <v>29</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="J13" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="K13" s="7" t="s">
-        <v>36</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
       <c r="L13" s="8" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="M13" s="8" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="N13" s="8" t="s">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="O13" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P13" s="7"/>
       <c r="Q13" s="7"/>
       <c r="R13" s="7">
-        <v>49442</v>
-      </c>
-      <c r="S13" s="7"/>
+        <v>0</v>
+      </c>
+      <c r="S13" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T13" s="7"/>
-      <c r="U13" s="7" t="s">
-        <v>41</v>
-      </c>
+      <c r="U13" s="7"/>
       <c r="V13" s="7"/>
       <c r="W13" s="7"/>
       <c r="X13" s="7"/>
-      <c r="Y13" s="7"/>
+      <c r="Y13" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="Z13" s="8" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AA13" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB13" s="7">
         <v>1</v>
@@ -1726,7 +2242,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="3">
-        <v>2026060052</v>
+        <v>2026060403</v>
       </c>
       <c r="C14" s="3">
         <v>1</v>
@@ -1735,57 +2251,55 @@
         <v>29</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>31</v>
+        <v>96</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>36</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
       <c r="L14" s="6" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="M14" s="6" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P14" s="3"/>
       <c r="Q14" s="3"/>
       <c r="R14" s="3">
-        <v>29640</v>
+        <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="T14" s="3"/>
       <c r="U14" s="3"/>
       <c r="V14" s="3"/>
       <c r="W14" s="3"/>
       <c r="X14" s="3"/>
-      <c r="Y14" s="3"/>
+      <c r="Y14" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="Z14" s="6" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="AA14" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB14" s="3">
         <v>1</v>
@@ -1796,7 +2310,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="7">
-        <v>2026060053</v>
+        <v>2026060673</v>
       </c>
       <c r="C15" s="7">
         <v>1</v>
@@ -1805,44 +2319,50 @@
         <v>29</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="K15" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>66</v>
+        <v>105</v>
       </c>
       <c r="M15" s="8" t="s">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="N15" s="8" t="s">
-        <v>81</v>
+        <v>107</v>
       </c>
       <c r="O15" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="P15" s="7"/>
-      <c r="Q15" s="7"/>
+        <v>39</v>
+      </c>
+      <c r="P15" s="7">
+        <v>7927</v>
+      </c>
+      <c r="Q15" s="7">
+        <v>17354</v>
+      </c>
       <c r="R15" s="7">
-        <v>29640</v>
-      </c>
-      <c r="S15" s="7"/>
+        <v>25584</v>
+      </c>
+      <c r="S15" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T15" s="7"/>
       <c r="U15" s="7"/>
       <c r="V15" s="7"/>
@@ -1850,19 +2370,21 @@
       <c r="X15" s="7"/>
       <c r="Y15" s="7"/>
       <c r="Z15" s="8" t="s">
-        <v>69</v>
+        <v>108</v>
       </c>
       <c r="AA15" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB15" s="7"/>
+        <v>40</v>
+      </c>
+      <c r="AB15" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="1:28">
       <c r="A16" s="3">
         <v>14</v>
       </c>
       <c r="B16" s="3">
-        <v>2026060050</v>
+        <v>2026060674</v>
       </c>
       <c r="C16" s="3">
         <v>1</v>
@@ -1871,46 +2393,48 @@
         <v>29</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="K16" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>66</v>
+        <v>105</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="P16" s="3"/>
-      <c r="Q16" s="3"/>
+        <v>48</v>
+      </c>
+      <c r="P16" s="3">
+        <v>7927</v>
+      </c>
+      <c r="Q16" s="3">
+        <v>17354</v>
+      </c>
       <c r="R16" s="3">
-        <v>37830</v>
-      </c>
-      <c r="S16" s="3" t="s">
-        <v>41</v>
-      </c>
+        <v>25584</v>
+      </c>
+      <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
@@ -1918,21 +2442,19 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="6" t="s">
-        <v>69</v>
+        <v>108</v>
       </c>
       <c r="AA16" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB16" s="3">
-        <v>1</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="AB16" s="3"/>
     </row>
     <row r="17" spans="1:28">
       <c r="A17" s="7">
         <v>15</v>
       </c>
       <c r="B17" s="7">
-        <v>2026060051</v>
+        <v>2026060125</v>
       </c>
       <c r="C17" s="7">
         <v>1</v>
@@ -1941,44 +2463,48 @@
         <v>29</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>31</v>
+        <v>109</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>83</v>
+        <v>111</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="K17" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L17" s="8" t="s">
-        <v>66</v>
+        <v>112</v>
       </c>
       <c r="M17" s="8" t="s">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="N17" s="8" t="s">
-        <v>85</v>
+        <v>114</v>
       </c>
       <c r="O17" s="7" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="P17" s="7"/>
-      <c r="Q17" s="7"/>
+      <c r="Q17" s="7">
+        <v>2375</v>
+      </c>
       <c r="R17" s="7">
-        <v>37830</v>
-      </c>
-      <c r="S17" s="7"/>
+        <v>129731</v>
+      </c>
+      <c r="S17" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T17" s="7"/>
       <c r="U17" s="7"/>
       <c r="V17" s="7"/>
@@ -1986,11 +2512,9 @@
       <c r="X17" s="7"/>
       <c r="Y17" s="7"/>
       <c r="Z17" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="AA17" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="AA17" s="7"/>
       <c r="AB17" s="7"/>
     </row>
     <row r="18" spans="1:28">
@@ -1998,7 +2522,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="3">
-        <v>2026060046</v>
+        <v>2026060126</v>
       </c>
       <c r="C18" s="3">
         <v>1</v>
@@ -2007,46 +2531,46 @@
         <v>29</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>31</v>
+        <v>109</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>87</v>
+        <v>110</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>66</v>
+        <v>112</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>89</v>
+        <v>113</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="P18" s="3"/>
-      <c r="Q18" s="3"/>
+      <c r="Q18" s="3">
+        <v>2375</v>
+      </c>
       <c r="R18" s="3">
-        <v>45926</v>
-      </c>
-      <c r="S18" s="3" t="s">
-        <v>41</v>
-      </c>
+        <v>129731</v>
+      </c>
+      <c r="S18" s="3"/>
       <c r="T18" s="3"/>
       <c r="U18" s="3"/>
       <c r="V18" s="3"/>
@@ -2054,21 +2578,17 @@
       <c r="X18" s="3"/>
       <c r="Y18" s="3"/>
       <c r="Z18" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="AA18" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB18" s="3">
-        <v>1</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="AA18" s="3"/>
+      <c r="AB18" s="3"/>
     </row>
     <row r="19" spans="1:28">
       <c r="A19" s="7">
         <v>17</v>
       </c>
       <c r="B19" s="7">
-        <v>2026060047</v>
+        <v>2026060762</v>
       </c>
       <c r="C19" s="7">
         <v>1</v>
@@ -2077,44 +2597,46 @@
         <v>29</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>86</v>
+        <v>115</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>87</v>
+        <v>116</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>88</v>
+        <v>117</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="K19" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L19" s="8" t="s">
-        <v>66</v>
+        <v>118</v>
       </c>
       <c r="M19" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="N19" s="8" t="s">
-        <v>90</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="N19" s="8"/>
       <c r="O19" s="7" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="P19" s="7"/>
-      <c r="Q19" s="7"/>
+      <c r="Q19" s="7">
+        <v>555</v>
+      </c>
       <c r="R19" s="7">
-        <v>45926</v>
-      </c>
-      <c r="S19" s="7"/>
+        <v>21603</v>
+      </c>
+      <c r="S19" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T19" s="7"/>
       <c r="U19" s="7"/>
       <c r="V19" s="7"/>
@@ -2122,19 +2644,21 @@
       <c r="X19" s="7"/>
       <c r="Y19" s="7"/>
       <c r="Z19" s="8" t="s">
-        <v>69</v>
+        <v>108</v>
       </c>
       <c r="AA19" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB19" s="7"/>
+        <v>40</v>
+      </c>
+      <c r="AB19" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="20" spans="1:28">
       <c r="A20" s="3">
         <v>18</v>
       </c>
       <c r="B20" s="3">
-        <v>2026060041</v>
+        <v>2026060763</v>
       </c>
       <c r="C20" s="3">
         <v>1</v>
@@ -2143,42 +2667,42 @@
         <v>29</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>91</v>
+        <v>115</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>92</v>
+        <v>116</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>66</v>
+        <v>118</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="N20" s="6" t="s">
-        <v>95</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="N20" s="6"/>
       <c r="O20" s="3" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="P20" s="3"/>
-      <c r="Q20" s="3"/>
+      <c r="Q20" s="3">
+        <v>555</v>
+      </c>
       <c r="R20" s="3">
-        <v>29640</v>
+        <v>21603</v>
       </c>
       <c r="S20" s="3"/>
       <c r="T20" s="3"/>
@@ -2188,21 +2712,19 @@
       <c r="X20" s="3"/>
       <c r="Y20" s="3"/>
       <c r="Z20" s="6" t="s">
-        <v>69</v>
+        <v>108</v>
       </c>
       <c r="AA20" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>1</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="AB20" s="3"/>
     </row>
     <row r="21" spans="1:28">
       <c r="A21" s="7">
         <v>19</v>
       </c>
       <c r="B21" s="7">
-        <v>2026060040</v>
+        <v>2026060108</v>
       </c>
       <c r="C21" s="7">
         <v>1</v>
@@ -2211,46 +2733,44 @@
         <v>29</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>31</v>
+        <v>109</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>91</v>
+        <v>120</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>92</v>
+        <v>121</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>93</v>
+        <v>122</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>54</v>
+        <v>123</v>
       </c>
       <c r="K21" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L21" s="8" t="s">
-        <v>66</v>
+        <v>124</v>
       </c>
       <c r="M21" s="8" t="s">
-        <v>94</v>
+        <v>125</v>
       </c>
       <c r="N21" s="8" t="s">
-        <v>95</v>
+        <v>126</v>
       </c>
       <c r="O21" s="7" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="P21" s="7"/>
       <c r="Q21" s="7"/>
       <c r="R21" s="7">
-        <v>29640</v>
-      </c>
-      <c r="S21" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>313246</v>
+      </c>
+      <c r="S21" s="7"/>
       <c r="T21" s="7"/>
       <c r="U21" s="7"/>
       <c r="V21" s="7"/>
@@ -2258,11 +2778,9 @@
       <c r="X21" s="7"/>
       <c r="Y21" s="7"/>
       <c r="Z21" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="AA21" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="AA21" s="7"/>
       <c r="AB21" s="7"/>
     </row>
     <row r="22" spans="1:28">
@@ -2270,7 +2788,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="3">
-        <v>2026060044</v>
+        <v>2026060107</v>
       </c>
       <c r="C22" s="3">
         <v>1</v>
@@ -2279,45 +2797,45 @@
         <v>29</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>31</v>
+        <v>109</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>86</v>
+        <v>121</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>54</v>
+        <v>123</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>66</v>
+        <v>124</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>99</v>
+        <v>126</v>
       </c>
       <c r="O22" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P22" s="3"/>
       <c r="Q22" s="3"/>
       <c r="R22" s="3">
-        <v>34235</v>
+        <v>313246</v>
       </c>
       <c r="S22" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="T22" s="3"/>
       <c r="U22" s="3"/>
@@ -2326,21 +2844,17 @@
       <c r="X22" s="3"/>
       <c r="Y22" s="3"/>
       <c r="Z22" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="AA22" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>1</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="AA22" s="3"/>
+      <c r="AB22" s="3"/>
     </row>
     <row r="23" spans="1:28">
       <c r="A23" s="7">
         <v>21</v>
       </c>
       <c r="B23" s="7">
-        <v>2026060045</v>
+        <v>2026060415</v>
       </c>
       <c r="C23" s="7">
         <v>1</v>
@@ -2349,44 +2863,46 @@
         <v>29</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="F23" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>96</v>
+        <v>127</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>86</v>
+        <v>128</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>54</v>
+        <v>123</v>
       </c>
       <c r="K23" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>66</v>
+        <v>130</v>
       </c>
       <c r="M23" s="8" t="s">
-        <v>98</v>
+        <v>131</v>
       </c>
       <c r="N23" s="8" t="s">
-        <v>99</v>
+        <v>132</v>
       </c>
       <c r="O23" s="7" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="P23" s="7"/>
       <c r="Q23" s="7"/>
       <c r="R23" s="7">
-        <v>34235</v>
-      </c>
-      <c r="S23" s="7"/>
+        <v>29215</v>
+      </c>
+      <c r="S23" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T23" s="7"/>
       <c r="U23" s="7"/>
       <c r="V23" s="7"/>
@@ -2394,19 +2910,21 @@
       <c r="X23" s="7"/>
       <c r="Y23" s="7"/>
       <c r="Z23" s="8" t="s">
-        <v>69</v>
+        <v>108</v>
       </c>
       <c r="AA23" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB23" s="7"/>
+        <v>40</v>
+      </c>
+      <c r="AB23" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="24" spans="1:28">
       <c r="A24" s="3">
         <v>22</v>
       </c>
       <c r="B24" s="3">
-        <v>2026060042</v>
+        <v>2026060416</v>
       </c>
       <c r="C24" s="3">
         <v>1</v>
@@ -2415,46 +2933,44 @@
         <v>29</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>92</v>
+        <v>127</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>96</v>
+        <v>128</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>54</v>
+        <v>123</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>66</v>
+        <v>130</v>
       </c>
       <c r="M24" s="6" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>102</v>
+        <v>132</v>
       </c>
       <c r="O24" s="3" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="P24" s="3"/>
       <c r="Q24" s="3"/>
       <c r="R24" s="3">
-        <v>17791</v>
-      </c>
-      <c r="S24" s="3" t="s">
-        <v>41</v>
-      </c>
+        <v>29215</v>
+      </c>
+      <c r="S24" s="3"/>
       <c r="T24" s="3"/>
       <c r="U24" s="3"/>
       <c r="V24" s="3"/>
@@ -2462,21 +2978,19 @@
       <c r="X24" s="3"/>
       <c r="Y24" s="3"/>
       <c r="Z24" s="6" t="s">
-        <v>69</v>
+        <v>108</v>
       </c>
       <c r="AA24" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB24" s="3">
-        <v>1</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="AB24" s="3"/>
     </row>
     <row r="25" spans="1:28">
       <c r="A25" s="7">
         <v>23</v>
       </c>
       <c r="B25" s="7">
-        <v>2026060043</v>
+        <v>2026060378</v>
       </c>
       <c r="C25" s="7">
         <v>1</v>
@@ -2485,44 +2999,44 @@
         <v>29</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="F25" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>92</v>
+        <v>42</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>96</v>
+        <v>133</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>100</v>
+        <v>134</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="K25" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L25" s="8" t="s">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="M25" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="N25" s="8" t="s">
-        <v>102</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="N25" s="8"/>
       <c r="O25" s="7" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="P25" s="7"/>
       <c r="Q25" s="7"/>
       <c r="R25" s="7">
-        <v>17791</v>
-      </c>
-      <c r="S25" s="7"/>
+        <v>36400</v>
+      </c>
+      <c r="S25" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T25" s="7"/>
       <c r="U25" s="7"/>
       <c r="V25" s="7"/>
@@ -2530,19 +3044,21 @@
       <c r="X25" s="7"/>
       <c r="Y25" s="7"/>
       <c r="Z25" s="8" t="s">
-        <v>69</v>
+        <v>108</v>
       </c>
       <c r="AA25" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB25" s="7"/>
+        <v>40</v>
+      </c>
+      <c r="AB25" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="26" spans="1:28">
       <c r="A26" s="3">
         <v>24</v>
       </c>
       <c r="B26" s="3">
-        <v>2026060061</v>
+        <v>2026060379</v>
       </c>
       <c r="C26" s="3">
         <v>1</v>
@@ -2551,46 +3067,42 @@
         <v>29</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>78</v>
+        <v>42</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>63</v>
+        <v>133</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>103</v>
+        <v>134</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="M26" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="N26" s="6" t="s">
-        <v>106</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="N26" s="6"/>
       <c r="O26" s="3" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="P26" s="3"/>
       <c r="Q26" s="3"/>
       <c r="R26" s="3">
-        <v>702</v>
-      </c>
-      <c r="S26" s="3" t="s">
-        <v>41</v>
-      </c>
+        <v>36400</v>
+      </c>
+      <c r="S26" s="3"/>
       <c r="T26" s="3"/>
       <c r="U26" s="3"/>
       <c r="V26" s="3"/>
@@ -2598,21 +3110,19 @@
       <c r="X26" s="3"/>
       <c r="Y26" s="3"/>
       <c r="Z26" s="6" t="s">
-        <v>69</v>
+        <v>108</v>
       </c>
       <c r="AA26" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB26" s="3">
-        <v>1</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="AB26" s="3"/>
     </row>
     <row r="27" spans="1:28">
       <c r="A27" s="7">
         <v>25</v>
       </c>
       <c r="B27" s="7">
-        <v>2026060062</v>
+        <v>2026060111</v>
       </c>
       <c r="C27" s="7">
         <v>1</v>
@@ -2621,42 +3131,42 @@
         <v>29</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>31</v>
+        <v>109</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>63</v>
+        <v>138</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>103</v>
+        <v>139</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
       <c r="K27" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L27" s="8" t="s">
-        <v>66</v>
+        <v>124</v>
       </c>
       <c r="M27" s="8" t="s">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="N27" s="8" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="O27" s="7" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="P27" s="7"/>
       <c r="Q27" s="7"/>
       <c r="R27" s="7">
-        <v>702</v>
+        <v>113426</v>
       </c>
       <c r="S27" s="7"/>
       <c r="T27" s="7"/>
@@ -2666,11 +3176,9 @@
       <c r="X27" s="7"/>
       <c r="Y27" s="7"/>
       <c r="Z27" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="AA27" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="AA27" s="7"/>
       <c r="AB27" s="7"/>
     </row>
     <row r="28" spans="1:28">
@@ -2678,7 +3186,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="3">
-        <v>2026060048</v>
+        <v>2026060110</v>
       </c>
       <c r="C28" s="3">
         <v>1</v>
@@ -2687,45 +3195,45 @@
         <v>29</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>31</v>
+        <v>109</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>87</v>
+        <v>137</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>82</v>
+        <v>138</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>107</v>
+        <v>139</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
       <c r="K28" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>66</v>
+        <v>124</v>
       </c>
       <c r="M28" s="6" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="O28" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P28" s="3"/>
       <c r="Q28" s="3"/>
       <c r="R28" s="3">
-        <v>5766</v>
+        <v>113426</v>
       </c>
       <c r="S28" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="T28" s="3"/>
       <c r="U28" s="3"/>
@@ -2734,21 +3242,17 @@
       <c r="X28" s="3"/>
       <c r="Y28" s="3"/>
       <c r="Z28" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="AA28" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB28" s="3">
-        <v>1</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="AA28" s="3"/>
+      <c r="AB28" s="3"/>
     </row>
     <row r="29" spans="1:28">
       <c r="A29" s="7">
         <v>27</v>
       </c>
       <c r="B29" s="7">
-        <v>2026060049</v>
+        <v>2026060411</v>
       </c>
       <c r="C29" s="7">
         <v>1</v>
@@ -2757,44 +3261,48 @@
         <v>29</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="F29" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>87</v>
+        <v>141</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>107</v>
+        <v>143</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>104</v>
+        <v>144</v>
       </c>
       <c r="K29" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L29" s="8" t="s">
-        <v>66</v>
+        <v>145</v>
       </c>
       <c r="M29" s="8" t="s">
-        <v>108</v>
+        <v>146</v>
       </c>
       <c r="N29" s="8" t="s">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="O29" s="7" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="P29" s="7"/>
-      <c r="Q29" s="7"/>
+      <c r="Q29" s="7">
+        <v>3009</v>
+      </c>
       <c r="R29" s="7">
-        <v>5766</v>
-      </c>
-      <c r="S29" s="7"/>
+        <v>386927</v>
+      </c>
+      <c r="S29" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T29" s="7"/>
       <c r="U29" s="7"/>
       <c r="V29" s="7"/>
@@ -2802,19 +3310,21 @@
       <c r="X29" s="7"/>
       <c r="Y29" s="7"/>
       <c r="Z29" s="8" t="s">
-        <v>69</v>
+        <v>108</v>
       </c>
       <c r="AA29" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB29" s="7"/>
+        <v>40</v>
+      </c>
+      <c r="AB29" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="30" spans="1:28">
       <c r="A30" s="3">
         <v>28</v>
       </c>
       <c r="B30" s="3">
-        <v>2026060081</v>
+        <v>2026060412</v>
       </c>
       <c r="C30" s="3">
         <v>1</v>
@@ -2823,46 +3333,46 @@
         <v>29</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>110</v>
+        <v>141</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>111</v>
+        <v>142</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>112</v>
+        <v>143</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>113</v>
+        <v>144</v>
       </c>
       <c r="K30" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>73</v>
+        <v>145</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>114</v>
+        <v>146</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="O30" s="3" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="P30" s="3"/>
-      <c r="Q30" s="3"/>
+      <c r="Q30" s="3">
+        <v>3009</v>
+      </c>
       <c r="R30" s="3">
-        <v>48</v>
-      </c>
-      <c r="S30" s="3" t="s">
-        <v>41</v>
-      </c>
+        <v>386927</v>
+      </c>
+      <c r="S30" s="3"/>
       <c r="T30" s="3"/>
       <c r="U30" s="3"/>
       <c r="V30" s="3"/>
@@ -2870,9 +3380,11 @@
       <c r="X30" s="3"/>
       <c r="Y30" s="3"/>
       <c r="Z30" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="AA30" s="3"/>
+        <v>108</v>
+      </c>
+      <c r="AA30" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="AB30" s="3"/>
     </row>
     <row r="31" spans="1:28">
@@ -2880,7 +3392,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="7">
-        <v>2026060082</v>
+        <v>2026060771</v>
       </c>
       <c r="C31" s="7">
         <v>1</v>
@@ -2889,44 +3401,48 @@
         <v>29</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>111</v>
+        <v>148</v>
       </c>
       <c r="I31" s="7" t="s">
-        <v>112</v>
+        <v>149</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>113</v>
+        <v>150</v>
       </c>
       <c r="K31" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L31" s="8" t="s">
-        <v>73</v>
+        <v>151</v>
       </c>
       <c r="M31" s="8" t="s">
-        <v>114</v>
+        <v>152</v>
       </c>
       <c r="N31" s="8" t="s">
-        <v>115</v>
+        <v>153</v>
       </c>
       <c r="O31" s="7" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="P31" s="7"/>
-      <c r="Q31" s="7"/>
+      <c r="Q31" s="7">
+        <v>5752</v>
+      </c>
       <c r="R31" s="7">
-        <v>48</v>
-      </c>
-      <c r="S31" s="7"/>
+        <v>34659</v>
+      </c>
+      <c r="S31" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T31" s="7"/>
       <c r="U31" s="7"/>
       <c r="V31" s="7"/>
@@ -2934,11 +3450,9 @@
       <c r="X31" s="7"/>
       <c r="Y31" s="7"/>
       <c r="Z31" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="AA31" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="AA31" s="7"/>
       <c r="AB31" s="7"/>
     </row>
     <row r="32" spans="1:28">
@@ -2946,7 +3460,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="3">
-        <v>2026060145</v>
+        <v>2026060772</v>
       </c>
       <c r="C32" s="3">
         <v>1</v>
@@ -2955,68 +3469,66 @@
         <v>29</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>116</v>
+        <v>147</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>70</v>
+        <v>148</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>117</v>
+        <v>149</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>59</v>
+        <v>150</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>73</v>
+        <v>151</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>119</v>
+        <v>153</v>
       </c>
       <c r="O32" s="3" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="P32" s="3"/>
-      <c r="Q32" s="3"/>
+      <c r="Q32" s="3">
+        <v>5752</v>
+      </c>
       <c r="R32" s="3">
-        <v>38244</v>
+        <v>34659</v>
       </c>
       <c r="S32" s="3"/>
       <c r="T32" s="3"/>
-      <c r="U32" s="3" t="s">
-        <v>41</v>
-      </c>
+      <c r="U32" s="3"/>
       <c r="V32" s="3"/>
       <c r="W32" s="3"/>
       <c r="X32" s="3"/>
       <c r="Y32" s="3"/>
       <c r="Z32" s="6" t="s">
-        <v>76</v>
+        <v>108</v>
       </c>
       <c r="AA32" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>1</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="AB32" s="3"/>
     </row>
     <row r="33" spans="1:28">
       <c r="A33" s="7">
         <v>31</v>
       </c>
       <c r="B33" s="7">
-        <v>2026060144</v>
+        <v>2026060127</v>
       </c>
       <c r="C33" s="7">
         <v>1</v>
@@ -3025,68 +3537,64 @@
         <v>29</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>31</v>
+        <v>109</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>33</v>
+        <v>154</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>116</v>
+        <v>155</v>
       </c>
       <c r="I33" s="7" t="s">
-        <v>120</v>
+        <v>156</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>59</v>
+        <v>157</v>
       </c>
       <c r="K33" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L33" s="8" t="s">
-        <v>73</v>
+        <v>112</v>
       </c>
       <c r="M33" s="8" t="s">
-        <v>118</v>
+        <v>158</v>
       </c>
       <c r="N33" s="8" t="s">
-        <v>121</v>
+        <v>159</v>
       </c>
       <c r="O33" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P33" s="7"/>
       <c r="Q33" s="7"/>
       <c r="R33" s="7">
-        <v>386259</v>
-      </c>
-      <c r="S33" s="7"/>
+        <v>212738</v>
+      </c>
+      <c r="S33" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T33" s="7"/>
-      <c r="U33" s="7" t="s">
-        <v>41</v>
-      </c>
+      <c r="U33" s="7"/>
       <c r="V33" s="7"/>
       <c r="W33" s="7"/>
       <c r="X33" s="7"/>
       <c r="Y33" s="7"/>
       <c r="Z33" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="AA33" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB33" s="7">
-        <v>1</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="AA33" s="7"/>
+      <c r="AB33" s="7"/>
     </row>
     <row r="34" spans="1:28">
       <c r="A34" s="3">
         <v>32</v>
       </c>
       <c r="B34" s="3">
-        <v>2026060143</v>
+        <v>2026060128</v>
       </c>
       <c r="C34" s="3">
         <v>1</v>
@@ -3095,68 +3603,62 @@
         <v>29</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>31</v>
+        <v>109</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>122</v>
+        <v>154</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>33</v>
+        <v>155</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>123</v>
+        <v>156</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>59</v>
+        <v>157</v>
       </c>
       <c r="K34" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>73</v>
+        <v>112</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>118</v>
+        <v>158</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>124</v>
+        <v>159</v>
       </c>
       <c r="O34" s="3" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="P34" s="3"/>
       <c r="Q34" s="3"/>
       <c r="R34" s="3">
-        <v>381383</v>
+        <v>212738</v>
       </c>
       <c r="S34" s="3"/>
       <c r="T34" s="3"/>
-      <c r="U34" s="3" t="s">
-        <v>41</v>
-      </c>
+      <c r="U34" s="3"/>
       <c r="V34" s="3"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
       <c r="Z34" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="AA34" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB34" s="3">
-        <v>1</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="AA34" s="3"/>
+      <c r="AB34" s="3"/>
     </row>
     <row r="35" spans="1:28">
       <c r="A35" s="7">
         <v>33</v>
       </c>
       <c r="B35" s="7">
-        <v>2026060142</v>
+        <v>2026060846</v>
       </c>
       <c r="C35" s="7">
         <v>1</v>
@@ -3165,57 +3667,53 @@
         <v>29</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="I35" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="J35" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="K35" s="7" t="s">
-        <v>36</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="J35" s="7"/>
+      <c r="K35" s="7"/>
       <c r="L35" s="8" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="M35" s="8" t="s">
-        <v>114</v>
+        <v>161</v>
       </c>
       <c r="N35" s="8" t="s">
-        <v>127</v>
+        <v>162</v>
       </c>
       <c r="O35" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P35" s="7"/>
       <c r="Q35" s="7"/>
       <c r="R35" s="7">
-        <v>31873</v>
-      </c>
-      <c r="S35" s="7"/>
+        <v>0</v>
+      </c>
+      <c r="S35" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T35" s="7"/>
-      <c r="U35" s="7" t="s">
-        <v>41</v>
-      </c>
+      <c r="U35" s="7"/>
       <c r="V35" s="7"/>
       <c r="W35" s="7"/>
       <c r="X35" s="7"/>
       <c r="Y35" s="7"/>
       <c r="Z35" s="8" t="s">
-        <v>76</v>
+        <v>163</v>
       </c>
       <c r="AA35" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB35" s="7">
         <v>1</v>
@@ -3226,7 +3724,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="3">
-        <v>2026060141</v>
+        <v>2026060445</v>
       </c>
       <c r="C36" s="3">
         <v>1</v>
@@ -3235,94 +3733,4240 @@
         <v>29</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>125</v>
+        <v>164</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="J36" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="K36" s="3" t="s">
-        <v>36</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="J36" s="3"/>
+      <c r="K36" s="3"/>
       <c r="L36" s="6" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>130</v>
+        <v>83</v>
       </c>
       <c r="O36" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P36" s="3"/>
       <c r="Q36" s="3"/>
       <c r="R36" s="3">
-        <v>30842</v>
+        <v>0</v>
       </c>
       <c r="S36" s="3"/>
-      <c r="T36" s="3"/>
-      <c r="U36" s="3" t="s">
-        <v>41</v>
-      </c>
+      <c r="T36" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="U36" s="3"/>
       <c r="V36" s="3"/>
       <c r="W36" s="3"/>
       <c r="X36" s="3"/>
       <c r="Y36" s="3"/>
       <c r="Z36" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="AA36" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB36" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:28">
+      <c r="A37" s="7">
+        <v>35</v>
+      </c>
+      <c r="B37" s="7">
+        <v>2026060840</v>
+      </c>
+      <c r="C37" s="7">
+        <v>1</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="G37" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="H37" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="I37" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="J37" s="7"/>
+      <c r="K37" s="7"/>
+      <c r="L37" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="M37" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="N37" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="O37" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P37" s="7"/>
+      <c r="Q37" s="7"/>
+      <c r="R37" s="7">
+        <v>0</v>
+      </c>
+      <c r="S37" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="T37" s="7"/>
+      <c r="U37" s="7"/>
+      <c r="V37" s="7"/>
+      <c r="W37" s="7"/>
+      <c r="X37" s="7"/>
+      <c r="Y37" s="7"/>
+      <c r="Z37" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="AA37" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB37" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:28">
+      <c r="A38" s="3">
+        <v>36</v>
+      </c>
+      <c r="B38" s="3">
+        <v>2026060812</v>
+      </c>
+      <c r="C38" s="3">
+        <v>1</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="J38" s="3"/>
+      <c r="K38" s="3"/>
+      <c r="L38" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="M38" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="N38" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="O38" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P38" s="3"/>
+      <c r="Q38" s="3"/>
+      <c r="R38" s="3">
+        <v>0</v>
+      </c>
+      <c r="S38" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="T38" s="3"/>
+      <c r="U38" s="3"/>
+      <c r="V38" s="3"/>
+      <c r="W38" s="3"/>
+      <c r="X38" s="3"/>
+      <c r="Y38" s="3"/>
+      <c r="Z38" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA38" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB38" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:28">
+      <c r="A39" s="7">
+        <v>37</v>
+      </c>
+      <c r="B39" s="7">
+        <v>2026060827</v>
+      </c>
+      <c r="C39" s="7">
+        <v>1</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="G39" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="H39" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="I39" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="J39" s="7"/>
+      <c r="K39" s="7"/>
+      <c r="L39" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="M39" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="N39" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="O39" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P39" s="7"/>
+      <c r="Q39" s="7"/>
+      <c r="R39" s="7">
+        <v>0</v>
+      </c>
+      <c r="S39" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="T39" s="7"/>
+      <c r="U39" s="7"/>
+      <c r="V39" s="7"/>
+      <c r="W39" s="7"/>
+      <c r="X39" s="7"/>
+      <c r="Y39" s="7"/>
+      <c r="Z39" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA39" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB39" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:28">
+      <c r="A40" s="3">
+        <v>38</v>
+      </c>
+      <c r="B40" s="3">
+        <v>2026060664</v>
+      </c>
+      <c r="C40" s="3">
+        <v>1</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L40" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="M40" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="N40" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="O40" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P40" s="3">
+        <v>2480</v>
+      </c>
+      <c r="Q40" s="3">
+        <v>3343</v>
+      </c>
+      <c r="R40" s="3">
+        <v>11884</v>
+      </c>
+      <c r="S40" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="T40" s="3"/>
+      <c r="U40" s="3"/>
+      <c r="V40" s="3"/>
+      <c r="W40" s="3"/>
+      <c r="X40" s="3"/>
+      <c r="Y40" s="3"/>
+      <c r="Z40" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="AA40" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB40" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:28">
+      <c r="A41" s="7">
+        <v>39</v>
+      </c>
+      <c r="B41" s="7">
+        <v>2026060665</v>
+      </c>
+      <c r="C41" s="7">
+        <v>1</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="G41" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="H41" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I41" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="J41" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="K41" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L41" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="M41" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="N41" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="O41" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="P41" s="7">
+        <v>2480</v>
+      </c>
+      <c r="Q41" s="7">
+        <v>3343</v>
+      </c>
+      <c r="R41" s="7">
+        <v>11884</v>
+      </c>
+      <c r="S41" s="7"/>
+      <c r="T41" s="7"/>
+      <c r="U41" s="7"/>
+      <c r="V41" s="7"/>
+      <c r="W41" s="7"/>
+      <c r="X41" s="7"/>
+      <c r="Y41" s="7"/>
+      <c r="Z41" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="AA41" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB41" s="7"/>
+    </row>
+    <row r="42" spans="1:28">
+      <c r="A42" s="3">
+        <v>40</v>
+      </c>
+      <c r="B42" s="3">
+        <v>2026060666</v>
+      </c>
+      <c r="C42" s="3">
+        <v>1</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L42" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="M42" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="N42" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="O42" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P42" s="3">
+        <v>624</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>1591</v>
+      </c>
+      <c r="R42" s="3">
+        <v>9357</v>
+      </c>
+      <c r="S42" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="T42" s="3"/>
+      <c r="U42" s="3"/>
+      <c r="V42" s="3"/>
+      <c r="W42" s="3"/>
+      <c r="X42" s="3"/>
+      <c r="Y42" s="3"/>
+      <c r="Z42" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="AA42" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB42" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:28">
+      <c r="A43" s="7">
+        <v>41</v>
+      </c>
+      <c r="B43" s="7">
+        <v>2026060667</v>
+      </c>
+      <c r="C43" s="7">
+        <v>1</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="G43" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H43" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="I43" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="J43" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="K43" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L43" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="M43" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="N43" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="O43" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="P43" s="7">
+        <v>624</v>
+      </c>
+      <c r="Q43" s="7">
+        <v>1591</v>
+      </c>
+      <c r="R43" s="7">
+        <v>9357</v>
+      </c>
+      <c r="S43" s="7"/>
+      <c r="T43" s="7"/>
+      <c r="U43" s="7"/>
+      <c r="V43" s="7"/>
+      <c r="W43" s="7"/>
+      <c r="X43" s="7"/>
+      <c r="Y43" s="7"/>
+      <c r="Z43" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="AA43" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB43" s="7"/>
+    </row>
+    <row r="44" spans="1:28">
+      <c r="A44" s="3">
+        <v>42</v>
+      </c>
+      <c r="B44" s="3">
+        <v>2026060572</v>
+      </c>
+      <c r="C44" s="3">
+        <v>1</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L44" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="M44" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="N44" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="O44" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P44" s="3"/>
+      <c r="Q44" s="3">
+        <v>449</v>
+      </c>
+      <c r="R44" s="3">
+        <v>4403</v>
+      </c>
+      <c r="S44" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="T44" s="3"/>
+      <c r="U44" s="3"/>
+      <c r="V44" s="3"/>
+      <c r="W44" s="3"/>
+      <c r="X44" s="3"/>
+      <c r="Y44" s="3"/>
+      <c r="Z44" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="AA44" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB44" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:28">
+      <c r="A45" s="7">
+        <v>43</v>
+      </c>
+      <c r="B45" s="7">
+        <v>2026060573</v>
+      </c>
+      <c r="C45" s="7">
+        <v>1</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G45" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="H45" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="I45" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="J45" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="K45" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L45" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="M45" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="N45" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="O45" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="P45" s="7"/>
+      <c r="Q45" s="7">
+        <v>449</v>
+      </c>
+      <c r="R45" s="7">
+        <v>4403</v>
+      </c>
+      <c r="S45" s="7"/>
+      <c r="T45" s="7"/>
+      <c r="U45" s="7"/>
+      <c r="V45" s="7"/>
+      <c r="W45" s="7"/>
+      <c r="X45" s="7"/>
+      <c r="Y45" s="7"/>
+      <c r="Z45" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="AA45" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB45" s="7"/>
+    </row>
+    <row r="46" spans="1:28">
+      <c r="A46" s="3">
+        <v>44</v>
+      </c>
+      <c r="B46" s="3">
+        <v>2026060824</v>
+      </c>
+      <c r="C46" s="3">
+        <v>1</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K46" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L46" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="M46" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="N46" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="O46" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P46" s="3"/>
+      <c r="Q46" s="3">
+        <v>449</v>
+      </c>
+      <c r="R46" s="3">
+        <v>4403</v>
+      </c>
+      <c r="S46" s="3"/>
+      <c r="T46" s="3"/>
+      <c r="U46" s="3"/>
+      <c r="V46" s="3"/>
+      <c r="W46" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="X46" s="3"/>
+      <c r="Y46" s="3"/>
+      <c r="Z46" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="AA46" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB46" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:28">
+      <c r="A47" s="7">
+        <v>45</v>
+      </c>
+      <c r="B47" s="7">
+        <v>2026060063</v>
+      </c>
+      <c r="C47" s="7">
+        <v>1</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="F47" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="G47" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="H47" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="I47" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="J47" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="K47" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L47" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="M47" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="N47" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="O47" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P47" s="7"/>
+      <c r="Q47" s="7"/>
+      <c r="R47" s="7">
+        <v>2818</v>
+      </c>
+      <c r="S47" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="T47" s="7"/>
+      <c r="U47" s="7"/>
+      <c r="V47" s="7"/>
+      <c r="W47" s="7"/>
+      <c r="X47" s="7"/>
+      <c r="Y47" s="7"/>
+      <c r="Z47" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="AA47" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB47" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:28">
+      <c r="A48" s="3">
+        <v>46</v>
+      </c>
+      <c r="B48" s="3">
+        <v>2026060064</v>
+      </c>
+      <c r="C48" s="3">
+        <v>1</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L48" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="M48" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="N48" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="O48" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="P48" s="3"/>
+      <c r="Q48" s="3"/>
+      <c r="R48" s="3">
+        <v>2818</v>
+      </c>
+      <c r="S48" s="3"/>
+      <c r="T48" s="3"/>
+      <c r="U48" s="3"/>
+      <c r="V48" s="3"/>
+      <c r="W48" s="3"/>
+      <c r="X48" s="3"/>
+      <c r="Y48" s="3"/>
+      <c r="Z48" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="AA48" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB48" s="3"/>
+    </row>
+    <row r="49" spans="1:28">
+      <c r="A49" s="7">
+        <v>47</v>
+      </c>
+      <c r="B49" s="7">
+        <v>2026060627</v>
+      </c>
+      <c r="C49" s="7">
+        <v>1</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="F49" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="G49" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="H49" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="I49" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="J49" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="K49" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L49" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="M49" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="N49" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="O49" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P49" s="7"/>
+      <c r="Q49" s="7"/>
+      <c r="R49" s="7">
+        <v>195048</v>
+      </c>
+      <c r="S49" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="T49" s="7"/>
+      <c r="U49" s="7"/>
+      <c r="V49" s="7"/>
+      <c r="W49" s="7"/>
+      <c r="X49" s="7"/>
+      <c r="Y49" s="7"/>
+      <c r="Z49" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="AA49" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB49" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:28">
+      <c r="A50" s="3">
+        <v>48</v>
+      </c>
+      <c r="B50" s="3">
+        <v>2026060628</v>
+      </c>
+      <c r="C50" s="3">
+        <v>1</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L50" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="M50" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="N50" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="O50" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="P50" s="3"/>
+      <c r="Q50" s="3"/>
+      <c r="R50" s="3">
+        <v>195048</v>
+      </c>
+      <c r="S50" s="3"/>
+      <c r="T50" s="3"/>
+      <c r="U50" s="3"/>
+      <c r="V50" s="3"/>
+      <c r="W50" s="3"/>
+      <c r="X50" s="3"/>
+      <c r="Y50" s="3"/>
+      <c r="Z50" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="AA50" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB50" s="3"/>
+    </row>
+    <row r="51" spans="1:28">
+      <c r="A51" s="7">
+        <v>49</v>
+      </c>
+      <c r="B51" s="7">
+        <v>2026060629</v>
+      </c>
+      <c r="C51" s="7">
+        <v>1</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E51" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="F51" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="G51" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="H51" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="I51" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="J51" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="K51" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L51" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="M51" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="N51" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="O51" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P51" s="7"/>
+      <c r="Q51" s="7"/>
+      <c r="R51" s="7">
+        <v>203621</v>
+      </c>
+      <c r="S51" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="T51" s="7"/>
+      <c r="U51" s="7"/>
+      <c r="V51" s="7"/>
+      <c r="W51" s="7"/>
+      <c r="X51" s="7"/>
+      <c r="Y51" s="7"/>
+      <c r="Z51" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="AA51" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB51" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:28">
+      <c r="A52" s="3">
+        <v>50</v>
+      </c>
+      <c r="B52" s="3">
+        <v>2026060630</v>
+      </c>
+      <c r="C52" s="3">
+        <v>1</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L52" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="M52" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="N52" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="O52" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="P52" s="3"/>
+      <c r="Q52" s="3"/>
+      <c r="R52" s="3">
+        <v>203621</v>
+      </c>
+      <c r="S52" s="3"/>
+      <c r="T52" s="3"/>
+      <c r="U52" s="3"/>
+      <c r="V52" s="3"/>
+      <c r="W52" s="3"/>
+      <c r="X52" s="3"/>
+      <c r="Y52" s="3"/>
+      <c r="Z52" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="AA52" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB52" s="3"/>
+    </row>
+    <row r="53" spans="1:28">
+      <c r="A53" s="7">
+        <v>51</v>
+      </c>
+      <c r="B53" s="7">
+        <v>2026060146</v>
+      </c>
+      <c r="C53" s="7">
+        <v>1</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="F53" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="G53" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="H53" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="I53" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="J53" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="K53" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L53" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="M53" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="N53" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="O53" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P53" s="7"/>
+      <c r="Q53" s="7"/>
+      <c r="R53" s="7">
+        <v>49442</v>
+      </c>
+      <c r="S53" s="7"/>
+      <c r="T53" s="7"/>
+      <c r="U53" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="V53" s="7"/>
+      <c r="W53" s="7"/>
+      <c r="X53" s="7"/>
+      <c r="Y53" s="7"/>
+      <c r="Z53" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA53" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB53" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:28">
+      <c r="A54" s="3">
+        <v>52</v>
+      </c>
+      <c r="B54" s="3">
+        <v>2026060052</v>
+      </c>
+      <c r="C54" s="3">
+        <v>1</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="K54" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L54" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="M54" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="N54" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="O54" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P54" s="3"/>
+      <c r="Q54" s="3"/>
+      <c r="R54" s="3">
+        <v>29640</v>
+      </c>
+      <c r="S54" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="T54" s="3"/>
+      <c r="U54" s="3"/>
+      <c r="V54" s="3"/>
+      <c r="W54" s="3"/>
+      <c r="X54" s="3"/>
+      <c r="Y54" s="3"/>
+      <c r="Z54" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="AA54" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB54" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:28">
+      <c r="A55" s="7">
+        <v>53</v>
+      </c>
+      <c r="B55" s="7">
+        <v>2026060053</v>
+      </c>
+      <c r="C55" s="7">
+        <v>1</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="F55" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="G55" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="H55" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="I55" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="J55" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="K55" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L55" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="M55" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="N55" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="O55" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="P55" s="7"/>
+      <c r="Q55" s="7"/>
+      <c r="R55" s="7">
+        <v>29640</v>
+      </c>
+      <c r="S55" s="7"/>
+      <c r="T55" s="7"/>
+      <c r="U55" s="7"/>
+      <c r="V55" s="7"/>
+      <c r="W55" s="7"/>
+      <c r="X55" s="7"/>
+      <c r="Y55" s="7"/>
+      <c r="Z55" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="AA55" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB55" s="7"/>
+    </row>
+    <row r="56" spans="1:28">
+      <c r="A56" s="3">
+        <v>54</v>
+      </c>
+      <c r="B56" s="3">
+        <v>2026060050</v>
+      </c>
+      <c r="C56" s="3">
+        <v>1</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="I56" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="J56" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="K56" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L56" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="M56" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="N56" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="O56" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+      <c r="R56" s="3">
+        <v>37830</v>
+      </c>
+      <c r="S56" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="T56" s="3"/>
+      <c r="U56" s="3"/>
+      <c r="V56" s="3"/>
+      <c r="W56" s="3"/>
+      <c r="X56" s="3"/>
+      <c r="Y56" s="3"/>
+      <c r="Z56" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="AA56" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB56" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:28">
+      <c r="A57" s="7">
+        <v>55</v>
+      </c>
+      <c r="B57" s="7">
+        <v>2026060051</v>
+      </c>
+      <c r="C57" s="7">
+        <v>1</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E57" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="F57" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="G57" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="H57" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="I57" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="J57" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="K57" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L57" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="M57" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="N57" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="O57" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="P57" s="7"/>
+      <c r="Q57" s="7"/>
+      <c r="R57" s="7">
+        <v>37830</v>
+      </c>
+      <c r="S57" s="7"/>
+      <c r="T57" s="7"/>
+      <c r="U57" s="7"/>
+      <c r="V57" s="7"/>
+      <c r="W57" s="7"/>
+      <c r="X57" s="7"/>
+      <c r="Y57" s="7"/>
+      <c r="Z57" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="AA57" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB57" s="7"/>
+    </row>
+    <row r="58" spans="1:28">
+      <c r="A58" s="3">
+        <v>56</v>
+      </c>
+      <c r="B58" s="3">
+        <v>2026060046</v>
+      </c>
+      <c r="C58" s="3">
+        <v>1</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="K58" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L58" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="M58" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="N58" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="O58" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P58" s="3"/>
+      <c r="Q58" s="3"/>
+      <c r="R58" s="3">
+        <v>45926</v>
+      </c>
+      <c r="S58" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="T58" s="3"/>
+      <c r="U58" s="3"/>
+      <c r="V58" s="3"/>
+      <c r="W58" s="3"/>
+      <c r="X58" s="3"/>
+      <c r="Y58" s="3"/>
+      <c r="Z58" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="AA58" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB58" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:28">
+      <c r="A59" s="7">
+        <v>57</v>
+      </c>
+      <c r="B59" s="7">
+        <v>2026060047</v>
+      </c>
+      <c r="C59" s="7">
+        <v>1</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E59" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="F59" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="G59" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H59" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="I59" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="J59" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="K59" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L59" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="M59" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="N59" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="O59" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="P59" s="7"/>
+      <c r="Q59" s="7"/>
+      <c r="R59" s="7">
+        <v>45926</v>
+      </c>
+      <c r="S59" s="7"/>
+      <c r="T59" s="7"/>
+      <c r="U59" s="7"/>
+      <c r="V59" s="7"/>
+      <c r="W59" s="7"/>
+      <c r="X59" s="7"/>
+      <c r="Y59" s="7"/>
+      <c r="Z59" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="AA59" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB59" s="7"/>
+    </row>
+    <row r="60" spans="1:28">
+      <c r="A60" s="3">
+        <v>58</v>
+      </c>
+      <c r="B60" s="3">
+        <v>2026060040</v>
+      </c>
+      <c r="C60" s="3">
+        <v>1</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="K60" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L60" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="M60" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="N60" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="O60" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P60" s="3"/>
+      <c r="Q60" s="3"/>
+      <c r="R60" s="3">
+        <v>29640</v>
+      </c>
+      <c r="S60" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="T60" s="3"/>
+      <c r="U60" s="3"/>
+      <c r="V60" s="3"/>
+      <c r="W60" s="3"/>
+      <c r="X60" s="3"/>
+      <c r="Y60" s="3"/>
+      <c r="Z60" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="AA60" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB60" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:28">
+      <c r="A61" s="7">
+        <v>59</v>
+      </c>
+      <c r="B61" s="7">
+        <v>2026060041</v>
+      </c>
+      <c r="C61" s="7">
+        <v>1</v>
+      </c>
+      <c r="D61" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E61" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="F61" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="G61" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="H61" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="I61" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="J61" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="K61" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L61" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="M61" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="N61" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="O61" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="P61" s="7"/>
+      <c r="Q61" s="7"/>
+      <c r="R61" s="7">
+        <v>29640</v>
+      </c>
+      <c r="S61" s="7"/>
+      <c r="T61" s="7"/>
+      <c r="U61" s="7"/>
+      <c r="V61" s="7"/>
+      <c r="W61" s="7"/>
+      <c r="X61" s="7"/>
+      <c r="Y61" s="7"/>
+      <c r="Z61" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="AA61" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB61" s="7"/>
+    </row>
+    <row r="62" spans="1:28">
+      <c r="A62" s="3">
+        <v>60</v>
+      </c>
+      <c r="B62" s="3">
+        <v>2026060044</v>
+      </c>
+      <c r="C62" s="3">
+        <v>1</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="K62" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L62" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="M62" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="N62" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="O62" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P62" s="3"/>
+      <c r="Q62" s="3"/>
+      <c r="R62" s="3">
+        <v>34235</v>
+      </c>
+      <c r="S62" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="T62" s="3"/>
+      <c r="U62" s="3"/>
+      <c r="V62" s="3"/>
+      <c r="W62" s="3"/>
+      <c r="X62" s="3"/>
+      <c r="Y62" s="3"/>
+      <c r="Z62" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="AA62" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB62" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:28">
+      <c r="A63" s="7">
+        <v>61</v>
+      </c>
+      <c r="B63" s="7">
+        <v>2026060045</v>
+      </c>
+      <c r="C63" s="7">
+        <v>1</v>
+      </c>
+      <c r="D63" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E63" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="F63" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="G63" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="H63" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I63" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="J63" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="K63" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L63" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="M63" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="N63" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="O63" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="P63" s="7"/>
+      <c r="Q63" s="7"/>
+      <c r="R63" s="7">
+        <v>34235</v>
+      </c>
+      <c r="S63" s="7"/>
+      <c r="T63" s="7"/>
+      <c r="U63" s="7"/>
+      <c r="V63" s="7"/>
+      <c r="W63" s="7"/>
+      <c r="X63" s="7"/>
+      <c r="Y63" s="7"/>
+      <c r="Z63" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="AA63" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB63" s="7"/>
+    </row>
+    <row r="64" spans="1:28">
+      <c r="A64" s="3">
+        <v>62</v>
+      </c>
+      <c r="B64" s="3">
+        <v>2026060042</v>
+      </c>
+      <c r="C64" s="3">
+        <v>1</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="J64" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="K64" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L64" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="M64" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="N64" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="O64" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P64" s="3"/>
+      <c r="Q64" s="3"/>
+      <c r="R64" s="3">
+        <v>17791</v>
+      </c>
+      <c r="S64" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="T64" s="3"/>
+      <c r="U64" s="3"/>
+      <c r="V64" s="3"/>
+      <c r="W64" s="3"/>
+      <c r="X64" s="3"/>
+      <c r="Y64" s="3"/>
+      <c r="Z64" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="AA64" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB64" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:28">
+      <c r="A65" s="7">
+        <v>63</v>
+      </c>
+      <c r="B65" s="7">
+        <v>2026060043</v>
+      </c>
+      <c r="C65" s="7">
+        <v>1</v>
+      </c>
+      <c r="D65" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E65" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="F65" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="G65" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="H65" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="I65" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="J65" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="K65" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L65" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="M65" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="N65" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="O65" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="P65" s="7"/>
+      <c r="Q65" s="7"/>
+      <c r="R65" s="7">
+        <v>17791</v>
+      </c>
+      <c r="S65" s="7"/>
+      <c r="T65" s="7"/>
+      <c r="U65" s="7"/>
+      <c r="V65" s="7"/>
+      <c r="W65" s="7"/>
+      <c r="X65" s="7"/>
+      <c r="Y65" s="7"/>
+      <c r="Z65" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="AA65" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB65" s="7"/>
+    </row>
+    <row r="66" spans="1:28">
+      <c r="A66" s="3">
+        <v>64</v>
+      </c>
+      <c r="B66" s="3">
+        <v>2026060385</v>
+      </c>
+      <c r="C66" s="3">
+        <v>1</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="K66" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L66" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="M66" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="N66" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="O66" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P66" s="3"/>
+      <c r="Q66" s="3"/>
+      <c r="R66" s="3">
+        <v>122434</v>
+      </c>
+      <c r="S66" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="T66" s="3"/>
+      <c r="U66" s="3"/>
+      <c r="V66" s="3"/>
+      <c r="W66" s="3"/>
+      <c r="X66" s="3"/>
+      <c r="Y66" s="3"/>
+      <c r="Z66" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="AA66" s="3"/>
+      <c r="AB66" s="3"/>
+    </row>
+    <row r="67" spans="1:28">
+      <c r="A67" s="7">
+        <v>65</v>
+      </c>
+      <c r="B67" s="7">
+        <v>2026060386</v>
+      </c>
+      <c r="C67" s="7">
+        <v>1</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E67" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="F67" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G67" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="H67" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I67" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="J67" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="K67" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L67" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="M67" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="N67" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="O67" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="P67" s="7"/>
+      <c r="Q67" s="7"/>
+      <c r="R67" s="7">
+        <v>122434</v>
+      </c>
+      <c r="S67" s="7"/>
+      <c r="T67" s="7"/>
+      <c r="U67" s="7"/>
+      <c r="V67" s="7"/>
+      <c r="W67" s="7"/>
+      <c r="X67" s="7"/>
+      <c r="Y67" s="7"/>
+      <c r="Z67" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="AA67" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB67" s="7"/>
+    </row>
+    <row r="68" spans="1:28">
+      <c r="A68" s="3">
+        <v>66</v>
+      </c>
+      <c r="B68" s="3">
+        <v>2026060061</v>
+      </c>
+      <c r="C68" s="3">
+        <v>1</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="I68" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="J68" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="K68" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L68" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="M68" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="N68" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="O68" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P68" s="3"/>
+      <c r="Q68" s="3"/>
+      <c r="R68" s="3">
+        <v>702</v>
+      </c>
+      <c r="S68" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="T68" s="3"/>
+      <c r="U68" s="3"/>
+      <c r="V68" s="3"/>
+      <c r="W68" s="3"/>
+      <c r="X68" s="3"/>
+      <c r="Y68" s="3"/>
+      <c r="Z68" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="AA68" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB68" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:28">
+      <c r="A69" s="7">
+        <v>67</v>
+      </c>
+      <c r="B69" s="7">
+        <v>2026060062</v>
+      </c>
+      <c r="C69" s="7">
+        <v>1</v>
+      </c>
+      <c r="D69" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E69" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="F69" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="G69" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="H69" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="I69" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="J69" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="K69" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L69" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="M69" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="N69" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="O69" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="P69" s="7"/>
+      <c r="Q69" s="7"/>
+      <c r="R69" s="7">
+        <v>702</v>
+      </c>
+      <c r="S69" s="7"/>
+      <c r="T69" s="7"/>
+      <c r="U69" s="7"/>
+      <c r="V69" s="7"/>
+      <c r="W69" s="7"/>
+      <c r="X69" s="7"/>
+      <c r="Y69" s="7"/>
+      <c r="Z69" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="AA69" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB69" s="7"/>
+    </row>
+    <row r="70" spans="1:28">
+      <c r="A70" s="3">
+        <v>68</v>
+      </c>
+      <c r="B70" s="3">
+        <v>2026060048</v>
+      </c>
+      <c r="C70" s="3">
+        <v>1</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="I70" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="J70" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="K70" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L70" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="M70" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="N70" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="O70" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P70" s="3"/>
+      <c r="Q70" s="3"/>
+      <c r="R70" s="3">
+        <v>5766</v>
+      </c>
+      <c r="S70" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="T70" s="3"/>
+      <c r="U70" s="3"/>
+      <c r="V70" s="3"/>
+      <c r="W70" s="3"/>
+      <c r="X70" s="3"/>
+      <c r="Y70" s="3"/>
+      <c r="Z70" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="AA70" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB70" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:28">
+      <c r="A71" s="7">
+        <v>69</v>
+      </c>
+      <c r="B71" s="7">
+        <v>2026060049</v>
+      </c>
+      <c r="C71" s="7">
+        <v>1</v>
+      </c>
+      <c r="D71" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E71" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="F71" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="G71" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="H71" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="I71" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="J71" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="K71" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L71" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="M71" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="N71" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="O71" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="P71" s="7"/>
+      <c r="Q71" s="7"/>
+      <c r="R71" s="7">
+        <v>5766</v>
+      </c>
+      <c r="S71" s="7"/>
+      <c r="T71" s="7"/>
+      <c r="U71" s="7"/>
+      <c r="V71" s="7"/>
+      <c r="W71" s="7"/>
+      <c r="X71" s="7"/>
+      <c r="Y71" s="7"/>
+      <c r="Z71" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="AA71" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB71" s="7"/>
+    </row>
+    <row r="72" spans="1:28">
+      <c r="A72" s="3">
+        <v>70</v>
+      </c>
+      <c r="B72" s="3">
+        <v>2026060819</v>
+      </c>
+      <c r="C72" s="3">
+        <v>1</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="K72" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L72" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="M72" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="N72" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="O72" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P72" s="3"/>
+      <c r="Q72" s="3">
+        <v>35761</v>
+      </c>
+      <c r="R72" s="3">
+        <v>68540</v>
+      </c>
+      <c r="S72" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="T72" s="3"/>
+      <c r="U72" s="3"/>
+      <c r="V72" s="3"/>
+      <c r="W72" s="3"/>
+      <c r="X72" s="3"/>
+      <c r="Y72" s="3"/>
+      <c r="Z72" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="AA72" s="3"/>
+      <c r="AB72" s="3"/>
+    </row>
+    <row r="73" spans="1:28">
+      <c r="A73" s="7">
+        <v>71</v>
+      </c>
+      <c r="B73" s="7">
+        <v>2026060820</v>
+      </c>
+      <c r="C73" s="7">
+        <v>1</v>
+      </c>
+      <c r="D73" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E73" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="F73" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="G73" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="H73" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="I73" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="J73" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="K73" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L73" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="M73" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="N73" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="O73" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="P73" s="7"/>
+      <c r="Q73" s="7">
+        <v>35761</v>
+      </c>
+      <c r="R73" s="7">
+        <v>68540</v>
+      </c>
+      <c r="S73" s="7"/>
+      <c r="T73" s="7"/>
+      <c r="U73" s="7"/>
+      <c r="V73" s="7"/>
+      <c r="W73" s="7"/>
+      <c r="X73" s="7"/>
+      <c r="Y73" s="7"/>
+      <c r="Z73" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="AA73" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB73" s="7"/>
+    </row>
+    <row r="74" spans="1:28">
+      <c r="A74" s="3">
+        <v>72</v>
+      </c>
+      <c r="B74" s="3">
+        <v>2026060526</v>
+      </c>
+      <c r="C74" s="3">
+        <v>1</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="I74" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="J74" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="K74" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L74" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="M74" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="N74" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="O74" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P74" s="3"/>
+      <c r="Q74" s="3"/>
+      <c r="R74" s="3">
+        <v>33686</v>
+      </c>
+      <c r="S74" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="T74" s="3"/>
+      <c r="U74" s="3"/>
+      <c r="V74" s="3"/>
+      <c r="W74" s="3"/>
+      <c r="X74" s="3"/>
+      <c r="Y74" s="3"/>
+      <c r="Z74" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="AA74" s="3"/>
+      <c r="AB74" s="3"/>
+    </row>
+    <row r="75" spans="1:28">
+      <c r="A75" s="7">
+        <v>73</v>
+      </c>
+      <c r="B75" s="7">
+        <v>2026060527</v>
+      </c>
+      <c r="C75" s="7">
+        <v>1</v>
+      </c>
+      <c r="D75" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E75" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="F75" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G75" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="H75" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="I75" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="J75" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="K75" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L75" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="M75" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="N75" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="O75" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="P75" s="7"/>
+      <c r="Q75" s="7"/>
+      <c r="R75" s="7">
+        <v>33686</v>
+      </c>
+      <c r="S75" s="7"/>
+      <c r="T75" s="7"/>
+      <c r="U75" s="7"/>
+      <c r="V75" s="7"/>
+      <c r="W75" s="7"/>
+      <c r="X75" s="7"/>
+      <c r="Y75" s="7"/>
+      <c r="Z75" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="AA75" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB75" s="7"/>
+    </row>
+    <row r="76" spans="1:28">
+      <c r="A76" s="3">
+        <v>74</v>
+      </c>
+      <c r="B76" s="3">
+        <v>2026060408</v>
+      </c>
+      <c r="C76" s="3">
+        <v>1</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="K76" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L76" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="M76" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="N76" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="O76" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P76" s="3"/>
+      <c r="Q76" s="3"/>
+      <c r="R76" s="3">
+        <v>19776</v>
+      </c>
+      <c r="S76" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="T76" s="3"/>
+      <c r="U76" s="3"/>
+      <c r="V76" s="3"/>
+      <c r="W76" s="3"/>
+      <c r="X76" s="3"/>
+      <c r="Y76" s="3"/>
+      <c r="Z76" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="AA76" s="3"/>
+      <c r="AB76" s="3"/>
+    </row>
+    <row r="77" spans="1:28">
+      <c r="A77" s="7">
+        <v>75</v>
+      </c>
+      <c r="B77" s="7">
+        <v>2026060409</v>
+      </c>
+      <c r="C77" s="7">
+        <v>1</v>
+      </c>
+      <c r="D77" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E77" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="F77" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G77" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="H77" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="I77" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="J77" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="K77" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L77" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="M77" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="N77" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="O77" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="P77" s="7"/>
+      <c r="Q77" s="7"/>
+      <c r="R77" s="7">
+        <v>19776</v>
+      </c>
+      <c r="S77" s="7"/>
+      <c r="T77" s="7"/>
+      <c r="U77" s="7"/>
+      <c r="V77" s="7"/>
+      <c r="W77" s="7"/>
+      <c r="X77" s="7"/>
+      <c r="Y77" s="7"/>
+      <c r="Z77" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="AA77" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB77" s="7"/>
+    </row>
+    <row r="78" spans="1:28">
+      <c r="A78" s="3">
         <v>76</v>
       </c>
-      <c r="AA36" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB36" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:28">
-      <c r="A37" s="9"/>
-      <c r="B37" s="9"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
-      <c r="H37" s="9"/>
-      <c r="I37" s="9"/>
-      <c r="J37" s="9"/>
-      <c r="K37" s="9"/>
-      <c r="L37" s="10"/>
-      <c r="M37" s="10"/>
-      <c r="N37" s="10"/>
-      <c r="O37" s="9"/>
-      <c r="P37" s="9"/>
-      <c r="Q37" s="9"/>
-      <c r="R37" s="9"/>
-      <c r="S37" s="9"/>
-      <c r="T37" s="9"/>
-      <c r="U37" s="9"/>
-      <c r="V37" s="9"/>
-      <c r="W37" s="9"/>
-      <c r="X37" s="9"/>
-      <c r="Y37" s="9"/>
-      <c r="Z37" s="10"/>
-      <c r="AA37" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="AB37" s="9">
-        <v>15</v>
+      <c r="B78" s="3">
+        <v>2026060389</v>
+      </c>
+      <c r="C78" s="3">
+        <v>1</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="I78" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="J78" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="K78" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L78" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="M78" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="N78" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="O78" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P78" s="3"/>
+      <c r="Q78" s="3"/>
+      <c r="R78" s="3">
+        <v>92779</v>
+      </c>
+      <c r="S78" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="T78" s="3"/>
+      <c r="U78" s="3"/>
+      <c r="V78" s="3"/>
+      <c r="W78" s="3"/>
+      <c r="X78" s="3"/>
+      <c r="Y78" s="3"/>
+      <c r="Z78" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="AA78" s="3"/>
+      <c r="AB78" s="3"/>
+    </row>
+    <row r="79" spans="1:28">
+      <c r="A79" s="7">
+        <v>77</v>
+      </c>
+      <c r="B79" s="7">
+        <v>2026060390</v>
+      </c>
+      <c r="C79" s="7">
+        <v>1</v>
+      </c>
+      <c r="D79" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E79" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="F79" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G79" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="H79" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="I79" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="J79" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="K79" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L79" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="M79" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="N79" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="O79" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="P79" s="7"/>
+      <c r="Q79" s="7"/>
+      <c r="R79" s="7">
+        <v>92779</v>
+      </c>
+      <c r="S79" s="7"/>
+      <c r="T79" s="7"/>
+      <c r="U79" s="7"/>
+      <c r="V79" s="7"/>
+      <c r="W79" s="7"/>
+      <c r="X79" s="7"/>
+      <c r="Y79" s="7"/>
+      <c r="Z79" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="AA79" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB79" s="7"/>
+    </row>
+    <row r="80" spans="1:28">
+      <c r="A80" s="3">
+        <v>78</v>
+      </c>
+      <c r="B80" s="3">
+        <v>2026060853</v>
+      </c>
+      <c r="C80" s="3">
+        <v>1</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="I80" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="J80" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="K80" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L80" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="M80" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="N80" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="O80" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P80" s="3"/>
+      <c r="Q80" s="3"/>
+      <c r="R80" s="3">
+        <v>92779</v>
+      </c>
+      <c r="S80" s="3"/>
+      <c r="T80" s="3"/>
+      <c r="U80" s="3"/>
+      <c r="V80" s="3"/>
+      <c r="W80" s="3"/>
+      <c r="X80" s="3"/>
+      <c r="Y80" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z80" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="AA80" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB80" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:28">
+      <c r="A81" s="7">
+        <v>79</v>
+      </c>
+      <c r="B81" s="7">
+        <v>2026060383</v>
+      </c>
+      <c r="C81" s="7">
+        <v>1</v>
+      </c>
+      <c r="D81" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E81" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="F81" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G81" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="H81" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="I81" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="J81" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="K81" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L81" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="M81" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="N81" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="O81" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P81" s="7"/>
+      <c r="Q81" s="7"/>
+      <c r="R81" s="7">
+        <v>207716</v>
+      </c>
+      <c r="S81" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="T81" s="7"/>
+      <c r="U81" s="7"/>
+      <c r="V81" s="7"/>
+      <c r="W81" s="7"/>
+      <c r="X81" s="7"/>
+      <c r="Y81" s="7"/>
+      <c r="Z81" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="AA81" s="7"/>
+      <c r="AB81" s="7"/>
+    </row>
+    <row r="82" spans="1:28">
+      <c r="A82" s="3">
+        <v>80</v>
+      </c>
+      <c r="B82" s="3">
+        <v>2026060384</v>
+      </c>
+      <c r="C82" s="3">
+        <v>1</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="I82" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="J82" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="K82" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L82" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="M82" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="N82" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="O82" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="P82" s="3"/>
+      <c r="Q82" s="3"/>
+      <c r="R82" s="3">
+        <v>207716</v>
+      </c>
+      <c r="S82" s="3"/>
+      <c r="T82" s="3"/>
+      <c r="U82" s="3"/>
+      <c r="V82" s="3"/>
+      <c r="W82" s="3"/>
+      <c r="X82" s="3"/>
+      <c r="Y82" s="3"/>
+      <c r="Z82" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="AA82" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="1:28">
+      <c r="A83" s="7">
+        <v>81</v>
+      </c>
+      <c r="B83" s="7">
+        <v>2026060569</v>
+      </c>
+      <c r="C83" s="7">
+        <v>1</v>
+      </c>
+      <c r="D83" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E83" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="F83" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G83" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="H83" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="I83" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="J83" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="K83" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L83" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="M83" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="N83" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="O83" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P83" s="7"/>
+      <c r="Q83" s="7"/>
+      <c r="R83" s="7">
+        <v>207716</v>
+      </c>
+      <c r="S83" s="7"/>
+      <c r="T83" s="7"/>
+      <c r="U83" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="V83" s="7"/>
+      <c r="W83" s="7"/>
+      <c r="X83" s="7"/>
+      <c r="Y83" s="7"/>
+      <c r="Z83" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA83" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB83" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:28">
+      <c r="A84" s="3">
+        <v>82</v>
+      </c>
+      <c r="B84" s="3">
+        <v>2026060387</v>
+      </c>
+      <c r="C84" s="3">
+        <v>1</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="I84" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="J84" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="K84" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L84" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="M84" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="N84" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="O84" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P84" s="3"/>
+      <c r="Q84" s="3"/>
+      <c r="R84" s="3">
+        <v>152071</v>
+      </c>
+      <c r="S84" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="T84" s="3"/>
+      <c r="U84" s="3"/>
+      <c r="V84" s="3"/>
+      <c r="W84" s="3"/>
+      <c r="X84" s="3"/>
+      <c r="Y84" s="3"/>
+      <c r="Z84" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="AA84" s="3"/>
+      <c r="AB84" s="3"/>
+    </row>
+    <row r="85" spans="1:28">
+      <c r="A85" s="7">
+        <v>83</v>
+      </c>
+      <c r="B85" s="7">
+        <v>2026060388</v>
+      </c>
+      <c r="C85" s="7">
+        <v>1</v>
+      </c>
+      <c r="D85" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E85" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="F85" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G85" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H85" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="I85" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="J85" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="K85" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L85" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="M85" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="N85" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="O85" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="P85" s="7"/>
+      <c r="Q85" s="7"/>
+      <c r="R85" s="7">
+        <v>152071</v>
+      </c>
+      <c r="S85" s="7"/>
+      <c r="T85" s="7"/>
+      <c r="U85" s="7"/>
+      <c r="V85" s="7"/>
+      <c r="W85" s="7"/>
+      <c r="X85" s="7"/>
+      <c r="Y85" s="7"/>
+      <c r="Z85" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="AA85" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB85" s="7"/>
+    </row>
+    <row r="86" spans="1:28">
+      <c r="A86" s="3">
+        <v>84</v>
+      </c>
+      <c r="B86" s="3">
+        <v>2026060570</v>
+      </c>
+      <c r="C86" s="3">
+        <v>1</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="H86" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="I86" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="J86" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="K86" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L86" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="M86" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="N86" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="O86" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P86" s="3"/>
+      <c r="Q86" s="3"/>
+      <c r="R86" s="3">
+        <v>152071</v>
+      </c>
+      <c r="S86" s="3"/>
+      <c r="T86" s="3"/>
+      <c r="U86" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V86" s="3"/>
+      <c r="W86" s="3"/>
+      <c r="X86" s="3"/>
+      <c r="Y86" s="3"/>
+      <c r="Z86" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA86" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB86" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:28">
+      <c r="A87" s="7">
+        <v>85</v>
+      </c>
+      <c r="B87" s="7">
+        <v>2026060081</v>
+      </c>
+      <c r="C87" s="7">
+        <v>1</v>
+      </c>
+      <c r="D87" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E87" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="F87" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="G87" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="H87" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="I87" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="J87" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="K87" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L87" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="M87" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="N87" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="O87" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P87" s="7"/>
+      <c r="Q87" s="7"/>
+      <c r="R87" s="7">
+        <v>48</v>
+      </c>
+      <c r="S87" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="T87" s="7"/>
+      <c r="U87" s="7"/>
+      <c r="V87" s="7"/>
+      <c r="W87" s="7"/>
+      <c r="X87" s="7"/>
+      <c r="Y87" s="7"/>
+      <c r="Z87" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="AA87" s="7"/>
+      <c r="AB87" s="7"/>
+    </row>
+    <row r="88" spans="1:28">
+      <c r="A88" s="3">
+        <v>86</v>
+      </c>
+      <c r="B88" s="3">
+        <v>2026060082</v>
+      </c>
+      <c r="C88" s="3">
+        <v>1</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="H88" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="I88" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="J88" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="K88" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L88" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="M88" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="N88" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="O88" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="P88" s="3"/>
+      <c r="Q88" s="3"/>
+      <c r="R88" s="3">
+        <v>48</v>
+      </c>
+      <c r="S88" s="3"/>
+      <c r="T88" s="3"/>
+      <c r="U88" s="3"/>
+      <c r="V88" s="3"/>
+      <c r="W88" s="3"/>
+      <c r="X88" s="3"/>
+      <c r="Y88" s="3"/>
+      <c r="Z88" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="AA88" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB88" s="3"/>
+    </row>
+    <row r="89" spans="1:28">
+      <c r="A89" s="7">
+        <v>87</v>
+      </c>
+      <c r="B89" s="7">
+        <v>2026060145</v>
+      </c>
+      <c r="C89" s="7">
+        <v>1</v>
+      </c>
+      <c r="D89" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E89" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="F89" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="G89" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="H89" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="I89" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="J89" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="K89" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L89" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="M89" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="N89" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="O89" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P89" s="7"/>
+      <c r="Q89" s="7"/>
+      <c r="R89" s="7">
+        <v>38244</v>
+      </c>
+      <c r="S89" s="7"/>
+      <c r="T89" s="7"/>
+      <c r="U89" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="V89" s="7"/>
+      <c r="W89" s="7"/>
+      <c r="X89" s="7"/>
+      <c r="Y89" s="7"/>
+      <c r="Z89" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA89" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB89" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:28">
+      <c r="A90" s="3">
+        <v>88</v>
+      </c>
+      <c r="B90" s="3">
+        <v>2026060144</v>
+      </c>
+      <c r="C90" s="3">
+        <v>1</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="G90" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="H90" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="I90" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="J90" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="K90" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L90" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="M90" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="N90" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="O90" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P90" s="3"/>
+      <c r="Q90" s="3"/>
+      <c r="R90" s="3">
+        <v>386259</v>
+      </c>
+      <c r="S90" s="3"/>
+      <c r="T90" s="3"/>
+      <c r="U90" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V90" s="3"/>
+      <c r="W90" s="3"/>
+      <c r="X90" s="3"/>
+      <c r="Y90" s="3"/>
+      <c r="Z90" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA90" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB90" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:28">
+      <c r="A91" s="7">
+        <v>89</v>
+      </c>
+      <c r="B91" s="7">
+        <v>2026060143</v>
+      </c>
+      <c r="C91" s="7">
+        <v>1</v>
+      </c>
+      <c r="D91" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E91" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="F91" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="G91" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="H91" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="I91" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="J91" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="K91" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L91" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="M91" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="N91" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="O91" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P91" s="7"/>
+      <c r="Q91" s="7"/>
+      <c r="R91" s="7">
+        <v>381383</v>
+      </c>
+      <c r="S91" s="7"/>
+      <c r="T91" s="7"/>
+      <c r="U91" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="V91" s="7"/>
+      <c r="W91" s="7"/>
+      <c r="X91" s="7"/>
+      <c r="Y91" s="7"/>
+      <c r="Z91" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA91" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB91" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:28">
+      <c r="A92" s="3">
+        <v>90</v>
+      </c>
+      <c r="B92" s="3">
+        <v>2026060142</v>
+      </c>
+      <c r="C92" s="3">
+        <v>1</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="F92" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="G92" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H92" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="I92" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="J92" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="K92" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L92" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="M92" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="N92" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="O92" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P92" s="3"/>
+      <c r="Q92" s="3"/>
+      <c r="R92" s="3">
+        <v>31873</v>
+      </c>
+      <c r="S92" s="3"/>
+      <c r="T92" s="3"/>
+      <c r="U92" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V92" s="3"/>
+      <c r="W92" s="3"/>
+      <c r="X92" s="3"/>
+      <c r="Y92" s="3"/>
+      <c r="Z92" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA92" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB92" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:28">
+      <c r="A93" s="7">
+        <v>91</v>
+      </c>
+      <c r="B93" s="7">
+        <v>2026060141</v>
+      </c>
+      <c r="C93" s="7">
+        <v>1</v>
+      </c>
+      <c r="D93" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E93" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="F93" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="G93" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="H93" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="I93" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="J93" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="K93" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L93" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="M93" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="N93" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="O93" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P93" s="7"/>
+      <c r="Q93" s="7"/>
+      <c r="R93" s="7">
+        <v>30842</v>
+      </c>
+      <c r="S93" s="7"/>
+      <c r="T93" s="7"/>
+      <c r="U93" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="V93" s="7"/>
+      <c r="W93" s="7"/>
+      <c r="X93" s="7"/>
+      <c r="Y93" s="7"/>
+      <c r="Z93" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA93" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB93" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:28">
+      <c r="A94" s="3">
+        <v>92</v>
+      </c>
+      <c r="B94" s="3">
+        <v>2026060510</v>
+      </c>
+      <c r="C94" s="3">
+        <v>1</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="J94" s="3"/>
+      <c r="K94" s="3"/>
+      <c r="L94" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="M94" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="N94" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="O94" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P94" s="3"/>
+      <c r="Q94" s="3"/>
+      <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="T94" s="3"/>
+      <c r="U94" s="3"/>
+      <c r="V94" s="3"/>
+      <c r="W94" s="3"/>
+      <c r="X94" s="3"/>
+      <c r="Y94" s="3"/>
+      <c r="Z94" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA94" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB94" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:28">
+      <c r="A95" s="7">
+        <v>93</v>
+      </c>
+      <c r="B95" s="7">
+        <v>2026060850</v>
+      </c>
+      <c r="C95" s="7">
+        <v>1</v>
+      </c>
+      <c r="D95" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E95" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="F95" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="G95" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="H95" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="I95" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="J95" s="7"/>
+      <c r="K95" s="7"/>
+      <c r="L95" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="M95" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="N95" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="O95" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P95" s="7"/>
+      <c r="Q95" s="7"/>
+      <c r="R95" s="7">
+        <v>0</v>
+      </c>
+      <c r="S95" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="T95" s="7"/>
+      <c r="U95" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="V95" s="7"/>
+      <c r="W95" s="7"/>
+      <c r="X95" s="7"/>
+      <c r="Y95" s="7"/>
+      <c r="Z95" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="AA95" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB95" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:28">
+      <c r="A96" s="3">
+        <v>94</v>
+      </c>
+      <c r="B96" s="3">
+        <v>2026060475</v>
+      </c>
+      <c r="C96" s="3">
+        <v>1</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="J96" s="3"/>
+      <c r="K96" s="3"/>
+      <c r="L96" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="M96" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="N96" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="O96" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P96" s="3"/>
+      <c r="Q96" s="3"/>
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="T96" s="3"/>
+      <c r="U96" s="3"/>
+      <c r="V96" s="3"/>
+      <c r="W96" s="3"/>
+      <c r="X96" s="3"/>
+      <c r="Y96" s="3"/>
+      <c r="Z96" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA96" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB96" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:28">
+      <c r="A97" s="7">
+        <v>95</v>
+      </c>
+      <c r="B97" s="7">
+        <v>2026060149</v>
+      </c>
+      <c r="C97" s="7">
+        <v>1</v>
+      </c>
+      <c r="D97" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E97" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="F97" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G97" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="H97" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="I97" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="J97" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="K97" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="L97" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="M97" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="N97" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="O97" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="P97" s="7"/>
+      <c r="Q97" s="7"/>
+      <c r="R97" s="7">
+        <v>0</v>
+      </c>
+      <c r="S97" s="7"/>
+      <c r="T97" s="7"/>
+      <c r="U97" s="7"/>
+      <c r="V97" s="7"/>
+      <c r="W97" s="7"/>
+      <c r="X97" s="7"/>
+      <c r="Y97" s="7"/>
+      <c r="Z97" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="AA97" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB97" s="7"/>
+    </row>
+    <row r="98" spans="1:28">
+      <c r="A98" s="9"/>
+      <c r="B98" s="9"/>
+      <c r="C98" s="9"/>
+      <c r="D98" s="9"/>
+      <c r="E98" s="9"/>
+      <c r="F98" s="9"/>
+      <c r="G98" s="9"/>
+      <c r="H98" s="9"/>
+      <c r="I98" s="9"/>
+      <c r="J98" s="9"/>
+      <c r="K98" s="9"/>
+      <c r="L98" s="10"/>
+      <c r="M98" s="10"/>
+      <c r="N98" s="10"/>
+      <c r="O98" s="9"/>
+      <c r="P98" s="9"/>
+      <c r="Q98" s="9"/>
+      <c r="R98" s="9"/>
+      <c r="S98" s="9"/>
+      <c r="T98" s="9"/>
+      <c r="U98" s="9"/>
+      <c r="V98" s="9"/>
+      <c r="W98" s="9"/>
+      <c r="X98" s="9"/>
+      <c r="Y98" s="9"/>
+      <c r="Z98" s="10"/>
+      <c r="AA98" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="AB98" s="9">
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/IM/202606_Service_Count_Report.xlsx
+++ b/IM/202606_Service_Count_Report.xlsx
@@ -11,14 +11,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Report'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$AA$98</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$AA$106</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="325">
   <si>
     <t>服務次數統計表        篩選月份：202606</t>
   </si>
@@ -194,6 +194,36 @@
     <t>士林</t>
   </si>
   <si>
+    <t>2026-06-04</t>
+  </si>
+  <si>
+    <t>10:34:00</t>
+  </si>
+  <si>
+    <t>T301800079</t>
+  </si>
+  <si>
+    <t>eS-3018A 黑白複合機</t>
+  </si>
+  <si>
+    <t xml:space="preserve">虹揚印刷股份有限公司 </t>
+  </si>
+  <si>
+    <t>新北市中和區橋和路120號9樓之7</t>
+  </si>
+  <si>
+    <t>9F</t>
+  </si>
+  <si>
+    <t>維修</t>
+  </si>
+  <si>
+    <t>換機</t>
+  </si>
+  <si>
+    <t>10:33:00</t>
+  </si>
+  <si>
     <t>2026-06-03</t>
   </si>
   <si>
@@ -218,6 +248,21 @@
     <t>天玉街</t>
   </si>
   <si>
+    <t>11:00:00</t>
+  </si>
+  <si>
+    <t>11:30:00</t>
+  </si>
+  <si>
+    <t>T302800122</t>
+  </si>
+  <si>
+    <t>新北市中和區橋和路120號6樓</t>
+  </si>
+  <si>
+    <t>6F</t>
+  </si>
+  <si>
     <t>10:30:00</t>
   </si>
   <si>
@@ -399,9 +444,6 @@
   </si>
   <si>
     <t>T301800078</t>
-  </si>
-  <si>
-    <t>eS-3018A 黑白複合機</t>
   </si>
   <si>
     <t>合作金庫商業銀行股份有限公司長庚分公司</t>
@@ -456,9 +498,6 @@
 送黑色碳粉 1</t>
   </si>
   <si>
-    <t>11:00:00</t>
-  </si>
-  <si>
     <t>12:11:00</t>
   </si>
   <si>
@@ -679,9 +718,6 @@
     <t>碳粉</t>
   </si>
   <si>
-    <t>11:30:00</t>
-  </si>
-  <si>
     <t>T302800053</t>
   </si>
   <si>
@@ -880,6 +916,33 @@
     <t>台北客服4樓中(黑)</t>
   </si>
   <si>
+    <t>THILF02691</t>
+  </si>
+  <si>
+    <t>新北市五股區五工五路18號</t>
+  </si>
+  <si>
+    <t>五股興珍店</t>
+  </si>
+  <si>
+    <t>THILF03227</t>
+  </si>
+  <si>
+    <t>新北市五股區四維路153號</t>
+  </si>
+  <si>
+    <t>五股四維店</t>
+  </si>
+  <si>
+    <t>THILF05003</t>
+  </si>
+  <si>
+    <t>新北市五股區中興路二段1號一樓</t>
+  </si>
+  <si>
+    <t>五股更寮店</t>
+  </si>
+  <si>
     <t>狄澤洋</t>
   </si>
   <si>
@@ -910,6 +973,24 @@
     <t>PMQ2 EDC SC7</t>
   </si>
   <si>
+    <t>THILF04680</t>
+  </si>
+  <si>
+    <t>一般件</t>
+  </si>
+  <si>
+    <t>其他</t>
+  </si>
+  <si>
+    <t>新北市板橋區江寧路三段49、51號一樓</t>
+  </si>
+  <si>
+    <t>板橋江寧店</t>
+  </si>
+  <si>
+    <t>電腦線路重新插拔測試正常</t>
+  </si>
+  <si>
     <t>14:25:00</t>
   </si>
   <si>
@@ -920,15 +1001,6 @@
   </si>
   <si>
     <t>板橋懷仁店</t>
-  </si>
-  <si>
-    <t>一般件</t>
-  </si>
-  <si>
-    <t>其他</t>
-  </si>
-  <si>
-    <t>維修</t>
   </si>
   <si>
     <t>票券紙無效票未撕除，排除後測試正常</t>
@@ -1348,7 +1420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AB98"/>
+  <dimension ref="A1:AB106"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="true" style="0"/>
@@ -1710,7 +1782,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="3">
-        <v>2026060623</v>
+        <v>2026060654</v>
       </c>
       <c r="C6" s="3">
         <v>1</v>
@@ -1725,36 +1797,36 @@
         <v>54</v>
       </c>
       <c r="G6" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="I6" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="J6" s="3" t="s">
         <v>57</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="K6" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L6" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="M6" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="M6" s="6" t="s">
+      <c r="N6" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="N6" s="6" t="s">
+      <c r="O6" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="O6" s="3" t="s">
-        <v>48</v>
       </c>
       <c r="P6" s="3"/>
       <c r="Q6" s="3"/>
       <c r="R6" s="3">
-        <v>83977</v>
+        <v>296675</v>
       </c>
       <c r="S6" s="3"/>
       <c r="T6" s="3"/>
@@ -1763,7 +1835,9 @@
       <c r="W6" s="3"/>
       <c r="X6" s="3"/>
       <c r="Y6" s="3"/>
-      <c r="Z6" s="6"/>
+      <c r="Z6" s="6" t="s">
+        <v>62</v>
+      </c>
       <c r="AA6" s="3" t="s">
         <v>40</v>
       </c>
@@ -1776,7 +1850,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="7">
-        <v>2026060404</v>
+        <v>2026060883</v>
       </c>
       <c r="C7" s="7">
         <v>1</v>
@@ -1788,37 +1862,39 @@
         <v>30</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>63</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="K7" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="M7" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="N7" s="8"/>
+        <v>59</v>
+      </c>
+      <c r="N7" s="8" t="s">
+        <v>60</v>
+      </c>
       <c r="O7" s="7" t="s">
         <v>48</v>
       </c>
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
       <c r="R7" s="7">
-        <v>142473</v>
+        <v>296675</v>
       </c>
       <c r="S7" s="7"/>
       <c r="T7" s="7"/>
@@ -1831,16 +1907,14 @@
       <c r="AA7" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AB7" s="7">
-        <v>1</v>
-      </c>
+      <c r="AB7" s="7"/>
     </row>
     <row r="8" spans="1:28">
       <c r="A8" s="3">
         <v>6</v>
       </c>
       <c r="B8" s="3">
-        <v>2026060855</v>
+        <v>2026060623</v>
       </c>
       <c r="C8" s="3">
         <v>1</v>
@@ -1852,50 +1926,48 @@
         <v>30</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="G8" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="J8" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>65</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="M8" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="N8" s="6"/>
+        <v>70</v>
+      </c>
+      <c r="N8" s="6" t="s">
+        <v>71</v>
+      </c>
       <c r="O8" s="3" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
       <c r="R8" s="3">
-        <v>142511</v>
-      </c>
-      <c r="S8" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>83977</v>
+      </c>
+      <c r="S8" s="3"/>
       <c r="T8" s="3"/>
       <c r="U8" s="3"/>
       <c r="V8" s="3"/>
       <c r="W8" s="3"/>
       <c r="X8" s="3"/>
       <c r="Y8" s="3"/>
-      <c r="Z8" s="6" t="s">
-        <v>41</v>
-      </c>
+      <c r="Z8" s="6"/>
       <c r="AA8" s="3" t="s">
         <v>40</v>
       </c>
@@ -1908,7 +1980,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="7">
-        <v>2026060391</v>
+        <v>2026060916</v>
       </c>
       <c r="C9" s="7">
         <v>1</v>
@@ -1920,37 +1992,39 @@
         <v>30</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="K9" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="M9" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="N9" s="8"/>
+        <v>75</v>
+      </c>
+      <c r="N9" s="8" t="s">
+        <v>76</v>
+      </c>
       <c r="O9" s="7" t="s">
         <v>48</v>
       </c>
       <c r="P9" s="7"/>
       <c r="Q9" s="7"/>
       <c r="R9" s="7">
-        <v>255338</v>
+        <v>37172</v>
       </c>
       <c r="S9" s="7"/>
       <c r="T9" s="7"/>
@@ -1972,7 +2046,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="3">
-        <v>2026060865</v>
+        <v>2026060404</v>
       </c>
       <c r="C10" s="3">
         <v>1</v>
@@ -1984,50 +2058,46 @@
         <v>30</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="M10" s="6" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="N10" s="6"/>
       <c r="O10" s="3" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
       <c r="R10" s="3">
-        <v>255417</v>
-      </c>
-      <c r="S10" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>142473</v>
+      </c>
+      <c r="S10" s="3"/>
       <c r="T10" s="3"/>
       <c r="U10" s="3"/>
       <c r="V10" s="3"/>
       <c r="W10" s="3"/>
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
-      <c r="Z10" s="6" t="s">
-        <v>77</v>
-      </c>
+      <c r="Z10" s="6"/>
       <c r="AA10" s="3" t="s">
         <v>40</v>
       </c>
@@ -2040,7 +2110,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="7">
-        <v>2026060464</v>
+        <v>2026060855</v>
       </c>
       <c r="C11" s="7">
         <v>1</v>
@@ -2052,47 +2122,49 @@
         <v>30</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="H11" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="I11" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="I11" s="7" t="s">
+      <c r="J11" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
+      <c r="K11" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="L11" s="8" t="s">
         <v>81</v>
       </c>
       <c r="M11" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="N11" s="8" t="s">
-        <v>83</v>
-      </c>
+      <c r="N11" s="8"/>
       <c r="O11" s="7" t="s">
         <v>39</v>
       </c>
       <c r="P11" s="7"/>
       <c r="Q11" s="7"/>
       <c r="R11" s="7">
-        <v>0</v>
-      </c>
-      <c r="S11" s="7"/>
+        <v>142511</v>
+      </c>
+      <c r="S11" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T11" s="7"/>
-      <c r="U11" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="U11" s="7"/>
       <c r="V11" s="7"/>
       <c r="W11" s="7"/>
       <c r="X11" s="7"/>
       <c r="Y11" s="7"/>
       <c r="Z11" s="8" t="s">
-        <v>84</v>
+        <v>41</v>
       </c>
       <c r="AA11" s="7" t="s">
         <v>40</v>
@@ -2106,7 +2178,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="3">
-        <v>2026060669</v>
+        <v>2026060391</v>
       </c>
       <c r="C12" s="3">
         <v>1</v>
@@ -2118,7 +2190,7 @@
         <v>30</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>85</v>
@@ -2129,39 +2201,35 @@
       <c r="I12" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
+      <c r="J12" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="L12" s="6" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="N12" s="6" t="s">
         <v>89</v>
       </c>
+      <c r="N12" s="6"/>
       <c r="O12" s="3" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
       <c r="R12" s="3">
-        <v>0</v>
-      </c>
-      <c r="S12" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>255338</v>
+      </c>
+      <c r="S12" s="3"/>
       <c r="T12" s="3"/>
       <c r="U12" s="3"/>
       <c r="V12" s="3"/>
       <c r="W12" s="3"/>
       <c r="X12" s="3"/>
-      <c r="Y12" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="Z12" s="6" t="s">
-        <v>90</v>
-      </c>
+      <c r="Y12" s="3"/>
+      <c r="Z12" s="6"/>
       <c r="AA12" s="3" t="s">
         <v>40</v>
       </c>
@@ -2174,7 +2242,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="7">
-        <v>2026060656</v>
+        <v>2026060865</v>
       </c>
       <c r="C13" s="7">
         <v>1</v>
@@ -2186,35 +2254,37 @@
         <v>30</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="G13" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="H13" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="H13" s="7" t="s">
-        <v>92</v>
-      </c>
       <c r="I13" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
+        <v>87</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="L13" s="8" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="M13" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="N13" s="8" t="s">
-        <v>95</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="N13" s="8"/>
       <c r="O13" s="7" t="s">
         <v>39</v>
       </c>
       <c r="P13" s="7"/>
       <c r="Q13" s="7"/>
       <c r="R13" s="7">
-        <v>0</v>
+        <v>255417</v>
       </c>
       <c r="S13" s="7" t="s">
         <v>40</v>
@@ -2224,11 +2294,9 @@
       <c r="V13" s="7"/>
       <c r="W13" s="7"/>
       <c r="X13" s="7"/>
-      <c r="Y13" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="Y13" s="7"/>
       <c r="Z13" s="8" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AA13" s="7" t="s">
         <v>40</v>
@@ -2242,7 +2310,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="3">
-        <v>2026060403</v>
+        <v>2026060464</v>
       </c>
       <c r="C14" s="3">
         <v>1</v>
@@ -2254,27 +2322,27 @@
         <v>30</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>96</v>
+        <v>31</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
       <c r="L14" s="6" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="M14" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>39</v>
@@ -2284,19 +2352,17 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="S14" s="3"/>
       <c r="T14" s="3"/>
-      <c r="U14" s="3"/>
+      <c r="U14" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="V14" s="3"/>
       <c r="W14" s="3"/>
       <c r="X14" s="3"/>
-      <c r="Y14" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="Y14" s="3"/>
       <c r="Z14" s="6" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>40</v>
@@ -2310,7 +2376,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="7">
-        <v>2026060673</v>
+        <v>2026060669</v>
       </c>
       <c r="C15" s="7">
         <v>1</v>
@@ -2319,46 +2385,38 @@
         <v>29</v>
       </c>
       <c r="E15" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="H15" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="F15" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="G15" s="7" t="s">
+      <c r="I15" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="H15" s="7" t="s">
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="M15" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="I15" s="7" t="s">
+      <c r="N15" s="8" t="s">
         <v>104</v>
-      </c>
-      <c r="J15" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="K15" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="L15" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="M15" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="N15" s="8" t="s">
-        <v>107</v>
       </c>
       <c r="O15" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="P15" s="7">
-        <v>7927</v>
-      </c>
-      <c r="Q15" s="7">
-        <v>17354</v>
-      </c>
+      <c r="P15" s="7"/>
+      <c r="Q15" s="7"/>
       <c r="R15" s="7">
-        <v>25584</v>
+        <v>0</v>
       </c>
       <c r="S15" s="7" t="s">
         <v>40</v>
@@ -2368,9 +2426,11 @@
       <c r="V15" s="7"/>
       <c r="W15" s="7"/>
       <c r="X15" s="7"/>
-      <c r="Y15" s="7"/>
+      <c r="Y15" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="Z15" s="8" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="AA15" s="7" t="s">
         <v>40</v>
@@ -2384,7 +2444,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="3">
-        <v>2026060674</v>
+        <v>2026060656</v>
       </c>
       <c r="C16" s="3">
         <v>1</v>
@@ -2393,68 +2453,66 @@
         <v>29</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>101</v>
+        <v>30</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>36</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3"/>
       <c r="L16" s="6" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="P16" s="3">
-        <v>7927</v>
-      </c>
-      <c r="Q16" s="3">
-        <v>17354</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
       <c r="R16" s="3">
-        <v>25584</v>
-      </c>
-      <c r="S16" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="S16" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-      <c r="Y16" s="3"/>
+      <c r="Y16" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="Z16" s="6" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="AA16" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AB16" s="3"/>
+      <c r="AB16" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="17" spans="1:28">
       <c r="A17" s="7">
         <v>15</v>
       </c>
       <c r="B17" s="7">
-        <v>2026060125</v>
+        <v>2026060403</v>
       </c>
       <c r="C17" s="7">
         <v>1</v>
@@ -2463,44 +2521,38 @@
         <v>29</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>101</v>
+        <v>30</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>79</v>
+        <v>112</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="J17" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="K17" s="7" t="s">
-        <v>36</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="J17" s="7"/>
+      <c r="K17" s="7"/>
       <c r="L17" s="8" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="M17" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N17" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O17" s="7" t="s">
         <v>39</v>
       </c>
       <c r="P17" s="7"/>
-      <c r="Q17" s="7">
-        <v>2375</v>
-      </c>
+      <c r="Q17" s="7"/>
       <c r="R17" s="7">
-        <v>129731</v>
+        <v>0</v>
       </c>
       <c r="S17" s="7" t="s">
         <v>40</v>
@@ -2510,19 +2562,25 @@
       <c r="V17" s="7"/>
       <c r="W17" s="7"/>
       <c r="X17" s="7"/>
-      <c r="Y17" s="7"/>
+      <c r="Y17" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="Z17" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="AA17" s="7"/>
-      <c r="AB17" s="7"/>
+        <v>105</v>
+      </c>
+      <c r="AA17" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB17" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="18" spans="1:28">
       <c r="A18" s="3">
         <v>16</v>
       </c>
       <c r="B18" s="3">
-        <v>2026060126</v>
+        <v>2026060673</v>
       </c>
       <c r="C18" s="3">
         <v>1</v>
@@ -2531,19 +2589,19 @@
         <v>29</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>109</v>
+        <v>64</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>35</v>
@@ -2552,25 +2610,29 @@
         <v>36</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="P18" s="3"/>
+        <v>39</v>
+      </c>
+      <c r="P18" s="3">
+        <v>7927</v>
+      </c>
       <c r="Q18" s="3">
-        <v>2375</v>
+        <v>17354</v>
       </c>
       <c r="R18" s="3">
-        <v>129731</v>
-      </c>
-      <c r="S18" s="3"/>
+        <v>25584</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T18" s="3"/>
       <c r="U18" s="3"/>
       <c r="V18" s="3"/>
@@ -2578,17 +2640,21 @@
       <c r="X18" s="3"/>
       <c r="Y18" s="3"/>
       <c r="Z18" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="AA18" s="3"/>
-      <c r="AB18" s="3"/>
+        <v>123</v>
+      </c>
+      <c r="AA18" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB18" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="19" spans="1:28">
       <c r="A19" s="7">
         <v>17</v>
       </c>
       <c r="B19" s="7">
-        <v>2026060762</v>
+        <v>2026060674</v>
       </c>
       <c r="C19" s="7">
         <v>1</v>
@@ -2597,19 +2663,19 @@
         <v>29</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="J19" s="7" t="s">
         <v>35</v>
@@ -2618,25 +2684,27 @@
         <v>36</v>
       </c>
       <c r="L19" s="8" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="M19" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="N19" s="8"/>
+        <v>121</v>
+      </c>
+      <c r="N19" s="8" t="s">
+        <v>122</v>
+      </c>
       <c r="O19" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="P19" s="7"/>
+        <v>48</v>
+      </c>
+      <c r="P19" s="7">
+        <v>7927</v>
+      </c>
       <c r="Q19" s="7">
-        <v>555</v>
+        <v>17354</v>
       </c>
       <c r="R19" s="7">
-        <v>21603</v>
-      </c>
-      <c r="S19" s="7" t="s">
-        <v>40</v>
-      </c>
+        <v>25584</v>
+      </c>
+      <c r="S19" s="7"/>
       <c r="T19" s="7"/>
       <c r="U19" s="7"/>
       <c r="V19" s="7"/>
@@ -2644,21 +2712,19 @@
       <c r="X19" s="7"/>
       <c r="Y19" s="7"/>
       <c r="Z19" s="8" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="AA19" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AB19" s="7">
-        <v>1</v>
-      </c>
+      <c r="AB19" s="7"/>
     </row>
     <row r="20" spans="1:28">
       <c r="A20" s="3">
         <v>18</v>
       </c>
       <c r="B20" s="3">
-        <v>2026060763</v>
+        <v>2026060126</v>
       </c>
       <c r="C20" s="3">
         <v>1</v>
@@ -2667,19 +2733,19 @@
         <v>29</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>54</v>
+        <v>124</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>115</v>
+        <v>94</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>35</v>
@@ -2688,21 +2754,23 @@
         <v>36</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="N20" s="6"/>
+        <v>128</v>
+      </c>
+      <c r="N20" s="6" t="s">
+        <v>129</v>
+      </c>
       <c r="O20" s="3" t="s">
         <v>48</v>
       </c>
       <c r="P20" s="3"/>
       <c r="Q20" s="3">
-        <v>555</v>
+        <v>2375</v>
       </c>
       <c r="R20" s="3">
-        <v>21603</v>
+        <v>129731</v>
       </c>
       <c r="S20" s="3"/>
       <c r="T20" s="3"/>
@@ -2712,11 +2780,9 @@
       <c r="X20" s="3"/>
       <c r="Y20" s="3"/>
       <c r="Z20" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="AA20" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="AA20" s="3"/>
       <c r="AB20" s="3"/>
     </row>
     <row r="21" spans="1:28">
@@ -2724,7 +2790,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="7">
-        <v>2026060108</v>
+        <v>2026060125</v>
       </c>
       <c r="C21" s="7">
         <v>1</v>
@@ -2733,44 +2799,48 @@
         <v>29</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>123</v>
+        <v>35</v>
       </c>
       <c r="K21" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L21" s="8" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="M21" s="8" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="N21" s="8" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="O21" s="7" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="P21" s="7"/>
-      <c r="Q21" s="7"/>
+      <c r="Q21" s="7">
+        <v>2375</v>
+      </c>
       <c r="R21" s="7">
-        <v>313246</v>
-      </c>
-      <c r="S21" s="7"/>
+        <v>129731</v>
+      </c>
+      <c r="S21" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T21" s="7"/>
       <c r="U21" s="7"/>
       <c r="V21" s="7"/>
@@ -2778,7 +2848,7 @@
       <c r="X21" s="7"/>
       <c r="Y21" s="7"/>
       <c r="Z21" s="8" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="AA21" s="7"/>
       <c r="AB21" s="7"/>
@@ -2788,7 +2858,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="3">
-        <v>2026060107</v>
+        <v>2026060762</v>
       </c>
       <c r="C22" s="3">
         <v>1</v>
@@ -2797,42 +2867,42 @@
         <v>29</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>109</v>
+        <v>64</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>123</v>
+        <v>35</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="N22" s="6" t="s">
-        <v>126</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="N22" s="6"/>
       <c r="O22" s="3" t="s">
         <v>39</v>
       </c>
       <c r="P22" s="3"/>
-      <c r="Q22" s="3"/>
+      <c r="Q22" s="3">
+        <v>555</v>
+      </c>
       <c r="R22" s="3">
-        <v>313246</v>
+        <v>21603</v>
       </c>
       <c r="S22" s="3" t="s">
         <v>40</v>
@@ -2844,17 +2914,21 @@
       <c r="X22" s="3"/>
       <c r="Y22" s="3"/>
       <c r="Z22" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="AA22" s="3"/>
-      <c r="AB22" s="3"/>
+        <v>123</v>
+      </c>
+      <c r="AA22" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB22" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="23" spans="1:28">
       <c r="A23" s="7">
         <v>21</v>
       </c>
       <c r="B23" s="7">
-        <v>2026060415</v>
+        <v>2026060763</v>
       </c>
       <c r="C23" s="7">
         <v>1</v>
@@ -2863,46 +2937,44 @@
         <v>29</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>123</v>
+        <v>35</v>
       </c>
       <c r="K23" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="M23" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="N23" s="8" t="s">
-        <v>132</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="N23" s="8"/>
       <c r="O23" s="7" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P23" s="7"/>
-      <c r="Q23" s="7"/>
+      <c r="Q23" s="7">
+        <v>555</v>
+      </c>
       <c r="R23" s="7">
-        <v>29215</v>
-      </c>
-      <c r="S23" s="7" t="s">
-        <v>40</v>
-      </c>
+        <v>21603</v>
+      </c>
+      <c r="S23" s="7"/>
       <c r="T23" s="7"/>
       <c r="U23" s="7"/>
       <c r="V23" s="7"/>
@@ -2910,21 +2982,19 @@
       <c r="X23" s="7"/>
       <c r="Y23" s="7"/>
       <c r="Z23" s="8" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="AA23" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AB23" s="7">
-        <v>1</v>
-      </c>
+      <c r="AB23" s="7"/>
     </row>
     <row r="24" spans="1:28">
       <c r="A24" s="3">
         <v>22</v>
       </c>
       <c r="B24" s="3">
-        <v>2026060416</v>
+        <v>2026060107</v>
       </c>
       <c r="C24" s="3">
         <v>1</v>
@@ -2933,44 +3003,46 @@
         <v>29</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>31</v>
+        <v>124</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>123</v>
+        <v>57</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="M24" s="6" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="O24" s="3" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="P24" s="3"/>
       <c r="Q24" s="3"/>
       <c r="R24" s="3">
-        <v>29215</v>
-      </c>
-      <c r="S24" s="3"/>
+        <v>313246</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T24" s="3"/>
       <c r="U24" s="3"/>
       <c r="V24" s="3"/>
@@ -2978,11 +3050,9 @@
       <c r="X24" s="3"/>
       <c r="Y24" s="3"/>
       <c r="Z24" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="AA24" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="AA24" s="3"/>
       <c r="AB24" s="3"/>
     </row>
     <row r="25" spans="1:28">
@@ -2990,7 +3060,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="7">
-        <v>2026060378</v>
+        <v>2026060108</v>
       </c>
       <c r="C25" s="7">
         <v>1</v>
@@ -2999,44 +3069,44 @@
         <v>29</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>31</v>
+        <v>124</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>42</v>
+        <v>135</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K25" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L25" s="8" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="M25" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="N25" s="8"/>
+        <v>139</v>
+      </c>
+      <c r="N25" s="8" t="s">
+        <v>140</v>
+      </c>
       <c r="O25" s="7" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P25" s="7"/>
       <c r="Q25" s="7"/>
       <c r="R25" s="7">
-        <v>36400</v>
-      </c>
-      <c r="S25" s="7" t="s">
-        <v>40</v>
-      </c>
+        <v>313246</v>
+      </c>
+      <c r="S25" s="7"/>
       <c r="T25" s="7"/>
       <c r="U25" s="7"/>
       <c r="V25" s="7"/>
@@ -3044,21 +3114,17 @@
       <c r="X25" s="7"/>
       <c r="Y25" s="7"/>
       <c r="Z25" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="AA25" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB25" s="7">
-        <v>1</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="AA25" s="7"/>
+      <c r="AB25" s="7"/>
     </row>
     <row r="26" spans="1:28">
       <c r="A26" s="3">
         <v>24</v>
       </c>
       <c r="B26" s="3">
-        <v>2026060379</v>
+        <v>2026060415</v>
       </c>
       <c r="C26" s="3">
         <v>1</v>
@@ -3067,42 +3133,46 @@
         <v>29</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>42</v>
+        <v>141</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="M26" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="N26" s="6"/>
+        <v>145</v>
+      </c>
+      <c r="N26" s="6" t="s">
+        <v>146</v>
+      </c>
       <c r="O26" s="3" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="P26" s="3"/>
       <c r="Q26" s="3"/>
       <c r="R26" s="3">
-        <v>36400</v>
-      </c>
-      <c r="S26" s="3"/>
+        <v>29215</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T26" s="3"/>
       <c r="U26" s="3"/>
       <c r="V26" s="3"/>
@@ -3110,19 +3180,21 @@
       <c r="X26" s="3"/>
       <c r="Y26" s="3"/>
       <c r="Z26" s="6" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="AA26" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AB26" s="3"/>
+      <c r="AB26" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="27" spans="1:28">
       <c r="A27" s="7">
         <v>25</v>
       </c>
       <c r="B27" s="7">
-        <v>2026060111</v>
+        <v>2026060416</v>
       </c>
       <c r="C27" s="7">
         <v>1</v>
@@ -3131,34 +3203,34 @@
         <v>29</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>109</v>
+        <v>31</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K27" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L27" s="8" t="s">
-        <v>124</v>
+        <v>144</v>
       </c>
       <c r="M27" s="8" t="s">
-        <v>125</v>
+        <v>145</v>
       </c>
       <c r="N27" s="8" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="O27" s="7" t="s">
         <v>48</v>
@@ -3166,7 +3238,7 @@
       <c r="P27" s="7"/>
       <c r="Q27" s="7"/>
       <c r="R27" s="7">
-        <v>113426</v>
+        <v>29215</v>
       </c>
       <c r="S27" s="7"/>
       <c r="T27" s="7"/>
@@ -3176,9 +3248,11 @@
       <c r="X27" s="7"/>
       <c r="Y27" s="7"/>
       <c r="Z27" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="AA27" s="7"/>
+        <v>123</v>
+      </c>
+      <c r="AA27" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="AB27" s="7"/>
     </row>
     <row r="28" spans="1:28">
@@ -3186,7 +3260,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="3">
-        <v>2026060110</v>
+        <v>2026060378</v>
       </c>
       <c r="C28" s="3">
         <v>1</v>
@@ -3195,42 +3269,40 @@
         <v>29</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>109</v>
+        <v>31</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>137</v>
+        <v>42</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="K28" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>124</v>
+        <v>149</v>
       </c>
       <c r="M28" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="N28" s="6" t="s">
-        <v>126</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="N28" s="6"/>
       <c r="O28" s="3" t="s">
         <v>39</v>
       </c>
       <c r="P28" s="3"/>
       <c r="Q28" s="3"/>
       <c r="R28" s="3">
-        <v>113426</v>
+        <v>36400</v>
       </c>
       <c r="S28" s="3" t="s">
         <v>40</v>
@@ -3242,17 +3314,21 @@
       <c r="X28" s="3"/>
       <c r="Y28" s="3"/>
       <c r="Z28" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="AA28" s="3"/>
-      <c r="AB28" s="3"/>
+        <v>123</v>
+      </c>
+      <c r="AA28" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB28" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="29" spans="1:28">
       <c r="A29" s="7">
         <v>27</v>
       </c>
       <c r="B29" s="7">
-        <v>2026060411</v>
+        <v>2026060379</v>
       </c>
       <c r="C29" s="7">
         <v>1</v>
@@ -3261,48 +3337,42 @@
         <v>29</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="F29" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>141</v>
+        <v>42</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>144</v>
+        <v>68</v>
       </c>
       <c r="K29" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L29" s="8" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="M29" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="N29" s="8" t="s">
-        <v>132</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="N29" s="8"/>
       <c r="O29" s="7" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P29" s="7"/>
-      <c r="Q29" s="7">
-        <v>3009</v>
-      </c>
+      <c r="Q29" s="7"/>
       <c r="R29" s="7">
-        <v>386927</v>
-      </c>
-      <c r="S29" s="7" t="s">
-        <v>40</v>
-      </c>
+        <v>36400</v>
+      </c>
+      <c r="S29" s="7"/>
       <c r="T29" s="7"/>
       <c r="U29" s="7"/>
       <c r="V29" s="7"/>
@@ -3310,21 +3380,19 @@
       <c r="X29" s="7"/>
       <c r="Y29" s="7"/>
       <c r="Z29" s="8" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="AA29" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AB29" s="7">
-        <v>1</v>
-      </c>
+      <c r="AB29" s="7"/>
     </row>
     <row r="30" spans="1:28">
       <c r="A30" s="3">
         <v>28</v>
       </c>
       <c r="B30" s="3">
-        <v>2026060412</v>
+        <v>2026060111</v>
       </c>
       <c r="C30" s="3">
         <v>1</v>
@@ -3333,44 +3401,42 @@
         <v>29</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>31</v>
+        <v>124</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>144</v>
+        <v>68</v>
       </c>
       <c r="K30" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="O30" s="3" t="s">
         <v>48</v>
       </c>
       <c r="P30" s="3"/>
-      <c r="Q30" s="3">
-        <v>3009</v>
-      </c>
+      <c r="Q30" s="3"/>
       <c r="R30" s="3">
-        <v>386927</v>
+        <v>113426</v>
       </c>
       <c r="S30" s="3"/>
       <c r="T30" s="3"/>
@@ -3380,11 +3446,9 @@
       <c r="X30" s="3"/>
       <c r="Y30" s="3"/>
       <c r="Z30" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="AA30" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="AA30" s="3"/>
       <c r="AB30" s="3"/>
     </row>
     <row r="31" spans="1:28">
@@ -3392,7 +3456,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="7">
-        <v>2026060771</v>
+        <v>2026060110</v>
       </c>
       <c r="C31" s="7">
         <v>1</v>
@@ -3401,44 +3465,42 @@
         <v>29</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>54</v>
+        <v>124</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="I31" s="7" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>150</v>
+        <v>68</v>
       </c>
       <c r="K31" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L31" s="8" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="M31" s="8" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="N31" s="8" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="O31" s="7" t="s">
         <v>39</v>
       </c>
       <c r="P31" s="7"/>
-      <c r="Q31" s="7">
-        <v>5752</v>
-      </c>
+      <c r="Q31" s="7"/>
       <c r="R31" s="7">
-        <v>34659</v>
+        <v>113426</v>
       </c>
       <c r="S31" s="7" t="s">
         <v>40</v>
@@ -3450,7 +3512,7 @@
       <c r="X31" s="7"/>
       <c r="Y31" s="7"/>
       <c r="Z31" s="8" t="s">
-        <v>108</v>
+        <v>154</v>
       </c>
       <c r="AA31" s="7"/>
       <c r="AB31" s="7"/>
@@ -3460,7 +3522,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="3">
-        <v>2026060772</v>
+        <v>2026060411</v>
       </c>
       <c r="C32" s="3">
         <v>1</v>
@@ -3469,46 +3531,48 @@
         <v>29</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>147</v>
+        <v>72</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="O32" s="3" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="P32" s="3"/>
       <c r="Q32" s="3">
-        <v>5752</v>
+        <v>3009</v>
       </c>
       <c r="R32" s="3">
-        <v>34659</v>
-      </c>
-      <c r="S32" s="3"/>
+        <v>386927</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T32" s="3"/>
       <c r="U32" s="3"/>
       <c r="V32" s="3"/>
@@ -3516,19 +3580,21 @@
       <c r="X32" s="3"/>
       <c r="Y32" s="3"/>
       <c r="Z32" s="6" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="AA32" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AB32" s="3"/>
+      <c r="AB32" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="33" spans="1:28">
       <c r="A33" s="7">
         <v>31</v>
       </c>
       <c r="B33" s="7">
-        <v>2026060127</v>
+        <v>2026060412</v>
       </c>
       <c r="C33" s="7">
         <v>1</v>
@@ -3537,13 +3603,13 @@
         <v>29</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>109</v>
+        <v>31</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>154</v>
+        <v>72</v>
       </c>
       <c r="H33" s="7" t="s">
         <v>155</v>
@@ -3558,25 +3624,25 @@
         <v>36</v>
       </c>
       <c r="L33" s="8" t="s">
-        <v>112</v>
+        <v>158</v>
       </c>
       <c r="M33" s="8" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="N33" s="8" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="O33" s="7" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P33" s="7"/>
-      <c r="Q33" s="7"/>
+      <c r="Q33" s="7">
+        <v>3009</v>
+      </c>
       <c r="R33" s="7">
-        <v>212738</v>
-      </c>
-      <c r="S33" s="7" t="s">
-        <v>40</v>
-      </c>
+        <v>386927</v>
+      </c>
+      <c r="S33" s="7"/>
       <c r="T33" s="7"/>
       <c r="U33" s="7"/>
       <c r="V33" s="7"/>
@@ -3584,9 +3650,11 @@
       <c r="X33" s="7"/>
       <c r="Y33" s="7"/>
       <c r="Z33" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="AA33" s="7"/>
+        <v>123</v>
+      </c>
+      <c r="AA33" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="AB33" s="7"/>
     </row>
     <row r="34" spans="1:28">
@@ -3594,7 +3662,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="3">
-        <v>2026060128</v>
+        <v>2026060771</v>
       </c>
       <c r="C34" s="3">
         <v>1</v>
@@ -3603,44 +3671,48 @@
         <v>29</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>109</v>
+        <v>64</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="K34" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>112</v>
+        <v>164</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="O34" s="3" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="P34" s="3"/>
-      <c r="Q34" s="3"/>
+      <c r="Q34" s="3">
+        <v>5752</v>
+      </c>
       <c r="R34" s="3">
-        <v>212738</v>
-      </c>
-      <c r="S34" s="3"/>
+        <v>34659</v>
+      </c>
+      <c r="S34" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T34" s="3"/>
       <c r="U34" s="3"/>
       <c r="V34" s="3"/>
@@ -3648,7 +3720,7 @@
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
       <c r="Z34" s="6" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="AA34" s="3"/>
       <c r="AB34" s="3"/>
@@ -3658,7 +3730,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="7">
-        <v>2026060846</v>
+        <v>2026060772</v>
       </c>
       <c r="C35" s="7">
         <v>1</v>
@@ -3667,42 +3739,46 @@
         <v>29</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>110</v>
+        <v>160</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>49</v>
+        <v>161</v>
       </c>
       <c r="I35" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="J35" s="7"/>
-      <c r="K35" s="7"/>
+        <v>162</v>
+      </c>
+      <c r="J35" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="K35" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="L35" s="8" t="s">
-        <v>81</v>
+        <v>164</v>
       </c>
       <c r="M35" s="8" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="N35" s="8" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="O35" s="7" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P35" s="7"/>
-      <c r="Q35" s="7"/>
+      <c r="Q35" s="7">
+        <v>5752</v>
+      </c>
       <c r="R35" s="7">
-        <v>0</v>
-      </c>
-      <c r="S35" s="7" t="s">
-        <v>40</v>
-      </c>
+        <v>34659</v>
+      </c>
+      <c r="S35" s="7"/>
       <c r="T35" s="7"/>
       <c r="U35" s="7"/>
       <c r="V35" s="7"/>
@@ -3710,21 +3786,19 @@
       <c r="X35" s="7"/>
       <c r="Y35" s="7"/>
       <c r="Z35" s="8" t="s">
-        <v>163</v>
+        <v>123</v>
       </c>
       <c r="AA35" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AB35" s="7">
-        <v>1</v>
-      </c>
+      <c r="AB35" s="7"/>
     </row>
     <row r="36" spans="1:28">
       <c r="A36" s="3">
         <v>34</v>
       </c>
       <c r="B36" s="3">
-        <v>2026060445</v>
+        <v>2026060127</v>
       </c>
       <c r="C36" s="3">
         <v>1</v>
@@ -3733,30 +3807,34 @@
         <v>29</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>31</v>
+        <v>124</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>78</v>
+        <v>167</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="J36" s="3"/>
-      <c r="K36" s="3"/>
+        <v>169</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="L36" s="6" t="s">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>82</v>
+        <v>171</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>83</v>
+        <v>172</v>
       </c>
       <c r="O36" s="3" t="s">
         <v>39</v>
@@ -3764,33 +3842,29 @@
       <c r="P36" s="3"/>
       <c r="Q36" s="3"/>
       <c r="R36" s="3">
-        <v>0</v>
-      </c>
-      <c r="S36" s="3"/>
-      <c r="T36" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>212738</v>
+      </c>
+      <c r="S36" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="T36" s="3"/>
       <c r="U36" s="3"/>
       <c r="V36" s="3"/>
       <c r="W36" s="3"/>
       <c r="X36" s="3"/>
       <c r="Y36" s="3"/>
       <c r="Z36" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="AA36" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB36" s="3">
-        <v>1</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="AA36" s="3"/>
+      <c r="AB36" s="3"/>
     </row>
     <row r="37" spans="1:28">
       <c r="A37" s="7">
         <v>35</v>
       </c>
       <c r="B37" s="7">
-        <v>2026060840</v>
+        <v>2026060128</v>
       </c>
       <c r="C37" s="7">
         <v>1</v>
@@ -3799,42 +3873,44 @@
         <v>29</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>54</v>
+        <v>124</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I37" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="J37" s="7"/>
-      <c r="K37" s="7"/>
+        <v>169</v>
+      </c>
+      <c r="J37" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="K37" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="L37" s="8" t="s">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="M37" s="8" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="N37" s="8" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O37" s="7" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P37" s="7"/>
       <c r="Q37" s="7"/>
       <c r="R37" s="7">
-        <v>0</v>
-      </c>
-      <c r="S37" s="7" t="s">
-        <v>40</v>
-      </c>
+        <v>212738</v>
+      </c>
+      <c r="S37" s="7"/>
       <c r="T37" s="7"/>
       <c r="U37" s="7"/>
       <c r="V37" s="7"/>
@@ -3842,21 +3918,17 @@
       <c r="X37" s="7"/>
       <c r="Y37" s="7"/>
       <c r="Z37" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="AA37" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB37" s="7">
-        <v>1</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="AA37" s="7"/>
+      <c r="AB37" s="7"/>
     </row>
     <row r="38" spans="1:28">
       <c r="A38" s="3">
         <v>36</v>
       </c>
       <c r="B38" s="3">
-        <v>2026060812</v>
+        <v>2026060846</v>
       </c>
       <c r="C38" s="3">
         <v>1</v>
@@ -3865,16 +3937,16 @@
         <v>29</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>171</v>
+        <v>125</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>172</v>
+        <v>49</v>
       </c>
       <c r="I38" s="3" t="s">
         <v>173</v>
@@ -3882,7 +3954,7 @@
       <c r="J38" s="3"/>
       <c r="K38" s="3"/>
       <c r="L38" s="6" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="M38" s="6" t="s">
         <v>174</v>
@@ -3908,7 +3980,7 @@
       <c r="X38" s="3"/>
       <c r="Y38" s="3"/>
       <c r="Z38" s="6" t="s">
-        <v>90</v>
+        <v>176</v>
       </c>
       <c r="AA38" s="3" t="s">
         <v>40</v>
@@ -3922,7 +3994,7 @@
         <v>37</v>
       </c>
       <c r="B39" s="7">
-        <v>2026060827</v>
+        <v>2026060445</v>
       </c>
       <c r="C39" s="7">
         <v>1</v>
@@ -3931,30 +4003,30 @@
         <v>29</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I39" s="7" t="s">
-        <v>177</v>
+        <v>95</v>
       </c>
       <c r="J39" s="7"/>
       <c r="K39" s="7"/>
       <c r="L39" s="8" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="M39" s="8" t="s">
-        <v>178</v>
+        <v>97</v>
       </c>
       <c r="N39" s="8" t="s">
-        <v>179</v>
+        <v>98</v>
       </c>
       <c r="O39" s="7" t="s">
         <v>39</v>
@@ -3964,17 +4036,17 @@
       <c r="R39" s="7">
         <v>0</v>
       </c>
-      <c r="S39" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="T39" s="7"/>
+      <c r="S39" s="7"/>
+      <c r="T39" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="U39" s="7"/>
       <c r="V39" s="7"/>
       <c r="W39" s="7"/>
       <c r="X39" s="7"/>
       <c r="Y39" s="7"/>
       <c r="Z39" s="8" t="s">
-        <v>90</v>
+        <v>178</v>
       </c>
       <c r="AA39" s="7" t="s">
         <v>40</v>
@@ -3988,7 +4060,7 @@
         <v>38</v>
       </c>
       <c r="B40" s="3">
-        <v>2026060664</v>
+        <v>2026060840</v>
       </c>
       <c r="C40" s="3">
         <v>1</v>
@@ -3997,28 +4069,24 @@
         <v>29</v>
       </c>
       <c r="E40" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H40" s="3" t="s">
         <v>180</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>32</v>
       </c>
       <c r="I40" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="J40" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="K40" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="J40" s="3"/>
+      <c r="K40" s="3"/>
       <c r="L40" s="6" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="M40" s="6" t="s">
         <v>182</v>
@@ -4029,14 +4097,10 @@
       <c r="O40" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="P40" s="3">
-        <v>2480</v>
-      </c>
-      <c r="Q40" s="3">
-        <v>3343</v>
-      </c>
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
       <c r="R40" s="3">
-        <v>11884</v>
+        <v>0</v>
       </c>
       <c r="S40" s="3" t="s">
         <v>40</v>
@@ -4048,7 +4112,7 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="6" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="AA40" s="3" t="s">
         <v>40</v>
@@ -4062,7 +4126,7 @@
         <v>39</v>
       </c>
       <c r="B41" s="7">
-        <v>2026060665</v>
+        <v>2026060812</v>
       </c>
       <c r="C41" s="7">
         <v>1</v>
@@ -4071,48 +4135,42 @@
         <v>29</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>180</v>
+        <v>116</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>102</v>
+        <v>184</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>32</v>
+        <v>185</v>
       </c>
       <c r="I41" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="J41" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="K41" s="7" t="s">
-        <v>36</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="J41" s="7"/>
+      <c r="K41" s="7"/>
       <c r="L41" s="8" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="M41" s="8" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="N41" s="8" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="O41" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="P41" s="7">
-        <v>2480</v>
-      </c>
-      <c r="Q41" s="7">
-        <v>3343</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="P41" s="7"/>
+      <c r="Q41" s="7"/>
       <c r="R41" s="7">
-        <v>11884</v>
-      </c>
-      <c r="S41" s="7"/>
+        <v>0</v>
+      </c>
+      <c r="S41" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T41" s="7"/>
       <c r="U41" s="7"/>
       <c r="V41" s="7"/>
@@ -4120,19 +4178,21 @@
       <c r="X41" s="7"/>
       <c r="Y41" s="7"/>
       <c r="Z41" s="8" t="s">
-        <v>184</v>
+        <v>105</v>
       </c>
       <c r="AA41" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AB41" s="7"/>
+      <c r="AB41" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="42" spans="1:28">
       <c r="A42" s="3">
         <v>40</v>
       </c>
       <c r="B42" s="3">
-        <v>2026060666</v>
+        <v>2026060827</v>
       </c>
       <c r="C42" s="3">
         <v>1</v>
@@ -4141,46 +4201,38 @@
         <v>29</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>180</v>
+        <v>116</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>32</v>
+        <v>93</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>62</v>
+        <v>189</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>36</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="J42" s="3"/>
+      <c r="K42" s="3"/>
       <c r="L42" s="6" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="M42" s="6" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="O42" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="P42" s="3">
-        <v>624</v>
-      </c>
-      <c r="Q42" s="3">
-        <v>1591</v>
-      </c>
+      <c r="P42" s="3"/>
+      <c r="Q42" s="3"/>
       <c r="R42" s="3">
-        <v>9357</v>
+        <v>0</v>
       </c>
       <c r="S42" s="3" t="s">
         <v>40</v>
@@ -4192,7 +4244,7 @@
       <c r="X42" s="3"/>
       <c r="Y42" s="3"/>
       <c r="Z42" s="6" t="s">
-        <v>184</v>
+        <v>105</v>
       </c>
       <c r="AA42" s="3" t="s">
         <v>40</v>
@@ -4206,7 +4258,7 @@
         <v>41</v>
       </c>
       <c r="B43" s="7">
-        <v>2026060667</v>
+        <v>2026060664</v>
       </c>
       <c r="C43" s="7">
         <v>1</v>
@@ -4215,19 +4267,19 @@
         <v>29</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="G43" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="H43" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="H43" s="7" t="s">
-        <v>62</v>
-      </c>
       <c r="I43" s="7" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="J43" s="7" t="s">
         <v>35</v>
@@ -4236,27 +4288,29 @@
         <v>36</v>
       </c>
       <c r="L43" s="8" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="M43" s="8" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="N43" s="8" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="O43" s="7" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="P43" s="7">
-        <v>624</v>
+        <v>2480</v>
       </c>
       <c r="Q43" s="7">
-        <v>1591</v>
+        <v>3343</v>
       </c>
       <c r="R43" s="7">
-        <v>9357</v>
-      </c>
-      <c r="S43" s="7"/>
+        <v>11884</v>
+      </c>
+      <c r="S43" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T43" s="7"/>
       <c r="U43" s="7"/>
       <c r="V43" s="7"/>
@@ -4264,19 +4318,21 @@
       <c r="X43" s="7"/>
       <c r="Y43" s="7"/>
       <c r="Z43" s="8" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="AA43" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AB43" s="7"/>
+      <c r="AB43" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="44" spans="1:28">
       <c r="A44" s="3">
         <v>42</v>
       </c>
       <c r="B44" s="3">
-        <v>2026060572</v>
+        <v>2026060665</v>
       </c>
       <c r="C44" s="3">
         <v>1</v>
@@ -4285,19 +4341,19 @@
         <v>29</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>110</v>
+        <v>32</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>35</v>
@@ -4306,27 +4362,27 @@
         <v>36</v>
       </c>
       <c r="L44" s="6" t="s">
-        <v>45</v>
+        <v>120</v>
       </c>
       <c r="M44" s="6" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="O44" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="P44" s="3"/>
+        <v>48</v>
+      </c>
+      <c r="P44" s="3">
+        <v>2480</v>
+      </c>
       <c r="Q44" s="3">
-        <v>449</v>
+        <v>3343</v>
       </c>
       <c r="R44" s="3">
-        <v>4403</v>
-      </c>
-      <c r="S44" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>11884</v>
+      </c>
+      <c r="S44" s="3"/>
       <c r="T44" s="3"/>
       <c r="U44" s="3"/>
       <c r="V44" s="3"/>
@@ -4334,21 +4390,19 @@
       <c r="X44" s="3"/>
       <c r="Y44" s="3"/>
       <c r="Z44" s="6" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="AA44" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AB44" s="3">
-        <v>1</v>
-      </c>
+      <c r="AB44" s="3"/>
     </row>
     <row r="45" spans="1:28">
       <c r="A45" s="7">
         <v>43</v>
       </c>
       <c r="B45" s="7">
-        <v>2026060573</v>
+        <v>2026060666</v>
       </c>
       <c r="C45" s="7">
         <v>1</v>
@@ -4357,19 +4411,19 @@
         <v>29</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>121</v>
+        <v>32</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="I45" s="7" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="J45" s="7" t="s">
         <v>35</v>
@@ -4378,25 +4432,29 @@
         <v>36</v>
       </c>
       <c r="L45" s="8" t="s">
-        <v>45</v>
+        <v>120</v>
       </c>
       <c r="M45" s="8" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="N45" s="8" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="O45" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="P45" s="7"/>
+        <v>39</v>
+      </c>
+      <c r="P45" s="7">
+        <v>624</v>
+      </c>
       <c r="Q45" s="7">
-        <v>449</v>
+        <v>1591</v>
       </c>
       <c r="R45" s="7">
-        <v>4403</v>
-      </c>
-      <c r="S45" s="7"/>
+        <v>9357</v>
+      </c>
+      <c r="S45" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T45" s="7"/>
       <c r="U45" s="7"/>
       <c r="V45" s="7"/>
@@ -4404,19 +4462,21 @@
       <c r="X45" s="7"/>
       <c r="Y45" s="7"/>
       <c r="Z45" s="8" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="AA45" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AB45" s="7"/>
+      <c r="AB45" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="46" spans="1:28">
       <c r="A46" s="3">
         <v>44</v>
       </c>
       <c r="B46" s="3">
-        <v>2026060824</v>
+        <v>2026060667</v>
       </c>
       <c r="C46" s="3">
         <v>1</v>
@@ -4425,19 +4485,19 @@
         <v>29</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>191</v>
+        <v>32</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>137</v>
+        <v>77</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="J46" s="3" t="s">
         <v>35</v>
@@ -4446,49 +4506,47 @@
         <v>36</v>
       </c>
       <c r="L46" s="6" t="s">
-        <v>45</v>
+        <v>120</v>
       </c>
       <c r="M46" s="6" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="O46" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="P46" s="3"/>
+        <v>48</v>
+      </c>
+      <c r="P46" s="3">
+        <v>624</v>
+      </c>
       <c r="Q46" s="3">
-        <v>449</v>
+        <v>1591</v>
       </c>
       <c r="R46" s="3">
-        <v>4403</v>
+        <v>9357</v>
       </c>
       <c r="S46" s="3"/>
       <c r="T46" s="3"/>
       <c r="U46" s="3"/>
       <c r="V46" s="3"/>
-      <c r="W46" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="W46" s="3"/>
       <c r="X46" s="3"/>
       <c r="Y46" s="3"/>
       <c r="Z46" s="6" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="AA46" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AB46" s="3">
-        <v>1</v>
-      </c>
+      <c r="AB46" s="3"/>
     </row>
     <row r="47" spans="1:28">
       <c r="A47" s="7">
         <v>45</v>
       </c>
       <c r="B47" s="7">
-        <v>2026060063</v>
+        <v>2026060572</v>
       </c>
       <c r="C47" s="7">
         <v>1</v>
@@ -4497,42 +4555,44 @@
         <v>29</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>109</v>
+        <v>31</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>193</v>
+        <v>136</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>194</v>
+        <v>125</v>
       </c>
       <c r="I47" s="7" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="J47" s="7" t="s">
-        <v>123</v>
+        <v>35</v>
       </c>
       <c r="K47" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L47" s="8" t="s">
-        <v>196</v>
+        <v>45</v>
       </c>
       <c r="M47" s="8" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="N47" s="8" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="O47" s="7" t="s">
         <v>39</v>
       </c>
       <c r="P47" s="7"/>
-      <c r="Q47" s="7"/>
+      <c r="Q47" s="7">
+        <v>449</v>
+      </c>
       <c r="R47" s="7">
-        <v>2818</v>
+        <v>4403</v>
       </c>
       <c r="S47" s="7" t="s">
         <v>40</v>
@@ -4544,7 +4604,7 @@
       <c r="X47" s="7"/>
       <c r="Y47" s="7"/>
       <c r="Z47" s="8" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="AA47" s="7" t="s">
         <v>40</v>
@@ -4558,7 +4618,7 @@
         <v>46</v>
       </c>
       <c r="B48" s="3">
-        <v>2026060064</v>
+        <v>2026060573</v>
       </c>
       <c r="C48" s="3">
         <v>1</v>
@@ -4567,42 +4627,44 @@
         <v>29</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>109</v>
+        <v>31</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>193</v>
+        <v>136</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>194</v>
+        <v>125</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>123</v>
+        <v>35</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L48" s="6" t="s">
-        <v>196</v>
+        <v>45</v>
       </c>
       <c r="M48" s="6" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="O48" s="3" t="s">
         <v>48</v>
       </c>
       <c r="P48" s="3"/>
-      <c r="Q48" s="3"/>
+      <c r="Q48" s="3">
+        <v>449</v>
+      </c>
       <c r="R48" s="3">
-        <v>2818</v>
+        <v>4403</v>
       </c>
       <c r="S48" s="3"/>
       <c r="T48" s="3"/>
@@ -4612,7 +4674,7 @@
       <c r="X48" s="3"/>
       <c r="Y48" s="3"/>
       <c r="Z48" s="6" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="AA48" s="3" t="s">
         <v>40</v>
@@ -4624,7 +4686,7 @@
         <v>47</v>
       </c>
       <c r="B49" s="7">
-        <v>2026060627</v>
+        <v>2026060824</v>
       </c>
       <c r="C49" s="7">
         <v>1</v>
@@ -4633,54 +4695,56 @@
         <v>29</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="H49" s="7" t="s">
-        <v>200</v>
+        <v>151</v>
       </c>
       <c r="I49" s="7" t="s">
         <v>201</v>
       </c>
       <c r="J49" s="7" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="K49" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L49" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="M49" s="8" t="s">
         <v>202</v>
       </c>
-      <c r="M49" s="8" t="s">
+      <c r="N49" s="8" t="s">
         <v>203</v>
-      </c>
-      <c r="N49" s="8" t="s">
-        <v>204</v>
       </c>
       <c r="O49" s="7" t="s">
         <v>39</v>
       </c>
       <c r="P49" s="7"/>
-      <c r="Q49" s="7"/>
+      <c r="Q49" s="7">
+        <v>449</v>
+      </c>
       <c r="R49" s="7">
-        <v>195048</v>
-      </c>
-      <c r="S49" s="7" t="s">
-        <v>40</v>
-      </c>
+        <v>4403</v>
+      </c>
+      <c r="S49" s="7"/>
       <c r="T49" s="7"/>
       <c r="U49" s="7"/>
       <c r="V49" s="7"/>
-      <c r="W49" s="7"/>
+      <c r="W49" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="X49" s="7"/>
       <c r="Y49" s="7"/>
       <c r="Z49" s="8" t="s">
-        <v>184</v>
+        <v>205</v>
       </c>
       <c r="AA49" s="7" t="s">
         <v>40</v>
@@ -4694,7 +4758,7 @@
         <v>48</v>
       </c>
       <c r="B50" s="3">
-        <v>2026060628</v>
+        <v>2026060064</v>
       </c>
       <c r="C50" s="3">
         <v>1</v>
@@ -4703,34 +4767,34 @@
         <v>29</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>54</v>
+        <v>124</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K50" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L50" s="6" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="M50" s="6" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="O50" s="3" t="s">
         <v>48</v>
@@ -4738,7 +4802,7 @@
       <c r="P50" s="3"/>
       <c r="Q50" s="3"/>
       <c r="R50" s="3">
-        <v>195048</v>
+        <v>2818</v>
       </c>
       <c r="S50" s="3"/>
       <c r="T50" s="3"/>
@@ -4748,19 +4812,21 @@
       <c r="X50" s="3"/>
       <c r="Y50" s="3"/>
       <c r="Z50" s="6" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="AA50" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AB50" s="3"/>
+      <c r="AB50" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="51" spans="1:28">
       <c r="A51" s="7">
         <v>49</v>
       </c>
       <c r="B51" s="7">
-        <v>2026060629</v>
+        <v>2026060063</v>
       </c>
       <c r="C51" s="7">
         <v>1</v>
@@ -4769,34 +4835,34 @@
         <v>29</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>54</v>
+        <v>124</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="H51" s="7" t="s">
-        <v>102</v>
+        <v>207</v>
       </c>
       <c r="I51" s="7" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="J51" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K51" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L51" s="8" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="M51" s="8" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="N51" s="8" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="O51" s="7" t="s">
         <v>39</v>
@@ -4804,7 +4870,7 @@
       <c r="P51" s="7"/>
       <c r="Q51" s="7"/>
       <c r="R51" s="7">
-        <v>203621</v>
+        <v>2818</v>
       </c>
       <c r="S51" s="7" t="s">
         <v>40</v>
@@ -4816,21 +4882,19 @@
       <c r="X51" s="7"/>
       <c r="Y51" s="7"/>
       <c r="Z51" s="8" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="AA51" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AB51" s="7">
-        <v>1</v>
-      </c>
+      <c r="AB51" s="7"/>
     </row>
     <row r="52" spans="1:28">
       <c r="A52" s="3">
         <v>50</v>
       </c>
       <c r="B52" s="3">
-        <v>2026060630</v>
+        <v>2026060627</v>
       </c>
       <c r="C52" s="3">
         <v>1</v>
@@ -4839,44 +4903,46 @@
         <v>29</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>102</v>
+        <v>213</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L52" s="6" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="M52" s="6" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="O52" s="3" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="P52" s="3"/>
       <c r="Q52" s="3"/>
       <c r="R52" s="3">
-        <v>203621</v>
-      </c>
-      <c r="S52" s="3"/>
+        <v>195048</v>
+      </c>
+      <c r="S52" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T52" s="3"/>
       <c r="U52" s="3"/>
       <c r="V52" s="3"/>
@@ -4884,19 +4950,21 @@
       <c r="X52" s="3"/>
       <c r="Y52" s="3"/>
       <c r="Z52" s="6" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="AA52" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AB52" s="3"/>
+      <c r="AB52" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="53" spans="1:28">
       <c r="A53" s="7">
         <v>51</v>
       </c>
       <c r="B53" s="7">
-        <v>2026060146</v>
+        <v>2026060628</v>
       </c>
       <c r="C53" s="7">
         <v>1</v>
@@ -4905,68 +4973,64 @@
         <v>29</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>109</v>
+        <v>64</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="H53" s="7" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="I53" s="7" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="J53" s="7" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="K53" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L53" s="8" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="M53" s="8" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="N53" s="8" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="O53" s="7" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P53" s="7"/>
       <c r="Q53" s="7"/>
       <c r="R53" s="7">
-        <v>49442</v>
+        <v>195048</v>
       </c>
       <c r="S53" s="7"/>
       <c r="T53" s="7"/>
-      <c r="U53" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="U53" s="7"/>
       <c r="V53" s="7"/>
       <c r="W53" s="7"/>
       <c r="X53" s="7"/>
       <c r="Y53" s="7"/>
       <c r="Z53" s="8" t="s">
-        <v>214</v>
+        <v>197</v>
       </c>
       <c r="AA53" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AB53" s="7">
-        <v>1</v>
-      </c>
+      <c r="AB53" s="7"/>
     </row>
     <row r="54" spans="1:28">
       <c r="A54" s="3">
         <v>52</v>
       </c>
       <c r="B54" s="3">
-        <v>2026060052</v>
+        <v>2026060629</v>
       </c>
       <c r="C54" s="3">
         <v>1</v>
@@ -4975,34 +5039,34 @@
         <v>29</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>109</v>
+        <v>64</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>147</v>
+        <v>117</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L54" s="6" t="s">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="M54" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="O54" s="3" t="s">
         <v>39</v>
@@ -5010,7 +5074,7 @@
       <c r="P54" s="3"/>
       <c r="Q54" s="3"/>
       <c r="R54" s="3">
-        <v>29640</v>
+        <v>203621</v>
       </c>
       <c r="S54" s="3" t="s">
         <v>40</v>
@@ -5022,7 +5086,7 @@
       <c r="X54" s="3"/>
       <c r="Y54" s="3"/>
       <c r="Z54" s="6" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="AA54" s="3" t="s">
         <v>40</v>
@@ -5036,7 +5100,7 @@
         <v>53</v>
       </c>
       <c r="B55" s="7">
-        <v>2026060053</v>
+        <v>2026060630</v>
       </c>
       <c r="C55" s="7">
         <v>1</v>
@@ -5045,34 +5109,34 @@
         <v>29</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>109</v>
+        <v>64</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="H55" s="7" t="s">
-        <v>147</v>
+        <v>117</v>
       </c>
       <c r="I55" s="7" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="J55" s="7" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="K55" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L55" s="8" t="s">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="M55" s="8" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="N55" s="8" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="O55" s="7" t="s">
         <v>48</v>
@@ -5080,7 +5144,7 @@
       <c r="P55" s="7"/>
       <c r="Q55" s="7"/>
       <c r="R55" s="7">
-        <v>29640</v>
+        <v>203621</v>
       </c>
       <c r="S55" s="7"/>
       <c r="T55" s="7"/>
@@ -5090,7 +5154,7 @@
       <c r="X55" s="7"/>
       <c r="Y55" s="7"/>
       <c r="Z55" s="8" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="AA55" s="7" t="s">
         <v>40</v>
@@ -5102,7 +5166,7 @@
         <v>54</v>
       </c>
       <c r="B56" s="3">
-        <v>2026060050</v>
+        <v>2026060146</v>
       </c>
       <c r="C56" s="3">
         <v>1</v>
@@ -5111,34 +5175,34 @@
         <v>29</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>141</v>
+        <v>221</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="K56" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L56" s="6" t="s">
-        <v>196</v>
+        <v>224</v>
       </c>
       <c r="M56" s="6" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="O56" s="3" t="s">
         <v>39</v>
@@ -5146,19 +5210,19 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3">
-        <v>37830</v>
-      </c>
-      <c r="S56" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>49442</v>
+      </c>
+      <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-      <c r="U56" s="3"/>
+      <c r="U56" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="6" t="s">
-        <v>184</v>
+        <v>227</v>
       </c>
       <c r="AA56" s="3" t="s">
         <v>40</v>
@@ -5172,7 +5236,7 @@
         <v>55</v>
       </c>
       <c r="B57" s="7">
-        <v>2026060051</v>
+        <v>2026060052</v>
       </c>
       <c r="C57" s="7">
         <v>1</v>
@@ -5181,44 +5245,46 @@
         <v>29</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>141</v>
+        <v>73</v>
       </c>
       <c r="H57" s="7" t="s">
-        <v>215</v>
+        <v>160</v>
       </c>
       <c r="I57" s="7" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="J57" s="7" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="K57" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L57" s="8" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="M57" s="8" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="N57" s="8" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="O57" s="7" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="P57" s="7"/>
       <c r="Q57" s="7"/>
       <c r="R57" s="7">
-        <v>37830</v>
-      </c>
-      <c r="S57" s="7"/>
+        <v>29640</v>
+      </c>
+      <c r="S57" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T57" s="7"/>
       <c r="U57" s="7"/>
       <c r="V57" s="7"/>
@@ -5226,19 +5292,21 @@
       <c r="X57" s="7"/>
       <c r="Y57" s="7"/>
       <c r="Z57" s="8" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="AA57" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AB57" s="7"/>
+      <c r="AB57" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="58" spans="1:28">
       <c r="A58" s="3">
         <v>56</v>
       </c>
       <c r="B58" s="3">
-        <v>2026060046</v>
+        <v>2026060053</v>
       </c>
       <c r="C58" s="3">
         <v>1</v>
@@ -5247,46 +5315,44 @@
         <v>29</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>62</v>
+        <v>160</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L58" s="6" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="M58" s="6" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="O58" s="3" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P58" s="3"/>
       <c r="Q58" s="3"/>
       <c r="R58" s="3">
-        <v>45926</v>
-      </c>
-      <c r="S58" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>29640</v>
+      </c>
+      <c r="S58" s="3"/>
       <c r="T58" s="3"/>
       <c r="U58" s="3"/>
       <c r="V58" s="3"/>
@@ -5294,21 +5360,19 @@
       <c r="X58" s="3"/>
       <c r="Y58" s="3"/>
       <c r="Z58" s="6" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="AA58" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AB58" s="3">
-        <v>1</v>
-      </c>
+      <c r="AB58" s="3"/>
     </row>
     <row r="59" spans="1:28">
       <c r="A59" s="7">
         <v>57</v>
       </c>
       <c r="B59" s="7">
-        <v>2026060047</v>
+        <v>2026060051</v>
       </c>
       <c r="C59" s="7">
         <v>1</v>
@@ -5317,34 +5381,34 @@
         <v>29</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>32</v>
+        <v>72</v>
       </c>
       <c r="H59" s="7" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="I59" s="7" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="J59" s="7" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="K59" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L59" s="8" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="M59" s="8" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="N59" s="8" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="O59" s="7" t="s">
         <v>48</v>
@@ -5352,7 +5416,7 @@
       <c r="P59" s="7"/>
       <c r="Q59" s="7"/>
       <c r="R59" s="7">
-        <v>45926</v>
+        <v>37830</v>
       </c>
       <c r="S59" s="7"/>
       <c r="T59" s="7"/>
@@ -5362,19 +5426,21 @@
       <c r="X59" s="7"/>
       <c r="Y59" s="7"/>
       <c r="Z59" s="8" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="AA59" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AB59" s="7"/>
+      <c r="AB59" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="60" spans="1:28">
       <c r="A60" s="3">
         <v>58</v>
       </c>
       <c r="B60" s="3">
-        <v>2026060040</v>
+        <v>2026060050</v>
       </c>
       <c r="C60" s="3">
         <v>1</v>
@@ -5383,34 +5449,34 @@
         <v>29</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>199</v>
+        <v>72</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>200</v>
+        <v>73</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L60" s="6" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="M60" s="6" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="O60" s="3" t="s">
         <v>39</v>
@@ -5418,7 +5484,7 @@
       <c r="P60" s="3"/>
       <c r="Q60" s="3"/>
       <c r="R60" s="3">
-        <v>29640</v>
+        <v>37830</v>
       </c>
       <c r="S60" s="3" t="s">
         <v>40</v>
@@ -5430,21 +5496,19 @@
       <c r="X60" s="3"/>
       <c r="Y60" s="3"/>
       <c r="Z60" s="6" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="AA60" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AB60" s="3">
-        <v>1</v>
-      </c>
+      <c r="AB60" s="3"/>
     </row>
     <row r="61" spans="1:28">
       <c r="A61" s="7">
         <v>59</v>
       </c>
       <c r="B61" s="7">
-        <v>2026060041</v>
+        <v>2026060046</v>
       </c>
       <c r="C61" s="7">
         <v>1</v>
@@ -5453,44 +5517,46 @@
         <v>29</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="G61" s="7" t="s">
-        <v>199</v>
+        <v>32</v>
       </c>
       <c r="H61" s="7" t="s">
-        <v>200</v>
+        <v>77</v>
       </c>
       <c r="I61" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="J61" s="7" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="K61" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L61" s="8" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="M61" s="8" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="N61" s="8" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="O61" s="7" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="P61" s="7"/>
       <c r="Q61" s="7"/>
       <c r="R61" s="7">
-        <v>29640</v>
-      </c>
-      <c r="S61" s="7"/>
+        <v>45926</v>
+      </c>
+      <c r="S61" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T61" s="7"/>
       <c r="U61" s="7"/>
       <c r="V61" s="7"/>
@@ -5498,19 +5564,21 @@
       <c r="X61" s="7"/>
       <c r="Y61" s="7"/>
       <c r="Z61" s="8" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="AA61" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AB61" s="7"/>
+      <c r="AB61" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="62" spans="1:28">
       <c r="A62" s="3">
         <v>60</v>
       </c>
       <c r="B62" s="3">
-        <v>2026060044</v>
+        <v>2026060047</v>
       </c>
       <c r="C62" s="3">
         <v>1</v>
@@ -5519,46 +5587,44 @@
         <v>29</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>102</v>
+        <v>32</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L62" s="6" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="M62" s="6" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="O62" s="3" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P62" s="3"/>
       <c r="Q62" s="3"/>
       <c r="R62" s="3">
-        <v>34235</v>
-      </c>
-      <c r="S62" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>45926</v>
+      </c>
+      <c r="S62" s="3"/>
       <c r="T62" s="3"/>
       <c r="U62" s="3"/>
       <c r="V62" s="3"/>
@@ -5566,21 +5632,19 @@
       <c r="X62" s="3"/>
       <c r="Y62" s="3"/>
       <c r="Z62" s="6" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="AA62" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AB62" s="3">
-        <v>1</v>
-      </c>
+      <c r="AB62" s="3"/>
     </row>
     <row r="63" spans="1:28">
       <c r="A63" s="7">
         <v>61</v>
       </c>
       <c r="B63" s="7">
-        <v>2026060045</v>
+        <v>2026060040</v>
       </c>
       <c r="C63" s="7">
         <v>1</v>
@@ -5589,44 +5653,46 @@
         <v>29</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="G63" s="7" t="s">
-        <v>102</v>
+        <v>212</v>
       </c>
       <c r="H63" s="7" t="s">
-        <v>32</v>
+        <v>213</v>
       </c>
       <c r="I63" s="7" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="J63" s="7" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="K63" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L63" s="8" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="M63" s="8" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="N63" s="8" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="O63" s="7" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="P63" s="7"/>
       <c r="Q63" s="7"/>
       <c r="R63" s="7">
-        <v>34235</v>
-      </c>
-      <c r="S63" s="7"/>
+        <v>29640</v>
+      </c>
+      <c r="S63" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T63" s="7"/>
       <c r="U63" s="7"/>
       <c r="V63" s="7"/>
@@ -5634,19 +5700,21 @@
       <c r="X63" s="7"/>
       <c r="Y63" s="7"/>
       <c r="Z63" s="8" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="AA63" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AB63" s="7"/>
+      <c r="AB63" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="64" spans="1:28">
       <c r="A64" s="3">
         <v>62</v>
       </c>
       <c r="B64" s="3">
-        <v>2026060042</v>
+        <v>2026060041</v>
       </c>
       <c r="C64" s="3">
         <v>1</v>
@@ -5655,46 +5723,44 @@
         <v>29</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>102</v>
+        <v>213</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="K64" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L64" s="6" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="M64" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="O64" s="3" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P64" s="3"/>
       <c r="Q64" s="3"/>
       <c r="R64" s="3">
-        <v>17791</v>
-      </c>
-      <c r="S64" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>29640</v>
+      </c>
+      <c r="S64" s="3"/>
       <c r="T64" s="3"/>
       <c r="U64" s="3"/>
       <c r="V64" s="3"/>
@@ -5702,21 +5768,19 @@
       <c r="X64" s="3"/>
       <c r="Y64" s="3"/>
       <c r="Z64" s="6" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="AA64" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AB64" s="3">
-        <v>1</v>
-      </c>
+      <c r="AB64" s="3"/>
     </row>
     <row r="65" spans="1:28">
       <c r="A65" s="7">
         <v>63</v>
       </c>
       <c r="B65" s="7">
-        <v>2026060043</v>
+        <v>2026060044</v>
       </c>
       <c r="C65" s="7">
         <v>1</v>
@@ -5725,44 +5789,46 @@
         <v>29</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="G65" s="7" t="s">
-        <v>200</v>
+        <v>117</v>
       </c>
       <c r="H65" s="7" t="s">
-        <v>102</v>
+        <v>32</v>
       </c>
       <c r="I65" s="7" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="J65" s="7" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="K65" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L65" s="8" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="M65" s="8" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="N65" s="8" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="O65" s="7" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="P65" s="7"/>
       <c r="Q65" s="7"/>
       <c r="R65" s="7">
-        <v>17791</v>
-      </c>
-      <c r="S65" s="7"/>
+        <v>34235</v>
+      </c>
+      <c r="S65" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T65" s="7"/>
       <c r="U65" s="7"/>
       <c r="V65" s="7"/>
@@ -5770,19 +5836,21 @@
       <c r="X65" s="7"/>
       <c r="Y65" s="7"/>
       <c r="Z65" s="8" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="AA65" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AB65" s="7"/>
+      <c r="AB65" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="66" spans="1:28">
       <c r="A66" s="3">
         <v>64</v>
       </c>
       <c r="B66" s="3">
-        <v>2026060385</v>
+        <v>2026060045</v>
       </c>
       <c r="C66" s="3">
         <v>1</v>
@@ -5791,46 +5859,44 @@
         <v>29</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>31</v>
+        <v>124</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>235</v>
+        <v>68</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L66" s="6" t="s">
-        <v>236</v>
+        <v>209</v>
       </c>
       <c r="M66" s="6" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="O66" s="3" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P66" s="3"/>
       <c r="Q66" s="3"/>
       <c r="R66" s="3">
-        <v>122434</v>
-      </c>
-      <c r="S66" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>34235</v>
+      </c>
+      <c r="S66" s="3"/>
       <c r="T66" s="3"/>
       <c r="U66" s="3"/>
       <c r="V66" s="3"/>
@@ -5838,9 +5904,11 @@
       <c r="X66" s="3"/>
       <c r="Y66" s="3"/>
       <c r="Z66" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="AA66" s="3"/>
+        <v>197</v>
+      </c>
+      <c r="AA66" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="AB66" s="3"/>
     </row>
     <row r="67" spans="1:28">
@@ -5848,7 +5916,7 @@
         <v>65</v>
       </c>
       <c r="B67" s="7">
-        <v>2026060386</v>
+        <v>2026060042</v>
       </c>
       <c r="C67" s="7">
         <v>1</v>
@@ -5857,44 +5925,46 @@
         <v>29</v>
       </c>
       <c r="E67" s="7" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>31</v>
+        <v>124</v>
       </c>
       <c r="G67" s="7" t="s">
-        <v>102</v>
+        <v>213</v>
       </c>
       <c r="H67" s="7" t="s">
-        <v>32</v>
+        <v>117</v>
       </c>
       <c r="I67" s="7" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="J67" s="7" t="s">
-        <v>235</v>
+        <v>68</v>
       </c>
       <c r="K67" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L67" s="8" t="s">
-        <v>236</v>
+        <v>209</v>
       </c>
       <c r="M67" s="8" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="N67" s="8" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="O67" s="7" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="P67" s="7"/>
       <c r="Q67" s="7"/>
       <c r="R67" s="7">
-        <v>122434</v>
-      </c>
-      <c r="S67" s="7"/>
+        <v>17791</v>
+      </c>
+      <c r="S67" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T67" s="7"/>
       <c r="U67" s="7"/>
       <c r="V67" s="7"/>
@@ -5902,19 +5972,21 @@
       <c r="X67" s="7"/>
       <c r="Y67" s="7"/>
       <c r="Z67" s="8" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="AA67" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AB67" s="7"/>
+      <c r="AB67" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="68" spans="1:28">
       <c r="A68" s="3">
         <v>66</v>
       </c>
       <c r="B68" s="3">
-        <v>2026060061</v>
+        <v>2026060043</v>
       </c>
       <c r="C68" s="3">
         <v>1</v>
@@ -5923,46 +5995,44 @@
         <v>29</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>147</v>
+        <v>213</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>193</v>
+        <v>117</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>235</v>
+        <v>68</v>
       </c>
       <c r="K68" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L68" s="6" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="M68" s="6" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="O68" s="3" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P68" s="3"/>
       <c r="Q68" s="3"/>
       <c r="R68" s="3">
-        <v>702</v>
-      </c>
-      <c r="S68" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>17791</v>
+      </c>
+      <c r="S68" s="3"/>
       <c r="T68" s="3"/>
       <c r="U68" s="3"/>
       <c r="V68" s="3"/>
@@ -5970,21 +6040,19 @@
       <c r="X68" s="3"/>
       <c r="Y68" s="3"/>
       <c r="Z68" s="6" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="AA68" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AB68" s="3">
-        <v>1</v>
-      </c>
+      <c r="AB68" s="3"/>
     </row>
     <row r="69" spans="1:28">
       <c r="A69" s="7">
         <v>67</v>
       </c>
       <c r="B69" s="7">
-        <v>2026060062</v>
+        <v>2026060385</v>
       </c>
       <c r="C69" s="7">
         <v>1</v>
@@ -5993,44 +6061,46 @@
         <v>29</v>
       </c>
       <c r="E69" s="7" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>109</v>
+        <v>31</v>
       </c>
       <c r="G69" s="7" t="s">
-        <v>147</v>
+        <v>117</v>
       </c>
       <c r="H69" s="7" t="s">
-        <v>193</v>
+        <v>32</v>
       </c>
       <c r="I69" s="7" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="J69" s="7" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="K69" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L69" s="8" t="s">
-        <v>196</v>
+        <v>248</v>
       </c>
       <c r="M69" s="8" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="N69" s="8" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="O69" s="7" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="P69" s="7"/>
       <c r="Q69" s="7"/>
       <c r="R69" s="7">
-        <v>702</v>
-      </c>
-      <c r="S69" s="7"/>
+        <v>122434</v>
+      </c>
+      <c r="S69" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T69" s="7"/>
       <c r="U69" s="7"/>
       <c r="V69" s="7"/>
@@ -6038,11 +6108,9 @@
       <c r="X69" s="7"/>
       <c r="Y69" s="7"/>
       <c r="Z69" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="AA69" s="7" t="s">
-        <v>40</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="AA69" s="7"/>
       <c r="AB69" s="7"/>
     </row>
     <row r="70" spans="1:28">
@@ -6050,7 +6118,7 @@
         <v>68</v>
       </c>
       <c r="B70" s="3">
-        <v>2026060048</v>
+        <v>2026060386</v>
       </c>
       <c r="C70" s="3">
         <v>1</v>
@@ -6059,46 +6127,44 @@
         <v>29</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>109</v>
+        <v>31</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>62</v>
+        <v>117</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>141</v>
+        <v>32</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="K70" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L70" s="6" t="s">
-        <v>196</v>
+        <v>248</v>
       </c>
       <c r="M70" s="6" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="O70" s="3" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P70" s="3"/>
       <c r="Q70" s="3"/>
       <c r="R70" s="3">
-        <v>5766</v>
-      </c>
-      <c r="S70" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>122434</v>
+      </c>
+      <c r="S70" s="3"/>
       <c r="T70" s="3"/>
       <c r="U70" s="3"/>
       <c r="V70" s="3"/>
@@ -6106,21 +6172,19 @@
       <c r="X70" s="3"/>
       <c r="Y70" s="3"/>
       <c r="Z70" s="6" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="AA70" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AB70" s="3">
-        <v>1</v>
-      </c>
+      <c r="AB70" s="3"/>
     </row>
     <row r="71" spans="1:28">
       <c r="A71" s="7">
         <v>69</v>
       </c>
       <c r="B71" s="7">
-        <v>2026060049</v>
+        <v>2026060061</v>
       </c>
       <c r="C71" s="7">
         <v>1</v>
@@ -6129,44 +6193,46 @@
         <v>29</v>
       </c>
       <c r="E71" s="7" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="G71" s="7" t="s">
-        <v>62</v>
+        <v>160</v>
       </c>
       <c r="H71" s="7" t="s">
-        <v>141</v>
+        <v>206</v>
       </c>
       <c r="I71" s="7" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="J71" s="7" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="K71" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L71" s="8" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="M71" s="8" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="N71" s="8" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="O71" s="7" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="P71" s="7"/>
       <c r="Q71" s="7"/>
       <c r="R71" s="7">
-        <v>5766</v>
-      </c>
-      <c r="S71" s="7"/>
+        <v>702</v>
+      </c>
+      <c r="S71" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T71" s="7"/>
       <c r="U71" s="7"/>
       <c r="V71" s="7"/>
@@ -6174,19 +6240,21 @@
       <c r="X71" s="7"/>
       <c r="Y71" s="7"/>
       <c r="Z71" s="8" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="AA71" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AB71" s="7"/>
+      <c r="AB71" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="72" spans="1:28">
       <c r="A72" s="3">
         <v>70</v>
       </c>
       <c r="B72" s="3">
-        <v>2026060819</v>
+        <v>2026060062</v>
       </c>
       <c r="C72" s="3">
         <v>1</v>
@@ -6195,48 +6263,44 @@
         <v>29</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>54</v>
+        <v>124</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>194</v>
+        <v>160</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>245</v>
+        <v>206</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L72" s="6" t="s">
-        <v>247</v>
+        <v>209</v>
       </c>
       <c r="M72" s="6" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>190</v>
+        <v>253</v>
       </c>
       <c r="O72" s="3" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P72" s="3"/>
-      <c r="Q72" s="3">
-        <v>35761</v>
-      </c>
+      <c r="Q72" s="3"/>
       <c r="R72" s="3">
-        <v>68540</v>
-      </c>
-      <c r="S72" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>702</v>
+      </c>
+      <c r="S72" s="3"/>
       <c r="T72" s="3"/>
       <c r="U72" s="3"/>
       <c r="V72" s="3"/>
@@ -6244,9 +6308,11 @@
       <c r="X72" s="3"/>
       <c r="Y72" s="3"/>
       <c r="Z72" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="AA72" s="3"/>
+        <v>197</v>
+      </c>
+      <c r="AA72" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="AB72" s="3"/>
     </row>
     <row r="73" spans="1:28">
@@ -6254,7 +6320,7 @@
         <v>71</v>
       </c>
       <c r="B73" s="7">
-        <v>2026060820</v>
+        <v>2026060048</v>
       </c>
       <c r="C73" s="7">
         <v>1</v>
@@ -6263,46 +6329,46 @@
         <v>29</v>
       </c>
       <c r="E73" s="7" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>54</v>
+        <v>124</v>
       </c>
       <c r="G73" s="7" t="s">
-        <v>194</v>
+        <v>77</v>
       </c>
       <c r="H73" s="7" t="s">
-        <v>245</v>
+        <v>72</v>
       </c>
       <c r="I73" s="7" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="J73" s="7" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="K73" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L73" s="8" t="s">
-        <v>247</v>
+        <v>209</v>
       </c>
       <c r="M73" s="8" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="N73" s="8" t="s">
-        <v>190</v>
+        <v>256</v>
       </c>
       <c r="O73" s="7" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="P73" s="7"/>
-      <c r="Q73" s="7">
-        <v>35761</v>
-      </c>
+      <c r="Q73" s="7"/>
       <c r="R73" s="7">
-        <v>68540</v>
-      </c>
-      <c r="S73" s="7"/>
+        <v>5766</v>
+      </c>
+      <c r="S73" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T73" s="7"/>
       <c r="U73" s="7"/>
       <c r="V73" s="7"/>
@@ -6310,19 +6376,21 @@
       <c r="X73" s="7"/>
       <c r="Y73" s="7"/>
       <c r="Z73" s="8" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="AA73" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AB73" s="7"/>
+      <c r="AB73" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="74" spans="1:28">
       <c r="A74" s="3">
         <v>72</v>
       </c>
       <c r="B74" s="3">
-        <v>2026060526</v>
+        <v>2026060049</v>
       </c>
       <c r="C74" s="3">
         <v>1</v>
@@ -6331,46 +6399,44 @@
         <v>29</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>31</v>
+        <v>124</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>65</v>
+        <v>247</v>
       </c>
       <c r="K74" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L74" s="6" t="s">
-        <v>250</v>
+        <v>209</v>
       </c>
       <c r="M74" s="6" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="O74" s="3" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P74" s="3"/>
       <c r="Q74" s="3"/>
       <c r="R74" s="3">
-        <v>33686</v>
-      </c>
-      <c r="S74" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>5766</v>
+      </c>
+      <c r="S74" s="3"/>
       <c r="T74" s="3"/>
       <c r="U74" s="3"/>
       <c r="V74" s="3"/>
@@ -6378,9 +6444,11 @@
       <c r="X74" s="3"/>
       <c r="Y74" s="3"/>
       <c r="Z74" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="AA74" s="3"/>
+        <v>197</v>
+      </c>
+      <c r="AA74" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="AB74" s="3"/>
     </row>
     <row r="75" spans="1:28">
@@ -6388,7 +6456,7 @@
         <v>73</v>
       </c>
       <c r="B75" s="7">
-        <v>2026060527</v>
+        <v>2026060819</v>
       </c>
       <c r="C75" s="7">
         <v>1</v>
@@ -6397,44 +6465,48 @@
         <v>29</v>
       </c>
       <c r="E75" s="7" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="G75" s="7" t="s">
-        <v>110</v>
+        <v>207</v>
       </c>
       <c r="H75" s="7" t="s">
-        <v>49</v>
+        <v>257</v>
       </c>
       <c r="I75" s="7" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="J75" s="7" t="s">
-        <v>65</v>
+        <v>163</v>
       </c>
       <c r="K75" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L75" s="8" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="M75" s="8" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="N75" s="8" t="s">
-        <v>252</v>
+        <v>203</v>
       </c>
       <c r="O75" s="7" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="P75" s="7"/>
-      <c r="Q75" s="7"/>
+      <c r="Q75" s="7">
+        <v>35761</v>
+      </c>
       <c r="R75" s="7">
-        <v>33686</v>
-      </c>
-      <c r="S75" s="7"/>
+        <v>68540</v>
+      </c>
+      <c r="S75" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T75" s="7"/>
       <c r="U75" s="7"/>
       <c r="V75" s="7"/>
@@ -6442,11 +6514,9 @@
       <c r="X75" s="7"/>
       <c r="Y75" s="7"/>
       <c r="Z75" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="AA75" s="7" t="s">
-        <v>40</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="AA75" s="7"/>
       <c r="AB75" s="7"/>
     </row>
     <row r="76" spans="1:28">
@@ -6454,7 +6524,7 @@
         <v>74</v>
       </c>
       <c r="B76" s="3">
-        <v>2026060408</v>
+        <v>2026060820</v>
       </c>
       <c r="C76" s="3">
         <v>1</v>
@@ -6463,46 +6533,46 @@
         <v>29</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>147</v>
+        <v>257</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="J76" s="3" t="s">
-        <v>65</v>
+        <v>163</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L76" s="6" t="s">
-        <v>236</v>
+        <v>259</v>
       </c>
       <c r="M76" s="6" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>255</v>
+        <v>203</v>
       </c>
       <c r="O76" s="3" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P76" s="3"/>
-      <c r="Q76" s="3"/>
+      <c r="Q76" s="3">
+        <v>35761</v>
+      </c>
       <c r="R76" s="3">
-        <v>19776</v>
-      </c>
-      <c r="S76" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>68540</v>
+      </c>
+      <c r="S76" s="3"/>
       <c r="T76" s="3"/>
       <c r="U76" s="3"/>
       <c r="V76" s="3"/>
@@ -6510,9 +6580,11 @@
       <c r="X76" s="3"/>
       <c r="Y76" s="3"/>
       <c r="Z76" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="AA76" s="3"/>
+        <v>197</v>
+      </c>
+      <c r="AA76" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="AB76" s="3"/>
     </row>
     <row r="77" spans="1:28">
@@ -6520,7 +6592,7 @@
         <v>75</v>
       </c>
       <c r="B77" s="7">
-        <v>2026060409</v>
+        <v>2026060922</v>
       </c>
       <c r="C77" s="7">
         <v>1</v>
@@ -6529,64 +6601,70 @@
         <v>29</v>
       </c>
       <c r="E77" s="7" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="G77" s="7" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="H77" s="7" t="s">
-        <v>147</v>
+        <v>257</v>
       </c>
       <c r="I77" s="7" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="J77" s="7" t="s">
-        <v>65</v>
+        <v>163</v>
       </c>
       <c r="K77" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L77" s="8" t="s">
-        <v>236</v>
+        <v>259</v>
       </c>
       <c r="M77" s="8" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="N77" s="8" t="s">
-        <v>255</v>
+        <v>203</v>
       </c>
       <c r="O77" s="7" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="P77" s="7"/>
-      <c r="Q77" s="7"/>
+      <c r="Q77" s="7">
+        <v>35761</v>
+      </c>
       <c r="R77" s="7">
-        <v>19776</v>
+        <v>68540</v>
       </c>
       <c r="S77" s="7"/>
       <c r="T77" s="7"/>
       <c r="U77" s="7"/>
       <c r="V77" s="7"/>
-      <c r="W77" s="7"/>
+      <c r="W77" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="X77" s="7"/>
       <c r="Y77" s="7"/>
       <c r="Z77" s="8" t="s">
-        <v>184</v>
+        <v>205</v>
       </c>
       <c r="AA77" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AB77" s="7"/>
+      <c r="AB77" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="78" spans="1:28">
       <c r="A78" s="3">
         <v>76</v>
       </c>
       <c r="B78" s="3">
-        <v>2026060389</v>
+        <v>2026060526</v>
       </c>
       <c r="C78" s="3">
         <v>1</v>
@@ -6595,34 +6673,34 @@
         <v>29</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="F78" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>62</v>
+        <v>125</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>141</v>
+        <v>49</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="J78" s="3" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="K78" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L78" s="6" t="s">
-        <v>236</v>
+        <v>262</v>
       </c>
       <c r="M78" s="6" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="O78" s="3" t="s">
         <v>39</v>
@@ -6630,7 +6708,7 @@
       <c r="P78" s="3"/>
       <c r="Q78" s="3"/>
       <c r="R78" s="3">
-        <v>92779</v>
+        <v>33686</v>
       </c>
       <c r="S78" s="3" t="s">
         <v>40</v>
@@ -6642,7 +6720,7 @@
       <c r="X78" s="3"/>
       <c r="Y78" s="3"/>
       <c r="Z78" s="6" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="AA78" s="3"/>
       <c r="AB78" s="3"/>
@@ -6652,7 +6730,7 @@
         <v>77</v>
       </c>
       <c r="B79" s="7">
-        <v>2026060390</v>
+        <v>2026060527</v>
       </c>
       <c r="C79" s="7">
         <v>1</v>
@@ -6661,34 +6739,34 @@
         <v>29</v>
       </c>
       <c r="E79" s="7" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="F79" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G79" s="7" t="s">
-        <v>62</v>
+        <v>125</v>
       </c>
       <c r="H79" s="7" t="s">
-        <v>141</v>
+        <v>49</v>
       </c>
       <c r="I79" s="7" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="J79" s="7" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="K79" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L79" s="8" t="s">
-        <v>236</v>
+        <v>262</v>
       </c>
       <c r="M79" s="8" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="N79" s="8" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="O79" s="7" t="s">
         <v>48</v>
@@ -6696,7 +6774,7 @@
       <c r="P79" s="7"/>
       <c r="Q79" s="7"/>
       <c r="R79" s="7">
-        <v>92779</v>
+        <v>33686</v>
       </c>
       <c r="S79" s="7"/>
       <c r="T79" s="7"/>
@@ -6706,7 +6784,7 @@
       <c r="X79" s="7"/>
       <c r="Y79" s="7"/>
       <c r="Z79" s="8" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="AA79" s="7" t="s">
         <v>40</v>
@@ -6718,7 +6796,7 @@
         <v>78</v>
       </c>
       <c r="B80" s="3">
-        <v>2026060853</v>
+        <v>2026060409</v>
       </c>
       <c r="C80" s="3">
         <v>1</v>
@@ -6727,42 +6805,42 @@
         <v>29</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>121</v>
+        <v>73</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>209</v>
+        <v>160</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="J80" s="3" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="K80" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L80" s="6" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="M80" s="6" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="O80" s="3" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P80" s="3"/>
       <c r="Q80" s="3"/>
       <c r="R80" s="3">
-        <v>92779</v>
+        <v>19776</v>
       </c>
       <c r="S80" s="3"/>
       <c r="T80" s="3"/>
@@ -6770,11 +6848,9 @@
       <c r="V80" s="3"/>
       <c r="W80" s="3"/>
       <c r="X80" s="3"/>
-      <c r="Y80" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="Y80" s="3"/>
       <c r="Z80" s="6" t="s">
-        <v>259</v>
+        <v>197</v>
       </c>
       <c r="AA80" s="3" t="s">
         <v>40</v>
@@ -6788,7 +6864,7 @@
         <v>79</v>
       </c>
       <c r="B81" s="7">
-        <v>2026060383</v>
+        <v>2026060408</v>
       </c>
       <c r="C81" s="7">
         <v>1</v>
@@ -6797,34 +6873,34 @@
         <v>29</v>
       </c>
       <c r="E81" s="7" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="F81" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G81" s="7" t="s">
-        <v>200</v>
+        <v>73</v>
       </c>
       <c r="H81" s="7" t="s">
-        <v>102</v>
+        <v>160</v>
       </c>
       <c r="I81" s="7" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="J81" s="7" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="K81" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L81" s="8" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="M81" s="8" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="N81" s="8" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="O81" s="7" t="s">
         <v>39</v>
@@ -6832,7 +6908,7 @@
       <c r="P81" s="7"/>
       <c r="Q81" s="7"/>
       <c r="R81" s="7">
-        <v>207716</v>
+        <v>19776</v>
       </c>
       <c r="S81" s="7" t="s">
         <v>40</v>
@@ -6844,7 +6920,7 @@
       <c r="X81" s="7"/>
       <c r="Y81" s="7"/>
       <c r="Z81" s="8" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="AA81" s="7"/>
       <c r="AB81" s="7"/>
@@ -6854,7 +6930,7 @@
         <v>80</v>
       </c>
       <c r="B82" s="3">
-        <v>2026060384</v>
+        <v>2026060389</v>
       </c>
       <c r="C82" s="3">
         <v>1</v>
@@ -6863,44 +6939,46 @@
         <v>29</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="F82" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>200</v>
+        <v>77</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>102</v>
+        <v>72</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="J82" s="3" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="K82" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L82" s="6" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="M82" s="6" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="O82" s="3" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3">
-        <v>207716</v>
-      </c>
-      <c r="S82" s="3"/>
+        <v>92779</v>
+      </c>
+      <c r="S82" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
@@ -6908,11 +6986,9 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="AA82" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
     </row>
     <row r="83" spans="1:28">
@@ -6920,7 +6996,7 @@
         <v>81</v>
       </c>
       <c r="B83" s="7">
-        <v>2026060569</v>
+        <v>2026060390</v>
       </c>
       <c r="C83" s="7">
         <v>1</v>
@@ -6929,68 +7005,64 @@
         <v>29</v>
       </c>
       <c r="E83" s="7" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="F83" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G83" s="7" t="s">
-        <v>194</v>
+        <v>77</v>
       </c>
       <c r="H83" s="7" t="s">
-        <v>245</v>
+        <v>72</v>
       </c>
       <c r="I83" s="7" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="J83" s="7" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="K83" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L83" s="8" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="M83" s="8" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="N83" s="8" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="O83" s="7" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P83" s="7"/>
       <c r="Q83" s="7"/>
       <c r="R83" s="7">
-        <v>207716</v>
+        <v>92779</v>
       </c>
       <c r="S83" s="7"/>
       <c r="T83" s="7"/>
-      <c r="U83" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="U83" s="7"/>
       <c r="V83" s="7"/>
       <c r="W83" s="7"/>
       <c r="X83" s="7"/>
       <c r="Y83" s="7"/>
       <c r="Z83" s="8" t="s">
-        <v>214</v>
+        <v>197</v>
       </c>
       <c r="AA83" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AB83" s="7">
-        <v>1</v>
-      </c>
+      <c r="AB83" s="7"/>
     </row>
     <row r="84" spans="1:28">
       <c r="A84" s="3">
         <v>82</v>
       </c>
       <c r="B84" s="3">
-        <v>2026060387</v>
+        <v>2026060853</v>
       </c>
       <c r="C84" s="3">
         <v>1</v>
@@ -6999,34 +7071,34 @@
         <v>29</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>32</v>
+        <v>136</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>62</v>
+        <v>222</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="J84" s="3" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="K84" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L84" s="6" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="M84" s="6" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="O84" s="3" t="s">
         <v>39</v>
@@ -7034,29 +7106,33 @@
       <c r="P84" s="3"/>
       <c r="Q84" s="3"/>
       <c r="R84" s="3">
-        <v>152071</v>
-      </c>
-      <c r="S84" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>92779</v>
+      </c>
+      <c r="S84" s="3"/>
       <c r="T84" s="3"/>
       <c r="U84" s="3"/>
       <c r="V84" s="3"/>
       <c r="W84" s="3"/>
       <c r="X84" s="3"/>
-      <c r="Y84" s="3"/>
+      <c r="Y84" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="Z84" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="AA84" s="3"/>
-      <c r="AB84" s="3"/>
+        <v>271</v>
+      </c>
+      <c r="AA84" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB84" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="85" spans="1:28">
       <c r="A85" s="7">
         <v>83</v>
       </c>
       <c r="B85" s="7">
-        <v>2026060388</v>
+        <v>2026060383</v>
       </c>
       <c r="C85" s="7">
         <v>1</v>
@@ -7065,44 +7141,46 @@
         <v>29</v>
       </c>
       <c r="E85" s="7" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="F85" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G85" s="7" t="s">
-        <v>32</v>
+        <v>213</v>
       </c>
       <c r="H85" s="7" t="s">
-        <v>62</v>
+        <v>117</v>
       </c>
       <c r="I85" s="7" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="J85" s="7" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="K85" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L85" s="8" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="M85" s="8" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="N85" s="8" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="O85" s="7" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="P85" s="7"/>
       <c r="Q85" s="7"/>
       <c r="R85" s="7">
-        <v>152071</v>
-      </c>
-      <c r="S85" s="7"/>
+        <v>207716</v>
+      </c>
+      <c r="S85" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T85" s="7"/>
       <c r="U85" s="7"/>
       <c r="V85" s="7"/>
@@ -7110,11 +7188,9 @@
       <c r="X85" s="7"/>
       <c r="Y85" s="7"/>
       <c r="Z85" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="AA85" s="7" t="s">
-        <v>40</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="AA85" s="7"/>
       <c r="AB85" s="7"/>
     </row>
     <row r="86" spans="1:28">
@@ -7122,7 +7198,7 @@
         <v>84</v>
       </c>
       <c r="B86" s="3">
-        <v>2026060570</v>
+        <v>2026060384</v>
       </c>
       <c r="C86" s="3">
         <v>1</v>
@@ -7131,68 +7207,64 @@
         <v>29</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="F86" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>245</v>
+        <v>213</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="J86" s="3" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="K86" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L86" s="6" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="M86" s="6" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="O86" s="3" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P86" s="3"/>
       <c r="Q86" s="3"/>
       <c r="R86" s="3">
-        <v>152071</v>
+        <v>207716</v>
       </c>
       <c r="S86" s="3"/>
       <c r="T86" s="3"/>
-      <c r="U86" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="U86" s="3"/>
       <c r="V86" s="3"/>
       <c r="W86" s="3"/>
       <c r="X86" s="3"/>
       <c r="Y86" s="3"/>
       <c r="Z86" s="6" t="s">
-        <v>214</v>
+        <v>197</v>
       </c>
       <c r="AA86" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AB86" s="3">
-        <v>1</v>
-      </c>
+      <c r="AB86" s="3"/>
     </row>
     <row r="87" spans="1:28">
       <c r="A87" s="7">
         <v>85</v>
       </c>
       <c r="B87" s="7">
-        <v>2026060081</v>
+        <v>2026060569</v>
       </c>
       <c r="C87" s="7">
         <v>1</v>
@@ -7201,34 +7273,34 @@
         <v>29</v>
       </c>
       <c r="E87" s="7" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="F87" s="7" t="s">
-        <v>109</v>
+        <v>31</v>
       </c>
       <c r="G87" s="7" t="s">
-        <v>245</v>
+        <v>207</v>
       </c>
       <c r="H87" s="7" t="s">
-        <v>78</v>
+        <v>257</v>
       </c>
       <c r="I87" s="7" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="J87" s="7" t="s">
-        <v>267</v>
+        <v>80</v>
       </c>
       <c r="K87" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L87" s="8" t="s">
-        <v>211</v>
+        <v>248</v>
       </c>
       <c r="M87" s="8" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="N87" s="8" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="O87" s="7" t="s">
         <v>39</v>
@@ -7236,29 +7308,33 @@
       <c r="P87" s="7"/>
       <c r="Q87" s="7"/>
       <c r="R87" s="7">
-        <v>48</v>
-      </c>
-      <c r="S87" s="7" t="s">
-        <v>40</v>
-      </c>
+        <v>207716</v>
+      </c>
+      <c r="S87" s="7"/>
       <c r="T87" s="7"/>
-      <c r="U87" s="7"/>
+      <c r="U87" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="V87" s="7"/>
       <c r="W87" s="7"/>
       <c r="X87" s="7"/>
       <c r="Y87" s="7"/>
       <c r="Z87" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="AA87" s="7"/>
-      <c r="AB87" s="7"/>
+        <v>227</v>
+      </c>
+      <c r="AA87" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB87" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="88" spans="1:28">
       <c r="A88" s="3">
         <v>86</v>
       </c>
       <c r="B88" s="3">
-        <v>2026060082</v>
+        <v>2026060387</v>
       </c>
       <c r="C88" s="3">
         <v>1</v>
@@ -7267,44 +7343,46 @@
         <v>29</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>109</v>
+        <v>31</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>245</v>
+        <v>32</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="J88" s="3" t="s">
-        <v>267</v>
+        <v>80</v>
       </c>
       <c r="K88" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L88" s="6" t="s">
-        <v>211</v>
+        <v>248</v>
       </c>
       <c r="M88" s="6" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="O88" s="3" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="P88" s="3"/>
       <c r="Q88" s="3"/>
       <c r="R88" s="3">
-        <v>48</v>
-      </c>
-      <c r="S88" s="3"/>
+        <v>152071</v>
+      </c>
+      <c r="S88" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T88" s="3"/>
       <c r="U88" s="3"/>
       <c r="V88" s="3"/>
@@ -7312,11 +7390,9 @@
       <c r="X88" s="3"/>
       <c r="Y88" s="3"/>
       <c r="Z88" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="AA88" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="AA88" s="3"/>
       <c r="AB88" s="3"/>
     </row>
     <row r="89" spans="1:28">
@@ -7324,7 +7400,7 @@
         <v>87</v>
       </c>
       <c r="B89" s="7">
-        <v>2026060145</v>
+        <v>2026060388</v>
       </c>
       <c r="C89" s="7">
         <v>1</v>
@@ -7333,68 +7409,64 @@
         <v>29</v>
       </c>
       <c r="E89" s="7" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>109</v>
+        <v>31</v>
       </c>
       <c r="G89" s="7" t="s">
-        <v>68</v>
+        <v>32</v>
       </c>
       <c r="H89" s="7" t="s">
-        <v>208</v>
+        <v>77</v>
       </c>
       <c r="I89" s="7" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="J89" s="7" t="s">
-        <v>157</v>
+        <v>80</v>
       </c>
       <c r="K89" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L89" s="8" t="s">
-        <v>211</v>
+        <v>248</v>
       </c>
       <c r="M89" s="8" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="N89" s="8" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="O89" s="7" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P89" s="7"/>
       <c r="Q89" s="7"/>
       <c r="R89" s="7">
-        <v>38244</v>
+        <v>152071</v>
       </c>
       <c r="S89" s="7"/>
       <c r="T89" s="7"/>
-      <c r="U89" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="U89" s="7"/>
       <c r="V89" s="7"/>
       <c r="W89" s="7"/>
       <c r="X89" s="7"/>
       <c r="Y89" s="7"/>
       <c r="Z89" s="8" t="s">
-        <v>214</v>
+        <v>197</v>
       </c>
       <c r="AA89" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AB89" s="7">
-        <v>1</v>
-      </c>
+      <c r="AB89" s="7"/>
     </row>
     <row r="90" spans="1:28">
       <c r="A90" s="3">
         <v>88</v>
       </c>
       <c r="B90" s="3">
-        <v>2026060144</v>
+        <v>2026060570</v>
       </c>
       <c r="C90" s="3">
         <v>1</v>
@@ -7403,34 +7475,34 @@
         <v>29</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>109</v>
+        <v>31</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>110</v>
+        <v>257</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="J90" s="3" t="s">
-        <v>157</v>
+        <v>80</v>
       </c>
       <c r="K90" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L90" s="6" t="s">
-        <v>211</v>
+        <v>248</v>
       </c>
       <c r="M90" s="6" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="O90" s="3" t="s">
         <v>39</v>
@@ -7438,7 +7510,7 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3">
-        <v>386259</v>
+        <v>152071</v>
       </c>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
@@ -7450,7 +7522,7 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="6" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="AA90" s="3" t="s">
         <v>40</v>
@@ -7464,7 +7536,7 @@
         <v>89</v>
       </c>
       <c r="B91" s="7">
-        <v>2026060143</v>
+        <v>2026060081</v>
       </c>
       <c r="C91" s="7">
         <v>1</v>
@@ -7473,34 +7545,34 @@
         <v>29</v>
       </c>
       <c r="E91" s="7" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="F91" s="7" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="G91" s="7" t="s">
-        <v>167</v>
+        <v>257</v>
       </c>
       <c r="H91" s="7" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="I91" s="7" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="J91" s="7" t="s">
-        <v>157</v>
+        <v>279</v>
       </c>
       <c r="K91" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L91" s="8" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="M91" s="8" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="N91" s="8" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="O91" s="7" t="s">
         <v>39</v>
@@ -7508,33 +7580,29 @@
       <c r="P91" s="7"/>
       <c r="Q91" s="7"/>
       <c r="R91" s="7">
-        <v>381383</v>
-      </c>
-      <c r="S91" s="7"/>
+        <v>48</v>
+      </c>
+      <c r="S91" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T91" s="7"/>
-      <c r="U91" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="U91" s="7"/>
       <c r="V91" s="7"/>
       <c r="W91" s="7"/>
       <c r="X91" s="7"/>
       <c r="Y91" s="7"/>
       <c r="Z91" s="8" t="s">
-        <v>214</v>
-      </c>
-      <c r="AA91" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB91" s="7">
-        <v>1</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="AA91" s="7"/>
+      <c r="AB91" s="7"/>
     </row>
     <row r="92" spans="1:28">
       <c r="A92" s="3">
         <v>90</v>
       </c>
       <c r="B92" s="3">
-        <v>2026060142</v>
+        <v>2026060082</v>
       </c>
       <c r="C92" s="3">
         <v>1</v>
@@ -7543,68 +7611,64 @@
         <v>29</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>166</v>
+        <v>257</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>167</v>
+        <v>93</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J92" s="3" t="s">
-        <v>157</v>
+        <v>279</v>
       </c>
       <c r="K92" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L92" s="6" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="M92" s="6" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="O92" s="3" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P92" s="3"/>
       <c r="Q92" s="3"/>
       <c r="R92" s="3">
-        <v>31873</v>
+        <v>48</v>
       </c>
       <c r="S92" s="3"/>
       <c r="T92" s="3"/>
-      <c r="U92" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="U92" s="3"/>
       <c r="V92" s="3"/>
       <c r="W92" s="3"/>
       <c r="X92" s="3"/>
       <c r="Y92" s="3"/>
       <c r="Z92" s="6" t="s">
-        <v>214</v>
+        <v>197</v>
       </c>
       <c r="AA92" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AB92" s="3">
-        <v>1</v>
-      </c>
+      <c r="AB92" s="3"/>
     </row>
     <row r="93" spans="1:28">
       <c r="A93" s="7">
         <v>91</v>
       </c>
       <c r="B93" s="7">
-        <v>2026060141</v>
+        <v>2026060145</v>
       </c>
       <c r="C93" s="7">
         <v>1</v>
@@ -7613,34 +7677,34 @@
         <v>29</v>
       </c>
       <c r="E93" s="7" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="F93" s="7" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="G93" s="7" t="s">
-        <v>279</v>
+        <v>83</v>
       </c>
       <c r="H93" s="7" t="s">
-        <v>166</v>
+        <v>221</v>
       </c>
       <c r="I93" s="7" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J93" s="7" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="K93" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L93" s="8" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="M93" s="8" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="N93" s="8" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="O93" s="7" t="s">
         <v>39</v>
@@ -7648,7 +7712,7 @@
       <c r="P93" s="7"/>
       <c r="Q93" s="7"/>
       <c r="R93" s="7">
-        <v>30842</v>
+        <v>38244</v>
       </c>
       <c r="S93" s="7"/>
       <c r="T93" s="7"/>
@@ -7660,7 +7724,7 @@
       <c r="X93" s="7"/>
       <c r="Y93" s="7"/>
       <c r="Z93" s="8" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="AA93" s="7" t="s">
         <v>40</v>
@@ -7674,7 +7738,7 @@
         <v>92</v>
       </c>
       <c r="B94" s="3">
-        <v>2026060510</v>
+        <v>2026060144</v>
       </c>
       <c r="C94" s="3">
         <v>1</v>
@@ -7683,30 +7747,34 @@
         <v>29</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>282</v>
+        <v>193</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>31</v>
+        <v>124</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>283</v>
+        <v>125</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>284</v>
+        <v>83</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="J94" s="3"/>
-      <c r="K94" s="3"/>
+      <c r="J94" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="L94" s="6" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="M94" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="N94" s="6" t="s">
         <v>286</v>
-      </c>
-      <c r="N94" s="6" t="s">
-        <v>287</v>
       </c>
       <c r="O94" s="3" t="s">
         <v>39</v>
@@ -7714,19 +7782,19 @@
       <c r="P94" s="3"/>
       <c r="Q94" s="3"/>
       <c r="R94" s="3">
-        <v>0</v>
-      </c>
-      <c r="S94" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>386259</v>
+      </c>
+      <c r="S94" s="3"/>
       <c r="T94" s="3"/>
-      <c r="U94" s="3"/>
+      <c r="U94" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="V94" s="3"/>
       <c r="W94" s="3"/>
       <c r="X94" s="3"/>
       <c r="Y94" s="3"/>
       <c r="Z94" s="6" t="s">
-        <v>90</v>
+        <v>227</v>
       </c>
       <c r="AA94" s="3" t="s">
         <v>40</v>
@@ -7740,7 +7808,7 @@
         <v>93</v>
       </c>
       <c r="B95" s="7">
-        <v>2026060850</v>
+        <v>2026060143</v>
       </c>
       <c r="C95" s="7">
         <v>1</v>
@@ -7749,30 +7817,34 @@
         <v>29</v>
       </c>
       <c r="E95" s="7" t="s">
-        <v>282</v>
+        <v>193</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>54</v>
+        <v>124</v>
       </c>
       <c r="G95" s="7" t="s">
-        <v>78</v>
+        <v>180</v>
       </c>
       <c r="H95" s="7" t="s">
-        <v>208</v>
+        <v>125</v>
       </c>
       <c r="I95" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="J95" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="K95" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L95" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="M95" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="N95" s="8" t="s">
         <v>288</v>
-      </c>
-      <c r="J95" s="7"/>
-      <c r="K95" s="7"/>
-      <c r="L95" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="M95" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="N95" s="8" t="s">
-        <v>290</v>
       </c>
       <c r="O95" s="7" t="s">
         <v>39</v>
@@ -7780,11 +7852,9 @@
       <c r="P95" s="7"/>
       <c r="Q95" s="7"/>
       <c r="R95" s="7">
-        <v>0</v>
-      </c>
-      <c r="S95" s="7" t="s">
-        <v>40</v>
-      </c>
+        <v>381383</v>
+      </c>
+      <c r="S95" s="7"/>
       <c r="T95" s="7"/>
       <c r="U95" s="7" t="s">
         <v>40</v>
@@ -7794,7 +7864,7 @@
       <c r="X95" s="7"/>
       <c r="Y95" s="7"/>
       <c r="Z95" s="8" t="s">
-        <v>291</v>
+        <v>227</v>
       </c>
       <c r="AA95" s="7" t="s">
         <v>40</v>
@@ -7808,7 +7878,7 @@
         <v>94</v>
       </c>
       <c r="B96" s="3">
-        <v>2026060475</v>
+        <v>2026060142</v>
       </c>
       <c r="C96" s="3">
         <v>1</v>
@@ -7817,30 +7887,34 @@
         <v>29</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>282</v>
+        <v>193</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>31</v>
+        <v>124</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>78</v>
+        <v>179</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>292</v>
+        <v>180</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="J96" s="3"/>
-      <c r="K96" s="3"/>
+        <v>289</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="K96" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="L96" s="6" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="M96" s="6" t="s">
-        <v>294</v>
+        <v>280</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="O96" s="3" t="s">
         <v>39</v>
@@ -7848,19 +7922,19 @@
       <c r="P96" s="3"/>
       <c r="Q96" s="3"/>
       <c r="R96" s="3">
-        <v>0</v>
-      </c>
-      <c r="S96" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>31873</v>
+      </c>
+      <c r="S96" s="3"/>
       <c r="T96" s="3"/>
-      <c r="U96" s="3"/>
+      <c r="U96" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="V96" s="3"/>
       <c r="W96" s="3"/>
       <c r="X96" s="3"/>
       <c r="Y96" s="3"/>
       <c r="Z96" s="6" t="s">
-        <v>90</v>
+        <v>227</v>
       </c>
       <c r="AA96" s="3" t="s">
         <v>40</v>
@@ -7874,7 +7948,7 @@
         <v>95</v>
       </c>
       <c r="B97" s="7">
-        <v>2026060149</v>
+        <v>2026060141</v>
       </c>
       <c r="C97" s="7">
         <v>1</v>
@@ -7883,90 +7957,632 @@
         <v>29</v>
       </c>
       <c r="E97" s="7" t="s">
-        <v>282</v>
+        <v>193</v>
       </c>
       <c r="F97" s="7" t="s">
-        <v>31</v>
+        <v>124</v>
       </c>
       <c r="G97" s="7" t="s">
-        <v>78</v>
+        <v>291</v>
       </c>
       <c r="H97" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="I97" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="I97" s="7" t="s">
+      <c r="J97" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="K97" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L97" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="M97" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="N97" s="8" t="s">
         <v>293</v>
       </c>
-      <c r="J97" s="7" t="s">
-        <v>296</v>
-      </c>
-      <c r="K97" s="7" t="s">
-        <v>297</v>
-      </c>
-      <c r="L97" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="M97" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="N97" s="8" t="s">
-        <v>295</v>
-      </c>
       <c r="O97" s="7" t="s">
-        <v>298</v>
+        <v>39</v>
       </c>
       <c r="P97" s="7"/>
       <c r="Q97" s="7"/>
       <c r="R97" s="7">
-        <v>0</v>
+        <v>30842</v>
       </c>
       <c r="S97" s="7"/>
       <c r="T97" s="7"/>
-      <c r="U97" s="7"/>
+      <c r="U97" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="V97" s="7"/>
       <c r="W97" s="7"/>
       <c r="X97" s="7"/>
       <c r="Y97" s="7"/>
       <c r="Z97" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="AA97" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB97" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:28">
+      <c r="A98" s="3">
+        <v>96</v>
+      </c>
+      <c r="B98" s="3">
+        <v>2026060898</v>
+      </c>
+      <c r="C98" s="3">
+        <v>1</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="F98" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G98" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H98" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="I98" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="J98" s="3"/>
+      <c r="K98" s="3"/>
+      <c r="L98" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="M98" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="N98" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="O98" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P98" s="3"/>
+      <c r="Q98" s="3"/>
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="T98" s="3"/>
+      <c r="U98" s="3"/>
+      <c r="V98" s="3"/>
+      <c r="W98" s="3"/>
+      <c r="X98" s="3"/>
+      <c r="Y98" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z98" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="AA98" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB98" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:28">
+      <c r="A99" s="7">
+        <v>97</v>
+      </c>
+      <c r="B99" s="7">
+        <v>2026060899</v>
+      </c>
+      <c r="C99" s="7">
+        <v>1</v>
+      </c>
+      <c r="D99" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E99" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="F99" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="G99" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="H99" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="I99" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="J99" s="7"/>
+      <c r="K99" s="7"/>
+      <c r="L99" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="M99" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="N99" s="8" t="s">
         <v>299</v>
       </c>
-      <c r="AA97" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB97" s="7"/>
-    </row>
-    <row r="98" spans="1:28">
-      <c r="A98" s="9"/>
-      <c r="B98" s="9"/>
-      <c r="C98" s="9"/>
-      <c r="D98" s="9"/>
-      <c r="E98" s="9"/>
-      <c r="F98" s="9"/>
-      <c r="G98" s="9"/>
-      <c r="H98" s="9"/>
-      <c r="I98" s="9"/>
-      <c r="J98" s="9"/>
-      <c r="K98" s="9"/>
-      <c r="L98" s="10"/>
-      <c r="M98" s="10"/>
-      <c r="N98" s="10"/>
-      <c r="O98" s="9"/>
-      <c r="P98" s="9"/>
-      <c r="Q98" s="9"/>
-      <c r="R98" s="9"/>
-      <c r="S98" s="9"/>
-      <c r="T98" s="9"/>
-      <c r="U98" s="9"/>
-      <c r="V98" s="9"/>
-      <c r="W98" s="9"/>
-      <c r="X98" s="9"/>
-      <c r="Y98" s="9"/>
-      <c r="Z98" s="10"/>
-      <c r="AA98" s="9" t="s">
+      <c r="O99" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P99" s="7"/>
+      <c r="Q99" s="7"/>
+      <c r="R99" s="7">
+        <v>0</v>
+      </c>
+      <c r="S99" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="T99" s="7"/>
+      <c r="U99" s="7"/>
+      <c r="V99" s="7"/>
+      <c r="W99" s="7"/>
+      <c r="X99" s="7"/>
+      <c r="Y99" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z99" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="AA99" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB99" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:28">
+      <c r="A100" s="3">
+        <v>98</v>
+      </c>
+      <c r="B100" s="3">
+        <v>2026060905</v>
+      </c>
+      <c r="C100" s="3">
+        <v>1</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="I100" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="AB98" s="9">
-        <v>49</v>
+      <c r="J100" s="3"/>
+      <c r="K100" s="3"/>
+      <c r="L100" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="M100" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="N100" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="O100" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P100" s="3"/>
+      <c r="Q100" s="3"/>
+      <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="T100" s="3"/>
+      <c r="U100" s="3"/>
+      <c r="V100" s="3"/>
+      <c r="W100" s="3"/>
+      <c r="X100" s="3"/>
+      <c r="Y100" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z100" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="AA100" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB100" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:28">
+      <c r="A101" s="7">
+        <v>99</v>
+      </c>
+      <c r="B101" s="7">
+        <v>2026060510</v>
+      </c>
+      <c r="C101" s="7">
+        <v>1</v>
+      </c>
+      <c r="D101" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E101" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="F101" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G101" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="H101" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="I101" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="J101" s="7"/>
+      <c r="K101" s="7"/>
+      <c r="L101" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="M101" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="N101" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="O101" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P101" s="7"/>
+      <c r="Q101" s="7"/>
+      <c r="R101" s="7">
+        <v>0</v>
+      </c>
+      <c r="S101" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="T101" s="7"/>
+      <c r="U101" s="7"/>
+      <c r="V101" s="7"/>
+      <c r="W101" s="7"/>
+      <c r="X101" s="7"/>
+      <c r="Y101" s="7"/>
+      <c r="Z101" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="AA101" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB101" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:28">
+      <c r="A102" s="3">
+        <v>100</v>
+      </c>
+      <c r="B102" s="3">
+        <v>2026060850</v>
+      </c>
+      <c r="C102" s="3">
+        <v>1</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="J102" s="3"/>
+      <c r="K102" s="3"/>
+      <c r="L102" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="M102" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="N102" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="O102" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
+      <c r="R102" s="3">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="T102" s="3"/>
+      <c r="U102" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V102" s="3"/>
+      <c r="W102" s="3"/>
+      <c r="X102" s="3"/>
+      <c r="Y102" s="3"/>
+      <c r="Z102" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="AA102" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB102" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:28">
+      <c r="A103" s="7">
+        <v>101</v>
+      </c>
+      <c r="B103" s="7">
+        <v>2026060831</v>
+      </c>
+      <c r="C103" s="7">
+        <v>1</v>
+      </c>
+      <c r="D103" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E103" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="F103" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="G103" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="H103" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="I103" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="J103" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="K103" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="L103" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="M103" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="N103" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="O103" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="P103" s="7"/>
+      <c r="Q103" s="7"/>
+      <c r="R103" s="7">
+        <v>0</v>
+      </c>
+      <c r="S103" s="7"/>
+      <c r="T103" s="7"/>
+      <c r="U103" s="7"/>
+      <c r="V103" s="7"/>
+      <c r="W103" s="7"/>
+      <c r="X103" s="7"/>
+      <c r="Y103" s="7"/>
+      <c r="Z103" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="AA103" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB103" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:28">
+      <c r="A104" s="3">
+        <v>102</v>
+      </c>
+      <c r="B104" s="3">
+        <v>2026060475</v>
+      </c>
+      <c r="C104" s="3">
+        <v>1</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="F104" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G104" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="H104" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="I104" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="J104" s="3"/>
+      <c r="K104" s="3"/>
+      <c r="L104" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="M104" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="N104" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="O104" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P104" s="3"/>
+      <c r="Q104" s="3"/>
+      <c r="R104" s="3">
+        <v>0</v>
+      </c>
+      <c r="S104" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="T104" s="3"/>
+      <c r="U104" s="3"/>
+      <c r="V104" s="3"/>
+      <c r="W104" s="3"/>
+      <c r="X104" s="3"/>
+      <c r="Y104" s="3"/>
+      <c r="Z104" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="AA104" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB104" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:28">
+      <c r="A105" s="7">
+        <v>103</v>
+      </c>
+      <c r="B105" s="7">
+        <v>2026060149</v>
+      </c>
+      <c r="C105" s="7">
+        <v>1</v>
+      </c>
+      <c r="D105" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E105" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="F105" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G105" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="H105" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="I105" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="J105" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="K105" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="L105" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="M105" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="N105" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="O105" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="P105" s="7"/>
+      <c r="Q105" s="7"/>
+      <c r="R105" s="7">
+        <v>0</v>
+      </c>
+      <c r="S105" s="7"/>
+      <c r="T105" s="7"/>
+      <c r="U105" s="7"/>
+      <c r="V105" s="7"/>
+      <c r="W105" s="7"/>
+      <c r="X105" s="7"/>
+      <c r="Y105" s="7"/>
+      <c r="Z105" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="AA105" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB105" s="7"/>
+    </row>
+    <row r="106" spans="1:28">
+      <c r="A106" s="9"/>
+      <c r="B106" s="9"/>
+      <c r="C106" s="9"/>
+      <c r="D106" s="9"/>
+      <c r="E106" s="9"/>
+      <c r="F106" s="9"/>
+      <c r="G106" s="9"/>
+      <c r="H106" s="9"/>
+      <c r="I106" s="9"/>
+      <c r="J106" s="9"/>
+      <c r="K106" s="9"/>
+      <c r="L106" s="10"/>
+      <c r="M106" s="10"/>
+      <c r="N106" s="10"/>
+      <c r="O106" s="9"/>
+      <c r="P106" s="9"/>
+      <c r="Q106" s="9"/>
+      <c r="R106" s="9"/>
+      <c r="S106" s="9"/>
+      <c r="T106" s="9"/>
+      <c r="U106" s="9"/>
+      <c r="V106" s="9"/>
+      <c r="W106" s="9"/>
+      <c r="X106" s="9"/>
+      <c r="Y106" s="9"/>
+      <c r="Z106" s="10"/>
+      <c r="AA106" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="AB106" s="9">
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/IM/202606_Service_Count_Report.xlsx
+++ b/IM/202606_Service_Count_Report.xlsx
@@ -11,14 +11,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Report'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$AA$106</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$AA$116</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="349">
   <si>
     <t>服務次數統計表        篩選月份：202606</t>
   </si>
@@ -224,6 +224,21 @@
     <t>10:33:00</t>
   </si>
   <si>
+    <t>16:33:00</t>
+  </si>
+  <si>
+    <t>16:58:00</t>
+  </si>
+  <si>
+    <t>T301800124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">寶璽印刷有限公司 </t>
+  </si>
+  <si>
+    <t>新北市中和區新民街112號5樓-7</t>
+  </si>
+  <si>
     <t>2026-06-03</t>
   </si>
   <si>
@@ -311,16 +326,43 @@
     <t>Pm 清定著積碳</t>
   </si>
   <si>
+    <t>16:15:00</t>
+  </si>
+  <si>
+    <t>16:35:00</t>
+  </si>
+  <si>
+    <t>T501500010</t>
+  </si>
+  <si>
+    <t>eS-5015AC 彩色複合機</t>
+  </si>
+  <si>
     <t>14:00:00</t>
   </si>
   <si>
+    <t>16:10:00</t>
+  </si>
+  <si>
+    <t>THILF02062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">萊爾富國際股份有限公司 </t>
+  </si>
+  <si>
+    <t>新北市中和區員山路502-7號</t>
+  </si>
+  <si>
+    <t>中和員山店</t>
+  </si>
+  <si>
+    <t>PMQ2 EDC SC7</t>
+  </si>
+  <si>
     <t>15:15:00</t>
   </si>
   <si>
     <t>THILF02442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">萊爾富國際股份有限公司 </t>
   </si>
   <si>
     <t>新北市八里區商港路46.48號</t>
@@ -670,6 +712,24 @@
     <t>異地備援泰山</t>
   </si>
   <si>
+    <t>T301800171</t>
+  </si>
+  <si>
+    <t>新北市新莊區中正區336-1號(新莊)</t>
+  </si>
+  <si>
+    <t>新莊</t>
+  </si>
+  <si>
+    <t>T301800174</t>
+  </si>
+  <si>
+    <t>新北市板橋區中山路1段10號5樓(板橋分校)</t>
+  </si>
+  <si>
+    <t>板橋</t>
+  </si>
+  <si>
     <t>08:30:00</t>
   </si>
   <si>
@@ -697,9 +757,6 @@
     <t>4F</t>
   </si>
   <si>
-    <t>16:10:00</t>
-  </si>
-  <si>
     <t>16:30:00</t>
   </si>
   <si>
@@ -727,6 +784,15 @@
     <t>業務部辦公室</t>
   </si>
   <si>
+    <t>14:30:00</t>
+  </si>
+  <si>
+    <t>T302800123</t>
+  </si>
+  <si>
+    <t>新北市三重區正義北路218號(三重分校)</t>
+  </si>
+  <si>
     <t>T302800152</t>
   </si>
   <si>
@@ -907,9 +973,6 @@
     <t>台北客服4樓後1LJ10(黑)</t>
   </si>
   <si>
-    <t>14:30:00</t>
-  </si>
-  <si>
     <t>T452800071</t>
   </si>
   <si>
@@ -934,6 +997,26 @@
     <t>五股四維店</t>
   </si>
   <si>
+    <t>THILF04144</t>
+  </si>
+  <si>
+    <t>一般件</t>
+  </si>
+  <si>
+    <t>其他</t>
+  </si>
+  <si>
+    <t>新北市新莊區化成路414號及416號一樓全部</t>
+  </si>
+  <si>
+    <t>新莊頭前店</t>
+  </si>
+  <si>
+    <t>更換手持
+換上8119011009
+換下8119009801</t>
+  </si>
+  <si>
     <t>THILF05003</t>
   </si>
   <si>
@@ -970,16 +1053,7 @@
     <t>板橋稚暉店</t>
   </si>
   <si>
-    <t>PMQ2 EDC SC7</t>
-  </si>
-  <si>
     <t>THILF04680</t>
-  </si>
-  <si>
-    <t>一般件</t>
-  </si>
-  <si>
-    <t>其他</t>
   </si>
   <si>
     <t>新北市板橋區江寧路三段49、51號一樓</t>
@@ -1420,7 +1494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AB106"/>
+  <dimension ref="A1:AB116"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="true" style="0"/>
@@ -1914,7 +1988,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="3">
-        <v>2026060623</v>
+        <v>2026061027</v>
       </c>
       <c r="C8" s="3">
         <v>1</v>
@@ -1926,39 +2000,37 @@
         <v>30</v>
       </c>
       <c r="F8" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="H8" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="I8" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="J8" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L8" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="M8" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="L8" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="M8" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="N8" s="6" t="s">
-        <v>71</v>
-      </c>
+      <c r="N8" s="6"/>
       <c r="O8" s="3" t="s">
         <v>48</v>
       </c>
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
       <c r="R8" s="3">
-        <v>83977</v>
+        <v>51947</v>
       </c>
       <c r="S8" s="3"/>
       <c r="T8" s="3"/>
@@ -1980,7 +2052,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="7">
-        <v>2026060916</v>
+        <v>2026060623</v>
       </c>
       <c r="C9" s="7">
         <v>1</v>
@@ -1992,25 +2064,25 @@
         <v>30</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="G9" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="I9" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="J9" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="I9" s="7" t="s">
+      <c r="K9" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L9" s="8" t="s">
         <v>74</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="K9" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>58</v>
       </c>
       <c r="M9" s="8" t="s">
         <v>75</v>
@@ -2024,7 +2096,7 @@
       <c r="P9" s="7"/>
       <c r="Q9" s="7"/>
       <c r="R9" s="7">
-        <v>37172</v>
+        <v>83977</v>
       </c>
       <c r="S9" s="7"/>
       <c r="T9" s="7"/>
@@ -2046,7 +2118,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="3">
-        <v>2026060404</v>
+        <v>2026060916</v>
       </c>
       <c r="C10" s="3">
         <v>1</v>
@@ -2058,7 +2130,7 @@
         <v>30</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>77</v>
@@ -2070,25 +2142,27 @@
         <v>79</v>
       </c>
       <c r="J10" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="M10" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="L10" s="6" t="s">
+      <c r="N10" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="M10" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="N10" s="6"/>
       <c r="O10" s="3" t="s">
         <v>48</v>
       </c>
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
       <c r="R10" s="3">
-        <v>142473</v>
+        <v>37172</v>
       </c>
       <c r="S10" s="3"/>
       <c r="T10" s="3"/>
@@ -2110,7 +2184,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="7">
-        <v>2026060855</v>
+        <v>2026060404</v>
       </c>
       <c r="C11" s="7">
         <v>1</v>
@@ -2122,50 +2196,46 @@
         <v>30</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="G11" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="H11" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="H11" s="7" t="s">
+      <c r="I11" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="I11" s="7" t="s">
-        <v>79</v>
-      </c>
       <c r="J11" s="7" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="K11" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="M11" s="8" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="N11" s="8"/>
       <c r="O11" s="7" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P11" s="7"/>
       <c r="Q11" s="7"/>
       <c r="R11" s="7">
-        <v>142511</v>
-      </c>
-      <c r="S11" s="7" t="s">
-        <v>40</v>
-      </c>
+        <v>142473</v>
+      </c>
+      <c r="S11" s="7"/>
       <c r="T11" s="7"/>
       <c r="U11" s="7"/>
       <c r="V11" s="7"/>
       <c r="W11" s="7"/>
       <c r="X11" s="7"/>
       <c r="Y11" s="7"/>
-      <c r="Z11" s="8" t="s">
-        <v>41</v>
-      </c>
+      <c r="Z11" s="8"/>
       <c r="AA11" s="7" t="s">
         <v>40</v>
       </c>
@@ -2178,7 +2248,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="3">
-        <v>2026060391</v>
+        <v>2026060855</v>
       </c>
       <c r="C12" s="3">
         <v>1</v>
@@ -2190,46 +2260,50 @@
         <v>30</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="G12" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="J12" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="H12" s="3" t="s">
+      <c r="K12" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L12" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="I12" s="3" t="s">
+      <c r="M12" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="L12" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="M12" s="6" t="s">
-        <v>89</v>
       </c>
       <c r="N12" s="6"/>
       <c r="O12" s="3" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
       <c r="R12" s="3">
-        <v>255338</v>
-      </c>
-      <c r="S12" s="3"/>
+        <v>142511</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T12" s="3"/>
       <c r="U12" s="3"/>
       <c r="V12" s="3"/>
       <c r="W12" s="3"/>
       <c r="X12" s="3"/>
       <c r="Y12" s="3"/>
-      <c r="Z12" s="6"/>
+      <c r="Z12" s="6" t="s">
+        <v>41</v>
+      </c>
       <c r="AA12" s="3" t="s">
         <v>40</v>
       </c>
@@ -2242,7 +2316,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="7">
-        <v>2026060865</v>
+        <v>2026060391</v>
       </c>
       <c r="C13" s="7">
         <v>1</v>
@@ -2254,7 +2328,7 @@
         <v>30</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="G13" s="7" t="s">
         <v>90</v>
@@ -2263,41 +2337,37 @@
         <v>91</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="K13" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="M13" s="8" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="N13" s="8"/>
       <c r="O13" s="7" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P13" s="7"/>
       <c r="Q13" s="7"/>
       <c r="R13" s="7">
-        <v>255417</v>
-      </c>
-      <c r="S13" s="7" t="s">
-        <v>40</v>
-      </c>
+        <v>255338</v>
+      </c>
+      <c r="S13" s="7"/>
       <c r="T13" s="7"/>
       <c r="U13" s="7"/>
       <c r="V13" s="7"/>
       <c r="W13" s="7"/>
       <c r="X13" s="7"/>
       <c r="Y13" s="7"/>
-      <c r="Z13" s="8" t="s">
-        <v>92</v>
-      </c>
+      <c r="Z13" s="8"/>
       <c r="AA13" s="7" t="s">
         <v>40</v>
       </c>
@@ -2310,7 +2380,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="3">
-        <v>2026060464</v>
+        <v>2026060865</v>
       </c>
       <c r="C14" s="3">
         <v>1</v>
@@ -2322,47 +2392,49 @@
         <v>30</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="G14" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L14" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="M14" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="M14" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="N14" s="6" t="s">
-        <v>98</v>
-      </c>
+      <c r="N14" s="6"/>
       <c r="O14" s="3" t="s">
         <v>39</v>
       </c>
       <c r="P14" s="3"/>
       <c r="Q14" s="3"/>
       <c r="R14" s="3">
-        <v>0</v>
-      </c>
-      <c r="S14" s="3"/>
+        <v>255417</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T14" s="3"/>
-      <c r="U14" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="U14" s="3"/>
       <c r="V14" s="3"/>
       <c r="W14" s="3"/>
       <c r="X14" s="3"/>
       <c r="Y14" s="3"/>
       <c r="Z14" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>40</v>
@@ -2376,7 +2448,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="7">
-        <v>2026060669</v>
+        <v>2026061028</v>
       </c>
       <c r="C15" s="7">
         <v>1</v>
@@ -2388,50 +2460,48 @@
         <v>30</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G15" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="I15" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="H15" s="7" t="s">
+      <c r="J15" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="I15" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
+      <c r="K15" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="L15" s="8" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="M15" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="N15" s="8" t="s">
-        <v>104</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="N15" s="8"/>
       <c r="O15" s="7" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P15" s="7"/>
-      <c r="Q15" s="7"/>
+      <c r="Q15" s="7">
+        <v>28808</v>
+      </c>
       <c r="R15" s="7">
-        <v>0</v>
-      </c>
-      <c r="S15" s="7" t="s">
-        <v>40</v>
-      </c>
+        <v>752353</v>
+      </c>
+      <c r="S15" s="7"/>
       <c r="T15" s="7"/>
       <c r="U15" s="7"/>
       <c r="V15" s="7"/>
       <c r="W15" s="7"/>
       <c r="X15" s="7"/>
-      <c r="Y15" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="Z15" s="8" t="s">
-        <v>105</v>
-      </c>
+      <c r="Y15" s="7"/>
+      <c r="Z15" s="8"/>
       <c r="AA15" s="7" t="s">
         <v>40</v>
       </c>
@@ -2444,7 +2514,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="3">
-        <v>2026060656</v>
+        <v>2026061018</v>
       </c>
       <c r="C16" s="3">
         <v>1</v>
@@ -2456,27 +2526,27 @@
         <v>30</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="6" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="O16" s="3" t="s">
         <v>39</v>
@@ -2498,7 +2568,7 @@
         <v>40</v>
       </c>
       <c r="Z16" s="6" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="AA16" s="3" t="s">
         <v>40</v>
@@ -2512,7 +2582,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="7">
-        <v>2026060403</v>
+        <v>2026060464</v>
       </c>
       <c r="C17" s="7">
         <v>1</v>
@@ -2524,27 +2594,27 @@
         <v>30</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>111</v>
+        <v>31</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="J17" s="7"/>
       <c r="K17" s="7"/>
       <c r="L17" s="8" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="M17" s="8" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="N17" s="8" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="O17" s="7" t="s">
         <v>39</v>
@@ -2554,19 +2624,17 @@
       <c r="R17" s="7">
         <v>0</v>
       </c>
-      <c r="S17" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="S17" s="7"/>
       <c r="T17" s="7"/>
-      <c r="U17" s="7"/>
+      <c r="U17" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="V17" s="7"/>
       <c r="W17" s="7"/>
       <c r="X17" s="7"/>
-      <c r="Y17" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="Y17" s="7"/>
       <c r="Z17" s="8" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="AA17" s="7" t="s">
         <v>40</v>
@@ -2580,7 +2648,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="3">
-        <v>2026060673</v>
+        <v>2026060669</v>
       </c>
       <c r="C18" s="3">
         <v>1</v>
@@ -2589,46 +2657,38 @@
         <v>29</v>
       </c>
       <c r="E18" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="F18" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="G18" s="3" t="s">
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
+      <c r="L18" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="M18" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="H18" s="3" t="s">
+      <c r="N18" s="6" t="s">
         <v>118</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="L18" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="M18" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="N18" s="6" t="s">
-        <v>122</v>
       </c>
       <c r="O18" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="P18" s="3">
-        <v>7927</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>17354</v>
-      </c>
+      <c r="P18" s="3"/>
+      <c r="Q18" s="3"/>
       <c r="R18" s="3">
-        <v>25584</v>
+        <v>0</v>
       </c>
       <c r="S18" s="3" t="s">
         <v>40</v>
@@ -2638,9 +2698,11 @@
       <c r="V18" s="3"/>
       <c r="W18" s="3"/>
       <c r="X18" s="3"/>
-      <c r="Y18" s="3"/>
+      <c r="Y18" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="Z18" s="6" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="AA18" s="3" t="s">
         <v>40</v>
@@ -2654,7 +2716,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="7">
-        <v>2026060674</v>
+        <v>2026060656</v>
       </c>
       <c r="C19" s="7">
         <v>1</v>
@@ -2663,68 +2725,66 @@
         <v>29</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>116</v>
+        <v>30</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="J19" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="K19" s="7" t="s">
-        <v>36</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="J19" s="7"/>
+      <c r="K19" s="7"/>
       <c r="L19" s="8" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="M19" s="8" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="N19" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="O19" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="P19" s="7">
-        <v>7927</v>
-      </c>
-      <c r="Q19" s="7">
-        <v>17354</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="P19" s="7"/>
+      <c r="Q19" s="7"/>
       <c r="R19" s="7">
-        <v>25584</v>
-      </c>
-      <c r="S19" s="7"/>
+        <v>0</v>
+      </c>
+      <c r="S19" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T19" s="7"/>
       <c r="U19" s="7"/>
       <c r="V19" s="7"/>
       <c r="W19" s="7"/>
       <c r="X19" s="7"/>
-      <c r="Y19" s="7"/>
+      <c r="Y19" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="Z19" s="8" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="AA19" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AB19" s="7"/>
+      <c r="AB19" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="20" spans="1:28">
       <c r="A20" s="3">
         <v>18</v>
       </c>
       <c r="B20" s="3">
-        <v>2026060126</v>
+        <v>2026060403</v>
       </c>
       <c r="C20" s="3">
         <v>1</v>
@@ -2733,28 +2793,24 @@
         <v>29</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>116</v>
+        <v>30</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>125</v>
+        <v>91</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>36</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3"/>
       <c r="L20" s="6" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="M20" s="6" t="s">
         <v>128</v>
@@ -2763,34 +2819,40 @@
         <v>129</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="P20" s="3"/>
-      <c r="Q20" s="3">
-        <v>2375</v>
-      </c>
+      <c r="Q20" s="3"/>
       <c r="R20" s="3">
-        <v>129731</v>
-      </c>
-      <c r="S20" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T20" s="3"/>
       <c r="U20" s="3"/>
       <c r="V20" s="3"/>
       <c r="W20" s="3"/>
       <c r="X20" s="3"/>
-      <c r="Y20" s="3"/>
+      <c r="Y20" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="Z20" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="AA20" s="3"/>
-      <c r="AB20" s="3"/>
+        <v>119</v>
+      </c>
+      <c r="AA20" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB20" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="21" spans="1:28">
       <c r="A21" s="7">
         <v>19</v>
       </c>
       <c r="B21" s="7">
-        <v>2026060125</v>
+        <v>2026060674</v>
       </c>
       <c r="C21" s="7">
         <v>1</v>
@@ -2799,19 +2861,19 @@
         <v>29</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>124</v>
+        <v>69</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>94</v>
+        <v>131</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="J21" s="7" t="s">
         <v>35</v>
@@ -2820,27 +2882,27 @@
         <v>36</v>
       </c>
       <c r="L21" s="8" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="M21" s="8" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="N21" s="8" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="O21" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="P21" s="7"/>
+        <v>48</v>
+      </c>
+      <c r="P21" s="7">
+        <v>7927</v>
+      </c>
       <c r="Q21" s="7">
-        <v>2375</v>
+        <v>17354</v>
       </c>
       <c r="R21" s="7">
-        <v>129731</v>
-      </c>
-      <c r="S21" s="7" t="s">
-        <v>40</v>
-      </c>
+        <v>25584</v>
+      </c>
+      <c r="S21" s="7"/>
       <c r="T21" s="7"/>
       <c r="U21" s="7"/>
       <c r="V21" s="7"/>
@@ -2848,17 +2910,21 @@
       <c r="X21" s="7"/>
       <c r="Y21" s="7"/>
       <c r="Z21" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="AA21" s="7"/>
-      <c r="AB21" s="7"/>
+        <v>137</v>
+      </c>
+      <c r="AA21" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB21" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="22" spans="1:28">
       <c r="A22" s="3">
         <v>20</v>
       </c>
       <c r="B22" s="3">
-        <v>2026060762</v>
+        <v>2026060673</v>
       </c>
       <c r="C22" s="3">
         <v>1</v>
@@ -2867,19 +2933,19 @@
         <v>29</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>35</v>
@@ -2888,21 +2954,25 @@
         <v>36</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="N22" s="6"/>
+        <v>135</v>
+      </c>
+      <c r="N22" s="6" t="s">
+        <v>136</v>
+      </c>
       <c r="O22" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="P22" s="3"/>
+      <c r="P22" s="3">
+        <v>7927</v>
+      </c>
       <c r="Q22" s="3">
-        <v>555</v>
+        <v>17354</v>
       </c>
       <c r="R22" s="3">
-        <v>21603</v>
+        <v>25584</v>
       </c>
       <c r="S22" s="3" t="s">
         <v>40</v>
@@ -2914,21 +2984,19 @@
       <c r="X22" s="3"/>
       <c r="Y22" s="3"/>
       <c r="Z22" s="6" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="AA22" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AB22" s="3">
-        <v>1</v>
-      </c>
+      <c r="AB22" s="3"/>
     </row>
     <row r="23" spans="1:28">
       <c r="A23" s="7">
         <v>21</v>
       </c>
       <c r="B23" s="7">
-        <v>2026060763</v>
+        <v>2026060125</v>
       </c>
       <c r="C23" s="7">
         <v>1</v>
@@ -2937,19 +3005,19 @@
         <v>29</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>64</v>
+        <v>138</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>130</v>
+        <v>109</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="J23" s="7" t="s">
         <v>35</v>
@@ -2958,23 +3026,27 @@
         <v>36</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="M23" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="N23" s="8"/>
+        <v>142</v>
+      </c>
+      <c r="N23" s="8" t="s">
+        <v>143</v>
+      </c>
       <c r="O23" s="7" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="P23" s="7"/>
       <c r="Q23" s="7">
-        <v>555</v>
+        <v>2375</v>
       </c>
       <c r="R23" s="7">
-        <v>21603</v>
-      </c>
-      <c r="S23" s="7"/>
+        <v>129731</v>
+      </c>
+      <c r="S23" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T23" s="7"/>
       <c r="U23" s="7"/>
       <c r="V23" s="7"/>
@@ -2982,11 +3054,9 @@
       <c r="X23" s="7"/>
       <c r="Y23" s="7"/>
       <c r="Z23" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="AA23" s="7" t="s">
-        <v>40</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="AA23" s="7"/>
       <c r="AB23" s="7"/>
     </row>
     <row r="24" spans="1:28">
@@ -2994,7 +3064,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="3">
-        <v>2026060107</v>
+        <v>2026060126</v>
       </c>
       <c r="C24" s="3">
         <v>1</v>
@@ -3003,46 +3073,46 @@
         <v>29</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>135</v>
+        <v>109</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="M24" s="6" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="O24" s="3" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P24" s="3"/>
-      <c r="Q24" s="3"/>
+      <c r="Q24" s="3">
+        <v>2375</v>
+      </c>
       <c r="R24" s="3">
-        <v>313246</v>
-      </c>
-      <c r="S24" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>129731</v>
+      </c>
+      <c r="S24" s="3"/>
       <c r="T24" s="3"/>
       <c r="U24" s="3"/>
       <c r="V24" s="3"/>
@@ -3050,7 +3120,7 @@
       <c r="X24" s="3"/>
       <c r="Y24" s="3"/>
       <c r="Z24" s="6" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="AA24" s="3"/>
       <c r="AB24" s="3"/>
@@ -3060,7 +3130,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="7">
-        <v>2026060108</v>
+        <v>2026060762</v>
       </c>
       <c r="C25" s="7">
         <v>1</v>
@@ -3069,44 +3139,46 @@
         <v>29</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>124</v>
+        <v>69</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="K25" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L25" s="8" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="M25" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="N25" s="8" t="s">
-        <v>140</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="N25" s="8"/>
       <c r="O25" s="7" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="P25" s="7"/>
-      <c r="Q25" s="7"/>
+      <c r="Q25" s="7">
+        <v>555</v>
+      </c>
       <c r="R25" s="7">
-        <v>313246</v>
-      </c>
-      <c r="S25" s="7"/>
+        <v>21603</v>
+      </c>
+      <c r="S25" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T25" s="7"/>
       <c r="U25" s="7"/>
       <c r="V25" s="7"/>
@@ -3114,17 +3186,21 @@
       <c r="X25" s="7"/>
       <c r="Y25" s="7"/>
       <c r="Z25" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="AA25" s="7"/>
-      <c r="AB25" s="7"/>
+        <v>137</v>
+      </c>
+      <c r="AA25" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB25" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="26" spans="1:28">
       <c r="A26" s="3">
         <v>24</v>
       </c>
       <c r="B26" s="3">
-        <v>2026060415</v>
+        <v>2026060763</v>
       </c>
       <c r="C26" s="3">
         <v>1</v>
@@ -3133,46 +3209,44 @@
         <v>29</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="M26" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="N26" s="6" t="s">
-        <v>146</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="N26" s="6"/>
       <c r="O26" s="3" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P26" s="3"/>
-      <c r="Q26" s="3"/>
+      <c r="Q26" s="3">
+        <v>555</v>
+      </c>
       <c r="R26" s="3">
-        <v>29215</v>
-      </c>
-      <c r="S26" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>21603</v>
+      </c>
+      <c r="S26" s="3"/>
       <c r="T26" s="3"/>
       <c r="U26" s="3"/>
       <c r="V26" s="3"/>
@@ -3180,21 +3254,19 @@
       <c r="X26" s="3"/>
       <c r="Y26" s="3"/>
       <c r="Z26" s="6" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="AA26" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AB26" s="3">
-        <v>1</v>
-      </c>
+      <c r="AB26" s="3"/>
     </row>
     <row r="27" spans="1:28">
       <c r="A27" s="7">
         <v>25</v>
       </c>
       <c r="B27" s="7">
-        <v>2026060416</v>
+        <v>2026060107</v>
       </c>
       <c r="C27" s="7">
         <v>1</v>
@@ -3203,19 +3275,19 @@
         <v>29</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>31</v>
+        <v>138</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="J27" s="7" t="s">
         <v>57</v>
@@ -3224,23 +3296,25 @@
         <v>36</v>
       </c>
       <c r="L27" s="8" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="M27" s="8" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="N27" s="8" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="O27" s="7" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="P27" s="7"/>
       <c r="Q27" s="7"/>
       <c r="R27" s="7">
-        <v>29215</v>
-      </c>
-      <c r="S27" s="7"/>
+        <v>313246</v>
+      </c>
+      <c r="S27" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T27" s="7"/>
       <c r="U27" s="7"/>
       <c r="V27" s="7"/>
@@ -3248,11 +3322,9 @@
       <c r="X27" s="7"/>
       <c r="Y27" s="7"/>
       <c r="Z27" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="AA27" s="7" t="s">
-        <v>40</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="AA27" s="7"/>
       <c r="AB27" s="7"/>
     </row>
     <row r="28" spans="1:28">
@@ -3260,7 +3332,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="3">
-        <v>2026060378</v>
+        <v>2026060108</v>
       </c>
       <c r="C28" s="3">
         <v>1</v>
@@ -3269,44 +3341,44 @@
         <v>29</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>31</v>
+        <v>138</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>42</v>
+        <v>149</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="K28" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="M28" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="N28" s="6"/>
+        <v>153</v>
+      </c>
+      <c r="N28" s="6" t="s">
+        <v>154</v>
+      </c>
       <c r="O28" s="3" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P28" s="3"/>
       <c r="Q28" s="3"/>
       <c r="R28" s="3">
-        <v>36400</v>
-      </c>
-      <c r="S28" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>313246</v>
+      </c>
+      <c r="S28" s="3"/>
       <c r="T28" s="3"/>
       <c r="U28" s="3"/>
       <c r="V28" s="3"/>
@@ -3314,21 +3386,17 @@
       <c r="X28" s="3"/>
       <c r="Y28" s="3"/>
       <c r="Z28" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="AA28" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB28" s="3">
-        <v>1</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="AA28" s="3"/>
+      <c r="AB28" s="3"/>
     </row>
     <row r="29" spans="1:28">
       <c r="A29" s="7">
         <v>27</v>
       </c>
       <c r="B29" s="7">
-        <v>2026060379</v>
+        <v>2026060415</v>
       </c>
       <c r="C29" s="7">
         <v>1</v>
@@ -3337,42 +3405,46 @@
         <v>29</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="F29" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>42</v>
+        <v>155</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="K29" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L29" s="8" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="M29" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="N29" s="8"/>
+        <v>159</v>
+      </c>
+      <c r="N29" s="8" t="s">
+        <v>160</v>
+      </c>
       <c r="O29" s="7" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="P29" s="7"/>
       <c r="Q29" s="7"/>
       <c r="R29" s="7">
-        <v>36400</v>
-      </c>
-      <c r="S29" s="7"/>
+        <v>29215</v>
+      </c>
+      <c r="S29" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T29" s="7"/>
       <c r="U29" s="7"/>
       <c r="V29" s="7"/>
@@ -3380,19 +3452,21 @@
       <c r="X29" s="7"/>
       <c r="Y29" s="7"/>
       <c r="Z29" s="8" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="AA29" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AB29" s="7"/>
+      <c r="AB29" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="30" spans="1:28">
       <c r="A30" s="3">
         <v>28</v>
       </c>
       <c r="B30" s="3">
-        <v>2026060111</v>
+        <v>2026060416</v>
       </c>
       <c r="C30" s="3">
         <v>1</v>
@@ -3401,34 +3475,34 @@
         <v>29</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>124</v>
+        <v>31</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="K30" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="O30" s="3" t="s">
         <v>48</v>
@@ -3436,7 +3510,7 @@
       <c r="P30" s="3"/>
       <c r="Q30" s="3"/>
       <c r="R30" s="3">
-        <v>113426</v>
+        <v>29215</v>
       </c>
       <c r="S30" s="3"/>
       <c r="T30" s="3"/>
@@ -3446,9 +3520,11 @@
       <c r="X30" s="3"/>
       <c r="Y30" s="3"/>
       <c r="Z30" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="AA30" s="3"/>
+        <v>137</v>
+      </c>
+      <c r="AA30" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="AB30" s="3"/>
     </row>
     <row r="31" spans="1:28">
@@ -3456,7 +3532,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="7">
-        <v>2026060110</v>
+        <v>2026060378</v>
       </c>
       <c r="C31" s="7">
         <v>1</v>
@@ -3465,42 +3541,40 @@
         <v>29</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>124</v>
+        <v>31</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>151</v>
+        <v>42</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="I31" s="7" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="K31" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L31" s="8" t="s">
-        <v>138</v>
+        <v>163</v>
       </c>
       <c r="M31" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="N31" s="8" t="s">
-        <v>140</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="N31" s="8"/>
       <c r="O31" s="7" t="s">
         <v>39</v>
       </c>
       <c r="P31" s="7"/>
       <c r="Q31" s="7"/>
       <c r="R31" s="7">
-        <v>113426</v>
+        <v>36400</v>
       </c>
       <c r="S31" s="7" t="s">
         <v>40</v>
@@ -3512,17 +3586,21 @@
       <c r="X31" s="7"/>
       <c r="Y31" s="7"/>
       <c r="Z31" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="AA31" s="7"/>
-      <c r="AB31" s="7"/>
+        <v>137</v>
+      </c>
+      <c r="AA31" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB31" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="32" spans="1:28">
       <c r="A32" s="3">
         <v>30</v>
       </c>
       <c r="B32" s="3">
-        <v>2026060411</v>
+        <v>2026060379</v>
       </c>
       <c r="C32" s="3">
         <v>1</v>
@@ -3531,48 +3609,42 @@
         <v>29</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>157</v>
+        <v>73</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="N32" s="6" t="s">
-        <v>146</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="N32" s="6"/>
       <c r="O32" s="3" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P32" s="3"/>
-      <c r="Q32" s="3">
-        <v>3009</v>
-      </c>
+      <c r="Q32" s="3"/>
       <c r="R32" s="3">
-        <v>386927</v>
-      </c>
-      <c r="S32" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>36400</v>
+      </c>
+      <c r="S32" s="3"/>
       <c r="T32" s="3"/>
       <c r="U32" s="3"/>
       <c r="V32" s="3"/>
@@ -3580,21 +3652,19 @@
       <c r="X32" s="3"/>
       <c r="Y32" s="3"/>
       <c r="Z32" s="6" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="AA32" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AB32" s="3">
-        <v>1</v>
-      </c>
+      <c r="AB32" s="3"/>
     </row>
     <row r="33" spans="1:28">
       <c r="A33" s="7">
         <v>31</v>
       </c>
       <c r="B33" s="7">
-        <v>2026060412</v>
+        <v>2026060110</v>
       </c>
       <c r="C33" s="7">
         <v>1</v>
@@ -3603,46 +3673,46 @@
         <v>29</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>31</v>
+        <v>138</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>72</v>
+        <v>165</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="I33" s="7" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>157</v>
+        <v>73</v>
       </c>
       <c r="K33" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L33" s="8" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="M33" s="8" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="N33" s="8" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="O33" s="7" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="P33" s="7"/>
-      <c r="Q33" s="7">
-        <v>3009</v>
-      </c>
+      <c r="Q33" s="7"/>
       <c r="R33" s="7">
-        <v>386927</v>
-      </c>
-      <c r="S33" s="7"/>
+        <v>113426</v>
+      </c>
+      <c r="S33" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T33" s="7"/>
       <c r="U33" s="7"/>
       <c r="V33" s="7"/>
@@ -3650,11 +3720,9 @@
       <c r="X33" s="7"/>
       <c r="Y33" s="7"/>
       <c r="Z33" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="AA33" s="7" t="s">
-        <v>40</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="AA33" s="7"/>
       <c r="AB33" s="7"/>
     </row>
     <row r="34" spans="1:28">
@@ -3662,7 +3730,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="3">
-        <v>2026060771</v>
+        <v>2026060111</v>
       </c>
       <c r="C34" s="3">
         <v>1</v>
@@ -3671,48 +3739,44 @@
         <v>29</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>64</v>
+        <v>138</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>163</v>
+        <v>73</v>
       </c>
       <c r="K34" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="O34" s="3" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P34" s="3"/>
-      <c r="Q34" s="3">
-        <v>5752</v>
-      </c>
+      <c r="Q34" s="3"/>
       <c r="R34" s="3">
-        <v>34659</v>
-      </c>
-      <c r="S34" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>113426</v>
+      </c>
+      <c r="S34" s="3"/>
       <c r="T34" s="3"/>
       <c r="U34" s="3"/>
       <c r="V34" s="3"/>
@@ -3720,7 +3784,7 @@
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
       <c r="Z34" s="6" t="s">
-        <v>123</v>
+        <v>168</v>
       </c>
       <c r="AA34" s="3"/>
       <c r="AB34" s="3"/>
@@ -3730,7 +3794,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="7">
-        <v>2026060772</v>
+        <v>2026060411</v>
       </c>
       <c r="C35" s="7">
         <v>1</v>
@@ -3739,46 +3803,48 @@
         <v>29</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="G35" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="H35" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="I35" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="J35" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="K35" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L35" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="M35" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="N35" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="H35" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="I35" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="J35" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="K35" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="L35" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="M35" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="N35" s="8" t="s">
-        <v>166</v>
-      </c>
       <c r="O35" s="7" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="P35" s="7"/>
       <c r="Q35" s="7">
-        <v>5752</v>
+        <v>3009</v>
       </c>
       <c r="R35" s="7">
-        <v>34659</v>
-      </c>
-      <c r="S35" s="7"/>
+        <v>386927</v>
+      </c>
+      <c r="S35" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T35" s="7"/>
       <c r="U35" s="7"/>
       <c r="V35" s="7"/>
@@ -3786,19 +3852,21 @@
       <c r="X35" s="7"/>
       <c r="Y35" s="7"/>
       <c r="Z35" s="8" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="AA35" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AB35" s="7"/>
+      <c r="AB35" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="36" spans="1:28">
       <c r="A36" s="3">
         <v>34</v>
       </c>
       <c r="B36" s="3">
-        <v>2026060127</v>
+        <v>2026060412</v>
       </c>
       <c r="C36" s="3">
         <v>1</v>
@@ -3807,46 +3875,46 @@
         <v>29</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>124</v>
+        <v>31</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>167</v>
+        <v>77</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K36" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>127</v>
+        <v>172</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="O36" s="3" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P36" s="3"/>
-      <c r="Q36" s="3"/>
+      <c r="Q36" s="3">
+        <v>3009</v>
+      </c>
       <c r="R36" s="3">
-        <v>212738</v>
-      </c>
-      <c r="S36" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>386927</v>
+      </c>
+      <c r="S36" s="3"/>
       <c r="T36" s="3"/>
       <c r="U36" s="3"/>
       <c r="V36" s="3"/>
@@ -3854,9 +3922,11 @@
       <c r="X36" s="3"/>
       <c r="Y36" s="3"/>
       <c r="Z36" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="AA36" s="3"/>
+        <v>137</v>
+      </c>
+      <c r="AA36" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="AB36" s="3"/>
     </row>
     <row r="37" spans="1:28">
@@ -3864,7 +3934,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="7">
-        <v>2026060128</v>
+        <v>2026060771</v>
       </c>
       <c r="C37" s="7">
         <v>1</v>
@@ -3873,44 +3943,48 @@
         <v>29</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>124</v>
+        <v>69</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="I37" s="7" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="J37" s="7" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="K37" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L37" s="8" t="s">
-        <v>127</v>
+        <v>178</v>
       </c>
       <c r="M37" s="8" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="N37" s="8" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="O37" s="7" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="P37" s="7"/>
-      <c r="Q37" s="7"/>
+      <c r="Q37" s="7">
+        <v>5752</v>
+      </c>
       <c r="R37" s="7">
-        <v>212738</v>
-      </c>
-      <c r="S37" s="7"/>
+        <v>34659</v>
+      </c>
+      <c r="S37" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T37" s="7"/>
       <c r="U37" s="7"/>
       <c r="V37" s="7"/>
@@ -3918,7 +3992,7 @@
       <c r="X37" s="7"/>
       <c r="Y37" s="7"/>
       <c r="Z37" s="8" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="AA37" s="7"/>
       <c r="AB37" s="7"/>
@@ -3928,7 +4002,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="3">
-        <v>2026060846</v>
+        <v>2026060772</v>
       </c>
       <c r="C38" s="3">
         <v>1</v>
@@ -3937,42 +4011,46 @@
         <v>29</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>125</v>
+        <v>174</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>49</v>
+        <v>175</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="J38" s="3"/>
-      <c r="K38" s="3"/>
+        <v>176</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="L38" s="6" t="s">
-        <v>96</v>
+        <v>178</v>
       </c>
       <c r="M38" s="6" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="O38" s="3" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P38" s="3"/>
-      <c r="Q38" s="3"/>
+      <c r="Q38" s="3">
+        <v>5752</v>
+      </c>
       <c r="R38" s="3">
-        <v>0</v>
-      </c>
-      <c r="S38" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>34659</v>
+      </c>
+      <c r="S38" s="3"/>
       <c r="T38" s="3"/>
       <c r="U38" s="3"/>
       <c r="V38" s="3"/>
@@ -3980,21 +4058,19 @@
       <c r="X38" s="3"/>
       <c r="Y38" s="3"/>
       <c r="Z38" s="6" t="s">
-        <v>176</v>
+        <v>137</v>
       </c>
       <c r="AA38" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AB38" s="3">
-        <v>1</v>
-      </c>
+      <c r="AB38" s="3"/>
     </row>
     <row r="39" spans="1:28">
       <c r="A39" s="7">
         <v>37</v>
       </c>
       <c r="B39" s="7">
-        <v>2026060445</v>
+        <v>2026060127</v>
       </c>
       <c r="C39" s="7">
         <v>1</v>
@@ -4003,30 +4079,34 @@
         <v>29</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>31</v>
+        <v>138</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>93</v>
+        <v>181</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="I39" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="J39" s="7"/>
-      <c r="K39" s="7"/>
+        <v>183</v>
+      </c>
+      <c r="J39" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="K39" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="L39" s="8" t="s">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="M39" s="8" t="s">
-        <v>97</v>
+        <v>185</v>
       </c>
       <c r="N39" s="8" t="s">
-        <v>98</v>
+        <v>186</v>
       </c>
       <c r="O39" s="7" t="s">
         <v>39</v>
@@ -4034,33 +4114,29 @@
       <c r="P39" s="7"/>
       <c r="Q39" s="7"/>
       <c r="R39" s="7">
-        <v>0</v>
-      </c>
-      <c r="S39" s="7"/>
-      <c r="T39" s="7" t="s">
-        <v>40</v>
-      </c>
+        <v>212738</v>
+      </c>
+      <c r="S39" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="T39" s="7"/>
       <c r="U39" s="7"/>
       <c r="V39" s="7"/>
       <c r="W39" s="7"/>
       <c r="X39" s="7"/>
       <c r="Y39" s="7"/>
       <c r="Z39" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="AA39" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB39" s="7">
-        <v>1</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="AA39" s="7"/>
+      <c r="AB39" s="7"/>
     </row>
     <row r="40" spans="1:28">
       <c r="A40" s="3">
         <v>38</v>
       </c>
       <c r="B40" s="3">
-        <v>2026060840</v>
+        <v>2026060128</v>
       </c>
       <c r="C40" s="3">
         <v>1</v>
@@ -4069,42 +4145,44 @@
         <v>29</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>64</v>
+        <v>138</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="J40" s="3"/>
-      <c r="K40" s="3"/>
+        <v>183</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="L40" s="6" t="s">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="M40" s="6" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="O40" s="3" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3">
-        <v>0</v>
-      </c>
-      <c r="S40" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>212738</v>
+      </c>
+      <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
@@ -4112,21 +4190,17 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="AA40" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB40" s="3">
-        <v>1</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="AA40" s="3"/>
+      <c r="AB40" s="3"/>
     </row>
     <row r="41" spans="1:28">
       <c r="A41" s="7">
         <v>39</v>
       </c>
       <c r="B41" s="7">
-        <v>2026060812</v>
+        <v>2026060846</v>
       </c>
       <c r="C41" s="7">
         <v>1</v>
@@ -4135,30 +4209,30 @@
         <v>29</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>184</v>
+        <v>139</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>185</v>
+        <v>49</v>
       </c>
       <c r="I41" s="7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="J41" s="7"/>
       <c r="K41" s="7"/>
       <c r="L41" s="8" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="M41" s="8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N41" s="8" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O41" s="7" t="s">
         <v>39</v>
@@ -4178,7 +4252,7 @@
       <c r="X41" s="7"/>
       <c r="Y41" s="7"/>
       <c r="Z41" s="8" t="s">
-        <v>105</v>
+        <v>190</v>
       </c>
       <c r="AA41" s="7" t="s">
         <v>40</v>
@@ -4192,7 +4266,7 @@
         <v>40</v>
       </c>
       <c r="B42" s="3">
-        <v>2026060827</v>
+        <v>2026060445</v>
       </c>
       <c r="C42" s="3">
         <v>1</v>
@@ -4201,30 +4275,30 @@
         <v>29</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>190</v>
+        <v>110</v>
       </c>
       <c r="J42" s="3"/>
       <c r="K42" s="3"/>
       <c r="L42" s="6" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="M42" s="6" t="s">
-        <v>191</v>
+        <v>111</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>192</v>
+        <v>112</v>
       </c>
       <c r="O42" s="3" t="s">
         <v>39</v>
@@ -4234,17 +4308,17 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-      <c r="S42" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="T42" s="3"/>
+      <c r="S42" s="3"/>
+      <c r="T42" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="U42" s="3"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
       <c r="Y42" s="3"/>
       <c r="Z42" s="6" t="s">
-        <v>105</v>
+        <v>192</v>
       </c>
       <c r="AA42" s="3" t="s">
         <v>40</v>
@@ -4258,7 +4332,7 @@
         <v>41</v>
       </c>
       <c r="B43" s="7">
-        <v>2026060664</v>
+        <v>2026060840</v>
       </c>
       <c r="C43" s="7">
         <v>1</v>
@@ -4267,46 +4341,38 @@
         <v>29</v>
       </c>
       <c r="E43" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="G43" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="F43" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G43" s="7" t="s">
-        <v>117</v>
-      </c>
       <c r="H43" s="7" t="s">
-        <v>32</v>
+        <v>194</v>
       </c>
       <c r="I43" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="J43" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="K43" s="7" t="s">
-        <v>36</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="J43" s="7"/>
+      <c r="K43" s="7"/>
       <c r="L43" s="8" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="M43" s="8" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N43" s="8" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O43" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="P43" s="7">
-        <v>2480</v>
-      </c>
-      <c r="Q43" s="7">
-        <v>3343</v>
-      </c>
+      <c r="P43" s="7"/>
+      <c r="Q43" s="7"/>
       <c r="R43" s="7">
-        <v>11884</v>
+        <v>0</v>
       </c>
       <c r="S43" s="7" t="s">
         <v>40</v>
@@ -4318,7 +4384,7 @@
       <c r="X43" s="7"/>
       <c r="Y43" s="7"/>
       <c r="Z43" s="8" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="AA43" s="7" t="s">
         <v>40</v>
@@ -4332,7 +4398,7 @@
         <v>42</v>
       </c>
       <c r="B44" s="3">
-        <v>2026060665</v>
+        <v>2026060812</v>
       </c>
       <c r="C44" s="3">
         <v>1</v>
@@ -4341,48 +4407,42 @@
         <v>29</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>193</v>
+        <v>130</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>117</v>
+        <v>198</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>32</v>
+        <v>199</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="K44" s="3" t="s">
-        <v>36</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="J44" s="3"/>
+      <c r="K44" s="3"/>
       <c r="L44" s="6" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="M44" s="6" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="O44" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="P44" s="3">
-        <v>2480</v>
-      </c>
-      <c r="Q44" s="3">
-        <v>3343</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="P44" s="3"/>
+      <c r="Q44" s="3"/>
       <c r="R44" s="3">
-        <v>11884</v>
-      </c>
-      <c r="S44" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="S44" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T44" s="3"/>
       <c r="U44" s="3"/>
       <c r="V44" s="3"/>
@@ -4390,19 +4450,21 @@
       <c r="X44" s="3"/>
       <c r="Y44" s="3"/>
       <c r="Z44" s="6" t="s">
-        <v>197</v>
+        <v>119</v>
       </c>
       <c r="AA44" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AB44" s="3"/>
+      <c r="AB44" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="45" spans="1:28">
       <c r="A45" s="7">
         <v>43</v>
       </c>
       <c r="B45" s="7">
-        <v>2026060666</v>
+        <v>2026060827</v>
       </c>
       <c r="C45" s="7">
         <v>1</v>
@@ -4411,46 +4473,38 @@
         <v>29</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>193</v>
+        <v>130</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>32</v>
+        <v>102</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>77</v>
+        <v>203</v>
       </c>
       <c r="I45" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="J45" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="K45" s="7" t="s">
-        <v>36</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="J45" s="7"/>
+      <c r="K45" s="7"/>
       <c r="L45" s="8" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="M45" s="8" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="N45" s="8" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="O45" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="P45" s="7">
-        <v>624</v>
-      </c>
-      <c r="Q45" s="7">
-        <v>1591</v>
-      </c>
+      <c r="P45" s="7"/>
+      <c r="Q45" s="7"/>
       <c r="R45" s="7">
-        <v>9357</v>
+        <v>0</v>
       </c>
       <c r="S45" s="7" t="s">
         <v>40</v>
@@ -4462,7 +4516,7 @@
       <c r="X45" s="7"/>
       <c r="Y45" s="7"/>
       <c r="Z45" s="8" t="s">
-        <v>197</v>
+        <v>119</v>
       </c>
       <c r="AA45" s="7" t="s">
         <v>40</v>
@@ -4476,7 +4530,7 @@
         <v>44</v>
       </c>
       <c r="B46" s="3">
-        <v>2026060667</v>
+        <v>2026060664</v>
       </c>
       <c r="C46" s="3">
         <v>1</v>
@@ -4485,19 +4539,19 @@
         <v>29</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G46" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="H46" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H46" s="3" t="s">
-        <v>77</v>
-      </c>
       <c r="I46" s="3" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="J46" s="3" t="s">
         <v>35</v>
@@ -4506,27 +4560,29 @@
         <v>36</v>
       </c>
       <c r="L46" s="6" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="M46" s="6" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="O46" s="3" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="P46" s="3">
-        <v>624</v>
+        <v>2480</v>
       </c>
       <c r="Q46" s="3">
-        <v>1591</v>
+        <v>3343</v>
       </c>
       <c r="R46" s="3">
-        <v>9357</v>
-      </c>
-      <c r="S46" s="3"/>
+        <v>11884</v>
+      </c>
+      <c r="S46" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T46" s="3"/>
       <c r="U46" s="3"/>
       <c r="V46" s="3"/>
@@ -4534,19 +4590,21 @@
       <c r="X46" s="3"/>
       <c r="Y46" s="3"/>
       <c r="Z46" s="6" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="AA46" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AB46" s="3"/>
+      <c r="AB46" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="47" spans="1:28">
       <c r="A47" s="7">
         <v>45</v>
       </c>
       <c r="B47" s="7">
-        <v>2026060572</v>
+        <v>2026060665</v>
       </c>
       <c r="C47" s="7">
         <v>1</v>
@@ -4555,19 +4613,19 @@
         <v>29</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>125</v>
+        <v>32</v>
       </c>
       <c r="I47" s="7" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="J47" s="7" t="s">
         <v>35</v>
@@ -4576,27 +4634,27 @@
         <v>36</v>
       </c>
       <c r="L47" s="8" t="s">
-        <v>45</v>
+        <v>134</v>
       </c>
       <c r="M47" s="8" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="N47" s="8" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="O47" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="P47" s="7"/>
+        <v>48</v>
+      </c>
+      <c r="P47" s="7">
+        <v>2480</v>
+      </c>
       <c r="Q47" s="7">
-        <v>449</v>
+        <v>3343</v>
       </c>
       <c r="R47" s="7">
-        <v>4403</v>
-      </c>
-      <c r="S47" s="7" t="s">
-        <v>40</v>
-      </c>
+        <v>11884</v>
+      </c>
+      <c r="S47" s="7"/>
       <c r="T47" s="7"/>
       <c r="U47" s="7"/>
       <c r="V47" s="7"/>
@@ -4604,21 +4662,19 @@
       <c r="X47" s="7"/>
       <c r="Y47" s="7"/>
       <c r="Z47" s="8" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="AA47" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AB47" s="7">
-        <v>1</v>
-      </c>
+      <c r="AB47" s="7"/>
     </row>
     <row r="48" spans="1:28">
       <c r="A48" s="3">
         <v>46</v>
       </c>
       <c r="B48" s="3">
-        <v>2026060573</v>
+        <v>2026060666</v>
       </c>
       <c r="C48" s="3">
         <v>1</v>
@@ -4627,19 +4683,19 @@
         <v>29</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>136</v>
+        <v>32</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="J48" s="3" t="s">
         <v>35</v>
@@ -4648,25 +4704,29 @@
         <v>36</v>
       </c>
       <c r="L48" s="6" t="s">
-        <v>45</v>
+        <v>134</v>
       </c>
       <c r="M48" s="6" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="O48" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="P48" s="3"/>
+        <v>39</v>
+      </c>
+      <c r="P48" s="3">
+        <v>624</v>
+      </c>
       <c r="Q48" s="3">
-        <v>449</v>
+        <v>1591</v>
       </c>
       <c r="R48" s="3">
-        <v>4403</v>
-      </c>
-      <c r="S48" s="3"/>
+        <v>9357</v>
+      </c>
+      <c r="S48" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T48" s="3"/>
       <c r="U48" s="3"/>
       <c r="V48" s="3"/>
@@ -4674,19 +4734,21 @@
       <c r="X48" s="3"/>
       <c r="Y48" s="3"/>
       <c r="Z48" s="6" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="AA48" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AB48" s="3"/>
+      <c r="AB48" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="49" spans="1:28">
       <c r="A49" s="7">
         <v>47</v>
       </c>
       <c r="B49" s="7">
-        <v>2026060824</v>
+        <v>2026060667</v>
       </c>
       <c r="C49" s="7">
         <v>1</v>
@@ -4695,19 +4757,19 @@
         <v>29</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>204</v>
+        <v>32</v>
       </c>
       <c r="H49" s="7" t="s">
-        <v>151</v>
+        <v>82</v>
       </c>
       <c r="I49" s="7" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="J49" s="7" t="s">
         <v>35</v>
@@ -4716,49 +4778,47 @@
         <v>36</v>
       </c>
       <c r="L49" s="8" t="s">
-        <v>45</v>
+        <v>134</v>
       </c>
       <c r="M49" s="8" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="N49" s="8" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="O49" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="P49" s="7"/>
+        <v>48</v>
+      </c>
+      <c r="P49" s="7">
+        <v>624</v>
+      </c>
       <c r="Q49" s="7">
-        <v>449</v>
+        <v>1591</v>
       </c>
       <c r="R49" s="7">
-        <v>4403</v>
+        <v>9357</v>
       </c>
       <c r="S49" s="7"/>
       <c r="T49" s="7"/>
       <c r="U49" s="7"/>
       <c r="V49" s="7"/>
-      <c r="W49" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="W49" s="7"/>
       <c r="X49" s="7"/>
       <c r="Y49" s="7"/>
       <c r="Z49" s="8" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="AA49" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AB49" s="7">
-        <v>1</v>
-      </c>
+      <c r="AB49" s="7"/>
     </row>
     <row r="50" spans="1:28">
       <c r="A50" s="3">
         <v>48</v>
       </c>
       <c r="B50" s="3">
-        <v>2026060064</v>
+        <v>2026060572</v>
       </c>
       <c r="C50" s="3">
         <v>1</v>
@@ -4767,44 +4827,48 @@
         <v>29</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>124</v>
+        <v>31</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>206</v>
+        <v>150</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>207</v>
+        <v>139</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="K50" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L50" s="6" t="s">
-        <v>209</v>
+        <v>45</v>
       </c>
       <c r="M50" s="6" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="O50" s="3" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="P50" s="3"/>
-      <c r="Q50" s="3"/>
+      <c r="Q50" s="3">
+        <v>449</v>
+      </c>
       <c r="R50" s="3">
-        <v>2818</v>
-      </c>
-      <c r="S50" s="3"/>
+        <v>4403</v>
+      </c>
+      <c r="S50" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T50" s="3"/>
       <c r="U50" s="3"/>
       <c r="V50" s="3"/>
@@ -4812,7 +4876,7 @@
       <c r="X50" s="3"/>
       <c r="Y50" s="3"/>
       <c r="Z50" s="6" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="AA50" s="3" t="s">
         <v>40</v>
@@ -4826,7 +4890,7 @@
         <v>49</v>
       </c>
       <c r="B51" s="7">
-        <v>2026060063</v>
+        <v>2026060573</v>
       </c>
       <c r="C51" s="7">
         <v>1</v>
@@ -4835,46 +4899,46 @@
         <v>29</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>124</v>
+        <v>31</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>206</v>
+        <v>150</v>
       </c>
       <c r="H51" s="7" t="s">
-        <v>207</v>
+        <v>139</v>
       </c>
       <c r="I51" s="7" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="J51" s="7" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="K51" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L51" s="8" t="s">
-        <v>209</v>
+        <v>45</v>
       </c>
       <c r="M51" s="8" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="N51" s="8" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="O51" s="7" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P51" s="7"/>
-      <c r="Q51" s="7"/>
+      <c r="Q51" s="7">
+        <v>449</v>
+      </c>
       <c r="R51" s="7">
-        <v>2818</v>
-      </c>
-      <c r="S51" s="7" t="s">
-        <v>40</v>
-      </c>
+        <v>4403</v>
+      </c>
+      <c r="S51" s="7"/>
       <c r="T51" s="7"/>
       <c r="U51" s="7"/>
       <c r="V51" s="7"/>
@@ -4882,7 +4946,7 @@
       <c r="X51" s="7"/>
       <c r="Y51" s="7"/>
       <c r="Z51" s="8" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="AA51" s="7" t="s">
         <v>40</v>
@@ -4894,7 +4958,7 @@
         <v>50</v>
       </c>
       <c r="B52" s="3">
-        <v>2026060627</v>
+        <v>2026060824</v>
       </c>
       <c r="C52" s="3">
         <v>1</v>
@@ -4903,28 +4967,28 @@
         <v>29</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>213</v>
+        <v>165</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L52" s="6" t="s">
-        <v>215</v>
+        <v>45</v>
       </c>
       <c r="M52" s="6" t="s">
         <v>216</v>
@@ -4936,21 +5000,23 @@
         <v>39</v>
       </c>
       <c r="P52" s="3"/>
-      <c r="Q52" s="3"/>
+      <c r="Q52" s="3">
+        <v>449</v>
+      </c>
       <c r="R52" s="3">
-        <v>195048</v>
-      </c>
-      <c r="S52" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>4403</v>
+      </c>
+      <c r="S52" s="3"/>
       <c r="T52" s="3"/>
       <c r="U52" s="3"/>
       <c r="V52" s="3"/>
-      <c r="W52" s="3"/>
+      <c r="W52" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="X52" s="3"/>
       <c r="Y52" s="3"/>
       <c r="Z52" s="6" t="s">
-        <v>197</v>
+        <v>219</v>
       </c>
       <c r="AA52" s="3" t="s">
         <v>40</v>
@@ -4964,7 +5030,7 @@
         <v>51</v>
       </c>
       <c r="B53" s="7">
-        <v>2026060628</v>
+        <v>2026060063</v>
       </c>
       <c r="C53" s="7">
         <v>1</v>
@@ -4973,44 +5039,46 @@
         <v>29</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>64</v>
+        <v>138</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="H53" s="7" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="I53" s="7" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="J53" s="7" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="K53" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L53" s="8" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="M53" s="8" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="N53" s="8" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="O53" s="7" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="P53" s="7"/>
       <c r="Q53" s="7"/>
       <c r="R53" s="7">
-        <v>195048</v>
-      </c>
-      <c r="S53" s="7"/>
+        <v>2818</v>
+      </c>
+      <c r="S53" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T53" s="7"/>
       <c r="U53" s="7"/>
       <c r="V53" s="7"/>
@@ -5018,19 +5086,21 @@
       <c r="X53" s="7"/>
       <c r="Y53" s="7"/>
       <c r="Z53" s="8" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="AA53" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AB53" s="7"/>
+      <c r="AB53" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="54" spans="1:28">
       <c r="A54" s="3">
         <v>52</v>
       </c>
       <c r="B54" s="3">
-        <v>2026060629</v>
+        <v>2026060064</v>
       </c>
       <c r="C54" s="3">
         <v>1</v>
@@ -5039,46 +5109,44 @@
         <v>29</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>64</v>
+        <v>138</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>117</v>
+        <v>221</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L54" s="6" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="M54" s="6" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="O54" s="3" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P54" s="3"/>
       <c r="Q54" s="3"/>
       <c r="R54" s="3">
-        <v>203621</v>
-      </c>
-      <c r="S54" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>2818</v>
+      </c>
+      <c r="S54" s="3"/>
       <c r="T54" s="3"/>
       <c r="U54" s="3"/>
       <c r="V54" s="3"/>
@@ -5086,21 +5154,19 @@
       <c r="X54" s="3"/>
       <c r="Y54" s="3"/>
       <c r="Z54" s="6" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="AA54" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AB54" s="3">
-        <v>1</v>
-      </c>
+      <c r="AB54" s="3"/>
     </row>
     <row r="55" spans="1:28">
       <c r="A55" s="7">
         <v>53</v>
       </c>
       <c r="B55" s="7">
-        <v>2026060630</v>
+        <v>2026061006</v>
       </c>
       <c r="C55" s="7">
         <v>1</v>
@@ -5109,44 +5175,46 @@
         <v>29</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>213</v>
+        <v>150</v>
       </c>
       <c r="H55" s="7" t="s">
-        <v>117</v>
+        <v>139</v>
       </c>
       <c r="I55" s="7" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="J55" s="7" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="K55" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L55" s="8" t="s">
-        <v>215</v>
+        <v>158</v>
       </c>
       <c r="M55" s="8" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="N55" s="8" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="O55" s="7" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="P55" s="7"/>
       <c r="Q55" s="7"/>
       <c r="R55" s="7">
-        <v>203621</v>
-      </c>
-      <c r="S55" s="7"/>
+        <v>57995</v>
+      </c>
+      <c r="S55" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T55" s="7"/>
       <c r="U55" s="7"/>
       <c r="V55" s="7"/>
@@ -5154,19 +5222,21 @@
       <c r="X55" s="7"/>
       <c r="Y55" s="7"/>
       <c r="Z55" s="8" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="AA55" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AB55" s="7"/>
+      <c r="AB55" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="56" spans="1:28">
       <c r="A56" s="3">
         <v>54</v>
       </c>
       <c r="B56" s="3">
-        <v>2026060146</v>
+        <v>2026061007</v>
       </c>
       <c r="C56" s="3">
         <v>1</v>
@@ -5175,68 +5245,64 @@
         <v>29</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>124</v>
+        <v>54</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>221</v>
+        <v>150</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>222</v>
+        <v>139</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="K56" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L56" s="6" t="s">
-        <v>224</v>
+        <v>158</v>
       </c>
       <c r="M56" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="O56" s="3" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3">
-        <v>49442</v>
+        <v>57995</v>
       </c>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-      <c r="U56" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="6" t="s">
-        <v>227</v>
+        <v>211</v>
       </c>
       <c r="AA56" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AB56" s="3">
-        <v>1</v>
-      </c>
+      <c r="AB56" s="3"/>
     </row>
     <row r="57" spans="1:28">
       <c r="A57" s="7">
         <v>55</v>
       </c>
       <c r="B57" s="7">
-        <v>2026060052</v>
+        <v>2026061008</v>
       </c>
       <c r="C57" s="7">
         <v>1</v>
@@ -5245,34 +5311,34 @@
         <v>29</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>124</v>
+        <v>54</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>73</v>
+        <v>139</v>
       </c>
       <c r="H57" s="7" t="s">
-        <v>160</v>
+        <v>49</v>
       </c>
       <c r="I57" s="7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="J57" s="7" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="K57" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L57" s="8" t="s">
-        <v>209</v>
+        <v>158</v>
       </c>
       <c r="M57" s="8" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N57" s="8" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O57" s="7" t="s">
         <v>39</v>
@@ -5280,7 +5346,7 @@
       <c r="P57" s="7"/>
       <c r="Q57" s="7"/>
       <c r="R57" s="7">
-        <v>29640</v>
+        <v>92221</v>
       </c>
       <c r="S57" s="7" t="s">
         <v>40</v>
@@ -5292,7 +5358,7 @@
       <c r="X57" s="7"/>
       <c r="Y57" s="7"/>
       <c r="Z57" s="8" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="AA57" s="7" t="s">
         <v>40</v>
@@ -5306,7 +5372,7 @@
         <v>56</v>
       </c>
       <c r="B58" s="3">
-        <v>2026060053</v>
+        <v>2026061009</v>
       </c>
       <c r="C58" s="3">
         <v>1</v>
@@ -5315,34 +5381,34 @@
         <v>29</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>124</v>
+        <v>54</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>73</v>
+        <v>139</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>160</v>
+        <v>49</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L58" s="6" t="s">
-        <v>209</v>
+        <v>158</v>
       </c>
       <c r="M58" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O58" s="3" t="s">
         <v>48</v>
@@ -5350,7 +5416,7 @@
       <c r="P58" s="3"/>
       <c r="Q58" s="3"/>
       <c r="R58" s="3">
-        <v>29640</v>
+        <v>92221</v>
       </c>
       <c r="S58" s="3"/>
       <c r="T58" s="3"/>
@@ -5360,7 +5426,7 @@
       <c r="X58" s="3"/>
       <c r="Y58" s="3"/>
       <c r="Z58" s="6" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="AA58" s="3" t="s">
         <v>40</v>
@@ -5372,7 +5438,7 @@
         <v>57</v>
       </c>
       <c r="B59" s="7">
-        <v>2026060051</v>
+        <v>2026060627</v>
       </c>
       <c r="C59" s="7">
         <v>1</v>
@@ -5381,44 +5447,46 @@
         <v>29</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>124</v>
+        <v>69</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>72</v>
+        <v>232</v>
       </c>
       <c r="H59" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="I59" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="J59" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="I59" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="J59" s="7" t="s">
-        <v>68</v>
-      </c>
       <c r="K59" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L59" s="8" t="s">
-        <v>209</v>
+        <v>235</v>
       </c>
       <c r="M59" s="8" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="N59" s="8" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="O59" s="7" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="P59" s="7"/>
       <c r="Q59" s="7"/>
       <c r="R59" s="7">
-        <v>37830</v>
-      </c>
-      <c r="S59" s="7"/>
+        <v>195048</v>
+      </c>
+      <c r="S59" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T59" s="7"/>
       <c r="U59" s="7"/>
       <c r="V59" s="7"/>
@@ -5426,7 +5494,7 @@
       <c r="X59" s="7"/>
       <c r="Y59" s="7"/>
       <c r="Z59" s="8" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="AA59" s="7" t="s">
         <v>40</v>
@@ -5440,7 +5508,7 @@
         <v>58</v>
       </c>
       <c r="B60" s="3">
-        <v>2026060050</v>
+        <v>2026060628</v>
       </c>
       <c r="C60" s="3">
         <v>1</v>
@@ -5449,46 +5517,44 @@
         <v>29</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>124</v>
+        <v>69</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>72</v>
+        <v>232</v>
       </c>
       <c r="H60" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="J60" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>68</v>
-      </c>
       <c r="K60" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L60" s="6" t="s">
-        <v>209</v>
+        <v>235</v>
       </c>
       <c r="M60" s="6" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="O60" s="3" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P60" s="3"/>
       <c r="Q60" s="3"/>
       <c r="R60" s="3">
-        <v>37830</v>
-      </c>
-      <c r="S60" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>195048</v>
+      </c>
+      <c r="S60" s="3"/>
       <c r="T60" s="3"/>
       <c r="U60" s="3"/>
       <c r="V60" s="3"/>
@@ -5496,7 +5562,7 @@
       <c r="X60" s="3"/>
       <c r="Y60" s="3"/>
       <c r="Z60" s="6" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="AA60" s="3" t="s">
         <v>40</v>
@@ -5508,7 +5574,7 @@
         <v>59</v>
       </c>
       <c r="B61" s="7">
-        <v>2026060046</v>
+        <v>2026060629</v>
       </c>
       <c r="C61" s="7">
         <v>1</v>
@@ -5517,34 +5583,34 @@
         <v>29</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>124</v>
+        <v>69</v>
       </c>
       <c r="G61" s="7" t="s">
-        <v>32</v>
+        <v>233</v>
       </c>
       <c r="H61" s="7" t="s">
-        <v>77</v>
+        <v>131</v>
       </c>
       <c r="I61" s="7" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="J61" s="7" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="K61" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L61" s="8" t="s">
-        <v>209</v>
+        <v>235</v>
       </c>
       <c r="M61" s="8" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="N61" s="8" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="O61" s="7" t="s">
         <v>39</v>
@@ -5552,7 +5618,7 @@
       <c r="P61" s="7"/>
       <c r="Q61" s="7"/>
       <c r="R61" s="7">
-        <v>45926</v>
+        <v>203621</v>
       </c>
       <c r="S61" s="7" t="s">
         <v>40</v>
@@ -5564,7 +5630,7 @@
       <c r="X61" s="7"/>
       <c r="Y61" s="7"/>
       <c r="Z61" s="8" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="AA61" s="7" t="s">
         <v>40</v>
@@ -5578,7 +5644,7 @@
         <v>60</v>
       </c>
       <c r="B62" s="3">
-        <v>2026060047</v>
+        <v>2026060630</v>
       </c>
       <c r="C62" s="3">
         <v>1</v>
@@ -5587,34 +5653,34 @@
         <v>29</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>124</v>
+        <v>69</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>32</v>
+        <v>233</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>77</v>
+        <v>131</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L62" s="6" t="s">
-        <v>209</v>
+        <v>235</v>
       </c>
       <c r="M62" s="6" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="O62" s="3" t="s">
         <v>48</v>
@@ -5622,7 +5688,7 @@
       <c r="P62" s="3"/>
       <c r="Q62" s="3"/>
       <c r="R62" s="3">
-        <v>45926</v>
+        <v>203621</v>
       </c>
       <c r="S62" s="3"/>
       <c r="T62" s="3"/>
@@ -5632,7 +5698,7 @@
       <c r="X62" s="3"/>
       <c r="Y62" s="3"/>
       <c r="Z62" s="6" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="AA62" s="3" t="s">
         <v>40</v>
@@ -5644,7 +5710,7 @@
         <v>61</v>
       </c>
       <c r="B63" s="7">
-        <v>2026060040</v>
+        <v>2026060146</v>
       </c>
       <c r="C63" s="7">
         <v>1</v>
@@ -5653,34 +5719,34 @@
         <v>29</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="G63" s="7" t="s">
-        <v>212</v>
+        <v>103</v>
       </c>
       <c r="H63" s="7" t="s">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="I63" s="7" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="J63" s="7" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="K63" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L63" s="8" t="s">
-        <v>209</v>
+        <v>243</v>
       </c>
       <c r="M63" s="8" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="N63" s="8" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="O63" s="7" t="s">
         <v>39</v>
@@ -5688,19 +5754,19 @@
       <c r="P63" s="7"/>
       <c r="Q63" s="7"/>
       <c r="R63" s="7">
-        <v>29640</v>
-      </c>
-      <c r="S63" s="7" t="s">
-        <v>40</v>
-      </c>
+        <v>49442</v>
+      </c>
+      <c r="S63" s="7"/>
       <c r="T63" s="7"/>
-      <c r="U63" s="7"/>
+      <c r="U63" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="V63" s="7"/>
       <c r="W63" s="7"/>
       <c r="X63" s="7"/>
       <c r="Y63" s="7"/>
       <c r="Z63" s="8" t="s">
-        <v>197</v>
+        <v>246</v>
       </c>
       <c r="AA63" s="7" t="s">
         <v>40</v>
@@ -5714,7 +5780,7 @@
         <v>62</v>
       </c>
       <c r="B64" s="3">
-        <v>2026060041</v>
+        <v>2026060052</v>
       </c>
       <c r="C64" s="3">
         <v>1</v>
@@ -5723,44 +5789,46 @@
         <v>29</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>212</v>
+        <v>78</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>213</v>
+        <v>174</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="K64" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L64" s="6" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="M64" s="6" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="O64" s="3" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="P64" s="3"/>
       <c r="Q64" s="3"/>
       <c r="R64" s="3">
         <v>29640</v>
       </c>
-      <c r="S64" s="3"/>
+      <c r="S64" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T64" s="3"/>
       <c r="U64" s="3"/>
       <c r="V64" s="3"/>
@@ -5768,19 +5836,21 @@
       <c r="X64" s="3"/>
       <c r="Y64" s="3"/>
       <c r="Z64" s="6" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="AA64" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AB64" s="3"/>
+      <c r="AB64" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="65" spans="1:28">
       <c r="A65" s="7">
         <v>63</v>
       </c>
       <c r="B65" s="7">
-        <v>2026060044</v>
+        <v>2026060053</v>
       </c>
       <c r="C65" s="7">
         <v>1</v>
@@ -5789,46 +5859,44 @@
         <v>29</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="G65" s="7" t="s">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="H65" s="7" t="s">
-        <v>32</v>
+        <v>174</v>
       </c>
       <c r="I65" s="7" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="J65" s="7" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="K65" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L65" s="8" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="M65" s="8" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="N65" s="8" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="O65" s="7" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P65" s="7"/>
       <c r="Q65" s="7"/>
       <c r="R65" s="7">
-        <v>34235</v>
-      </c>
-      <c r="S65" s="7" t="s">
-        <v>40</v>
-      </c>
+        <v>29640</v>
+      </c>
+      <c r="S65" s="7"/>
       <c r="T65" s="7"/>
       <c r="U65" s="7"/>
       <c r="V65" s="7"/>
@@ -5836,21 +5904,19 @@
       <c r="X65" s="7"/>
       <c r="Y65" s="7"/>
       <c r="Z65" s="8" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="AA65" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AB65" s="7">
-        <v>1</v>
-      </c>
+      <c r="AB65" s="7"/>
     </row>
     <row r="66" spans="1:28">
       <c r="A66" s="3">
         <v>64</v>
       </c>
       <c r="B66" s="3">
-        <v>2026060045</v>
+        <v>2026061004</v>
       </c>
       <c r="C66" s="3">
         <v>1</v>
@@ -5859,44 +5925,46 @@
         <v>29</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>124</v>
+        <v>54</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>117</v>
+        <v>250</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>32</v>
+        <v>150</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L66" s="6" t="s">
-        <v>209</v>
+        <v>158</v>
       </c>
       <c r="M66" s="6" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>242</v>
+        <v>217</v>
       </c>
       <c r="O66" s="3" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="P66" s="3"/>
       <c r="Q66" s="3"/>
       <c r="R66" s="3">
-        <v>34235</v>
-      </c>
-      <c r="S66" s="3"/>
+        <v>8317</v>
+      </c>
+      <c r="S66" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T66" s="3"/>
       <c r="U66" s="3"/>
       <c r="V66" s="3"/>
@@ -5904,19 +5972,21 @@
       <c r="X66" s="3"/>
       <c r="Y66" s="3"/>
       <c r="Z66" s="6" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="AA66" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AB66" s="3"/>
+      <c r="AB66" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="67" spans="1:28">
       <c r="A67" s="7">
         <v>65</v>
       </c>
       <c r="B67" s="7">
-        <v>2026060042</v>
+        <v>2026061005</v>
       </c>
       <c r="C67" s="7">
         <v>1</v>
@@ -5925,46 +5995,44 @@
         <v>29</v>
       </c>
       <c r="E67" s="7" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>124</v>
+        <v>54</v>
       </c>
       <c r="G67" s="7" t="s">
-        <v>213</v>
+        <v>250</v>
       </c>
       <c r="H67" s="7" t="s">
-        <v>117</v>
+        <v>150</v>
       </c>
       <c r="I67" s="7" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="J67" s="7" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="K67" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L67" s="8" t="s">
-        <v>209</v>
+        <v>158</v>
       </c>
       <c r="M67" s="8" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="N67" s="8" t="s">
-        <v>245</v>
+        <v>217</v>
       </c>
       <c r="O67" s="7" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P67" s="7"/>
       <c r="Q67" s="7"/>
       <c r="R67" s="7">
-        <v>17791</v>
-      </c>
-      <c r="S67" s="7" t="s">
-        <v>40</v>
-      </c>
+        <v>8317</v>
+      </c>
+      <c r="S67" s="7"/>
       <c r="T67" s="7"/>
       <c r="U67" s="7"/>
       <c r="V67" s="7"/>
@@ -5972,21 +6040,19 @@
       <c r="X67" s="7"/>
       <c r="Y67" s="7"/>
       <c r="Z67" s="8" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="AA67" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AB67" s="7">
-        <v>1</v>
-      </c>
+      <c r="AB67" s="7"/>
     </row>
     <row r="68" spans="1:28">
       <c r="A68" s="3">
         <v>66</v>
       </c>
       <c r="B68" s="3">
-        <v>2026060043</v>
+        <v>2026060050</v>
       </c>
       <c r="C68" s="3">
         <v>1</v>
@@ -5995,44 +6061,46 @@
         <v>29</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>213</v>
+        <v>77</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="K68" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L68" s="6" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="M68" s="6" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="O68" s="3" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="P68" s="3"/>
       <c r="Q68" s="3"/>
       <c r="R68" s="3">
-        <v>17791</v>
-      </c>
-      <c r="S68" s="3"/>
+        <v>37830</v>
+      </c>
+      <c r="S68" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T68" s="3"/>
       <c r="U68" s="3"/>
       <c r="V68" s="3"/>
@@ -6040,19 +6108,21 @@
       <c r="X68" s="3"/>
       <c r="Y68" s="3"/>
       <c r="Z68" s="6" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="AA68" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AB68" s="3"/>
+      <c r="AB68" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="69" spans="1:28">
       <c r="A69" s="7">
         <v>67</v>
       </c>
       <c r="B69" s="7">
-        <v>2026060385</v>
+        <v>2026060051</v>
       </c>
       <c r="C69" s="7">
         <v>1</v>
@@ -6061,46 +6131,44 @@
         <v>29</v>
       </c>
       <c r="E69" s="7" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>31</v>
+        <v>138</v>
       </c>
       <c r="G69" s="7" t="s">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="H69" s="7" t="s">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="I69" s="7" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="J69" s="7" t="s">
-        <v>247</v>
+        <v>73</v>
       </c>
       <c r="K69" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L69" s="8" t="s">
-        <v>248</v>
+        <v>223</v>
       </c>
       <c r="M69" s="8" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="N69" s="8" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="O69" s="7" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P69" s="7"/>
       <c r="Q69" s="7"/>
       <c r="R69" s="7">
-        <v>122434</v>
-      </c>
-      <c r="S69" s="7" t="s">
-        <v>40</v>
-      </c>
+        <v>37830</v>
+      </c>
+      <c r="S69" s="7"/>
       <c r="T69" s="7"/>
       <c r="U69" s="7"/>
       <c r="V69" s="7"/>
@@ -6108,9 +6176,11 @@
       <c r="X69" s="7"/>
       <c r="Y69" s="7"/>
       <c r="Z69" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="AA69" s="7"/>
+        <v>211</v>
+      </c>
+      <c r="AA69" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="AB69" s="7"/>
     </row>
     <row r="70" spans="1:28">
@@ -6118,7 +6188,7 @@
         <v>68</v>
       </c>
       <c r="B70" s="3">
-        <v>2026060386</v>
+        <v>2026060047</v>
       </c>
       <c r="C70" s="3">
         <v>1</v>
@@ -6127,34 +6197,34 @@
         <v>29</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>31</v>
+        <v>138</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>117</v>
+        <v>32</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>32</v>
+        <v>82</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>247</v>
+        <v>73</v>
       </c>
       <c r="K70" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L70" s="6" t="s">
-        <v>248</v>
+        <v>223</v>
       </c>
       <c r="M70" s="6" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="O70" s="3" t="s">
         <v>48</v>
@@ -6162,7 +6232,7 @@
       <c r="P70" s="3"/>
       <c r="Q70" s="3"/>
       <c r="R70" s="3">
-        <v>122434</v>
+        <v>45926</v>
       </c>
       <c r="S70" s="3"/>
       <c r="T70" s="3"/>
@@ -6172,19 +6242,21 @@
       <c r="X70" s="3"/>
       <c r="Y70" s="3"/>
       <c r="Z70" s="6" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="AA70" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AB70" s="3"/>
+      <c r="AB70" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="71" spans="1:28">
       <c r="A71" s="7">
         <v>69</v>
       </c>
       <c r="B71" s="7">
-        <v>2026060061</v>
+        <v>2026060046</v>
       </c>
       <c r="C71" s="7">
         <v>1</v>
@@ -6193,34 +6265,34 @@
         <v>29</v>
       </c>
       <c r="E71" s="7" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="G71" s="7" t="s">
-        <v>160</v>
+        <v>32</v>
       </c>
       <c r="H71" s="7" t="s">
-        <v>206</v>
+        <v>82</v>
       </c>
       <c r="I71" s="7" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="J71" s="7" t="s">
-        <v>247</v>
+        <v>73</v>
       </c>
       <c r="K71" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L71" s="8" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="M71" s="8" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="N71" s="8" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="O71" s="7" t="s">
         <v>39</v>
@@ -6228,7 +6300,7 @@
       <c r="P71" s="7"/>
       <c r="Q71" s="7"/>
       <c r="R71" s="7">
-        <v>702</v>
+        <v>45926</v>
       </c>
       <c r="S71" s="7" t="s">
         <v>40</v>
@@ -6240,21 +6312,19 @@
       <c r="X71" s="7"/>
       <c r="Y71" s="7"/>
       <c r="Z71" s="8" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="AA71" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AB71" s="7">
-        <v>1</v>
-      </c>
+      <c r="AB71" s="7"/>
     </row>
     <row r="72" spans="1:28">
       <c r="A72" s="3">
         <v>70</v>
       </c>
       <c r="B72" s="3">
-        <v>2026060062</v>
+        <v>2026060040</v>
       </c>
       <c r="C72" s="3">
         <v>1</v>
@@ -6263,44 +6333,46 @@
         <v>29</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>160</v>
+        <v>232</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>206</v>
+        <v>233</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>247</v>
+        <v>73</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L72" s="6" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="M72" s="6" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="O72" s="3" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="P72" s="3"/>
       <c r="Q72" s="3"/>
       <c r="R72" s="3">
-        <v>702</v>
-      </c>
-      <c r="S72" s="3"/>
+        <v>29640</v>
+      </c>
+      <c r="S72" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T72" s="3"/>
       <c r="U72" s="3"/>
       <c r="V72" s="3"/>
@@ -6308,19 +6380,21 @@
       <c r="X72" s="3"/>
       <c r="Y72" s="3"/>
       <c r="Z72" s="6" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="AA72" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AB72" s="3"/>
+      <c r="AB72" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="73" spans="1:28">
       <c r="A73" s="7">
         <v>71</v>
       </c>
       <c r="B73" s="7">
-        <v>2026060048</v>
+        <v>2026060041</v>
       </c>
       <c r="C73" s="7">
         <v>1</v>
@@ -6329,46 +6403,44 @@
         <v>29</v>
       </c>
       <c r="E73" s="7" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="G73" s="7" t="s">
-        <v>77</v>
+        <v>232</v>
       </c>
       <c r="H73" s="7" t="s">
-        <v>72</v>
+        <v>233</v>
       </c>
       <c r="I73" s="7" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="J73" s="7" t="s">
-        <v>247</v>
+        <v>73</v>
       </c>
       <c r="K73" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L73" s="8" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="M73" s="8" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="N73" s="8" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="O73" s="7" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P73" s="7"/>
       <c r="Q73" s="7"/>
       <c r="R73" s="7">
-        <v>5766</v>
-      </c>
-      <c r="S73" s="7" t="s">
-        <v>40</v>
-      </c>
+        <v>29640</v>
+      </c>
+      <c r="S73" s="7"/>
       <c r="T73" s="7"/>
       <c r="U73" s="7"/>
       <c r="V73" s="7"/>
@@ -6376,21 +6448,19 @@
       <c r="X73" s="7"/>
       <c r="Y73" s="7"/>
       <c r="Z73" s="8" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="AA73" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AB73" s="7">
-        <v>1</v>
-      </c>
+      <c r="AB73" s="7"/>
     </row>
     <row r="74" spans="1:28">
       <c r="A74" s="3">
         <v>72</v>
       </c>
       <c r="B74" s="3">
-        <v>2026060049</v>
+        <v>2026060044</v>
       </c>
       <c r="C74" s="3">
         <v>1</v>
@@ -6399,44 +6469,46 @@
         <v>29</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>77</v>
+        <v>131</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>72</v>
+        <v>32</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>247</v>
+        <v>73</v>
       </c>
       <c r="K74" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L74" s="6" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="M74" s="6" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="O74" s="3" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="P74" s="3"/>
       <c r="Q74" s="3"/>
       <c r="R74" s="3">
-        <v>5766</v>
-      </c>
-      <c r="S74" s="3"/>
+        <v>34235</v>
+      </c>
+      <c r="S74" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T74" s="3"/>
       <c r="U74" s="3"/>
       <c r="V74" s="3"/>
@@ -6444,19 +6516,21 @@
       <c r="X74" s="3"/>
       <c r="Y74" s="3"/>
       <c r="Z74" s="6" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="AA74" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AB74" s="3"/>
+      <c r="AB74" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="75" spans="1:28">
       <c r="A75" s="7">
         <v>73</v>
       </c>
       <c r="B75" s="7">
-        <v>2026060819</v>
+        <v>2026060045</v>
       </c>
       <c r="C75" s="7">
         <v>1</v>
@@ -6465,48 +6539,44 @@
         <v>29</v>
       </c>
       <c r="E75" s="7" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>64</v>
+        <v>138</v>
       </c>
       <c r="G75" s="7" t="s">
-        <v>207</v>
+        <v>131</v>
       </c>
       <c r="H75" s="7" t="s">
-        <v>257</v>
+        <v>32</v>
       </c>
       <c r="I75" s="7" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="J75" s="7" t="s">
-        <v>163</v>
+        <v>73</v>
       </c>
       <c r="K75" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L75" s="8" t="s">
-        <v>259</v>
+        <v>223</v>
       </c>
       <c r="M75" s="8" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N75" s="8" t="s">
-        <v>203</v>
+        <v>264</v>
       </c>
       <c r="O75" s="7" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P75" s="7"/>
-      <c r="Q75" s="7">
-        <v>35761</v>
-      </c>
+      <c r="Q75" s="7"/>
       <c r="R75" s="7">
-        <v>68540</v>
-      </c>
-      <c r="S75" s="7" t="s">
-        <v>40</v>
-      </c>
+        <v>34235</v>
+      </c>
+      <c r="S75" s="7"/>
       <c r="T75" s="7"/>
       <c r="U75" s="7"/>
       <c r="V75" s="7"/>
@@ -6514,9 +6584,11 @@
       <c r="X75" s="7"/>
       <c r="Y75" s="7"/>
       <c r="Z75" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="AA75" s="7"/>
+        <v>211</v>
+      </c>
+      <c r="AA75" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="AB75" s="7"/>
     </row>
     <row r="76" spans="1:28">
@@ -6524,7 +6596,7 @@
         <v>74</v>
       </c>
       <c r="B76" s="3">
-        <v>2026060820</v>
+        <v>2026060042</v>
       </c>
       <c r="C76" s="3">
         <v>1</v>
@@ -6533,46 +6605,46 @@
         <v>29</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>64</v>
+        <v>138</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>207</v>
+        <v>233</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>257</v>
+        <v>131</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="J76" s="3" t="s">
-        <v>163</v>
+        <v>73</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L76" s="6" t="s">
-        <v>259</v>
+        <v>223</v>
       </c>
       <c r="M76" s="6" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>203</v>
+        <v>267</v>
       </c>
       <c r="O76" s="3" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="P76" s="3"/>
-      <c r="Q76" s="3">
-        <v>35761</v>
-      </c>
+      <c r="Q76" s="3"/>
       <c r="R76" s="3">
-        <v>68540</v>
-      </c>
-      <c r="S76" s="3"/>
+        <v>17791</v>
+      </c>
+      <c r="S76" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T76" s="3"/>
       <c r="U76" s="3"/>
       <c r="V76" s="3"/>
@@ -6580,19 +6652,21 @@
       <c r="X76" s="3"/>
       <c r="Y76" s="3"/>
       <c r="Z76" s="6" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="AA76" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AB76" s="3"/>
+      <c r="AB76" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="77" spans="1:28">
       <c r="A77" s="7">
         <v>75</v>
       </c>
       <c r="B77" s="7">
-        <v>2026060922</v>
+        <v>2026060043</v>
       </c>
       <c r="C77" s="7">
         <v>1</v>
@@ -6601,70 +6675,64 @@
         <v>29</v>
       </c>
       <c r="E77" s="7" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>54</v>
+        <v>138</v>
       </c>
       <c r="G77" s="7" t="s">
-        <v>207</v>
+        <v>233</v>
       </c>
       <c r="H77" s="7" t="s">
-        <v>257</v>
+        <v>131</v>
       </c>
       <c r="I77" s="7" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="J77" s="7" t="s">
-        <v>163</v>
+        <v>73</v>
       </c>
       <c r="K77" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L77" s="8" t="s">
-        <v>259</v>
+        <v>223</v>
       </c>
       <c r="M77" s="8" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="N77" s="8" t="s">
-        <v>203</v>
+        <v>267</v>
       </c>
       <c r="O77" s="7" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P77" s="7"/>
-      <c r="Q77" s="7">
-        <v>35761</v>
-      </c>
+      <c r="Q77" s="7"/>
       <c r="R77" s="7">
-        <v>68540</v>
+        <v>17791</v>
       </c>
       <c r="S77" s="7"/>
       <c r="T77" s="7"/>
       <c r="U77" s="7"/>
       <c r="V77" s="7"/>
-      <c r="W77" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="W77" s="7"/>
       <c r="X77" s="7"/>
       <c r="Y77" s="7"/>
       <c r="Z77" s="8" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="AA77" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AB77" s="7">
-        <v>1</v>
-      </c>
+      <c r="AB77" s="7"/>
     </row>
     <row r="78" spans="1:28">
       <c r="A78" s="3">
         <v>76</v>
       </c>
       <c r="B78" s="3">
-        <v>2026060526</v>
+        <v>2026060385</v>
       </c>
       <c r="C78" s="3">
         <v>1</v>
@@ -6673,34 +6741,34 @@
         <v>29</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="F78" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="J78" s="3" t="s">
-        <v>80</v>
+        <v>269</v>
       </c>
       <c r="K78" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L78" s="6" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="M78" s="6" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="O78" s="3" t="s">
         <v>39</v>
@@ -6708,7 +6776,7 @@
       <c r="P78" s="3"/>
       <c r="Q78" s="3"/>
       <c r="R78" s="3">
-        <v>33686</v>
+        <v>122434</v>
       </c>
       <c r="S78" s="3" t="s">
         <v>40</v>
@@ -6720,7 +6788,7 @@
       <c r="X78" s="3"/>
       <c r="Y78" s="3"/>
       <c r="Z78" s="6" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="AA78" s="3"/>
       <c r="AB78" s="3"/>
@@ -6730,7 +6798,7 @@
         <v>77</v>
       </c>
       <c r="B79" s="7">
-        <v>2026060527</v>
+        <v>2026060386</v>
       </c>
       <c r="C79" s="7">
         <v>1</v>
@@ -6739,34 +6807,34 @@
         <v>29</v>
       </c>
       <c r="E79" s="7" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="F79" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G79" s="7" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="H79" s="7" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="I79" s="7" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="J79" s="7" t="s">
-        <v>80</v>
+        <v>269</v>
       </c>
       <c r="K79" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L79" s="8" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="M79" s="8" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="N79" s="8" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="O79" s="7" t="s">
         <v>48</v>
@@ -6774,7 +6842,7 @@
       <c r="P79" s="7"/>
       <c r="Q79" s="7"/>
       <c r="R79" s="7">
-        <v>33686</v>
+        <v>122434</v>
       </c>
       <c r="S79" s="7"/>
       <c r="T79" s="7"/>
@@ -6784,7 +6852,7 @@
       <c r="X79" s="7"/>
       <c r="Y79" s="7"/>
       <c r="Z79" s="8" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="AA79" s="7" t="s">
         <v>40</v>
@@ -6796,7 +6864,7 @@
         <v>78</v>
       </c>
       <c r="B80" s="3">
-        <v>2026060409</v>
+        <v>2026060061</v>
       </c>
       <c r="C80" s="3">
         <v>1</v>
@@ -6805,44 +6873,46 @@
         <v>29</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>31</v>
+        <v>138</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>73</v>
+        <v>174</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>160</v>
+        <v>220</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="J80" s="3" t="s">
-        <v>80</v>
+        <v>269</v>
       </c>
       <c r="K80" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L80" s="6" t="s">
-        <v>248</v>
+        <v>223</v>
       </c>
       <c r="M80" s="6" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="O80" s="3" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="P80" s="3"/>
       <c r="Q80" s="3"/>
       <c r="R80" s="3">
-        <v>19776</v>
-      </c>
-      <c r="S80" s="3"/>
+        <v>702</v>
+      </c>
+      <c r="S80" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T80" s="3"/>
       <c r="U80" s="3"/>
       <c r="V80" s="3"/>
@@ -6850,7 +6920,7 @@
       <c r="X80" s="3"/>
       <c r="Y80" s="3"/>
       <c r="Z80" s="6" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="AA80" s="3" t="s">
         <v>40</v>
@@ -6864,7 +6934,7 @@
         <v>79</v>
       </c>
       <c r="B81" s="7">
-        <v>2026060408</v>
+        <v>2026060062</v>
       </c>
       <c r="C81" s="7">
         <v>1</v>
@@ -6873,46 +6943,44 @@
         <v>29</v>
       </c>
       <c r="E81" s="7" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>31</v>
+        <v>138</v>
       </c>
       <c r="G81" s="7" t="s">
-        <v>73</v>
+        <v>174</v>
       </c>
       <c r="H81" s="7" t="s">
-        <v>160</v>
+        <v>220</v>
       </c>
       <c r="I81" s="7" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="J81" s="7" t="s">
-        <v>80</v>
+        <v>269</v>
       </c>
       <c r="K81" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L81" s="8" t="s">
-        <v>248</v>
+        <v>223</v>
       </c>
       <c r="M81" s="8" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="N81" s="8" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="O81" s="7" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P81" s="7"/>
       <c r="Q81" s="7"/>
       <c r="R81" s="7">
-        <v>19776</v>
-      </c>
-      <c r="S81" s="7" t="s">
-        <v>40</v>
-      </c>
+        <v>702</v>
+      </c>
+      <c r="S81" s="7"/>
       <c r="T81" s="7"/>
       <c r="U81" s="7"/>
       <c r="V81" s="7"/>
@@ -6920,9 +6988,11 @@
       <c r="X81" s="7"/>
       <c r="Y81" s="7"/>
       <c r="Z81" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="AA81" s="7"/>
+        <v>211</v>
+      </c>
+      <c r="AA81" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="AB81" s="7"/>
     </row>
     <row r="82" spans="1:28">
@@ -6930,7 +7000,7 @@
         <v>80</v>
       </c>
       <c r="B82" s="3">
-        <v>2026060389</v>
+        <v>2026060048</v>
       </c>
       <c r="C82" s="3">
         <v>1</v>
@@ -6939,34 +7009,34 @@
         <v>29</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>31</v>
+        <v>138</v>
       </c>
       <c r="G82" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="H82" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="H82" s="3" t="s">
-        <v>72</v>
-      </c>
       <c r="I82" s="3" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="J82" s="3" t="s">
-        <v>80</v>
+        <v>269</v>
       </c>
       <c r="K82" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L82" s="6" t="s">
-        <v>248</v>
+        <v>223</v>
       </c>
       <c r="M82" s="6" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="O82" s="3" t="s">
         <v>39</v>
@@ -6974,7 +7044,7 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3">
-        <v>92779</v>
+        <v>5766</v>
       </c>
       <c r="S82" s="3" t="s">
         <v>40</v>
@@ -6986,17 +7056,21 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="AA82" s="3"/>
-      <c r="AB82" s="3"/>
+        <v>211</v>
+      </c>
+      <c r="AA82" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB82" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="83" spans="1:28">
       <c r="A83" s="7">
         <v>81</v>
       </c>
       <c r="B83" s="7">
-        <v>2026060390</v>
+        <v>2026060049</v>
       </c>
       <c r="C83" s="7">
         <v>1</v>
@@ -7005,34 +7079,34 @@
         <v>29</v>
       </c>
       <c r="E83" s="7" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>31</v>
+        <v>138</v>
       </c>
       <c r="G83" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="H83" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="H83" s="7" t="s">
-        <v>72</v>
-      </c>
       <c r="I83" s="7" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="J83" s="7" t="s">
-        <v>80</v>
+        <v>269</v>
       </c>
       <c r="K83" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L83" s="8" t="s">
-        <v>248</v>
+        <v>223</v>
       </c>
       <c r="M83" s="8" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="N83" s="8" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="O83" s="7" t="s">
         <v>48</v>
@@ -7040,7 +7114,7 @@
       <c r="P83" s="7"/>
       <c r="Q83" s="7"/>
       <c r="R83" s="7">
-        <v>92779</v>
+        <v>5766</v>
       </c>
       <c r="S83" s="7"/>
       <c r="T83" s="7"/>
@@ -7050,7 +7124,7 @@
       <c r="X83" s="7"/>
       <c r="Y83" s="7"/>
       <c r="Z83" s="8" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="AA83" s="7" t="s">
         <v>40</v>
@@ -7062,7 +7136,7 @@
         <v>82</v>
       </c>
       <c r="B84" s="3">
-        <v>2026060853</v>
+        <v>2026060819</v>
       </c>
       <c r="C84" s="3">
         <v>1</v>
@@ -7071,68 +7145,66 @@
         <v>29</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>136</v>
+        <v>221</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>222</v>
+        <v>279</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="J84" s="3" t="s">
-        <v>80</v>
+        <v>177</v>
       </c>
       <c r="K84" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L84" s="6" t="s">
-        <v>248</v>
+        <v>281</v>
       </c>
       <c r="M84" s="6" t="s">
-        <v>269</v>
+        <v>282</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>270</v>
+        <v>217</v>
       </c>
       <c r="O84" s="3" t="s">
         <v>39</v>
       </c>
       <c r="P84" s="3"/>
-      <c r="Q84" s="3"/>
+      <c r="Q84" s="3">
+        <v>35761</v>
+      </c>
       <c r="R84" s="3">
-        <v>92779</v>
-      </c>
-      <c r="S84" s="3"/>
+        <v>68540</v>
+      </c>
+      <c r="S84" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T84" s="3"/>
       <c r="U84" s="3"/>
       <c r="V84" s="3"/>
       <c r="W84" s="3"/>
       <c r="X84" s="3"/>
-      <c r="Y84" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="Y84" s="3"/>
       <c r="Z84" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="AA84" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB84" s="3">
-        <v>1</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="AA84" s="3"/>
+      <c r="AB84" s="3"/>
     </row>
     <row r="85" spans="1:28">
       <c r="A85" s="7">
         <v>83</v>
       </c>
       <c r="B85" s="7">
-        <v>2026060383</v>
+        <v>2026060820</v>
       </c>
       <c r="C85" s="7">
         <v>1</v>
@@ -7141,46 +7213,46 @@
         <v>29</v>
       </c>
       <c r="E85" s="7" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="G85" s="7" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="H85" s="7" t="s">
-        <v>117</v>
+        <v>279</v>
       </c>
       <c r="I85" s="7" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="J85" s="7" t="s">
-        <v>80</v>
+        <v>177</v>
       </c>
       <c r="K85" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L85" s="8" t="s">
-        <v>248</v>
+        <v>281</v>
       </c>
       <c r="M85" s="8" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="N85" s="8" t="s">
-        <v>274</v>
+        <v>217</v>
       </c>
       <c r="O85" s="7" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P85" s="7"/>
-      <c r="Q85" s="7"/>
+      <c r="Q85" s="7">
+        <v>35761</v>
+      </c>
       <c r="R85" s="7">
-        <v>207716</v>
-      </c>
-      <c r="S85" s="7" t="s">
-        <v>40</v>
-      </c>
+        <v>68540</v>
+      </c>
+      <c r="S85" s="7"/>
       <c r="T85" s="7"/>
       <c r="U85" s="7"/>
       <c r="V85" s="7"/>
@@ -7188,9 +7260,11 @@
       <c r="X85" s="7"/>
       <c r="Y85" s="7"/>
       <c r="Z85" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="AA85" s="7"/>
+        <v>211</v>
+      </c>
+      <c r="AA85" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="AB85" s="7"/>
     </row>
     <row r="86" spans="1:28">
@@ -7198,7 +7272,7 @@
         <v>84</v>
       </c>
       <c r="B86" s="3">
-        <v>2026060384</v>
+        <v>2026060922</v>
       </c>
       <c r="C86" s="3">
         <v>1</v>
@@ -7207,64 +7281,70 @@
         <v>29</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>117</v>
+        <v>279</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="J86" s="3" t="s">
-        <v>80</v>
+        <v>177</v>
       </c>
       <c r="K86" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L86" s="6" t="s">
-        <v>248</v>
+        <v>281</v>
       </c>
       <c r="M86" s="6" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>274</v>
+        <v>217</v>
       </c>
       <c r="O86" s="3" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="P86" s="3"/>
-      <c r="Q86" s="3"/>
+      <c r="Q86" s="3">
+        <v>35761</v>
+      </c>
       <c r="R86" s="3">
-        <v>207716</v>
+        <v>68540</v>
       </c>
       <c r="S86" s="3"/>
       <c r="T86" s="3"/>
       <c r="U86" s="3"/>
       <c r="V86" s="3"/>
-      <c r="W86" s="3"/>
+      <c r="W86" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="X86" s="3"/>
       <c r="Y86" s="3"/>
       <c r="Z86" s="6" t="s">
-        <v>197</v>
+        <v>219</v>
       </c>
       <c r="AA86" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AB86" s="3"/>
+      <c r="AB86" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="87" spans="1:28">
       <c r="A87" s="7">
         <v>85</v>
       </c>
       <c r="B87" s="7">
-        <v>2026060569</v>
+        <v>2026060526</v>
       </c>
       <c r="C87" s="7">
         <v>1</v>
@@ -7273,34 +7353,34 @@
         <v>29</v>
       </c>
       <c r="E87" s="7" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="F87" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G87" s="7" t="s">
-        <v>207</v>
+        <v>139</v>
       </c>
       <c r="H87" s="7" t="s">
-        <v>257</v>
+        <v>49</v>
       </c>
       <c r="I87" s="7" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="J87" s="7" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="K87" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L87" s="8" t="s">
-        <v>248</v>
+        <v>284</v>
       </c>
       <c r="M87" s="8" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="N87" s="8" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="O87" s="7" t="s">
         <v>39</v>
@@ -7308,33 +7388,29 @@
       <c r="P87" s="7"/>
       <c r="Q87" s="7"/>
       <c r="R87" s="7">
-        <v>207716</v>
-      </c>
-      <c r="S87" s="7"/>
+        <v>33686</v>
+      </c>
+      <c r="S87" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T87" s="7"/>
-      <c r="U87" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="U87" s="7"/>
       <c r="V87" s="7"/>
       <c r="W87" s="7"/>
       <c r="X87" s="7"/>
       <c r="Y87" s="7"/>
       <c r="Z87" s="8" t="s">
-        <v>227</v>
-      </c>
-      <c r="AA87" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB87" s="7">
-        <v>1</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="AA87" s="7"/>
+      <c r="AB87" s="7"/>
     </row>
     <row r="88" spans="1:28">
       <c r="A88" s="3">
         <v>86</v>
       </c>
       <c r="B88" s="3">
-        <v>2026060387</v>
+        <v>2026060527</v>
       </c>
       <c r="C88" s="3">
         <v>1</v>
@@ -7343,46 +7419,44 @@
         <v>29</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="F88" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>32</v>
+        <v>139</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="J88" s="3" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="K88" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L88" s="6" t="s">
-        <v>248</v>
+        <v>284</v>
       </c>
       <c r="M88" s="6" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="O88" s="3" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P88" s="3"/>
       <c r="Q88" s="3"/>
       <c r="R88" s="3">
-        <v>152071</v>
-      </c>
-      <c r="S88" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>33686</v>
+      </c>
+      <c r="S88" s="3"/>
       <c r="T88" s="3"/>
       <c r="U88" s="3"/>
       <c r="V88" s="3"/>
@@ -7390,9 +7464,11 @@
       <c r="X88" s="3"/>
       <c r="Y88" s="3"/>
       <c r="Z88" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="AA88" s="3"/>
+        <v>211</v>
+      </c>
+      <c r="AA88" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="AB88" s="3"/>
     </row>
     <row r="89" spans="1:28">
@@ -7400,7 +7476,7 @@
         <v>87</v>
       </c>
       <c r="B89" s="7">
-        <v>2026060388</v>
+        <v>2026060408</v>
       </c>
       <c r="C89" s="7">
         <v>1</v>
@@ -7409,44 +7485,46 @@
         <v>29</v>
       </c>
       <c r="E89" s="7" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="F89" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G89" s="7" t="s">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="H89" s="7" t="s">
-        <v>77</v>
+        <v>174</v>
       </c>
       <c r="I89" s="7" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="J89" s="7" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="K89" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L89" s="8" t="s">
-        <v>248</v>
+        <v>270</v>
       </c>
       <c r="M89" s="8" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="N89" s="8" t="s">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="O89" s="7" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="P89" s="7"/>
       <c r="Q89" s="7"/>
       <c r="R89" s="7">
-        <v>152071</v>
-      </c>
-      <c r="S89" s="7"/>
+        <v>19776</v>
+      </c>
+      <c r="S89" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T89" s="7"/>
       <c r="U89" s="7"/>
       <c r="V89" s="7"/>
@@ -7454,11 +7532,9 @@
       <c r="X89" s="7"/>
       <c r="Y89" s="7"/>
       <c r="Z89" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="AA89" s="7" t="s">
-        <v>40</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="AA89" s="7"/>
       <c r="AB89" s="7"/>
     </row>
     <row r="90" spans="1:28">
@@ -7466,7 +7542,7 @@
         <v>88</v>
       </c>
       <c r="B90" s="3">
-        <v>2026060570</v>
+        <v>2026060409</v>
       </c>
       <c r="C90" s="3">
         <v>1</v>
@@ -7475,68 +7551,64 @@
         <v>29</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="F90" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>257</v>
+        <v>78</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>93</v>
+        <v>174</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="J90" s="3" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="K90" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L90" s="6" t="s">
-        <v>248</v>
+        <v>270</v>
       </c>
       <c r="M90" s="6" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="O90" s="3" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3">
-        <v>152071</v>
+        <v>19776</v>
       </c>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-      <c r="U90" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="6" t="s">
-        <v>227</v>
+        <v>211</v>
       </c>
       <c r="AA90" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AB90" s="3">
-        <v>1</v>
-      </c>
+      <c r="AB90" s="3"/>
     </row>
     <row r="91" spans="1:28">
       <c r="A91" s="7">
         <v>89</v>
       </c>
       <c r="B91" s="7">
-        <v>2026060081</v>
+        <v>2026060389</v>
       </c>
       <c r="C91" s="7">
         <v>1</v>
@@ -7545,34 +7617,34 @@
         <v>29</v>
       </c>
       <c r="E91" s="7" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="F91" s="7" t="s">
-        <v>124</v>
+        <v>31</v>
       </c>
       <c r="G91" s="7" t="s">
-        <v>257</v>
+        <v>82</v>
       </c>
       <c r="H91" s="7" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="I91" s="7" t="s">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="J91" s="7" t="s">
-        <v>279</v>
+        <v>85</v>
       </c>
       <c r="K91" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L91" s="8" t="s">
-        <v>224</v>
+        <v>270</v>
       </c>
       <c r="M91" s="8" t="s">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="N91" s="8" t="s">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="O91" s="7" t="s">
         <v>39</v>
@@ -7580,7 +7652,7 @@
       <c r="P91" s="7"/>
       <c r="Q91" s="7"/>
       <c r="R91" s="7">
-        <v>48</v>
+        <v>92779</v>
       </c>
       <c r="S91" s="7" t="s">
         <v>40</v>
@@ -7592,7 +7664,7 @@
       <c r="X91" s="7"/>
       <c r="Y91" s="7"/>
       <c r="Z91" s="8" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="AA91" s="7"/>
       <c r="AB91" s="7"/>
@@ -7602,7 +7674,7 @@
         <v>90</v>
       </c>
       <c r="B92" s="3">
-        <v>2026060082</v>
+        <v>2026060390</v>
       </c>
       <c r="C92" s="3">
         <v>1</v>
@@ -7611,34 +7683,34 @@
         <v>29</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>124</v>
+        <v>31</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>257</v>
+        <v>82</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="J92" s="3" t="s">
-        <v>279</v>
+        <v>85</v>
       </c>
       <c r="K92" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L92" s="6" t="s">
-        <v>224</v>
+        <v>270</v>
       </c>
       <c r="M92" s="6" t="s">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="O92" s="3" t="s">
         <v>48</v>
@@ -7646,7 +7718,7 @@
       <c r="P92" s="3"/>
       <c r="Q92" s="3"/>
       <c r="R92" s="3">
-        <v>48</v>
+        <v>92779</v>
       </c>
       <c r="S92" s="3"/>
       <c r="T92" s="3"/>
@@ -7656,7 +7728,7 @@
       <c r="X92" s="3"/>
       <c r="Y92" s="3"/>
       <c r="Z92" s="6" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="AA92" s="3" t="s">
         <v>40</v>
@@ -7668,7 +7740,7 @@
         <v>91</v>
       </c>
       <c r="B93" s="7">
-        <v>2026060145</v>
+        <v>2026060853</v>
       </c>
       <c r="C93" s="7">
         <v>1</v>
@@ -7677,34 +7749,34 @@
         <v>29</v>
       </c>
       <c r="E93" s="7" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="F93" s="7" t="s">
-        <v>124</v>
+        <v>69</v>
       </c>
       <c r="G93" s="7" t="s">
-        <v>83</v>
+        <v>150</v>
       </c>
       <c r="H93" s="7" t="s">
-        <v>221</v>
+        <v>241</v>
       </c>
       <c r="I93" s="7" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="J93" s="7" t="s">
-        <v>170</v>
+        <v>85</v>
       </c>
       <c r="K93" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L93" s="8" t="s">
-        <v>224</v>
+        <v>270</v>
       </c>
       <c r="M93" s="8" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="N93" s="8" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="O93" s="7" t="s">
         <v>39</v>
@@ -7712,19 +7784,19 @@
       <c r="P93" s="7"/>
       <c r="Q93" s="7"/>
       <c r="R93" s="7">
-        <v>38244</v>
+        <v>92779</v>
       </c>
       <c r="S93" s="7"/>
       <c r="T93" s="7"/>
-      <c r="U93" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="U93" s="7"/>
       <c r="V93" s="7"/>
       <c r="W93" s="7"/>
       <c r="X93" s="7"/>
-      <c r="Y93" s="7"/>
+      <c r="Y93" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="Z93" s="8" t="s">
-        <v>227</v>
+        <v>293</v>
       </c>
       <c r="AA93" s="7" t="s">
         <v>40</v>
@@ -7738,7 +7810,7 @@
         <v>92</v>
       </c>
       <c r="B94" s="3">
-        <v>2026060144</v>
+        <v>2026060384</v>
       </c>
       <c r="C94" s="3">
         <v>1</v>
@@ -7747,54 +7819,52 @@
         <v>29</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>124</v>
+        <v>31</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>125</v>
+        <v>233</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="J94" s="3" t="s">
-        <v>170</v>
+        <v>85</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L94" s="6" t="s">
-        <v>224</v>
+        <v>270</v>
       </c>
       <c r="M94" s="6" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="O94" s="3" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P94" s="3"/>
       <c r="Q94" s="3"/>
       <c r="R94" s="3">
-        <v>386259</v>
+        <v>207716</v>
       </c>
       <c r="S94" s="3"/>
       <c r="T94" s="3"/>
-      <c r="U94" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="U94" s="3"/>
       <c r="V94" s="3"/>
       <c r="W94" s="3"/>
       <c r="X94" s="3"/>
       <c r="Y94" s="3"/>
       <c r="Z94" s="6" t="s">
-        <v>227</v>
+        <v>211</v>
       </c>
       <c r="AA94" s="3" t="s">
         <v>40</v>
@@ -7808,7 +7878,7 @@
         <v>93</v>
       </c>
       <c r="B95" s="7">
-        <v>2026060143</v>
+        <v>2026060383</v>
       </c>
       <c r="C95" s="7">
         <v>1</v>
@@ -7817,34 +7887,34 @@
         <v>29</v>
       </c>
       <c r="E95" s="7" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>124</v>
+        <v>31</v>
       </c>
       <c r="G95" s="7" t="s">
-        <v>180</v>
+        <v>233</v>
       </c>
       <c r="H95" s="7" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="I95" s="7" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="J95" s="7" t="s">
-        <v>170</v>
+        <v>85</v>
       </c>
       <c r="K95" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L95" s="8" t="s">
-        <v>224</v>
+        <v>270</v>
       </c>
       <c r="M95" s="8" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="N95" s="8" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="O95" s="7" t="s">
         <v>39</v>
@@ -7852,33 +7922,29 @@
       <c r="P95" s="7"/>
       <c r="Q95" s="7"/>
       <c r="R95" s="7">
-        <v>381383</v>
-      </c>
-      <c r="S95" s="7"/>
+        <v>207716</v>
+      </c>
+      <c r="S95" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T95" s="7"/>
-      <c r="U95" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="U95" s="7"/>
       <c r="V95" s="7"/>
       <c r="W95" s="7"/>
       <c r="X95" s="7"/>
       <c r="Y95" s="7"/>
       <c r="Z95" s="8" t="s">
-        <v>227</v>
-      </c>
-      <c r="AA95" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB95" s="7">
-        <v>1</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="AA95" s="7"/>
+      <c r="AB95" s="7"/>
     </row>
     <row r="96" spans="1:28">
       <c r="A96" s="3">
         <v>94</v>
       </c>
       <c r="B96" s="3">
-        <v>2026060142</v>
+        <v>2026060569</v>
       </c>
       <c r="C96" s="3">
         <v>1</v>
@@ -7887,34 +7953,34 @@
         <v>29</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>124</v>
+        <v>31</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>179</v>
+        <v>221</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>180</v>
+        <v>279</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="J96" s="3" t="s">
-        <v>170</v>
+        <v>85</v>
       </c>
       <c r="K96" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L96" s="6" t="s">
-        <v>224</v>
+        <v>270</v>
       </c>
       <c r="M96" s="6" t="s">
-        <v>280</v>
+        <v>295</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="O96" s="3" t="s">
         <v>39</v>
@@ -7922,7 +7988,7 @@
       <c r="P96" s="3"/>
       <c r="Q96" s="3"/>
       <c r="R96" s="3">
-        <v>31873</v>
+        <v>207716</v>
       </c>
       <c r="S96" s="3"/>
       <c r="T96" s="3"/>
@@ -7934,7 +8000,7 @@
       <c r="X96" s="3"/>
       <c r="Y96" s="3"/>
       <c r="Z96" s="6" t="s">
-        <v>227</v>
+        <v>246</v>
       </c>
       <c r="AA96" s="3" t="s">
         <v>40</v>
@@ -7948,7 +8014,7 @@
         <v>95</v>
       </c>
       <c r="B97" s="7">
-        <v>2026060141</v>
+        <v>2026060387</v>
       </c>
       <c r="C97" s="7">
         <v>1</v>
@@ -7957,34 +8023,34 @@
         <v>29</v>
       </c>
       <c r="E97" s="7" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="F97" s="7" t="s">
-        <v>124</v>
+        <v>31</v>
       </c>
       <c r="G97" s="7" t="s">
-        <v>291</v>
+        <v>32</v>
       </c>
       <c r="H97" s="7" t="s">
-        <v>179</v>
+        <v>82</v>
       </c>
       <c r="I97" s="7" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="J97" s="7" t="s">
-        <v>170</v>
+        <v>85</v>
       </c>
       <c r="K97" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L97" s="8" t="s">
-        <v>224</v>
+        <v>270</v>
       </c>
       <c r="M97" s="8" t="s">
-        <v>283</v>
+        <v>298</v>
       </c>
       <c r="N97" s="8" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="O97" s="7" t="s">
         <v>39</v>
@@ -7992,33 +8058,29 @@
       <c r="P97" s="7"/>
       <c r="Q97" s="7"/>
       <c r="R97" s="7">
-        <v>30842</v>
-      </c>
-      <c r="S97" s="7"/>
+        <v>152071</v>
+      </c>
+      <c r="S97" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T97" s="7"/>
-      <c r="U97" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="U97" s="7"/>
       <c r="V97" s="7"/>
       <c r="W97" s="7"/>
       <c r="X97" s="7"/>
       <c r="Y97" s="7"/>
       <c r="Z97" s="8" t="s">
-        <v>227</v>
-      </c>
-      <c r="AA97" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB97" s="7">
-        <v>1</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="AA97" s="7"/>
+      <c r="AB97" s="7"/>
     </row>
     <row r="98" spans="1:28">
       <c r="A98" s="3">
         <v>96</v>
       </c>
       <c r="B98" s="3">
-        <v>2026060898</v>
+        <v>2026060388</v>
       </c>
       <c r="C98" s="3">
         <v>1</v>
@@ -8027,66 +8089,64 @@
         <v>29</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="G98" s="3" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="J98" s="3"/>
-      <c r="K98" s="3"/>
+        <v>297</v>
+      </c>
+      <c r="J98" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="K98" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="L98" s="6" t="s">
-        <v>96</v>
+        <v>270</v>
       </c>
       <c r="M98" s="6" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="O98" s="3" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P98" s="3"/>
       <c r="Q98" s="3"/>
       <c r="R98" s="3">
-        <v>0</v>
-      </c>
-      <c r="S98" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>152071</v>
+      </c>
+      <c r="S98" s="3"/>
       <c r="T98" s="3"/>
       <c r="U98" s="3"/>
       <c r="V98" s="3"/>
       <c r="W98" s="3"/>
       <c r="X98" s="3"/>
-      <c r="Y98" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="Y98" s="3"/>
       <c r="Z98" s="6" t="s">
-        <v>105</v>
+        <v>211</v>
       </c>
       <c r="AA98" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AB98" s="3">
-        <v>1</v>
-      </c>
+      <c r="AB98" s="3"/>
     </row>
     <row r="99" spans="1:28">
       <c r="A99" s="7">
         <v>97</v>
       </c>
       <c r="B99" s="7">
-        <v>2026060899</v>
+        <v>2026060570</v>
       </c>
       <c r="C99" s="7">
         <v>1</v>
@@ -8095,24 +8155,28 @@
         <v>29</v>
       </c>
       <c r="E99" s="7" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="F99" s="7" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="G99" s="7" t="s">
-        <v>72</v>
+        <v>279</v>
       </c>
       <c r="H99" s="7" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="I99" s="7" t="s">
         <v>297</v>
       </c>
-      <c r="J99" s="7"/>
-      <c r="K99" s="7"/>
+      <c r="J99" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="K99" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="L99" s="8" t="s">
-        <v>96</v>
+        <v>270</v>
       </c>
       <c r="M99" s="8" t="s">
         <v>298</v>
@@ -8126,21 +8190,19 @@
       <c r="P99" s="7"/>
       <c r="Q99" s="7"/>
       <c r="R99" s="7">
-        <v>0</v>
-      </c>
-      <c r="S99" s="7" t="s">
-        <v>40</v>
-      </c>
+        <v>152071</v>
+      </c>
+      <c r="S99" s="7"/>
       <c r="T99" s="7"/>
-      <c r="U99" s="7"/>
+      <c r="U99" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="V99" s="7"/>
       <c r="W99" s="7"/>
       <c r="X99" s="7"/>
-      <c r="Y99" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="Y99" s="7"/>
       <c r="Z99" s="8" t="s">
-        <v>105</v>
+        <v>246</v>
       </c>
       <c r="AA99" s="7" t="s">
         <v>40</v>
@@ -8154,7 +8216,7 @@
         <v>98</v>
       </c>
       <c r="B100" s="3">
-        <v>2026060905</v>
+        <v>2026060081</v>
       </c>
       <c r="C100" s="3">
         <v>1</v>
@@ -8163,30 +8225,34 @@
         <v>29</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="F100" s="3" t="s">
-        <v>54</v>
+        <v>138</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>73</v>
+        <v>279</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>160</v>
+        <v>102</v>
       </c>
       <c r="I100" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="J100" s="3"/>
-      <c r="K100" s="3"/>
+      <c r="J100" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="L100" s="6" t="s">
-        <v>96</v>
+        <v>243</v>
       </c>
       <c r="M100" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O100" s="3" t="s">
         <v>39</v>
@@ -8194,7 +8260,7 @@
       <c r="P100" s="3"/>
       <c r="Q100" s="3"/>
       <c r="R100" s="3">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="S100" s="3" t="s">
         <v>40</v>
@@ -8204,25 +8270,19 @@
       <c r="V100" s="3"/>
       <c r="W100" s="3"/>
       <c r="X100" s="3"/>
-      <c r="Y100" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="Y100" s="3"/>
       <c r="Z100" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="AA100" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB100" s="3">
-        <v>1</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="AA100" s="3"/>
+      <c r="AB100" s="3"/>
     </row>
     <row r="101" spans="1:28">
       <c r="A101" s="7">
         <v>99</v>
       </c>
       <c r="B101" s="7">
-        <v>2026060510</v>
+        <v>2026060082</v>
       </c>
       <c r="C101" s="7">
         <v>1</v>
@@ -8231,42 +8291,44 @@
         <v>29</v>
       </c>
       <c r="E101" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="F101" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="G101" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="H101" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="I101" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="J101" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="K101" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L101" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="M101" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="N101" s="8" t="s">
         <v>303</v>
       </c>
-      <c r="F101" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G101" s="7" t="s">
-        <v>304</v>
-      </c>
-      <c r="H101" s="7" t="s">
-        <v>305</v>
-      </c>
-      <c r="I101" s="7" t="s">
-        <v>306</v>
-      </c>
-      <c r="J101" s="7"/>
-      <c r="K101" s="7"/>
-      <c r="L101" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="M101" s="8" t="s">
-        <v>307</v>
-      </c>
-      <c r="N101" s="8" t="s">
-        <v>308</v>
-      </c>
       <c r="O101" s="7" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P101" s="7"/>
       <c r="Q101" s="7"/>
       <c r="R101" s="7">
-        <v>0</v>
-      </c>
-      <c r="S101" s="7" t="s">
-        <v>40</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="S101" s="7"/>
       <c r="T101" s="7"/>
       <c r="U101" s="7"/>
       <c r="V101" s="7"/>
@@ -8274,21 +8336,19 @@
       <c r="X101" s="7"/>
       <c r="Y101" s="7"/>
       <c r="Z101" s="8" t="s">
-        <v>105</v>
+        <v>211</v>
       </c>
       <c r="AA101" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AB101" s="7">
-        <v>1</v>
-      </c>
+      <c r="AB101" s="7"/>
     </row>
     <row r="102" spans="1:28">
       <c r="A102" s="3">
         <v>100</v>
       </c>
       <c r="B102" s="3">
-        <v>2026060850</v>
+        <v>2026060145</v>
       </c>
       <c r="C102" s="3">
         <v>1</v>
@@ -8297,30 +8357,34 @@
         <v>29</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>303</v>
+        <v>207</v>
       </c>
       <c r="F102" s="3" t="s">
-        <v>64</v>
+        <v>138</v>
       </c>
       <c r="G102" s="3" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>221</v>
+        <v>103</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="J102" s="3"/>
-      <c r="K102" s="3"/>
+        <v>304</v>
+      </c>
+      <c r="J102" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="K102" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="L102" s="6" t="s">
-        <v>96</v>
+        <v>243</v>
       </c>
       <c r="M102" s="6" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="O102" s="3" t="s">
         <v>39</v>
@@ -8328,11 +8392,9 @@
       <c r="P102" s="3"/>
       <c r="Q102" s="3"/>
       <c r="R102" s="3">
-        <v>0</v>
-      </c>
-      <c r="S102" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>38244</v>
+      </c>
+      <c r="S102" s="3"/>
       <c r="T102" s="3"/>
       <c r="U102" s="3" t="s">
         <v>40</v>
@@ -8342,7 +8404,7 @@
       <c r="X102" s="3"/>
       <c r="Y102" s="3"/>
       <c r="Z102" s="6" t="s">
-        <v>312</v>
+        <v>246</v>
       </c>
       <c r="AA102" s="3" t="s">
         <v>40</v>
@@ -8356,7 +8418,7 @@
         <v>101</v>
       </c>
       <c r="B103" s="7">
-        <v>2026060831</v>
+        <v>2026060144</v>
       </c>
       <c r="C103" s="7">
         <v>1</v>
@@ -8365,52 +8427,54 @@
         <v>29</v>
       </c>
       <c r="E103" s="7" t="s">
-        <v>303</v>
+        <v>207</v>
       </c>
       <c r="F103" s="7" t="s">
-        <v>54</v>
+        <v>138</v>
       </c>
       <c r="G103" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H103" s="7" t="s">
-        <v>207</v>
+        <v>88</v>
       </c>
       <c r="I103" s="7" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="J103" s="7" t="s">
-        <v>314</v>
+        <v>184</v>
       </c>
       <c r="K103" s="7" t="s">
-        <v>315</v>
+        <v>36</v>
       </c>
       <c r="L103" s="8" t="s">
-        <v>96</v>
+        <v>243</v>
       </c>
       <c r="M103" s="8" t="s">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="N103" s="8" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="O103" s="7" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="P103" s="7"/>
       <c r="Q103" s="7"/>
       <c r="R103" s="7">
-        <v>0</v>
+        <v>386259</v>
       </c>
       <c r="S103" s="7"/>
       <c r="T103" s="7"/>
-      <c r="U103" s="7"/>
+      <c r="U103" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="V103" s="7"/>
       <c r="W103" s="7"/>
       <c r="X103" s="7"/>
       <c r="Y103" s="7"/>
       <c r="Z103" s="8" t="s">
-        <v>318</v>
+        <v>246</v>
       </c>
       <c r="AA103" s="7" t="s">
         <v>40</v>
@@ -8424,7 +8488,7 @@
         <v>102</v>
       </c>
       <c r="B104" s="3">
-        <v>2026060475</v>
+        <v>2026060143</v>
       </c>
       <c r="C104" s="3">
         <v>1</v>
@@ -8433,30 +8497,34 @@
         <v>29</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>303</v>
+        <v>207</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>31</v>
+        <v>138</v>
       </c>
       <c r="G104" s="3" t="s">
-        <v>93</v>
+        <v>194</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>319</v>
+        <v>139</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="J104" s="3"/>
-      <c r="K104" s="3"/>
+        <v>309</v>
+      </c>
+      <c r="J104" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="K104" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="L104" s="6" t="s">
-        <v>96</v>
+        <v>243</v>
       </c>
       <c r="M104" s="6" t="s">
-        <v>321</v>
+        <v>305</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="O104" s="3" t="s">
         <v>39</v>
@@ -8464,19 +8532,19 @@
       <c r="P104" s="3"/>
       <c r="Q104" s="3"/>
       <c r="R104" s="3">
-        <v>0</v>
-      </c>
-      <c r="S104" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>381383</v>
+      </c>
+      <c r="S104" s="3"/>
       <c r="T104" s="3"/>
-      <c r="U104" s="3"/>
+      <c r="U104" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="V104" s="3"/>
       <c r="W104" s="3"/>
       <c r="X104" s="3"/>
       <c r="Y104" s="3"/>
       <c r="Z104" s="6" t="s">
-        <v>105</v>
+        <v>246</v>
       </c>
       <c r="AA104" s="3" t="s">
         <v>40</v>
@@ -8490,7 +8558,7 @@
         <v>103</v>
       </c>
       <c r="B105" s="7">
-        <v>2026060149</v>
+        <v>2026060142</v>
       </c>
       <c r="C105" s="7">
         <v>1</v>
@@ -8499,90 +8567,770 @@
         <v>29</v>
       </c>
       <c r="E105" s="7" t="s">
-        <v>303</v>
+        <v>207</v>
       </c>
       <c r="F105" s="7" t="s">
-        <v>31</v>
+        <v>138</v>
       </c>
       <c r="G105" s="7" t="s">
-        <v>93</v>
+        <v>193</v>
       </c>
       <c r="H105" s="7" t="s">
-        <v>319</v>
+        <v>194</v>
       </c>
       <c r="I105" s="7" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="J105" s="7" t="s">
-        <v>314</v>
+        <v>184</v>
       </c>
       <c r="K105" s="7" t="s">
-        <v>315</v>
+        <v>36</v>
       </c>
       <c r="L105" s="8" t="s">
-        <v>96</v>
+        <v>243</v>
       </c>
       <c r="M105" s="8" t="s">
-        <v>321</v>
+        <v>302</v>
       </c>
       <c r="N105" s="8" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="O105" s="7" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="P105" s="7"/>
       <c r="Q105" s="7"/>
       <c r="R105" s="7">
-        <v>0</v>
+        <v>31873</v>
       </c>
       <c r="S105" s="7"/>
       <c r="T105" s="7"/>
-      <c r="U105" s="7"/>
+      <c r="U105" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="V105" s="7"/>
       <c r="W105" s="7"/>
       <c r="X105" s="7"/>
       <c r="Y105" s="7"/>
       <c r="Z105" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="AA105" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB105" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:28">
+      <c r="A106" s="3">
+        <v>104</v>
+      </c>
+      <c r="B106" s="3">
+        <v>2026060141</v>
+      </c>
+      <c r="C106" s="3">
+        <v>1</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="F106" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="G106" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="H106" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="I106" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="J106" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="K106" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L106" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="M106" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="N106" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="O106" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P106" s="3"/>
+      <c r="Q106" s="3"/>
+      <c r="R106" s="3">
+        <v>30842</v>
+      </c>
+      <c r="S106" s="3"/>
+      <c r="T106" s="3"/>
+      <c r="U106" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V106" s="3"/>
+      <c r="W106" s="3"/>
+      <c r="X106" s="3"/>
+      <c r="Y106" s="3"/>
+      <c r="Z106" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="AA106" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB106" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:28">
+      <c r="A107" s="7">
+        <v>105</v>
+      </c>
+      <c r="B107" s="7">
+        <v>2026060898</v>
+      </c>
+      <c r="C107" s="7">
+        <v>1</v>
+      </c>
+      <c r="D107" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E107" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="F107" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="G107" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="H107" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="I107" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="J107" s="7"/>
+      <c r="K107" s="7"/>
+      <c r="L107" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="M107" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="N107" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="O107" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P107" s="7"/>
+      <c r="Q107" s="7"/>
+      <c r="R107" s="7">
+        <v>0</v>
+      </c>
+      <c r="S107" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="T107" s="7"/>
+      <c r="U107" s="7"/>
+      <c r="V107" s="7"/>
+      <c r="W107" s="7"/>
+      <c r="X107" s="7"/>
+      <c r="Y107" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z107" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="AA107" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB107" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:28">
+      <c r="A108" s="3">
+        <v>106</v>
+      </c>
+      <c r="B108" s="3">
+        <v>2026060899</v>
+      </c>
+      <c r="C108" s="3">
+        <v>1</v>
+      </c>
+      <c r="D108" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E108" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="F108" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G108" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H108" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="I108" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="J108" s="3"/>
+      <c r="K108" s="3"/>
+      <c r="L108" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="M108" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="N108" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="O108" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P108" s="3"/>
+      <c r="Q108" s="3"/>
+      <c r="R108" s="3">
+        <v>0</v>
+      </c>
+      <c r="S108" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="T108" s="3"/>
+      <c r="U108" s="3"/>
+      <c r="V108" s="3"/>
+      <c r="W108" s="3"/>
+      <c r="X108" s="3"/>
+      <c r="Y108" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z108" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="AA108" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB108" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:28">
+      <c r="A109" s="7">
+        <v>107</v>
+      </c>
+      <c r="B109" s="7">
+        <v>2026060873</v>
+      </c>
+      <c r="C109" s="7">
+        <v>1</v>
+      </c>
+      <c r="D109" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E109" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="F109" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="G109" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="H109" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="I109" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="J109" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="K109" s="7" t="s">
         <v>323</v>
       </c>
-      <c r="AA105" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB105" s="7"/>
-    </row>
-    <row r="106" spans="1:28">
-      <c r="A106" s="9"/>
-      <c r="B106" s="9"/>
-      <c r="C106" s="9"/>
-      <c r="D106" s="9"/>
-      <c r="E106" s="9"/>
-      <c r="F106" s="9"/>
-      <c r="G106" s="9"/>
-      <c r="H106" s="9"/>
-      <c r="I106" s="9"/>
-      <c r="J106" s="9"/>
-      <c r="K106" s="9"/>
-      <c r="L106" s="10"/>
-      <c r="M106" s="10"/>
-      <c r="N106" s="10"/>
-      <c r="O106" s="9"/>
-      <c r="P106" s="9"/>
-      <c r="Q106" s="9"/>
-      <c r="R106" s="9"/>
-      <c r="S106" s="9"/>
-      <c r="T106" s="9"/>
-      <c r="U106" s="9"/>
-      <c r="V106" s="9"/>
-      <c r="W106" s="9"/>
-      <c r="X106" s="9"/>
-      <c r="Y106" s="9"/>
-      <c r="Z106" s="10"/>
-      <c r="AA106" s="9" t="s">
+      <c r="L109" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="M109" s="8" t="s">
         <v>324</v>
       </c>
-      <c r="AB106" s="9">
-        <v>57</v>
+      <c r="N109" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="O109" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="P109" s="7"/>
+      <c r="Q109" s="7"/>
+      <c r="R109" s="7">
+        <v>0</v>
+      </c>
+      <c r="S109" s="7"/>
+      <c r="T109" s="7"/>
+      <c r="U109" s="7"/>
+      <c r="V109" s="7"/>
+      <c r="W109" s="7"/>
+      <c r="X109" s="7"/>
+      <c r="Y109" s="7"/>
+      <c r="Z109" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="AA109" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB109" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:28">
+      <c r="A110" s="3">
+        <v>108</v>
+      </c>
+      <c r="B110" s="3">
+        <v>2026060905</v>
+      </c>
+      <c r="C110" s="3">
+        <v>1</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E110" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="F110" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G110" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H110" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="I110" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="J110" s="3"/>
+      <c r="K110" s="3"/>
+      <c r="L110" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="M110" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="N110" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="O110" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P110" s="3"/>
+      <c r="Q110" s="3"/>
+      <c r="R110" s="3">
+        <v>0</v>
+      </c>
+      <c r="S110" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="T110" s="3"/>
+      <c r="U110" s="3"/>
+      <c r="V110" s="3"/>
+      <c r="W110" s="3"/>
+      <c r="X110" s="3"/>
+      <c r="Y110" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z110" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="AA110" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB110" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:28">
+      <c r="A111" s="7">
+        <v>109</v>
+      </c>
+      <c r="B111" s="7">
+        <v>2026060510</v>
+      </c>
+      <c r="C111" s="7">
+        <v>1</v>
+      </c>
+      <c r="D111" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E111" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="F111" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G111" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="H111" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="I111" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="J111" s="7"/>
+      <c r="K111" s="7"/>
+      <c r="L111" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="M111" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="N111" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="O111" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P111" s="7"/>
+      <c r="Q111" s="7"/>
+      <c r="R111" s="7">
+        <v>0</v>
+      </c>
+      <c r="S111" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="T111" s="7"/>
+      <c r="U111" s="7"/>
+      <c r="V111" s="7"/>
+      <c r="W111" s="7"/>
+      <c r="X111" s="7"/>
+      <c r="Y111" s="7"/>
+      <c r="Z111" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="AA111" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB111" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:28">
+      <c r="A112" s="3">
+        <v>110</v>
+      </c>
+      <c r="B112" s="3">
+        <v>2026060850</v>
+      </c>
+      <c r="C112" s="3">
+        <v>1</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E112" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="F112" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="G112" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="H112" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="I112" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="J112" s="3"/>
+      <c r="K112" s="3"/>
+      <c r="L112" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="M112" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="N112" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="O112" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P112" s="3"/>
+      <c r="Q112" s="3"/>
+      <c r="R112" s="3">
+        <v>0</v>
+      </c>
+      <c r="S112" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="T112" s="3"/>
+      <c r="U112" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V112" s="3"/>
+      <c r="W112" s="3"/>
+      <c r="X112" s="3"/>
+      <c r="Y112" s="3"/>
+      <c r="Z112" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="AA112" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB112" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:28">
+      <c r="A113" s="7">
+        <v>111</v>
+      </c>
+      <c r="B113" s="7">
+        <v>2026060831</v>
+      </c>
+      <c r="C113" s="7">
+        <v>1</v>
+      </c>
+      <c r="D113" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E113" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="F113" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="G113" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="H113" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="I113" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="J113" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="K113" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="L113" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="M113" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="N113" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="O113" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="P113" s="7"/>
+      <c r="Q113" s="7"/>
+      <c r="R113" s="7">
+        <v>0</v>
+      </c>
+      <c r="S113" s="7"/>
+      <c r="T113" s="7"/>
+      <c r="U113" s="7"/>
+      <c r="V113" s="7"/>
+      <c r="W113" s="7"/>
+      <c r="X113" s="7"/>
+      <c r="Y113" s="7"/>
+      <c r="Z113" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="AA113" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB113" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:28">
+      <c r="A114" s="3">
+        <v>112</v>
+      </c>
+      <c r="B114" s="3">
+        <v>2026060475</v>
+      </c>
+      <c r="C114" s="3">
+        <v>1</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E114" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="F114" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G114" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="H114" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="I114" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="J114" s="3"/>
+      <c r="K114" s="3"/>
+      <c r="L114" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="M114" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="N114" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="O114" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P114" s="3"/>
+      <c r="Q114" s="3"/>
+      <c r="R114" s="3">
+        <v>0</v>
+      </c>
+      <c r="S114" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="T114" s="3"/>
+      <c r="U114" s="3"/>
+      <c r="V114" s="3"/>
+      <c r="W114" s="3"/>
+      <c r="X114" s="3"/>
+      <c r="Y114" s="3"/>
+      <c r="Z114" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="AA114" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB114" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:28">
+      <c r="A115" s="7">
+        <v>113</v>
+      </c>
+      <c r="B115" s="7">
+        <v>2026060149</v>
+      </c>
+      <c r="C115" s="7">
+        <v>1</v>
+      </c>
+      <c r="D115" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E115" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="F115" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G115" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="H115" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="I115" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="J115" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="K115" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="L115" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="M115" s="8" t="s">
+        <v>345</v>
+      </c>
+      <c r="N115" s="8" t="s">
+        <v>346</v>
+      </c>
+      <c r="O115" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="P115" s="7"/>
+      <c r="Q115" s="7"/>
+      <c r="R115" s="7">
+        <v>0</v>
+      </c>
+      <c r="S115" s="7"/>
+      <c r="T115" s="7"/>
+      <c r="U115" s="7"/>
+      <c r="V115" s="7"/>
+      <c r="W115" s="7"/>
+      <c r="X115" s="7"/>
+      <c r="Y115" s="7"/>
+      <c r="Z115" s="8" t="s">
+        <v>347</v>
+      </c>
+      <c r="AA115" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB115" s="7"/>
+    </row>
+    <row r="116" spans="1:28">
+      <c r="A116" s="9"/>
+      <c r="B116" s="9"/>
+      <c r="C116" s="9"/>
+      <c r="D116" s="9"/>
+      <c r="E116" s="9"/>
+      <c r="F116" s="9"/>
+      <c r="G116" s="9"/>
+      <c r="H116" s="9"/>
+      <c r="I116" s="9"/>
+      <c r="J116" s="9"/>
+      <c r="K116" s="9"/>
+      <c r="L116" s="10"/>
+      <c r="M116" s="10"/>
+      <c r="N116" s="10"/>
+      <c r="O116" s="9"/>
+      <c r="P116" s="9"/>
+      <c r="Q116" s="9"/>
+      <c r="R116" s="9"/>
+      <c r="S116" s="9"/>
+      <c r="T116" s="9"/>
+      <c r="U116" s="9"/>
+      <c r="V116" s="9"/>
+      <c r="W116" s="9"/>
+      <c r="X116" s="9"/>
+      <c r="Y116" s="9"/>
+      <c r="Z116" s="10"/>
+      <c r="AA116" s="9" t="s">
+        <v>348</v>
+      </c>
+      <c r="AB116" s="9">
+        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/IM/202606_Service_Count_Report.xlsx
+++ b/IM/202606_Service_Count_Report.xlsx
@@ -5247,7 +5247,7 @@
         <v>45</v>
       </c>
       <c r="B47" s="7">
-        <v>2026061563</v>
+        <v>2026061564</v>
       </c>
       <c r="C47" s="7">
         <v>1</v>
@@ -5286,7 +5286,7 @@
         <v>218</v>
       </c>
       <c r="O47" s="7" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="P47" s="7"/>
       <c r="Q47" s="7">
@@ -5295,13 +5295,9 @@
       <c r="R47" s="7">
         <v>15624</v>
       </c>
-      <c r="S47" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="S47" s="7"/>
       <c r="T47" s="7"/>
-      <c r="U47" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="U47" s="7"/>
       <c r="V47" s="7"/>
       <c r="W47" s="7"/>
       <c r="X47" s="7"/>
@@ -5321,7 +5317,7 @@
         <v>46</v>
       </c>
       <c r="B48" s="3">
-        <v>2026061564</v>
+        <v>2026061563</v>
       </c>
       <c r="C48" s="3">
         <v>1</v>
@@ -5360,7 +5356,7 @@
         <v>218</v>
       </c>
       <c r="O48" s="3" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="P48" s="3"/>
       <c r="Q48" s="3">
@@ -5369,9 +5365,13 @@
       <c r="R48" s="3">
         <v>15624</v>
       </c>
-      <c r="S48" s="3"/>
+      <c r="S48" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T48" s="3"/>
-      <c r="U48" s="3"/>
+      <c r="U48" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="V48" s="3"/>
       <c r="W48" s="3"/>
       <c r="X48" s="3"/>
@@ -6467,7 +6467,7 @@
         <v>63</v>
       </c>
       <c r="B65" s="7">
-        <v>2026060411</v>
+        <v>2026060412</v>
       </c>
       <c r="C65" s="7">
         <v>1</v>
@@ -6506,7 +6506,7 @@
         <v>241</v>
       </c>
       <c r="O65" s="7" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="P65" s="7"/>
       <c r="Q65" s="7">
@@ -6515,9 +6515,7 @@
       <c r="R65" s="7">
         <v>386927</v>
       </c>
-      <c r="S65" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="S65" s="7"/>
       <c r="T65" s="7"/>
       <c r="U65" s="7"/>
       <c r="V65" s="7"/>
@@ -6539,7 +6537,7 @@
         <v>64</v>
       </c>
       <c r="B66" s="3">
-        <v>2026060412</v>
+        <v>2026060411</v>
       </c>
       <c r="C66" s="3">
         <v>1</v>
@@ -6578,7 +6576,7 @@
         <v>241</v>
       </c>
       <c r="O66" s="3" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="P66" s="3"/>
       <c r="Q66" s="3">
@@ -6587,7 +6585,9 @@
       <c r="R66" s="3">
         <v>386927</v>
       </c>
-      <c r="S66" s="3"/>
+      <c r="S66" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T66" s="3"/>
       <c r="U66" s="3"/>
       <c r="V66" s="3"/>
@@ -6743,7 +6743,7 @@
         <v>67</v>
       </c>
       <c r="B69" s="7">
-        <v>2026060127</v>
+        <v>2026060128</v>
       </c>
       <c r="C69" s="7">
         <v>1</v>
@@ -6782,16 +6782,14 @@
         <v>267</v>
       </c>
       <c r="O69" s="7" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="P69" s="7"/>
       <c r="Q69" s="7"/>
       <c r="R69" s="7">
         <v>212738</v>
       </c>
-      <c r="S69" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="S69" s="7"/>
       <c r="T69" s="7"/>
       <c r="U69" s="7"/>
       <c r="V69" s="7"/>
@@ -6809,7 +6807,7 @@
         <v>68</v>
       </c>
       <c r="B70" s="3">
-        <v>2026060128</v>
+        <v>2026060127</v>
       </c>
       <c r="C70" s="3">
         <v>1</v>
@@ -6848,14 +6846,16 @@
         <v>267</v>
       </c>
       <c r="O70" s="3" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="P70" s="3"/>
       <c r="Q70" s="3"/>
       <c r="R70" s="3">
         <v>212738</v>
       </c>
-      <c r="S70" s="3"/>
+      <c r="S70" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T70" s="3"/>
       <c r="U70" s="3"/>
       <c r="V70" s="3"/>
@@ -8547,7 +8547,7 @@
         <v>94</v>
       </c>
       <c r="B96" s="3">
-        <v>2026060665</v>
+        <v>2026060664</v>
       </c>
       <c r="C96" s="3">
         <v>1</v>
@@ -8586,7 +8586,7 @@
         <v>353</v>
       </c>
       <c r="O96" s="3" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="P96" s="3">
         <v>2480</v>
@@ -8597,7 +8597,9 @@
       <c r="R96" s="3">
         <v>11884</v>
       </c>
-      <c r="S96" s="3"/>
+      <c r="S96" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T96" s="3"/>
       <c r="U96" s="3"/>
       <c r="V96" s="3"/>
@@ -8619,7 +8621,7 @@
         <v>95</v>
       </c>
       <c r="B97" s="7">
-        <v>2026060664</v>
+        <v>2026060665</v>
       </c>
       <c r="C97" s="7">
         <v>1</v>
@@ -8658,7 +8660,7 @@
         <v>353</v>
       </c>
       <c r="O97" s="7" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="P97" s="7">
         <v>2480</v>
@@ -8669,9 +8671,7 @@
       <c r="R97" s="7">
         <v>11884</v>
       </c>
-      <c r="S97" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="S97" s="7"/>
       <c r="T97" s="7"/>
       <c r="U97" s="7"/>
       <c r="V97" s="7"/>
@@ -10421,7 +10421,7 @@
         <v>121</v>
       </c>
       <c r="B123" s="7">
-        <v>2026061104</v>
+        <v>2026061103</v>
       </c>
       <c r="C123" s="7">
         <v>1</v>
@@ -10458,14 +10458,16 @@
       </c>
       <c r="N123" s="8"/>
       <c r="O123" s="7" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="P123" s="7"/>
       <c r="Q123" s="7"/>
       <c r="R123" s="7">
         <v>66000</v>
       </c>
-      <c r="S123" s="7"/>
+      <c r="S123" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T123" s="7"/>
       <c r="U123" s="7"/>
       <c r="V123" s="7"/>
@@ -10487,7 +10489,7 @@
         <v>122</v>
       </c>
       <c r="B124" s="3">
-        <v>2026061103</v>
+        <v>2026061104</v>
       </c>
       <c r="C124" s="3">
         <v>1</v>
@@ -10524,16 +10526,14 @@
       </c>
       <c r="N124" s="6"/>
       <c r="O124" s="3" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="P124" s="3"/>
       <c r="Q124" s="3"/>
       <c r="R124" s="3">
         <v>66000</v>
       </c>
-      <c r="S124" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="S124" s="3"/>
       <c r="T124" s="3"/>
       <c r="U124" s="3"/>
       <c r="V124" s="3"/>
@@ -10623,7 +10623,7 @@
         <v>124</v>
       </c>
       <c r="B126" s="3">
-        <v>2026060053</v>
+        <v>2026060052</v>
       </c>
       <c r="C126" s="3">
         <v>1</v>
@@ -10662,14 +10662,16 @@
         <v>406</v>
       </c>
       <c r="O126" s="3" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="P126" s="3"/>
       <c r="Q126" s="3"/>
       <c r="R126" s="3">
         <v>29640</v>
       </c>
-      <c r="S126" s="3"/>
+      <c r="S126" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T126" s="3"/>
       <c r="U126" s="3"/>
       <c r="V126" s="3"/>
@@ -10691,7 +10693,7 @@
         <v>125</v>
       </c>
       <c r="B127" s="7">
-        <v>2026060052</v>
+        <v>2026060053</v>
       </c>
       <c r="C127" s="7">
         <v>1</v>
@@ -10730,16 +10732,14 @@
         <v>406</v>
       </c>
       <c r="O127" s="7" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="P127" s="7"/>
       <c r="Q127" s="7"/>
       <c r="R127" s="7">
         <v>29640</v>
       </c>
-      <c r="S127" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="S127" s="7"/>
       <c r="T127" s="7"/>
       <c r="U127" s="7"/>
       <c r="V127" s="7"/>
@@ -12251,7 +12251,7 @@
         <v>148</v>
       </c>
       <c r="B150" s="3">
-        <v>2026060049</v>
+        <v>2026060048</v>
       </c>
       <c r="C150" s="3">
         <v>1</v>
@@ -12290,14 +12290,16 @@
         <v>438</v>
       </c>
       <c r="O150" s="3" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="P150" s="3"/>
       <c r="Q150" s="3"/>
       <c r="R150" s="3">
         <v>5766</v>
       </c>
-      <c r="S150" s="3"/>
+      <c r="S150" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T150" s="3"/>
       <c r="U150" s="3"/>
       <c r="V150" s="3"/>
@@ -12319,7 +12321,7 @@
         <v>149</v>
       </c>
       <c r="B151" s="7">
-        <v>2026060048</v>
+        <v>2026060049</v>
       </c>
       <c r="C151" s="7">
         <v>1</v>
@@ -12358,16 +12360,14 @@
         <v>438</v>
       </c>
       <c r="O151" s="7" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="P151" s="7"/>
       <c r="Q151" s="7"/>
       <c r="R151" s="7">
         <v>5766</v>
       </c>
-      <c r="S151" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="S151" s="7"/>
       <c r="T151" s="7"/>
       <c r="U151" s="7"/>
       <c r="V151" s="7"/>
@@ -12727,7 +12727,7 @@
         <v>155</v>
       </c>
       <c r="B157" s="7">
-        <v>2026060526</v>
+        <v>2026060527</v>
       </c>
       <c r="C157" s="7">
         <v>1</v>
@@ -12766,16 +12766,14 @@
         <v>448</v>
       </c>
       <c r="O157" s="7" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="P157" s="7"/>
       <c r="Q157" s="7"/>
       <c r="R157" s="7">
         <v>33686</v>
       </c>
-      <c r="S157" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="S157" s="7"/>
       <c r="T157" s="7"/>
       <c r="U157" s="7"/>
       <c r="V157" s="7"/>
@@ -12785,15 +12783,19 @@
       <c r="Z157" s="8" t="s">
         <v>349</v>
       </c>
-      <c r="AA157" s="7"/>
-      <c r="AB157" s="7"/>
+      <c r="AA157" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB157" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="158" spans="1:28">
       <c r="A158" s="3">
         <v>156</v>
       </c>
       <c r="B158" s="3">
-        <v>2026060527</v>
+        <v>2026060526</v>
       </c>
       <c r="C158" s="3">
         <v>1</v>
@@ -12832,14 +12834,16 @@
         <v>448</v>
       </c>
       <c r="O158" s="3" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="P158" s="3"/>
       <c r="Q158" s="3"/>
       <c r="R158" s="3">
         <v>33686</v>
       </c>
-      <c r="S158" s="3"/>
+      <c r="S158" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T158" s="3"/>
       <c r="U158" s="3"/>
       <c r="V158" s="3"/>
@@ -12849,9 +12853,7 @@
       <c r="Z158" s="6" t="s">
         <v>349</v>
       </c>
-      <c r="AA158" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="AA158" s="3"/>
       <c r="AB158" s="3"/>
     </row>
     <row r="159" spans="1:28">
@@ -15089,7 +15091,7 @@
         <v>190</v>
       </c>
       <c r="B192" s="3">
-        <v>2026061260</v>
+        <v>2026061529</v>
       </c>
       <c r="C192" s="3">
         <v>1</v>
@@ -15112,12 +15114,8 @@
       <c r="I192" s="3" t="s">
         <v>519</v>
       </c>
-      <c r="J192" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="K192" s="3" t="s">
-        <v>197</v>
-      </c>
+      <c r="J192" s="3"/>
+      <c r="K192" s="3"/>
       <c r="L192" s="6" t="s">
         <v>167</v>
       </c>
@@ -15128,14 +15126,16 @@
         <v>521</v>
       </c>
       <c r="O192" s="3" t="s">
-        <v>94</v>
+        <v>39</v>
       </c>
       <c r="P192" s="3"/>
       <c r="Q192" s="3"/>
       <c r="R192" s="3">
         <v>0</v>
       </c>
-      <c r="S192" s="3"/>
+      <c r="S192" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T192" s="3"/>
       <c r="U192" s="3"/>
       <c r="V192" s="3"/>
@@ -15143,7 +15143,7 @@
       <c r="X192" s="3"/>
       <c r="Y192" s="3"/>
       <c r="Z192" s="6" t="s">
-        <v>522</v>
+        <v>181</v>
       </c>
       <c r="AA192" s="3" t="s">
         <v>40</v>
@@ -15157,7 +15157,7 @@
         <v>191</v>
       </c>
       <c r="B193" s="7">
-        <v>2026061529</v>
+        <v>2026061260</v>
       </c>
       <c r="C193" s="7">
         <v>1</v>
@@ -15180,8 +15180,12 @@
       <c r="I193" s="7" t="s">
         <v>519</v>
       </c>
-      <c r="J193" s="7"/>
-      <c r="K193" s="7"/>
+      <c r="J193" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="K193" s="7" t="s">
+        <v>197</v>
+      </c>
       <c r="L193" s="8" t="s">
         <v>167</v>
       </c>
@@ -15192,16 +15196,14 @@
         <v>521</v>
       </c>
       <c r="O193" s="7" t="s">
-        <v>39</v>
+        <v>94</v>
       </c>
       <c r="P193" s="7"/>
       <c r="Q193" s="7"/>
       <c r="R193" s="7">
         <v>0</v>
       </c>
-      <c r="S193" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="S193" s="7"/>
       <c r="T193" s="7"/>
       <c r="U193" s="7"/>
       <c r="V193" s="7"/>
@@ -15209,7 +15211,7 @@
       <c r="X193" s="7"/>
       <c r="Y193" s="7"/>
       <c r="Z193" s="8" t="s">
-        <v>181</v>
+        <v>522</v>
       </c>
       <c r="AA193" s="7" t="s">
         <v>40</v>
@@ -15221,7 +15223,7 @@
         <v>192</v>
       </c>
       <c r="B194" s="3">
-        <v>2026060475</v>
+        <v>2026060149</v>
       </c>
       <c r="C194" s="3">
         <v>1</v>
@@ -15244,8 +15246,12 @@
       <c r="I194" s="3" t="s">
         <v>524</v>
       </c>
-      <c r="J194" s="3"/>
-      <c r="K194" s="3"/>
+      <c r="J194" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="K194" s="3" t="s">
+        <v>197</v>
+      </c>
       <c r="L194" s="6" t="s">
         <v>167</v>
       </c>
@@ -15256,16 +15262,14 @@
         <v>526</v>
       </c>
       <c r="O194" s="3" t="s">
-        <v>39</v>
+        <v>94</v>
       </c>
       <c r="P194" s="3"/>
       <c r="Q194" s="3"/>
       <c r="R194" s="3">
         <v>0</v>
       </c>
-      <c r="S194" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="S194" s="3"/>
       <c r="T194" s="3"/>
       <c r="U194" s="3"/>
       <c r="V194" s="3"/>
@@ -15273,7 +15277,7 @@
       <c r="X194" s="3"/>
       <c r="Y194" s="3"/>
       <c r="Z194" s="6" t="s">
-        <v>181</v>
+        <v>527</v>
       </c>
       <c r="AA194" s="3" t="s">
         <v>40</v>
@@ -15287,7 +15291,7 @@
         <v>193</v>
       </c>
       <c r="B195" s="7">
-        <v>2026060149</v>
+        <v>2026060475</v>
       </c>
       <c r="C195" s="7">
         <v>1</v>
@@ -15310,12 +15314,8 @@
       <c r="I195" s="7" t="s">
         <v>524</v>
       </c>
-      <c r="J195" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="K195" s="7" t="s">
-        <v>197</v>
-      </c>
+      <c r="J195" s="7"/>
+      <c r="K195" s="7"/>
       <c r="L195" s="8" t="s">
         <v>167</v>
       </c>
@@ -15326,14 +15326,16 @@
         <v>526</v>
       </c>
       <c r="O195" s="7" t="s">
-        <v>94</v>
+        <v>39</v>
       </c>
       <c r="P195" s="7"/>
       <c r="Q195" s="7"/>
       <c r="R195" s="7">
         <v>0</v>
       </c>
-      <c r="S195" s="7"/>
+      <c r="S195" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T195" s="7"/>
       <c r="U195" s="7"/>
       <c r="V195" s="7"/>
@@ -15341,7 +15343,7 @@
       <c r="X195" s="7"/>
       <c r="Y195" s="7"/>
       <c r="Z195" s="8" t="s">
-        <v>527</v>
+        <v>181</v>
       </c>
       <c r="AA195" s="7" t="s">
         <v>40</v>
@@ -15583,7 +15585,7 @@
         <v>546</v>
       </c>
       <c r="AB199" s="9">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>

--- a/IM/202606_Service_Count_Report.xlsx
+++ b/IM/202606_Service_Count_Report.xlsx
@@ -11,14 +11,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Report'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$AA$199</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$AA$200</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="547">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="549">
   <si>
     <t>服務次數統計表        篩選月份：202606</t>
   </si>
@@ -1294,6 +1294,12 @@
   </si>
   <si>
     <t>走道</t>
+  </si>
+  <si>
+    <t>2026-06-10</t>
+  </si>
+  <si>
+    <t>多台卡機無法使用 確認為伺服器設定問題</t>
   </si>
   <si>
     <t>T302800154</t>
@@ -2105,7 +2111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AB199"/>
+  <dimension ref="A1:AB200"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="true" style="0"/>
@@ -4969,7 +4975,7 @@
         <v>41</v>
       </c>
       <c r="B43" s="7">
-        <v>2026060673</v>
+        <v>2026060674</v>
       </c>
       <c r="C43" s="7">
         <v>1</v>
@@ -5008,7 +5014,7 @@
         <v>207</v>
       </c>
       <c r="O43" s="7" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="P43" s="7">
         <v>7927</v>
@@ -5019,9 +5025,7 @@
       <c r="R43" s="7">
         <v>25584</v>
       </c>
-      <c r="S43" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="S43" s="7"/>
       <c r="T43" s="7"/>
       <c r="U43" s="7"/>
       <c r="V43" s="7"/>
@@ -5043,7 +5047,7 @@
         <v>42</v>
       </c>
       <c r="B44" s="3">
-        <v>2026060674</v>
+        <v>2026060673</v>
       </c>
       <c r="C44" s="3">
         <v>1</v>
@@ -5082,7 +5086,7 @@
         <v>207</v>
       </c>
       <c r="O44" s="3" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="P44" s="3">
         <v>7927</v>
@@ -5093,7 +5097,9 @@
       <c r="R44" s="3">
         <v>25584</v>
       </c>
-      <c r="S44" s="3"/>
+      <c r="S44" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T44" s="3"/>
       <c r="U44" s="3"/>
       <c r="V44" s="3"/>
@@ -5247,7 +5253,7 @@
         <v>45</v>
       </c>
       <c r="B47" s="7">
-        <v>2026061564</v>
+        <v>2026061563</v>
       </c>
       <c r="C47" s="7">
         <v>1</v>
@@ -5286,7 +5292,7 @@
         <v>218</v>
       </c>
       <c r="O47" s="7" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="P47" s="7"/>
       <c r="Q47" s="7">
@@ -5295,9 +5301,13 @@
       <c r="R47" s="7">
         <v>15624</v>
       </c>
-      <c r="S47" s="7"/>
+      <c r="S47" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T47" s="7"/>
-      <c r="U47" s="7"/>
+      <c r="U47" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="V47" s="7"/>
       <c r="W47" s="7"/>
       <c r="X47" s="7"/>
@@ -5317,7 +5327,7 @@
         <v>46</v>
       </c>
       <c r="B48" s="3">
-        <v>2026061563</v>
+        <v>2026061564</v>
       </c>
       <c r="C48" s="3">
         <v>1</v>
@@ -5356,7 +5366,7 @@
         <v>218</v>
       </c>
       <c r="O48" s="3" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="P48" s="3"/>
       <c r="Q48" s="3">
@@ -5365,13 +5375,9 @@
       <c r="R48" s="3">
         <v>15624</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="S48" s="3"/>
       <c r="T48" s="3"/>
-      <c r="U48" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="U48" s="3"/>
       <c r="V48" s="3"/>
       <c r="W48" s="3"/>
       <c r="X48" s="3"/>
@@ -5999,7 +6005,7 @@
         <v>56</v>
       </c>
       <c r="B58" s="3">
-        <v>2026060378</v>
+        <v>2026060379</v>
       </c>
       <c r="C58" s="3">
         <v>1</v>
@@ -6036,16 +6042,14 @@
       </c>
       <c r="N58" s="6"/>
       <c r="O58" s="3" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="P58" s="3"/>
       <c r="Q58" s="3"/>
       <c r="R58" s="3">
         <v>36400</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="S58" s="3"/>
       <c r="T58" s="3"/>
       <c r="U58" s="3"/>
       <c r="V58" s="3"/>
@@ -6067,7 +6071,7 @@
         <v>57</v>
       </c>
       <c r="B59" s="7">
-        <v>2026060379</v>
+        <v>2026060378</v>
       </c>
       <c r="C59" s="7">
         <v>1</v>
@@ -6104,14 +6108,16 @@
       </c>
       <c r="N59" s="8"/>
       <c r="O59" s="7" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="P59" s="7"/>
       <c r="Q59" s="7"/>
       <c r="R59" s="7">
         <v>36400</v>
       </c>
-      <c r="S59" s="7"/>
+      <c r="S59" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T59" s="7"/>
       <c r="U59" s="7"/>
       <c r="V59" s="7"/>
@@ -6467,7 +6473,7 @@
         <v>63</v>
       </c>
       <c r="B65" s="7">
-        <v>2026060412</v>
+        <v>2026060411</v>
       </c>
       <c r="C65" s="7">
         <v>1</v>
@@ -6506,7 +6512,7 @@
         <v>241</v>
       </c>
       <c r="O65" s="7" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="P65" s="7"/>
       <c r="Q65" s="7">
@@ -6515,7 +6521,9 @@
       <c r="R65" s="7">
         <v>386927</v>
       </c>
-      <c r="S65" s="7"/>
+      <c r="S65" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T65" s="7"/>
       <c r="U65" s="7"/>
       <c r="V65" s="7"/>
@@ -6537,7 +6545,7 @@
         <v>64</v>
       </c>
       <c r="B66" s="3">
-        <v>2026060411</v>
+        <v>2026060412</v>
       </c>
       <c r="C66" s="3">
         <v>1</v>
@@ -6576,7 +6584,7 @@
         <v>241</v>
       </c>
       <c r="O66" s="3" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="P66" s="3"/>
       <c r="Q66" s="3">
@@ -6585,9 +6593,7 @@
       <c r="R66" s="3">
         <v>386927</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="S66" s="3"/>
       <c r="T66" s="3"/>
       <c r="U66" s="3"/>
       <c r="V66" s="3"/>
@@ -6743,7 +6749,7 @@
         <v>67</v>
       </c>
       <c r="B69" s="7">
-        <v>2026060128</v>
+        <v>2026060127</v>
       </c>
       <c r="C69" s="7">
         <v>1</v>
@@ -6782,14 +6788,16 @@
         <v>267</v>
       </c>
       <c r="O69" s="7" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="P69" s="7"/>
       <c r="Q69" s="7"/>
       <c r="R69" s="7">
         <v>212738</v>
       </c>
-      <c r="S69" s="7"/>
+      <c r="S69" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T69" s="7"/>
       <c r="U69" s="7"/>
       <c r="V69" s="7"/>
@@ -6807,7 +6815,7 @@
         <v>68</v>
       </c>
       <c r="B70" s="3">
-        <v>2026060127</v>
+        <v>2026060128</v>
       </c>
       <c r="C70" s="3">
         <v>1</v>
@@ -6846,16 +6854,14 @@
         <v>267</v>
       </c>
       <c r="O70" s="3" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="P70" s="3"/>
       <c r="Q70" s="3"/>
       <c r="R70" s="3">
         <v>212738</v>
       </c>
-      <c r="S70" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="S70" s="3"/>
       <c r="T70" s="3"/>
       <c r="U70" s="3"/>
       <c r="V70" s="3"/>
@@ -6873,7 +6879,7 @@
         <v>69</v>
       </c>
       <c r="B71" s="7">
-        <v>2026061436</v>
+        <v>2026061437</v>
       </c>
       <c r="C71" s="7">
         <v>1</v>
@@ -6912,7 +6918,7 @@
         <v>271</v>
       </c>
       <c r="O71" s="7" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="P71" s="7"/>
       <c r="Q71" s="7">
@@ -6921,9 +6927,7 @@
       <c r="R71" s="7">
         <v>221294</v>
       </c>
-      <c r="S71" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="S71" s="7"/>
       <c r="T71" s="7"/>
       <c r="U71" s="7"/>
       <c r="V71" s="7"/>
@@ -6941,7 +6945,7 @@
         <v>70</v>
       </c>
       <c r="B72" s="3">
-        <v>2026061437</v>
+        <v>2026061436</v>
       </c>
       <c r="C72" s="3">
         <v>1</v>
@@ -6980,7 +6984,7 @@
         <v>271</v>
       </c>
       <c r="O72" s="3" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="P72" s="3"/>
       <c r="Q72" s="3">
@@ -6989,7 +6993,9 @@
       <c r="R72" s="3">
         <v>221294</v>
       </c>
-      <c r="S72" s="3"/>
+      <c r="S72" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T72" s="3"/>
       <c r="U72" s="3"/>
       <c r="V72" s="3"/>
@@ -9739,7 +9745,7 @@
         <v>111</v>
       </c>
       <c r="B113" s="7">
-        <v>2026061006</v>
+        <v>2026061007</v>
       </c>
       <c r="C113" s="7">
         <v>1</v>
@@ -9778,16 +9784,14 @@
         <v>383</v>
       </c>
       <c r="O113" s="7" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="P113" s="7"/>
       <c r="Q113" s="7"/>
       <c r="R113" s="7">
         <v>57995</v>
       </c>
-      <c r="S113" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="S113" s="7"/>
       <c r="T113" s="7"/>
       <c r="U113" s="7"/>
       <c r="V113" s="7"/>
@@ -9809,7 +9813,7 @@
         <v>112</v>
       </c>
       <c r="B114" s="3">
-        <v>2026061007</v>
+        <v>2026061006</v>
       </c>
       <c r="C114" s="3">
         <v>1</v>
@@ -9848,14 +9852,16 @@
         <v>383</v>
       </c>
       <c r="O114" s="3" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="P114" s="3"/>
       <c r="Q114" s="3"/>
       <c r="R114" s="3">
         <v>57995</v>
       </c>
-      <c r="S114" s="3"/>
+      <c r="S114" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T114" s="3"/>
       <c r="U114" s="3"/>
       <c r="V114" s="3"/>
@@ -11443,7 +11449,7 @@
         <v>136</v>
       </c>
       <c r="B138" s="3">
-        <v>2026060040</v>
+        <v>2026061645</v>
       </c>
       <c r="C138" s="3">
         <v>1</v>
@@ -11455,16 +11461,16 @@
         <v>345</v>
       </c>
       <c r="F138" s="3" t="s">
-        <v>209</v>
+        <v>417</v>
       </c>
       <c r="G138" s="3" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="H138" s="3" t="s">
-        <v>354</v>
+        <v>137</v>
       </c>
       <c r="I138" s="3" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="J138" s="3" t="s">
         <v>117</v>
@@ -11476,22 +11482,20 @@
         <v>377</v>
       </c>
       <c r="M138" s="6" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="O138" s="3" t="s">
-        <v>39</v>
+        <v>94</v>
       </c>
       <c r="P138" s="3"/>
       <c r="Q138" s="3"/>
       <c r="R138" s="3">
-        <v>29640</v>
-      </c>
-      <c r="S138" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>45926</v>
+      </c>
+      <c r="S138" s="3"/>
       <c r="T138" s="3"/>
       <c r="U138" s="3"/>
       <c r="V138" s="3"/>
@@ -11499,7 +11503,7 @@
       <c r="X138" s="3"/>
       <c r="Y138" s="3"/>
       <c r="Z138" s="6" t="s">
-        <v>349</v>
+        <v>418</v>
       </c>
       <c r="AA138" s="3" t="s">
         <v>40</v>
@@ -11513,7 +11517,7 @@
         <v>137</v>
       </c>
       <c r="B139" s="7">
-        <v>2026060041</v>
+        <v>2026060040</v>
       </c>
       <c r="C139" s="7">
         <v>1</v>
@@ -11534,7 +11538,7 @@
         <v>354</v>
       </c>
       <c r="I139" s="7" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="J139" s="7" t="s">
         <v>117</v>
@@ -11546,20 +11550,22 @@
         <v>377</v>
       </c>
       <c r="M139" s="8" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="N139" s="8" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="O139" s="7" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="P139" s="7"/>
       <c r="Q139" s="7"/>
       <c r="R139" s="7">
         <v>29640</v>
       </c>
-      <c r="S139" s="7"/>
+      <c r="S139" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T139" s="7"/>
       <c r="U139" s="7"/>
       <c r="V139" s="7"/>
@@ -11572,14 +11578,16 @@
       <c r="AA139" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AB139" s="7"/>
+      <c r="AB139" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="140" spans="1:28">
       <c r="A140" s="3">
         <v>138</v>
       </c>
       <c r="B140" s="3">
-        <v>2026060044</v>
+        <v>2026060041</v>
       </c>
       <c r="C140" s="3">
         <v>1</v>
@@ -11594,13 +11602,13 @@
         <v>209</v>
       </c>
       <c r="G140" s="3" t="s">
-        <v>202</v>
+        <v>359</v>
       </c>
       <c r="H140" s="3" t="s">
-        <v>50</v>
+        <v>354</v>
       </c>
       <c r="I140" s="3" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="J140" s="3" t="s">
         <v>117</v>
@@ -11612,22 +11620,20 @@
         <v>377</v>
       </c>
       <c r="M140" s="6" t="s">
+        <v>420</v>
+      </c>
+      <c r="N140" s="6" t="s">
         <v>421</v>
       </c>
-      <c r="N140" s="6" t="s">
-        <v>422</v>
-      </c>
       <c r="O140" s="3" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="P140" s="3"/>
       <c r="Q140" s="3"/>
       <c r="R140" s="3">
-        <v>34235</v>
-      </c>
-      <c r="S140" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>29640</v>
+      </c>
+      <c r="S140" s="3"/>
       <c r="T140" s="3"/>
       <c r="U140" s="3"/>
       <c r="V140" s="3"/>
@@ -11640,16 +11646,14 @@
       <c r="AA140" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AB140" s="3">
-        <v>1</v>
-      </c>
+      <c r="AB140" s="3"/>
     </row>
     <row r="141" spans="1:28">
       <c r="A141" s="7">
         <v>139</v>
       </c>
       <c r="B141" s="7">
-        <v>2026060045</v>
+        <v>2026060044</v>
       </c>
       <c r="C141" s="7">
         <v>1</v>
@@ -11670,7 +11674,7 @@
         <v>50</v>
       </c>
       <c r="I141" s="7" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="J141" s="7" t="s">
         <v>117</v>
@@ -11682,20 +11686,22 @@
         <v>377</v>
       </c>
       <c r="M141" s="8" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="N141" s="8" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="O141" s="7" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="P141" s="7"/>
       <c r="Q141" s="7"/>
       <c r="R141" s="7">
         <v>34235</v>
       </c>
-      <c r="S141" s="7"/>
+      <c r="S141" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T141" s="7"/>
       <c r="U141" s="7"/>
       <c r="V141" s="7"/>
@@ -11708,14 +11714,16 @@
       <c r="AA141" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AB141" s="7"/>
+      <c r="AB141" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="142" spans="1:28">
       <c r="A142" s="3">
         <v>140</v>
       </c>
       <c r="B142" s="3">
-        <v>2026060042</v>
+        <v>2026060045</v>
       </c>
       <c r="C142" s="3">
         <v>1</v>
@@ -11730,13 +11738,13 @@
         <v>209</v>
       </c>
       <c r="G142" s="3" t="s">
-        <v>354</v>
+        <v>202</v>
       </c>
       <c r="H142" s="3" t="s">
-        <v>202</v>
+        <v>50</v>
       </c>
       <c r="I142" s="3" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="J142" s="3" t="s">
         <v>117</v>
@@ -11748,22 +11756,20 @@
         <v>377</v>
       </c>
       <c r="M142" s="6" t="s">
+        <v>423</v>
+      </c>
+      <c r="N142" s="6" t="s">
         <v>424</v>
       </c>
-      <c r="N142" s="6" t="s">
-        <v>370</v>
-      </c>
       <c r="O142" s="3" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="P142" s="3"/>
       <c r="Q142" s="3"/>
       <c r="R142" s="3">
-        <v>17791</v>
-      </c>
-      <c r="S142" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>34235</v>
+      </c>
+      <c r="S142" s="3"/>
       <c r="T142" s="3"/>
       <c r="U142" s="3"/>
       <c r="V142" s="3"/>
@@ -11776,16 +11782,14 @@
       <c r="AA142" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AB142" s="3">
-        <v>1</v>
-      </c>
+      <c r="AB142" s="3"/>
     </row>
     <row r="143" spans="1:28">
       <c r="A143" s="7">
         <v>141</v>
       </c>
       <c r="B143" s="7">
-        <v>2026060043</v>
+        <v>2026060042</v>
       </c>
       <c r="C143" s="7">
         <v>1</v>
@@ -11806,7 +11810,7 @@
         <v>202</v>
       </c>
       <c r="I143" s="7" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="J143" s="7" t="s">
         <v>117</v>
@@ -11818,20 +11822,22 @@
         <v>377</v>
       </c>
       <c r="M143" s="8" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="N143" s="8" t="s">
         <v>370</v>
       </c>
       <c r="O143" s="7" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="P143" s="7"/>
       <c r="Q143" s="7"/>
       <c r="R143" s="7">
         <v>17791</v>
       </c>
-      <c r="S143" s="7"/>
+      <c r="S143" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T143" s="7"/>
       <c r="U143" s="7"/>
       <c r="V143" s="7"/>
@@ -11844,14 +11850,16 @@
       <c r="AA143" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AB143" s="7"/>
+      <c r="AB143" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="144" spans="1:28">
       <c r="A144" s="3">
         <v>142</v>
       </c>
       <c r="B144" s="3">
-        <v>2026060385</v>
+        <v>2026060043</v>
       </c>
       <c r="C144" s="3">
         <v>1</v>
@@ -11863,43 +11871,41 @@
         <v>345</v>
       </c>
       <c r="F144" s="3" t="s">
-        <v>49</v>
+        <v>209</v>
       </c>
       <c r="G144" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="H144" s="3" t="s">
         <v>202</v>
-      </c>
-      <c r="H144" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="I144" s="3" t="s">
         <v>425</v>
       </c>
       <c r="J144" s="3" t="s">
-        <v>426</v>
+        <v>117</v>
       </c>
       <c r="K144" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L144" s="6" t="s">
-        <v>427</v>
+        <v>377</v>
       </c>
       <c r="M144" s="6" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>429</v>
+        <v>370</v>
       </c>
       <c r="O144" s="3" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="P144" s="3"/>
       <c r="Q144" s="3"/>
       <c r="R144" s="3">
-        <v>122434</v>
-      </c>
-      <c r="S144" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>17791</v>
+      </c>
+      <c r="S144" s="3"/>
       <c r="T144" s="3"/>
       <c r="U144" s="3"/>
       <c r="V144" s="3"/>
@@ -11909,7 +11915,9 @@
       <c r="Z144" s="6" t="s">
         <v>349</v>
       </c>
-      <c r="AA144" s="3"/>
+      <c r="AA144" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="AB144" s="3"/>
     </row>
     <row r="145" spans="1:28">
@@ -11938,22 +11946,22 @@
         <v>50</v>
       </c>
       <c r="I145" s="7" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="J145" s="7" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K145" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L145" s="8" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="M145" s="8" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="N145" s="8" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="O145" s="7" t="s">
         <v>60</v>
@@ -11976,14 +11984,16 @@
       <c r="AA145" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AB145" s="7"/>
+      <c r="AB145" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="146" spans="1:28">
       <c r="A146" s="3">
         <v>144</v>
       </c>
       <c r="B146" s="3">
-        <v>2026061412</v>
+        <v>2026060385</v>
       </c>
       <c r="C146" s="3">
         <v>1</v>
@@ -11995,31 +12005,31 @@
         <v>345</v>
       </c>
       <c r="F146" s="3" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="G146" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="H146" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="H146" s="3" t="s">
-        <v>137</v>
-      </c>
       <c r="I146" s="3" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="J146" s="3" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K146" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L146" s="6" t="s">
-        <v>373</v>
+        <v>429</v>
       </c>
       <c r="M146" s="6" t="s">
+        <v>430</v>
+      </c>
+      <c r="N146" s="6" t="s">
         <v>431</v>
-      </c>
-      <c r="N146" s="6" t="s">
-        <v>432</v>
       </c>
       <c r="O146" s="3" t="s">
         <v>39</v>
@@ -12027,7 +12037,7 @@
       <c r="P146" s="3"/>
       <c r="Q146" s="3"/>
       <c r="R146" s="3">
-        <v>13563</v>
+        <v>122434</v>
       </c>
       <c r="S146" s="3" t="s">
         <v>40</v>
@@ -12049,7 +12059,7 @@
         <v>145</v>
       </c>
       <c r="B147" s="7">
-        <v>2026061413</v>
+        <v>2026061412</v>
       </c>
       <c r="C147" s="7">
         <v>1</v>
@@ -12070,10 +12080,10 @@
         <v>137</v>
       </c>
       <c r="I147" s="7" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="J147" s="7" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K147" s="7" t="s">
         <v>36</v>
@@ -12082,20 +12092,22 @@
         <v>373</v>
       </c>
       <c r="M147" s="8" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="N147" s="8" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="O147" s="7" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="P147" s="7"/>
       <c r="Q147" s="7"/>
       <c r="R147" s="7">
         <v>13563</v>
       </c>
-      <c r="S147" s="7"/>
+      <c r="S147" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T147" s="7"/>
       <c r="U147" s="7"/>
       <c r="V147" s="7"/>
@@ -12105,9 +12117,7 @@
       <c r="Z147" s="8" t="s">
         <v>349</v>
       </c>
-      <c r="AA147" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="AA147" s="7"/>
       <c r="AB147" s="7"/>
     </row>
     <row r="148" spans="1:28">
@@ -12115,7 +12125,7 @@
         <v>146</v>
       </c>
       <c r="B148" s="3">
-        <v>2026060061</v>
+        <v>2026061413</v>
       </c>
       <c r="C148" s="3">
         <v>1</v>
@@ -12127,43 +12137,41 @@
         <v>345</v>
       </c>
       <c r="F148" s="3" t="s">
-        <v>209</v>
+        <v>31</v>
       </c>
       <c r="G148" s="3" t="s">
-        <v>257</v>
+        <v>50</v>
       </c>
       <c r="H148" s="3" t="s">
-        <v>70</v>
+        <v>137</v>
       </c>
       <c r="I148" s="3" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="J148" s="3" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K148" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L148" s="6" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="M148" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="N148" s="6" t="s">
         <v>434</v>
       </c>
-      <c r="N148" s="6" t="s">
-        <v>435</v>
-      </c>
       <c r="O148" s="3" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="P148" s="3"/>
       <c r="Q148" s="3"/>
       <c r="R148" s="3">
-        <v>702</v>
-      </c>
-      <c r="S148" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>13563</v>
+      </c>
+      <c r="S148" s="3"/>
       <c r="T148" s="3"/>
       <c r="U148" s="3"/>
       <c r="V148" s="3"/>
@@ -12176,16 +12184,14 @@
       <c r="AA148" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AB148" s="3">
-        <v>1</v>
-      </c>
+      <c r="AB148" s="3"/>
     </row>
     <row r="149" spans="1:28">
       <c r="A149" s="7">
         <v>147</v>
       </c>
       <c r="B149" s="7">
-        <v>2026060062</v>
+        <v>2026060061</v>
       </c>
       <c r="C149" s="7">
         <v>1</v>
@@ -12206,10 +12212,10 @@
         <v>70</v>
       </c>
       <c r="I149" s="7" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="J149" s="7" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K149" s="7" t="s">
         <v>36</v>
@@ -12218,20 +12224,22 @@
         <v>377</v>
       </c>
       <c r="M149" s="8" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="N149" s="8" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="O149" s="7" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="P149" s="7"/>
       <c r="Q149" s="7"/>
       <c r="R149" s="7">
         <v>702</v>
       </c>
-      <c r="S149" s="7"/>
+      <c r="S149" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T149" s="7"/>
       <c r="U149" s="7"/>
       <c r="V149" s="7"/>
@@ -12244,14 +12252,16 @@
       <c r="AA149" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AB149" s="7"/>
+      <c r="AB149" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="150" spans="1:28">
       <c r="A150" s="3">
         <v>148</v>
       </c>
       <c r="B150" s="3">
-        <v>2026060048</v>
+        <v>2026060062</v>
       </c>
       <c r="C150" s="3">
         <v>1</v>
@@ -12266,16 +12276,16 @@
         <v>209</v>
       </c>
       <c r="G150" s="3" t="s">
-        <v>137</v>
+        <v>257</v>
       </c>
       <c r="H150" s="3" t="s">
-        <v>106</v>
+        <v>70</v>
       </c>
       <c r="I150" s="3" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="J150" s="3" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K150" s="3" t="s">
         <v>36</v>
@@ -12284,22 +12294,20 @@
         <v>377</v>
       </c>
       <c r="M150" s="6" t="s">
+        <v>436</v>
+      </c>
+      <c r="N150" s="6" t="s">
         <v>437</v>
       </c>
-      <c r="N150" s="6" t="s">
-        <v>438</v>
-      </c>
       <c r="O150" s="3" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="P150" s="3"/>
       <c r="Q150" s="3"/>
       <c r="R150" s="3">
-        <v>5766</v>
-      </c>
-      <c r="S150" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>702</v>
+      </c>
+      <c r="S150" s="3"/>
       <c r="T150" s="3"/>
       <c r="U150" s="3"/>
       <c r="V150" s="3"/>
@@ -12312,16 +12320,14 @@
       <c r="AA150" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AB150" s="3">
-        <v>1</v>
-      </c>
+      <c r="AB150" s="3"/>
     </row>
     <row r="151" spans="1:28">
       <c r="A151" s="7">
         <v>149</v>
       </c>
       <c r="B151" s="7">
-        <v>2026060049</v>
+        <v>2026060048</v>
       </c>
       <c r="C151" s="7">
         <v>1</v>
@@ -12342,10 +12348,10 @@
         <v>106</v>
       </c>
       <c r="I151" s="7" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="J151" s="7" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K151" s="7" t="s">
         <v>36</v>
@@ -12354,20 +12360,22 @@
         <v>377</v>
       </c>
       <c r="M151" s="8" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="N151" s="8" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="O151" s="7" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="P151" s="7"/>
       <c r="Q151" s="7"/>
       <c r="R151" s="7">
         <v>5766</v>
       </c>
-      <c r="S151" s="7"/>
+      <c r="S151" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T151" s="7"/>
       <c r="U151" s="7"/>
       <c r="V151" s="7"/>
@@ -12380,14 +12388,16 @@
       <c r="AA151" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AB151" s="7"/>
+      <c r="AB151" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="152" spans="1:28">
       <c r="A152" s="3">
         <v>150</v>
       </c>
       <c r="B152" s="3">
-        <v>2026061105</v>
+        <v>2026060049</v>
       </c>
       <c r="C152" s="3">
         <v>1</v>
@@ -12399,7 +12409,7 @@
         <v>345</v>
       </c>
       <c r="F152" s="3" t="s">
-        <v>42</v>
+        <v>209</v>
       </c>
       <c r="G152" s="3" t="s">
         <v>137</v>
@@ -12408,32 +12418,32 @@
         <v>106</v>
       </c>
       <c r="I152" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J152" s="3" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K152" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L152" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="M152" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="N152" s="6" t="s">
         <v>440</v>
       </c>
-      <c r="M152" s="6" t="s">
-        <v>441</v>
-      </c>
-      <c r="N152" s="6"/>
       <c r="O152" s="3" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="P152" s="3"/>
       <c r="Q152" s="3"/>
       <c r="R152" s="3">
-        <v>167548</v>
-      </c>
-      <c r="S152" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>5766</v>
+      </c>
+      <c r="S152" s="3"/>
       <c r="T152" s="3"/>
       <c r="U152" s="3"/>
       <c r="V152" s="3"/>
@@ -12446,16 +12456,14 @@
       <c r="AA152" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AB152" s="3">
-        <v>1</v>
-      </c>
+      <c r="AB152" s="3"/>
     </row>
     <row r="153" spans="1:28">
       <c r="A153" s="7">
         <v>151</v>
       </c>
       <c r="B153" s="7">
-        <v>2026061106</v>
+        <v>2026061105</v>
       </c>
       <c r="C153" s="7">
         <v>1</v>
@@ -12476,30 +12484,32 @@
         <v>106</v>
       </c>
       <c r="I153" s="7" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="J153" s="7" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K153" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L153" s="8" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="M153" s="8" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="N153" s="8"/>
       <c r="O153" s="7" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="P153" s="7"/>
       <c r="Q153" s="7"/>
       <c r="R153" s="7">
         <v>167548</v>
       </c>
-      <c r="S153" s="7"/>
+      <c r="S153" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T153" s="7"/>
       <c r="U153" s="7"/>
       <c r="V153" s="7"/>
@@ -12512,14 +12522,16 @@
       <c r="AA153" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AB153" s="7"/>
+      <c r="AB153" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="154" spans="1:28">
       <c r="A154" s="3">
         <v>152</v>
       </c>
       <c r="B154" s="3">
-        <v>2026060819</v>
+        <v>2026061106</v>
       </c>
       <c r="C154" s="3">
         <v>1</v>
@@ -12531,45 +12543,39 @@
         <v>345</v>
       </c>
       <c r="F154" s="3" t="s">
-        <v>113</v>
+        <v>42</v>
       </c>
       <c r="G154" s="3" t="s">
-        <v>303</v>
+        <v>137</v>
       </c>
       <c r="H154" s="3" t="s">
-        <v>315</v>
+        <v>106</v>
       </c>
       <c r="I154" s="3" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="J154" s="3" t="s">
-        <v>133</v>
+        <v>428</v>
       </c>
       <c r="K154" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L154" s="6" t="s">
+        <v>442</v>
+      </c>
+      <c r="M154" s="6" t="s">
         <v>443</v>
       </c>
-      <c r="M154" s="6" t="s">
-        <v>444</v>
-      </c>
-      <c r="N154" s="6" t="s">
-        <v>358</v>
-      </c>
+      <c r="N154" s="6"/>
       <c r="O154" s="3" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="P154" s="3"/>
-      <c r="Q154" s="3">
-        <v>35761</v>
-      </c>
+      <c r="Q154" s="3"/>
       <c r="R154" s="3">
-        <v>68540</v>
-      </c>
-      <c r="S154" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>167548</v>
+      </c>
+      <c r="S154" s="3"/>
       <c r="T154" s="3"/>
       <c r="U154" s="3"/>
       <c r="V154" s="3"/>
@@ -12579,7 +12585,9 @@
       <c r="Z154" s="6" t="s">
         <v>349</v>
       </c>
-      <c r="AA154" s="3"/>
+      <c r="AA154" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="AB154" s="3"/>
     </row>
     <row r="155" spans="1:28">
@@ -12587,7 +12595,7 @@
         <v>153</v>
       </c>
       <c r="B155" s="7">
-        <v>2026060820</v>
+        <v>2026060819</v>
       </c>
       <c r="C155" s="7">
         <v>1</v>
@@ -12608,7 +12616,7 @@
         <v>315</v>
       </c>
       <c r="I155" s="7" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="J155" s="7" t="s">
         <v>133</v>
@@ -12617,16 +12625,16 @@
         <v>36</v>
       </c>
       <c r="L155" s="8" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="M155" s="8" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="N155" s="8" t="s">
         <v>358</v>
       </c>
       <c r="O155" s="7" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="P155" s="7"/>
       <c r="Q155" s="7">
@@ -12635,7 +12643,9 @@
       <c r="R155" s="7">
         <v>68540</v>
       </c>
-      <c r="S155" s="7"/>
+      <c r="S155" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T155" s="7"/>
       <c r="U155" s="7"/>
       <c r="V155" s="7"/>
@@ -12645,9 +12655,7 @@
       <c r="Z155" s="8" t="s">
         <v>349</v>
       </c>
-      <c r="AA155" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="AA155" s="7"/>
       <c r="AB155" s="7"/>
     </row>
     <row r="156" spans="1:28">
@@ -12655,7 +12663,7 @@
         <v>154</v>
       </c>
       <c r="B156" s="3">
-        <v>2026060922</v>
+        <v>2026060820</v>
       </c>
       <c r="C156" s="3">
         <v>1</v>
@@ -12667,7 +12675,7 @@
         <v>345</v>
       </c>
       <c r="F156" s="3" t="s">
-        <v>87</v>
+        <v>113</v>
       </c>
       <c r="G156" s="3" t="s">
         <v>303</v>
@@ -12676,7 +12684,7 @@
         <v>315</v>
       </c>
       <c r="I156" s="3" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="J156" s="3" t="s">
         <v>133</v>
@@ -12685,16 +12693,16 @@
         <v>36</v>
       </c>
       <c r="L156" s="6" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="M156" s="6" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="N156" s="6" t="s">
         <v>358</v>
       </c>
       <c r="O156" s="3" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="P156" s="3"/>
       <c r="Q156" s="3">
@@ -12707,27 +12715,23 @@
       <c r="T156" s="3"/>
       <c r="U156" s="3"/>
       <c r="V156" s="3"/>
-      <c r="W156" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="W156" s="3"/>
       <c r="X156" s="3"/>
       <c r="Y156" s="3"/>
       <c r="Z156" s="6" t="s">
-        <v>366</v>
+        <v>349</v>
       </c>
       <c r="AA156" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AB156" s="3">
-        <v>1</v>
-      </c>
+      <c r="AB156" s="3"/>
     </row>
     <row r="157" spans="1:28">
       <c r="A157" s="7">
         <v>155</v>
       </c>
       <c r="B157" s="7">
-        <v>2026060527</v>
+        <v>2026060922</v>
       </c>
       <c r="C157" s="7">
         <v>1</v>
@@ -12739,49 +12743,53 @@
         <v>345</v>
       </c>
       <c r="F157" s="7" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="G157" s="7" t="s">
-        <v>210</v>
+        <v>303</v>
       </c>
       <c r="H157" s="7" t="s">
-        <v>75</v>
+        <v>315</v>
       </c>
       <c r="I157" s="7" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="J157" s="7" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="K157" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L157" s="8" t="s">
+        <v>445</v>
+      </c>
+      <c r="M157" s="8" t="s">
         <v>446</v>
       </c>
-      <c r="M157" s="8" t="s">
-        <v>447</v>
-      </c>
       <c r="N157" s="8" t="s">
-        <v>448</v>
+        <v>358</v>
       </c>
       <c r="O157" s="7" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="P157" s="7"/>
-      <c r="Q157" s="7"/>
+      <c r="Q157" s="7">
+        <v>35761</v>
+      </c>
       <c r="R157" s="7">
-        <v>33686</v>
+        <v>68540</v>
       </c>
       <c r="S157" s="7"/>
       <c r="T157" s="7"/>
       <c r="U157" s="7"/>
       <c r="V157" s="7"/>
-      <c r="W157" s="7"/>
+      <c r="W157" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="X157" s="7"/>
       <c r="Y157" s="7"/>
       <c r="Z157" s="8" t="s">
-        <v>349</v>
+        <v>366</v>
       </c>
       <c r="AA157" s="7" t="s">
         <v>40</v>
@@ -12816,7 +12824,7 @@
         <v>75</v>
       </c>
       <c r="I158" s="3" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="J158" s="3" t="s">
         <v>140</v>
@@ -12825,13 +12833,13 @@
         <v>36</v>
       </c>
       <c r="L158" s="6" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="M158" s="6" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="N158" s="6" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="O158" s="3" t="s">
         <v>39</v>
@@ -12861,7 +12869,7 @@
         <v>157</v>
       </c>
       <c r="B159" s="7">
-        <v>2026060408</v>
+        <v>2026060527</v>
       </c>
       <c r="C159" s="7">
         <v>1</v>
@@ -12876,13 +12884,13 @@
         <v>49</v>
       </c>
       <c r="G159" s="7" t="s">
-        <v>43</v>
+        <v>210</v>
       </c>
       <c r="H159" s="7" t="s">
-        <v>257</v>
+        <v>75</v>
       </c>
       <c r="I159" s="7" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="J159" s="7" t="s">
         <v>140</v>
@@ -12891,25 +12899,23 @@
         <v>36</v>
       </c>
       <c r="L159" s="8" t="s">
-        <v>427</v>
+        <v>448</v>
       </c>
       <c r="M159" s="8" t="s">
+        <v>449</v>
+      </c>
+      <c r="N159" s="8" t="s">
         <v>450</v>
       </c>
-      <c r="N159" s="8" t="s">
-        <v>451</v>
-      </c>
       <c r="O159" s="7" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="P159" s="7"/>
       <c r="Q159" s="7"/>
       <c r="R159" s="7">
-        <v>19776</v>
-      </c>
-      <c r="S159" s="7" t="s">
-        <v>40</v>
-      </c>
+        <v>33686</v>
+      </c>
+      <c r="S159" s="7"/>
       <c r="T159" s="7"/>
       <c r="U159" s="7"/>
       <c r="V159" s="7"/>
@@ -12919,7 +12925,9 @@
       <c r="Z159" s="8" t="s">
         <v>349</v>
       </c>
-      <c r="AA159" s="7"/>
+      <c r="AA159" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="AB159" s="7"/>
     </row>
     <row r="160" spans="1:28">
@@ -12927,7 +12935,7 @@
         <v>158</v>
       </c>
       <c r="B160" s="3">
-        <v>2026060409</v>
+        <v>2026060408</v>
       </c>
       <c r="C160" s="3">
         <v>1</v>
@@ -12948,7 +12956,7 @@
         <v>257</v>
       </c>
       <c r="I160" s="3" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J160" s="3" t="s">
         <v>140</v>
@@ -12957,23 +12965,25 @@
         <v>36</v>
       </c>
       <c r="L160" s="6" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="M160" s="6" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="N160" s="6" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="O160" s="3" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="P160" s="3"/>
       <c r="Q160" s="3"/>
       <c r="R160" s="3">
         <v>19776</v>
       </c>
-      <c r="S160" s="3"/>
+      <c r="S160" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T160" s="3"/>
       <c r="U160" s="3"/>
       <c r="V160" s="3"/>
@@ -12983,9 +12993,7 @@
       <c r="Z160" s="6" t="s">
         <v>349</v>
       </c>
-      <c r="AA160" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="AA160" s="3"/>
       <c r="AB160" s="3"/>
     </row>
     <row r="161" spans="1:28">
@@ -12993,7 +13001,7 @@
         <v>159</v>
       </c>
       <c r="B161" s="7">
-        <v>2026060389</v>
+        <v>2026060409</v>
       </c>
       <c r="C161" s="7">
         <v>1</v>
@@ -13008,13 +13016,13 @@
         <v>49</v>
       </c>
       <c r="G161" s="7" t="s">
-        <v>137</v>
+        <v>43</v>
       </c>
       <c r="H161" s="7" t="s">
-        <v>106</v>
+        <v>257</v>
       </c>
       <c r="I161" s="7" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="J161" s="7" t="s">
         <v>140</v>
@@ -13023,25 +13031,23 @@
         <v>36</v>
       </c>
       <c r="L161" s="8" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="M161" s="8" t="s">
+        <v>452</v>
+      </c>
+      <c r="N161" s="8" t="s">
         <v>453</v>
       </c>
-      <c r="N161" s="8" t="s">
-        <v>454</v>
-      </c>
       <c r="O161" s="7" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="P161" s="7"/>
       <c r="Q161" s="7"/>
       <c r="R161" s="7">
-        <v>92779</v>
-      </c>
-      <c r="S161" s="7" t="s">
-        <v>40</v>
-      </c>
+        <v>19776</v>
+      </c>
+      <c r="S161" s="7"/>
       <c r="T161" s="7"/>
       <c r="U161" s="7"/>
       <c r="V161" s="7"/>
@@ -13051,7 +13057,9 @@
       <c r="Z161" s="8" t="s">
         <v>349</v>
       </c>
-      <c r="AA161" s="7"/>
+      <c r="AA161" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="AB161" s="7"/>
     </row>
     <row r="162" spans="1:28">
@@ -13059,7 +13067,7 @@
         <v>160</v>
       </c>
       <c r="B162" s="3">
-        <v>2026060390</v>
+        <v>2026060389</v>
       </c>
       <c r="C162" s="3">
         <v>1</v>
@@ -13080,7 +13088,7 @@
         <v>106</v>
       </c>
       <c r="I162" s="3" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="J162" s="3" t="s">
         <v>140</v>
@@ -13089,23 +13097,25 @@
         <v>36</v>
       </c>
       <c r="L162" s="6" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="M162" s="6" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="N162" s="6" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="O162" s="3" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="P162" s="3"/>
       <c r="Q162" s="3"/>
       <c r="R162" s="3">
         <v>92779</v>
       </c>
-      <c r="S162" s="3"/>
+      <c r="S162" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T162" s="3"/>
       <c r="U162" s="3"/>
       <c r="V162" s="3"/>
@@ -13115,9 +13125,7 @@
       <c r="Z162" s="6" t="s">
         <v>349</v>
       </c>
-      <c r="AA162" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="AA162" s="3"/>
       <c r="AB162" s="3"/>
     </row>
     <row r="163" spans="1:28">
@@ -13125,7 +13133,7 @@
         <v>161</v>
       </c>
       <c r="B163" s="7">
-        <v>2026060853</v>
+        <v>2026060390</v>
       </c>
       <c r="C163" s="7">
         <v>1</v>
@@ -13137,16 +13145,16 @@
         <v>345</v>
       </c>
       <c r="F163" s="7" t="s">
-        <v>113</v>
+        <v>49</v>
       </c>
       <c r="G163" s="7" t="s">
-        <v>105</v>
+        <v>137</v>
       </c>
       <c r="H163" s="7" t="s">
-        <v>234</v>
+        <v>106</v>
       </c>
       <c r="I163" s="7" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="J163" s="7" t="s">
         <v>140</v>
@@ -13155,16 +13163,16 @@
         <v>36</v>
       </c>
       <c r="L163" s="8" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="M163" s="8" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="N163" s="8" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="O163" s="7" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="P163" s="7"/>
       <c r="Q163" s="7"/>
@@ -13177,25 +13185,21 @@
       <c r="V163" s="7"/>
       <c r="W163" s="7"/>
       <c r="X163" s="7"/>
-      <c r="Y163" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="Y163" s="7"/>
       <c r="Z163" s="8" t="s">
-        <v>455</v>
+        <v>349</v>
       </c>
       <c r="AA163" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AB163" s="7">
-        <v>1</v>
-      </c>
+      <c r="AB163" s="7"/>
     </row>
     <row r="164" spans="1:28">
       <c r="A164" s="3">
         <v>162</v>
       </c>
       <c r="B164" s="3">
-        <v>2026060383</v>
+        <v>2026060853</v>
       </c>
       <c r="C164" s="3">
         <v>1</v>
@@ -13207,16 +13211,16 @@
         <v>345</v>
       </c>
       <c r="F164" s="3" t="s">
-        <v>49</v>
+        <v>113</v>
       </c>
       <c r="G164" s="3" t="s">
-        <v>354</v>
+        <v>105</v>
       </c>
       <c r="H164" s="3" t="s">
-        <v>202</v>
+        <v>234</v>
       </c>
       <c r="I164" s="3" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="J164" s="3" t="s">
         <v>140</v>
@@ -13225,13 +13229,13 @@
         <v>36</v>
       </c>
       <c r="L164" s="6" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="M164" s="6" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="N164" s="6" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="O164" s="3" t="s">
         <v>39</v>
@@ -13239,29 +13243,33 @@
       <c r="P164" s="3"/>
       <c r="Q164" s="3"/>
       <c r="R164" s="3">
-        <v>207716</v>
-      </c>
-      <c r="S164" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>92779</v>
+      </c>
+      <c r="S164" s="3"/>
       <c r="T164" s="3"/>
       <c r="U164" s="3"/>
       <c r="V164" s="3"/>
       <c r="W164" s="3"/>
       <c r="X164" s="3"/>
-      <c r="Y164" s="3"/>
+      <c r="Y164" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="Z164" s="6" t="s">
-        <v>349</v>
-      </c>
-      <c r="AA164" s="3"/>
-      <c r="AB164" s="3"/>
+        <v>457</v>
+      </c>
+      <c r="AA164" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB164" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="165" spans="1:28">
       <c r="A165" s="7">
         <v>163</v>
       </c>
       <c r="B165" s="7">
-        <v>2026060384</v>
+        <v>2026060383</v>
       </c>
       <c r="C165" s="7">
         <v>1</v>
@@ -13282,7 +13290,7 @@
         <v>202</v>
       </c>
       <c r="I165" s="7" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="J165" s="7" t="s">
         <v>140</v>
@@ -13291,23 +13299,25 @@
         <v>36</v>
       </c>
       <c r="L165" s="8" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="M165" s="8" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="N165" s="8" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="O165" s="7" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="P165" s="7"/>
       <c r="Q165" s="7"/>
       <c r="R165" s="7">
         <v>207716</v>
       </c>
-      <c r="S165" s="7"/>
+      <c r="S165" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T165" s="7"/>
       <c r="U165" s="7"/>
       <c r="V165" s="7"/>
@@ -13317,9 +13327,7 @@
       <c r="Z165" s="8" t="s">
         <v>349</v>
       </c>
-      <c r="AA165" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="AA165" s="7"/>
       <c r="AB165" s="7"/>
     </row>
     <row r="166" spans="1:28">
@@ -13327,7 +13335,7 @@
         <v>164</v>
       </c>
       <c r="B166" s="3">
-        <v>2026060569</v>
+        <v>2026060384</v>
       </c>
       <c r="C166" s="3">
         <v>1</v>
@@ -13342,13 +13350,13 @@
         <v>49</v>
       </c>
       <c r="G166" s="3" t="s">
-        <v>303</v>
+        <v>354</v>
       </c>
       <c r="H166" s="3" t="s">
-        <v>315</v>
+        <v>202</v>
       </c>
       <c r="I166" s="3" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="J166" s="3" t="s">
         <v>140</v>
@@ -13357,16 +13365,16 @@
         <v>36</v>
       </c>
       <c r="L166" s="6" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="M166" s="6" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="N166" s="6" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="O166" s="3" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="P166" s="3"/>
       <c r="Q166" s="3"/>
@@ -13375,29 +13383,25 @@
       </c>
       <c r="S166" s="3"/>
       <c r="T166" s="3"/>
-      <c r="U166" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="U166" s="3"/>
       <c r="V166" s="3"/>
       <c r="W166" s="3"/>
       <c r="X166" s="3"/>
       <c r="Y166" s="3"/>
       <c r="Z166" s="6" t="s">
-        <v>403</v>
+        <v>349</v>
       </c>
       <c r="AA166" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AB166" s="3">
-        <v>1</v>
-      </c>
+      <c r="AB166" s="3"/>
     </row>
     <row r="167" spans="1:28">
       <c r="A167" s="7">
         <v>165</v>
       </c>
       <c r="B167" s="7">
-        <v>2026060387</v>
+        <v>2026060569</v>
       </c>
       <c r="C167" s="7">
         <v>1</v>
@@ -13412,13 +13416,13 @@
         <v>49</v>
       </c>
       <c r="G167" s="7" t="s">
-        <v>50</v>
+        <v>303</v>
       </c>
       <c r="H167" s="7" t="s">
-        <v>137</v>
+        <v>315</v>
       </c>
       <c r="I167" s="7" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="J167" s="7" t="s">
         <v>140</v>
@@ -13427,13 +13431,13 @@
         <v>36</v>
       </c>
       <c r="L167" s="8" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="M167" s="8" t="s">
+        <v>459</v>
+      </c>
+      <c r="N167" s="8" t="s">
         <v>460</v>
-      </c>
-      <c r="N167" s="8" t="s">
-        <v>461</v>
       </c>
       <c r="O167" s="7" t="s">
         <v>39</v>
@@ -13441,29 +13445,33 @@
       <c r="P167" s="7"/>
       <c r="Q167" s="7"/>
       <c r="R167" s="7">
-        <v>152071</v>
-      </c>
-      <c r="S167" s="7" t="s">
-        <v>40</v>
-      </c>
+        <v>207716</v>
+      </c>
+      <c r="S167" s="7"/>
       <c r="T167" s="7"/>
-      <c r="U167" s="7"/>
+      <c r="U167" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="V167" s="7"/>
       <c r="W167" s="7"/>
       <c r="X167" s="7"/>
       <c r="Y167" s="7"/>
       <c r="Z167" s="8" t="s">
-        <v>349</v>
-      </c>
-      <c r="AA167" s="7"/>
-      <c r="AB167" s="7"/>
+        <v>403</v>
+      </c>
+      <c r="AA167" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB167" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="168" spans="1:28">
       <c r="A168" s="3">
         <v>166</v>
       </c>
       <c r="B168" s="3">
-        <v>2026060388</v>
+        <v>2026060387</v>
       </c>
       <c r="C168" s="3">
         <v>1</v>
@@ -13484,7 +13492,7 @@
         <v>137</v>
       </c>
       <c r="I168" s="3" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="J168" s="3" t="s">
         <v>140</v>
@@ -13493,23 +13501,25 @@
         <v>36</v>
       </c>
       <c r="L168" s="6" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="M168" s="6" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="N168" s="6" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="O168" s="3" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="P168" s="3"/>
       <c r="Q168" s="3"/>
       <c r="R168" s="3">
         <v>152071</v>
       </c>
-      <c r="S168" s="3"/>
+      <c r="S168" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T168" s="3"/>
       <c r="U168" s="3"/>
       <c r="V168" s="3"/>
@@ -13519,9 +13529,7 @@
       <c r="Z168" s="6" t="s">
         <v>349</v>
       </c>
-      <c r="AA168" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="AA168" s="3"/>
       <c r="AB168" s="3"/>
     </row>
     <row r="169" spans="1:28">
@@ -13529,7 +13537,7 @@
         <v>167</v>
       </c>
       <c r="B169" s="7">
-        <v>2026060570</v>
+        <v>2026060388</v>
       </c>
       <c r="C169" s="7">
         <v>1</v>
@@ -13544,13 +13552,13 @@
         <v>49</v>
       </c>
       <c r="G169" s="7" t="s">
-        <v>315</v>
+        <v>50</v>
       </c>
       <c r="H169" s="7" t="s">
-        <v>164</v>
+        <v>137</v>
       </c>
       <c r="I169" s="7" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="J169" s="7" t="s">
         <v>140</v>
@@ -13559,16 +13567,16 @@
         <v>36</v>
       </c>
       <c r="L169" s="8" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="M169" s="8" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="N169" s="8" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="O169" s="7" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="P169" s="7"/>
       <c r="Q169" s="7"/>
@@ -13577,29 +13585,25 @@
       </c>
       <c r="S169" s="7"/>
       <c r="T169" s="7"/>
-      <c r="U169" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="U169" s="7"/>
       <c r="V169" s="7"/>
       <c r="W169" s="7"/>
       <c r="X169" s="7"/>
       <c r="Y169" s="7"/>
       <c r="Z169" s="8" t="s">
-        <v>403</v>
+        <v>349</v>
       </c>
       <c r="AA169" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AB169" s="7">
-        <v>1</v>
-      </c>
+      <c r="AB169" s="7"/>
     </row>
     <row r="170" spans="1:28">
       <c r="A170" s="3">
         <v>168</v>
       </c>
       <c r="B170" s="3">
-        <v>2026061402</v>
+        <v>2026060570</v>
       </c>
       <c r="C170" s="3">
         <v>1</v>
@@ -13611,31 +13615,31 @@
         <v>345</v>
       </c>
       <c r="F170" s="3" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="G170" s="3" t="s">
-        <v>359</v>
+        <v>315</v>
       </c>
       <c r="H170" s="3" t="s">
-        <v>354</v>
+        <v>164</v>
       </c>
       <c r="I170" s="3" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="J170" s="3" t="s">
-        <v>463</v>
+        <v>140</v>
       </c>
       <c r="K170" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L170" s="6" t="s">
-        <v>464</v>
+        <v>429</v>
       </c>
       <c r="M170" s="6" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="N170" s="6" t="s">
-        <v>383</v>
+        <v>463</v>
       </c>
       <c r="O170" s="3" t="s">
         <v>39</v>
@@ -13643,29 +13647,33 @@
       <c r="P170" s="3"/>
       <c r="Q170" s="3"/>
       <c r="R170" s="3">
-        <v>6530</v>
-      </c>
-      <c r="S170" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>152071</v>
+      </c>
+      <c r="S170" s="3"/>
       <c r="T170" s="3"/>
-      <c r="U170" s="3"/>
+      <c r="U170" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="V170" s="3"/>
       <c r="W170" s="3"/>
       <c r="X170" s="3"/>
       <c r="Y170" s="3"/>
       <c r="Z170" s="6" t="s">
-        <v>349</v>
-      </c>
-      <c r="AA170" s="3"/>
-      <c r="AB170" s="3"/>
+        <v>403</v>
+      </c>
+      <c r="AA170" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB170" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="171" spans="1:28">
       <c r="A171" s="7">
         <v>169</v>
       </c>
       <c r="B171" s="7">
-        <v>2026061403</v>
+        <v>2026061402</v>
       </c>
       <c r="C171" s="7">
         <v>1</v>
@@ -13686,32 +13694,34 @@
         <v>354</v>
       </c>
       <c r="I171" s="7" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="J171" s="7" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="K171" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L171" s="8" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="M171" s="8" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="N171" s="8" t="s">
         <v>383</v>
       </c>
       <c r="O171" s="7" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="P171" s="7"/>
       <c r="Q171" s="7"/>
       <c r="R171" s="7">
         <v>6530</v>
       </c>
-      <c r="S171" s="7"/>
+      <c r="S171" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T171" s="7"/>
       <c r="U171" s="7"/>
       <c r="V171" s="7"/>
@@ -13721,9 +13731,7 @@
       <c r="Z171" s="8" t="s">
         <v>349</v>
       </c>
-      <c r="AA171" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="AA171" s="7"/>
       <c r="AB171" s="7"/>
     </row>
     <row r="172" spans="1:28">
@@ -13731,7 +13739,7 @@
         <v>170</v>
       </c>
       <c r="B172" s="3">
-        <v>2026060081</v>
+        <v>2026061403</v>
       </c>
       <c r="C172" s="3">
         <v>1</v>
@@ -13743,43 +13751,41 @@
         <v>345</v>
       </c>
       <c r="F172" s="3" t="s">
-        <v>209</v>
+        <v>31</v>
       </c>
       <c r="G172" s="3" t="s">
-        <v>315</v>
+        <v>359</v>
       </c>
       <c r="H172" s="3" t="s">
-        <v>164</v>
+        <v>354</v>
       </c>
       <c r="I172" s="3" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="J172" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="K172" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L172" s="6" t="s">
-        <v>400</v>
+        <v>466</v>
       </c>
       <c r="M172" s="6" t="s">
         <v>467</v>
       </c>
       <c r="N172" s="6" t="s">
-        <v>468</v>
+        <v>383</v>
       </c>
       <c r="O172" s="3" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="P172" s="3"/>
       <c r="Q172" s="3"/>
       <c r="R172" s="3">
-        <v>48</v>
-      </c>
-      <c r="S172" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>6530</v>
+      </c>
+      <c r="S172" s="3"/>
       <c r="T172" s="3"/>
       <c r="U172" s="3"/>
       <c r="V172" s="3"/>
@@ -13789,7 +13795,9 @@
       <c r="Z172" s="6" t="s">
         <v>349</v>
       </c>
-      <c r="AA172" s="3"/>
+      <c r="AA172" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="AB172" s="3"/>
     </row>
     <row r="173" spans="1:28">
@@ -13797,7 +13805,7 @@
         <v>171</v>
       </c>
       <c r="B173" s="7">
-        <v>2026060082</v>
+        <v>2026060081</v>
       </c>
       <c r="C173" s="7">
         <v>1</v>
@@ -13818,10 +13826,10 @@
         <v>164</v>
       </c>
       <c r="I173" s="7" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="J173" s="7" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="K173" s="7" t="s">
         <v>36</v>
@@ -13830,20 +13838,22 @@
         <v>400</v>
       </c>
       <c r="M173" s="8" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="N173" s="8" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="O173" s="7" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="P173" s="7"/>
       <c r="Q173" s="7"/>
       <c r="R173" s="7">
         <v>48</v>
       </c>
-      <c r="S173" s="7"/>
+      <c r="S173" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T173" s="7"/>
       <c r="U173" s="7"/>
       <c r="V173" s="7"/>
@@ -13853,9 +13863,7 @@
       <c r="Z173" s="8" t="s">
         <v>349</v>
       </c>
-      <c r="AA173" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="AA173" s="7"/>
       <c r="AB173" s="7"/>
     </row>
     <row r="174" spans="1:28">
@@ -13863,7 +13871,7 @@
         <v>172</v>
       </c>
       <c r="B174" s="3">
-        <v>2026061407</v>
+        <v>2026060082</v>
       </c>
       <c r="C174" s="3">
         <v>1</v>
@@ -13875,43 +13883,41 @@
         <v>345</v>
       </c>
       <c r="F174" s="3" t="s">
-        <v>31</v>
+        <v>209</v>
       </c>
       <c r="G174" s="3" t="s">
-        <v>202</v>
+        <v>315</v>
       </c>
       <c r="H174" s="3" t="s">
-        <v>50</v>
+        <v>164</v>
       </c>
       <c r="I174" s="3" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="J174" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="K174" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L174" s="6" t="s">
-        <v>373</v>
+        <v>400</v>
       </c>
       <c r="M174" s="6" t="s">
+        <v>469</v>
+      </c>
+      <c r="N174" s="6" t="s">
         <v>470</v>
       </c>
-      <c r="N174" s="6" t="s">
-        <v>432</v>
-      </c>
       <c r="O174" s="3" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="P174" s="3"/>
       <c r="Q174" s="3"/>
       <c r="R174" s="3">
-        <v>478</v>
-      </c>
-      <c r="S174" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="S174" s="3"/>
       <c r="T174" s="3"/>
       <c r="U174" s="3"/>
       <c r="V174" s="3"/>
@@ -13921,7 +13927,9 @@
       <c r="Z174" s="6" t="s">
         <v>349</v>
       </c>
-      <c r="AA174" s="3"/>
+      <c r="AA174" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="AB174" s="3"/>
     </row>
     <row r="175" spans="1:28">
@@ -13929,7 +13937,7 @@
         <v>173</v>
       </c>
       <c r="B175" s="7">
-        <v>2026061408</v>
+        <v>2026061407</v>
       </c>
       <c r="C175" s="7">
         <v>1</v>
@@ -13950,10 +13958,10 @@
         <v>50</v>
       </c>
       <c r="I175" s="7" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="J175" s="7" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="K175" s="7" t="s">
         <v>36</v>
@@ -13962,20 +13970,22 @@
         <v>373</v>
       </c>
       <c r="M175" s="8" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="N175" s="8" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="O175" s="7" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="P175" s="7"/>
       <c r="Q175" s="7"/>
       <c r="R175" s="7">
         <v>478</v>
       </c>
-      <c r="S175" s="7"/>
+      <c r="S175" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T175" s="7"/>
       <c r="U175" s="7"/>
       <c r="V175" s="7"/>
@@ -13985,9 +13995,7 @@
       <c r="Z175" s="8" t="s">
         <v>349</v>
       </c>
-      <c r="AA175" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="AA175" s="7"/>
       <c r="AB175" s="7"/>
     </row>
     <row r="176" spans="1:28">
@@ -13995,7 +14003,7 @@
         <v>174</v>
       </c>
       <c r="B176" s="3">
-        <v>2026060145</v>
+        <v>2026061408</v>
       </c>
       <c r="C176" s="3">
         <v>1</v>
@@ -14007,65 +14015,61 @@
         <v>345</v>
       </c>
       <c r="F176" s="3" t="s">
-        <v>209</v>
+        <v>31</v>
       </c>
       <c r="G176" s="3" t="s">
-        <v>143</v>
+        <v>202</v>
       </c>
       <c r="H176" s="3" t="s">
-        <v>165</v>
+        <v>50</v>
       </c>
       <c r="I176" s="3" t="s">
         <v>471</v>
       </c>
       <c r="J176" s="3" t="s">
-        <v>265</v>
+        <v>465</v>
       </c>
       <c r="K176" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L176" s="6" t="s">
-        <v>400</v>
+        <v>373</v>
       </c>
       <c r="M176" s="6" t="s">
         <v>472</v>
       </c>
       <c r="N176" s="6" t="s">
-        <v>473</v>
+        <v>434</v>
       </c>
       <c r="O176" s="3" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="P176" s="3"/>
       <c r="Q176" s="3"/>
       <c r="R176" s="3">
-        <v>38244</v>
+        <v>478</v>
       </c>
       <c r="S176" s="3"/>
       <c r="T176" s="3"/>
-      <c r="U176" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="U176" s="3"/>
       <c r="V176" s="3"/>
       <c r="W176" s="3"/>
       <c r="X176" s="3"/>
       <c r="Y176" s="3"/>
       <c r="Z176" s="6" t="s">
-        <v>403</v>
+        <v>349</v>
       </c>
       <c r="AA176" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AB176" s="3">
-        <v>1</v>
-      </c>
+      <c r="AB176" s="3"/>
     </row>
     <row r="177" spans="1:28">
       <c r="A177" s="7">
         <v>175</v>
       </c>
       <c r="B177" s="7">
-        <v>2026060144</v>
+        <v>2026060145</v>
       </c>
       <c r="C177" s="7">
         <v>1</v>
@@ -14080,13 +14084,13 @@
         <v>209</v>
       </c>
       <c r="G177" s="7" t="s">
-        <v>210</v>
+        <v>143</v>
       </c>
       <c r="H177" s="7" t="s">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="I177" s="7" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="J177" s="7" t="s">
         <v>265</v>
@@ -14098,7 +14102,7 @@
         <v>400</v>
       </c>
       <c r="M177" s="8" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="N177" s="8" t="s">
         <v>475</v>
@@ -14109,7 +14113,7 @@
       <c r="P177" s="7"/>
       <c r="Q177" s="7"/>
       <c r="R177" s="7">
-        <v>386259</v>
+        <v>38244</v>
       </c>
       <c r="S177" s="7"/>
       <c r="T177" s="7"/>
@@ -14135,7 +14139,7 @@
         <v>176</v>
       </c>
       <c r="B178" s="3">
-        <v>2026060143</v>
+        <v>2026060144</v>
       </c>
       <c r="C178" s="3">
         <v>1</v>
@@ -14150,10 +14154,10 @@
         <v>209</v>
       </c>
       <c r="G178" s="3" t="s">
-        <v>291</v>
+        <v>210</v>
       </c>
       <c r="H178" s="3" t="s">
-        <v>210</v>
+        <v>143</v>
       </c>
       <c r="I178" s="3" t="s">
         <v>476</v>
@@ -14168,7 +14172,7 @@
         <v>400</v>
       </c>
       <c r="M178" s="6" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="N178" s="6" t="s">
         <v>477</v>
@@ -14179,7 +14183,7 @@
       <c r="P178" s="3"/>
       <c r="Q178" s="3"/>
       <c r="R178" s="3">
-        <v>381383</v>
+        <v>386259</v>
       </c>
       <c r="S178" s="3"/>
       <c r="T178" s="3"/>
@@ -14205,7 +14209,7 @@
         <v>177</v>
       </c>
       <c r="B179" s="7">
-        <v>2026060142</v>
+        <v>2026060143</v>
       </c>
       <c r="C179" s="7">
         <v>1</v>
@@ -14220,10 +14224,10 @@
         <v>209</v>
       </c>
       <c r="G179" s="7" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H179" s="7" t="s">
-        <v>291</v>
+        <v>210</v>
       </c>
       <c r="I179" s="7" t="s">
         <v>478</v>
@@ -14238,7 +14242,7 @@
         <v>400</v>
       </c>
       <c r="M179" s="8" t="s">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="N179" s="8" t="s">
         <v>479</v>
@@ -14249,7 +14253,7 @@
       <c r="P179" s="7"/>
       <c r="Q179" s="7"/>
       <c r="R179" s="7">
-        <v>31873</v>
+        <v>381383</v>
       </c>
       <c r="S179" s="7"/>
       <c r="T179" s="7"/>
@@ -14275,7 +14279,7 @@
         <v>178</v>
       </c>
       <c r="B180" s="3">
-        <v>2026060141</v>
+        <v>2026060142</v>
       </c>
       <c r="C180" s="3">
         <v>1</v>
@@ -14290,10 +14294,10 @@
         <v>209</v>
       </c>
       <c r="G180" s="3" t="s">
-        <v>225</v>
+        <v>290</v>
       </c>
       <c r="H180" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="I180" s="3" t="s">
         <v>480</v>
@@ -14308,7 +14312,7 @@
         <v>400</v>
       </c>
       <c r="M180" s="6" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="N180" s="6" t="s">
         <v>481</v>
@@ -14319,7 +14323,7 @@
       <c r="P180" s="3"/>
       <c r="Q180" s="3"/>
       <c r="R180" s="3">
-        <v>30842</v>
+        <v>31873</v>
       </c>
       <c r="S180" s="3"/>
       <c r="T180" s="3"/>
@@ -14345,7 +14349,7 @@
         <v>179</v>
       </c>
       <c r="B181" s="7">
-        <v>2026061273</v>
+        <v>2026060141</v>
       </c>
       <c r="C181" s="7">
         <v>1</v>
@@ -14357,27 +14361,31 @@
         <v>345</v>
       </c>
       <c r="F181" s="7" t="s">
-        <v>66</v>
+        <v>209</v>
       </c>
       <c r="G181" s="7" t="s">
-        <v>257</v>
+        <v>225</v>
       </c>
       <c r="H181" s="7" t="s">
-        <v>70</v>
+        <v>290</v>
       </c>
       <c r="I181" s="7" t="s">
         <v>482</v>
       </c>
-      <c r="J181" s="7"/>
-      <c r="K181" s="7"/>
+      <c r="J181" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="K181" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="L181" s="8" t="s">
-        <v>167</v>
+        <v>400</v>
       </c>
       <c r="M181" s="8" t="s">
+        <v>474</v>
+      </c>
+      <c r="N181" s="8" t="s">
         <v>483</v>
-      </c>
-      <c r="N181" s="8" t="s">
-        <v>484</v>
       </c>
       <c r="O181" s="7" t="s">
         <v>39</v>
@@ -14385,21 +14393,19 @@
       <c r="P181" s="7"/>
       <c r="Q181" s="7"/>
       <c r="R181" s="7">
-        <v>0</v>
-      </c>
-      <c r="S181" s="7" t="s">
-        <v>40</v>
-      </c>
+        <v>30842</v>
+      </c>
+      <c r="S181" s="7"/>
       <c r="T181" s="7"/>
-      <c r="U181" s="7"/>
+      <c r="U181" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="V181" s="7"/>
       <c r="W181" s="7"/>
       <c r="X181" s="7"/>
-      <c r="Y181" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="Y181" s="7"/>
       <c r="Z181" s="8" t="s">
-        <v>181</v>
+        <v>403</v>
       </c>
       <c r="AA181" s="7" t="s">
         <v>40</v>
@@ -14413,7 +14419,7 @@
         <v>180</v>
       </c>
       <c r="B182" s="3">
-        <v>2026060898</v>
+        <v>2026061273</v>
       </c>
       <c r="C182" s="3">
         <v>1</v>
@@ -14425,16 +14431,16 @@
         <v>345</v>
       </c>
       <c r="F182" s="3" t="s">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="G182" s="3" t="s">
-        <v>137</v>
+        <v>257</v>
       </c>
       <c r="H182" s="3" t="s">
-        <v>106</v>
+        <v>70</v>
       </c>
       <c r="I182" s="3" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="J182" s="3"/>
       <c r="K182" s="3"/>
@@ -14442,10 +14448,10 @@
         <v>167</v>
       </c>
       <c r="M182" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="N182" s="6" t="s">
         <v>486</v>
-      </c>
-      <c r="N182" s="6" t="s">
-        <v>487</v>
       </c>
       <c r="O182" s="3" t="s">
         <v>39</v>
@@ -14481,7 +14487,7 @@
         <v>181</v>
       </c>
       <c r="B183" s="7">
-        <v>2026060899</v>
+        <v>2026060898</v>
       </c>
       <c r="C183" s="7">
         <v>1</v>
@@ -14496,13 +14502,13 @@
         <v>87</v>
       </c>
       <c r="G183" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="H183" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="H183" s="7" t="s">
-        <v>43</v>
-      </c>
       <c r="I183" s="7" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="J183" s="7"/>
       <c r="K183" s="7"/>
@@ -14510,10 +14516,10 @@
         <v>167</v>
       </c>
       <c r="M183" s="8" t="s">
+        <v>488</v>
+      </c>
+      <c r="N183" s="8" t="s">
         <v>489</v>
-      </c>
-      <c r="N183" s="8" t="s">
-        <v>490</v>
       </c>
       <c r="O183" s="7" t="s">
         <v>39</v>
@@ -14549,7 +14555,7 @@
         <v>182</v>
       </c>
       <c r="B184" s="3">
-        <v>2026060873</v>
+        <v>2026060899</v>
       </c>
       <c r="C184" s="3">
         <v>1</v>
@@ -14564,46 +14570,46 @@
         <v>87</v>
       </c>
       <c r="G184" s="3" t="s">
-        <v>315</v>
+        <v>106</v>
       </c>
       <c r="H184" s="3" t="s">
-        <v>164</v>
+        <v>43</v>
       </c>
       <c r="I184" s="3" t="s">
-        <v>491</v>
-      </c>
-      <c r="J184" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="K184" s="3" t="s">
-        <v>197</v>
-      </c>
+        <v>490</v>
+      </c>
+      <c r="J184" s="3"/>
+      <c r="K184" s="3"/>
       <c r="L184" s="6" t="s">
         <v>167</v>
       </c>
       <c r="M184" s="6" t="s">
+        <v>491</v>
+      </c>
+      <c r="N184" s="6" t="s">
         <v>492</v>
       </c>
-      <c r="N184" s="6" t="s">
-        <v>493</v>
-      </c>
       <c r="O184" s="3" t="s">
-        <v>94</v>
+        <v>39</v>
       </c>
       <c r="P184" s="3"/>
       <c r="Q184" s="3"/>
       <c r="R184" s="3">
         <v>0</v>
       </c>
-      <c r="S184" s="3"/>
+      <c r="S184" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T184" s="3"/>
       <c r="U184" s="3"/>
       <c r="V184" s="3"/>
       <c r="W184" s="3"/>
       <c r="X184" s="3"/>
-      <c r="Y184" s="3"/>
+      <c r="Y184" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="Z184" s="6" t="s">
-        <v>494</v>
+        <v>181</v>
       </c>
       <c r="AA184" s="3" t="s">
         <v>40</v>
@@ -14617,7 +14623,7 @@
         <v>183</v>
       </c>
       <c r="B185" s="7">
-        <v>2026061276</v>
+        <v>2026060873</v>
       </c>
       <c r="C185" s="7">
         <v>1</v>
@@ -14629,49 +14635,49 @@
         <v>345</v>
       </c>
       <c r="F185" s="7" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="G185" s="7" t="s">
-        <v>70</v>
+        <v>315</v>
       </c>
       <c r="H185" s="7" t="s">
-        <v>303</v>
+        <v>164</v>
       </c>
       <c r="I185" s="7" t="s">
-        <v>495</v>
-      </c>
-      <c r="J185" s="7"/>
-      <c r="K185" s="7"/>
+        <v>493</v>
+      </c>
+      <c r="J185" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="K185" s="7" t="s">
+        <v>197</v>
+      </c>
       <c r="L185" s="8" t="s">
         <v>167</v>
       </c>
       <c r="M185" s="8" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="N185" s="8" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="O185" s="7" t="s">
-        <v>39</v>
+        <v>94</v>
       </c>
       <c r="P185" s="7"/>
       <c r="Q185" s="7"/>
       <c r="R185" s="7">
         <v>0</v>
       </c>
-      <c r="S185" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="S185" s="7"/>
       <c r="T185" s="7"/>
       <c r="U185" s="7"/>
       <c r="V185" s="7"/>
       <c r="W185" s="7"/>
       <c r="X185" s="7"/>
-      <c r="Y185" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="Y185" s="7"/>
       <c r="Z185" s="8" t="s">
-        <v>181</v>
+        <v>496</v>
       </c>
       <c r="AA185" s="7" t="s">
         <v>40</v>
@@ -14685,7 +14691,7 @@
         <v>184</v>
       </c>
       <c r="B186" s="3">
-        <v>2026061219</v>
+        <v>2026061276</v>
       </c>
       <c r="C186" s="3">
         <v>1</v>
@@ -14697,49 +14703,49 @@
         <v>345</v>
       </c>
       <c r="F186" s="3" t="s">
-        <v>298</v>
+        <v>66</v>
       </c>
       <c r="G186" s="3" t="s">
-        <v>210</v>
+        <v>70</v>
       </c>
       <c r="H186" s="3" t="s">
-        <v>234</v>
+        <v>303</v>
       </c>
       <c r="I186" s="3" t="s">
-        <v>498</v>
-      </c>
-      <c r="J186" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="K186" s="3" t="s">
-        <v>197</v>
-      </c>
+        <v>497</v>
+      </c>
+      <c r="J186" s="3"/>
+      <c r="K186" s="3"/>
       <c r="L186" s="6" t="s">
         <v>167</v>
       </c>
       <c r="M186" s="6" t="s">
+        <v>498</v>
+      </c>
+      <c r="N186" s="6" t="s">
         <v>499</v>
       </c>
-      <c r="N186" s="6" t="s">
-        <v>500</v>
-      </c>
       <c r="O186" s="3" t="s">
-        <v>94</v>
+        <v>39</v>
       </c>
       <c r="P186" s="3"/>
       <c r="Q186" s="3"/>
       <c r="R186" s="3">
         <v>0</v>
       </c>
-      <c r="S186" s="3"/>
+      <c r="S186" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T186" s="3"/>
       <c r="U186" s="3"/>
       <c r="V186" s="3"/>
       <c r="W186" s="3"/>
       <c r="X186" s="3"/>
-      <c r="Y186" s="3"/>
+      <c r="Y186" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="Z186" s="6" t="s">
-        <v>501</v>
+        <v>181</v>
       </c>
       <c r="AA186" s="3" t="s">
         <v>40</v>
@@ -14753,7 +14759,7 @@
         <v>185</v>
       </c>
       <c r="B187" s="7">
-        <v>2026061283</v>
+        <v>2026061219</v>
       </c>
       <c r="C187" s="7">
         <v>1</v>
@@ -14765,49 +14771,49 @@
         <v>345</v>
       </c>
       <c r="F187" s="7" t="s">
-        <v>66</v>
+        <v>298</v>
       </c>
       <c r="G187" s="7" t="s">
-        <v>303</v>
+        <v>210</v>
       </c>
       <c r="H187" s="7" t="s">
-        <v>315</v>
+        <v>234</v>
       </c>
       <c r="I187" s="7" t="s">
-        <v>498</v>
-      </c>
-      <c r="J187" s="7"/>
-      <c r="K187" s="7"/>
+        <v>500</v>
+      </c>
+      <c r="J187" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="K187" s="7" t="s">
+        <v>197</v>
+      </c>
       <c r="L187" s="8" t="s">
         <v>167</v>
       </c>
       <c r="M187" s="8" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="N187" s="8" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="O187" s="7" t="s">
-        <v>39</v>
+        <v>94</v>
       </c>
       <c r="P187" s="7"/>
       <c r="Q187" s="7"/>
       <c r="R187" s="7">
         <v>0</v>
       </c>
-      <c r="S187" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="S187" s="7"/>
       <c r="T187" s="7"/>
       <c r="U187" s="7"/>
       <c r="V187" s="7"/>
       <c r="W187" s="7"/>
       <c r="X187" s="7"/>
-      <c r="Y187" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="Y187" s="7"/>
       <c r="Z187" s="8" t="s">
-        <v>181</v>
+        <v>503</v>
       </c>
       <c r="AA187" s="7" t="s">
         <v>40</v>
@@ -14821,7 +14827,7 @@
         <v>186</v>
       </c>
       <c r="B188" s="3">
-        <v>2026060905</v>
+        <v>2026061283</v>
       </c>
       <c r="C188" s="3">
         <v>1</v>
@@ -14833,16 +14839,16 @@
         <v>345</v>
       </c>
       <c r="F188" s="3" t="s">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="G188" s="3" t="s">
-        <v>43</v>
+        <v>303</v>
       </c>
       <c r="H188" s="3" t="s">
-        <v>257</v>
+        <v>315</v>
       </c>
       <c r="I188" s="3" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="J188" s="3"/>
       <c r="K188" s="3"/>
@@ -14850,10 +14856,10 @@
         <v>167</v>
       </c>
       <c r="M188" s="6" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="N188" s="6" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="O188" s="3" t="s">
         <v>39</v>
@@ -14889,7 +14895,7 @@
         <v>187</v>
       </c>
       <c r="B189" s="7">
-        <v>2026060510</v>
+        <v>2026060905</v>
       </c>
       <c r="C189" s="7">
         <v>1</v>
@@ -14898,19 +14904,19 @@
         <v>29</v>
       </c>
       <c r="E189" s="7" t="s">
-        <v>505</v>
+        <v>345</v>
       </c>
       <c r="F189" s="7" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="G189" s="7" t="s">
-        <v>506</v>
+        <v>43</v>
       </c>
       <c r="H189" s="7" t="s">
-        <v>507</v>
+        <v>257</v>
       </c>
       <c r="I189" s="7" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="J189" s="7"/>
       <c r="K189" s="7"/>
@@ -14918,10 +14924,10 @@
         <v>167</v>
       </c>
       <c r="M189" s="8" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="N189" s="8" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="O189" s="7" t="s">
         <v>39</v>
@@ -14939,7 +14945,9 @@
       <c r="V189" s="7"/>
       <c r="W189" s="7"/>
       <c r="X189" s="7"/>
-      <c r="Y189" s="7"/>
+      <c r="Y189" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="Z189" s="8" t="s">
         <v>181</v>
       </c>
@@ -14955,7 +14963,7 @@
         <v>188</v>
       </c>
       <c r="B190" s="3">
-        <v>2026060850</v>
+        <v>2026060510</v>
       </c>
       <c r="C190" s="3">
         <v>1</v>
@@ -14964,19 +14972,19 @@
         <v>29</v>
       </c>
       <c r="E190" s="3" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="F190" s="3" t="s">
-        <v>113</v>
+        <v>49</v>
       </c>
       <c r="G190" s="3" t="s">
-        <v>164</v>
+        <v>508</v>
       </c>
       <c r="H190" s="3" t="s">
-        <v>165</v>
+        <v>509</v>
       </c>
       <c r="I190" s="3" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="J190" s="3"/>
       <c r="K190" s="3"/>
@@ -14984,10 +14992,10 @@
         <v>167</v>
       </c>
       <c r="M190" s="6" t="s">
+        <v>511</v>
+      </c>
+      <c r="N190" s="6" t="s">
         <v>512</v>
-      </c>
-      <c r="N190" s="6" t="s">
-        <v>513</v>
       </c>
       <c r="O190" s="3" t="s">
         <v>39</v>
@@ -15001,15 +15009,13 @@
         <v>40</v>
       </c>
       <c r="T190" s="3"/>
-      <c r="U190" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="U190" s="3"/>
       <c r="V190" s="3"/>
       <c r="W190" s="3"/>
       <c r="X190" s="3"/>
       <c r="Y190" s="3"/>
       <c r="Z190" s="6" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="AA190" s="3" t="s">
         <v>40</v>
@@ -15023,7 +15029,7 @@
         <v>189</v>
       </c>
       <c r="B191" s="7">
-        <v>2026060831</v>
+        <v>2026060850</v>
       </c>
       <c r="C191" s="7">
         <v>1</v>
@@ -15032,52 +15038,52 @@
         <v>29</v>
       </c>
       <c r="E191" s="7" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="F191" s="7" t="s">
-        <v>87</v>
+        <v>113</v>
       </c>
       <c r="G191" s="7" t="s">
-        <v>237</v>
+        <v>164</v>
       </c>
       <c r="H191" s="7" t="s">
-        <v>303</v>
+        <v>165</v>
       </c>
       <c r="I191" s="7" t="s">
-        <v>514</v>
-      </c>
-      <c r="J191" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="K191" s="7" t="s">
-        <v>197</v>
-      </c>
+        <v>513</v>
+      </c>
+      <c r="J191" s="7"/>
+      <c r="K191" s="7"/>
       <c r="L191" s="8" t="s">
         <v>167</v>
       </c>
       <c r="M191" s="8" t="s">
+        <v>514</v>
+      </c>
+      <c r="N191" s="8" t="s">
         <v>515</v>
       </c>
-      <c r="N191" s="8" t="s">
-        <v>516</v>
-      </c>
       <c r="O191" s="7" t="s">
-        <v>94</v>
+        <v>39</v>
       </c>
       <c r="P191" s="7"/>
       <c r="Q191" s="7"/>
       <c r="R191" s="7">
         <v>0</v>
       </c>
-      <c r="S191" s="7"/>
+      <c r="S191" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T191" s="7"/>
-      <c r="U191" s="7"/>
+      <c r="U191" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="V191" s="7"/>
       <c r="W191" s="7"/>
       <c r="X191" s="7"/>
       <c r="Y191" s="7"/>
       <c r="Z191" s="8" t="s">
-        <v>517</v>
+        <v>170</v>
       </c>
       <c r="AA191" s="7" t="s">
         <v>40</v>
@@ -15091,7 +15097,7 @@
         <v>190</v>
       </c>
       <c r="B192" s="3">
-        <v>2026061529</v>
+        <v>2026060831</v>
       </c>
       <c r="C192" s="3">
         <v>1</v>
@@ -15100,42 +15106,44 @@
         <v>29</v>
       </c>
       <c r="E192" s="3" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="F192" s="3" t="s">
-        <v>31</v>
+        <v>87</v>
       </c>
       <c r="G192" s="3" t="s">
-        <v>518</v>
+        <v>237</v>
       </c>
       <c r="H192" s="3" t="s">
-        <v>237</v>
+        <v>303</v>
       </c>
       <c r="I192" s="3" t="s">
-        <v>519</v>
-      </c>
-      <c r="J192" s="3"/>
-      <c r="K192" s="3"/>
+        <v>516</v>
+      </c>
+      <c r="J192" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="K192" s="3" t="s">
+        <v>197</v>
+      </c>
       <c r="L192" s="6" t="s">
         <v>167</v>
       </c>
       <c r="M192" s="6" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="N192" s="6" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="O192" s="3" t="s">
-        <v>39</v>
+        <v>94</v>
       </c>
       <c r="P192" s="3"/>
       <c r="Q192" s="3"/>
       <c r="R192" s="3">
         <v>0</v>
       </c>
-      <c r="S192" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="S192" s="3"/>
       <c r="T192" s="3"/>
       <c r="U192" s="3"/>
       <c r="V192" s="3"/>
@@ -15143,7 +15151,7 @@
       <c r="X192" s="3"/>
       <c r="Y192" s="3"/>
       <c r="Z192" s="6" t="s">
-        <v>181</v>
+        <v>519</v>
       </c>
       <c r="AA192" s="3" t="s">
         <v>40</v>
@@ -15157,7 +15165,7 @@
         <v>191</v>
       </c>
       <c r="B193" s="7">
-        <v>2026061260</v>
+        <v>2026061529</v>
       </c>
       <c r="C193" s="7">
         <v>1</v>
@@ -15166,44 +15174,42 @@
         <v>29</v>
       </c>
       <c r="E193" s="7" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="F193" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G193" s="7" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="H193" s="7" t="s">
         <v>237</v>
       </c>
       <c r="I193" s="7" t="s">
-        <v>519</v>
-      </c>
-      <c r="J193" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="K193" s="7" t="s">
-        <v>197</v>
-      </c>
+        <v>521</v>
+      </c>
+      <c r="J193" s="7"/>
+      <c r="K193" s="7"/>
       <c r="L193" s="8" t="s">
         <v>167</v>
       </c>
       <c r="M193" s="8" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="N193" s="8" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="O193" s="7" t="s">
-        <v>94</v>
+        <v>39</v>
       </c>
       <c r="P193" s="7"/>
       <c r="Q193" s="7"/>
       <c r="R193" s="7">
         <v>0</v>
       </c>
-      <c r="S193" s="7"/>
+      <c r="S193" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T193" s="7"/>
       <c r="U193" s="7"/>
       <c r="V193" s="7"/>
@@ -15211,19 +15217,21 @@
       <c r="X193" s="7"/>
       <c r="Y193" s="7"/>
       <c r="Z193" s="8" t="s">
-        <v>522</v>
+        <v>181</v>
       </c>
       <c r="AA193" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AB193" s="7"/>
+      <c r="AB193" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="194" spans="1:28">
       <c r="A194" s="3">
         <v>192</v>
       </c>
       <c r="B194" s="3">
-        <v>2026060149</v>
+        <v>2026061260</v>
       </c>
       <c r="C194" s="3">
         <v>1</v>
@@ -15232,19 +15240,19 @@
         <v>29</v>
       </c>
       <c r="E194" s="3" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="F194" s="3" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="G194" s="3" t="s">
-        <v>164</v>
+        <v>520</v>
       </c>
       <c r="H194" s="3" t="s">
-        <v>523</v>
+        <v>237</v>
       </c>
       <c r="I194" s="3" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="J194" s="3" t="s">
         <v>196</v>
@@ -15256,10 +15264,10 @@
         <v>167</v>
       </c>
       <c r="M194" s="6" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="N194" s="6" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="O194" s="3" t="s">
         <v>94</v>
@@ -15277,21 +15285,19 @@
       <c r="X194" s="3"/>
       <c r="Y194" s="3"/>
       <c r="Z194" s="6" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="AA194" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AB194" s="3">
-        <v>1</v>
-      </c>
+      <c r="AB194" s="3"/>
     </row>
     <row r="195" spans="1:28">
       <c r="A195" s="7">
         <v>193</v>
       </c>
       <c r="B195" s="7">
-        <v>2026060475</v>
+        <v>2026060149</v>
       </c>
       <c r="C195" s="7">
         <v>1</v>
@@ -15300,7 +15306,7 @@
         <v>29</v>
       </c>
       <c r="E195" s="7" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="F195" s="7" t="s">
         <v>49</v>
@@ -15309,33 +15315,35 @@
         <v>164</v>
       </c>
       <c r="H195" s="7" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="I195" s="7" t="s">
-        <v>524</v>
-      </c>
-      <c r="J195" s="7"/>
-      <c r="K195" s="7"/>
+        <v>526</v>
+      </c>
+      <c r="J195" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="K195" s="7" t="s">
+        <v>197</v>
+      </c>
       <c r="L195" s="8" t="s">
         <v>167</v>
       </c>
       <c r="M195" s="8" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="N195" s="8" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="O195" s="7" t="s">
-        <v>39</v>
+        <v>94</v>
       </c>
       <c r="P195" s="7"/>
       <c r="Q195" s="7"/>
       <c r="R195" s="7">
         <v>0</v>
       </c>
-      <c r="S195" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="S195" s="7"/>
       <c r="T195" s="7"/>
       <c r="U195" s="7"/>
       <c r="V195" s="7"/>
@@ -15343,19 +15351,21 @@
       <c r="X195" s="7"/>
       <c r="Y195" s="7"/>
       <c r="Z195" s="8" t="s">
-        <v>181</v>
+        <v>529</v>
       </c>
       <c r="AA195" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AB195" s="7"/>
+      <c r="AB195" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="196" spans="1:28">
       <c r="A196" s="3">
         <v>194</v>
       </c>
       <c r="B196" s="3">
-        <v>2026061222</v>
+        <v>2026060475</v>
       </c>
       <c r="C196" s="3">
         <v>1</v>
@@ -15364,44 +15374,42 @@
         <v>29</v>
       </c>
       <c r="E196" s="3" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="F196" s="3" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="G196" s="3" t="s">
-        <v>106</v>
+        <v>164</v>
       </c>
       <c r="H196" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="I196" s="3" t="s">
-        <v>529</v>
-      </c>
-      <c r="J196" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="K196" s="3" t="s">
-        <v>197</v>
-      </c>
+        <v>526</v>
+      </c>
+      <c r="J196" s="3"/>
+      <c r="K196" s="3"/>
       <c r="L196" s="6" t="s">
         <v>167</v>
       </c>
       <c r="M196" s="6" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="N196" s="6" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="O196" s="3" t="s">
-        <v>94</v>
+        <v>39</v>
       </c>
       <c r="P196" s="3"/>
       <c r="Q196" s="3"/>
       <c r="R196" s="3">
         <v>0</v>
       </c>
-      <c r="S196" s="3"/>
+      <c r="S196" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T196" s="3"/>
       <c r="U196" s="3"/>
       <c r="V196" s="3"/>
@@ -15409,21 +15417,19 @@
       <c r="X196" s="3"/>
       <c r="Y196" s="3"/>
       <c r="Z196" s="6" t="s">
-        <v>532</v>
+        <v>181</v>
       </c>
       <c r="AA196" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AB196" s="3">
-        <v>1</v>
-      </c>
+      <c r="AB196" s="3"/>
     </row>
     <row r="197" spans="1:28">
       <c r="A197" s="7">
         <v>195</v>
       </c>
       <c r="B197" s="7">
-        <v>2026061172</v>
+        <v>2026061222</v>
       </c>
       <c r="C197" s="7">
         <v>1</v>
@@ -15432,34 +15438,34 @@
         <v>29</v>
       </c>
       <c r="E197" s="7" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="F197" s="7" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G197" s="7" t="s">
-        <v>70</v>
+        <v>106</v>
       </c>
       <c r="H197" s="7" t="s">
+        <v>530</v>
+      </c>
+      <c r="I197" s="7" t="s">
+        <v>531</v>
+      </c>
+      <c r="J197" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="K197" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="L197" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="M197" s="8" t="s">
+        <v>532</v>
+      </c>
+      <c r="N197" s="8" t="s">
         <v>533</v>
-      </c>
-      <c r="I197" s="7" t="s">
-        <v>534</v>
-      </c>
-      <c r="J197" s="7" t="s">
-        <v>535</v>
-      </c>
-      <c r="K197" s="7" t="s">
-        <v>536</v>
-      </c>
-      <c r="L197" s="8" t="s">
-        <v>537</v>
-      </c>
-      <c r="M197" s="8" t="s">
-        <v>538</v>
-      </c>
-      <c r="N197" s="8" t="s">
-        <v>539</v>
       </c>
       <c r="O197" s="7" t="s">
         <v>94</v>
@@ -15477,7 +15483,7 @@
       <c r="X197" s="7"/>
       <c r="Y197" s="7"/>
       <c r="Z197" s="8" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="AA197" s="7" t="s">
         <v>40</v>
@@ -15491,7 +15497,7 @@
         <v>196</v>
       </c>
       <c r="B198" s="3">
-        <v>2026061173</v>
+        <v>2026061172</v>
       </c>
       <c r="C198" s="3">
         <v>1</v>
@@ -15500,7 +15506,7 @@
         <v>29</v>
       </c>
       <c r="E198" s="3" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="F198" s="3" t="s">
         <v>42</v>
@@ -15509,25 +15515,25 @@
         <v>70</v>
       </c>
       <c r="H198" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="I198" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="J198" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="K198" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="L198" s="6" t="s">
+        <v>539</v>
+      </c>
+      <c r="M198" s="6" t="s">
+        <v>540</v>
+      </c>
+      <c r="N198" s="6" t="s">
         <v>541</v>
-      </c>
-      <c r="I198" s="3" t="s">
-        <v>542</v>
-      </c>
-      <c r="J198" s="3" t="s">
-        <v>535</v>
-      </c>
-      <c r="K198" s="3" t="s">
-        <v>536</v>
-      </c>
-      <c r="L198" s="6" t="s">
-        <v>537</v>
-      </c>
-      <c r="M198" s="6" t="s">
-        <v>543</v>
-      </c>
-      <c r="N198" s="6" t="s">
-        <v>544</v>
       </c>
       <c r="O198" s="3" t="s">
         <v>94</v>
@@ -15545,47 +15551,115 @@
       <c r="X198" s="3"/>
       <c r="Y198" s="3"/>
       <c r="Z198" s="6" t="s">
+        <v>542</v>
+      </c>
+      <c r="AA198" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB198" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199" spans="1:28">
+      <c r="A199" s="7">
+        <v>197</v>
+      </c>
+      <c r="B199" s="7">
+        <v>2026061173</v>
+      </c>
+      <c r="C199" s="7">
+        <v>1</v>
+      </c>
+      <c r="D199" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E199" s="7" t="s">
+        <v>507</v>
+      </c>
+      <c r="F199" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G199" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="H199" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="I199" s="7" t="s">
+        <v>544</v>
+      </c>
+      <c r="J199" s="7" t="s">
+        <v>537</v>
+      </c>
+      <c r="K199" s="7" t="s">
+        <v>538</v>
+      </c>
+      <c r="L199" s="8" t="s">
+        <v>539</v>
+      </c>
+      <c r="M199" s="8" t="s">
         <v>545</v>
       </c>
-      <c r="AA198" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB198" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="199" spans="1:28">
-      <c r="A199" s="9"/>
-      <c r="B199" s="9"/>
-      <c r="C199" s="9"/>
-      <c r="D199" s="9"/>
-      <c r="E199" s="9"/>
-      <c r="F199" s="9"/>
-      <c r="G199" s="9"/>
-      <c r="H199" s="9"/>
-      <c r="I199" s="9"/>
-      <c r="J199" s="9"/>
-      <c r="K199" s="9"/>
-      <c r="L199" s="10"/>
-      <c r="M199" s="10"/>
-      <c r="N199" s="10"/>
-      <c r="O199" s="9"/>
-      <c r="P199" s="9"/>
-      <c r="Q199" s="9"/>
-      <c r="R199" s="9"/>
-      <c r="S199" s="9"/>
-      <c r="T199" s="9"/>
-      <c r="U199" s="9"/>
-      <c r="V199" s="9"/>
-      <c r="W199" s="9"/>
-      <c r="X199" s="9"/>
-      <c r="Y199" s="9"/>
-      <c r="Z199" s="10"/>
-      <c r="AA199" s="9" t="s">
+      <c r="N199" s="8" t="s">
         <v>546</v>
       </c>
-      <c r="AB199" s="9">
-        <v>119</v>
+      <c r="O199" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="P199" s="7"/>
+      <c r="Q199" s="7"/>
+      <c r="R199" s="7">
+        <v>0</v>
+      </c>
+      <c r="S199" s="7"/>
+      <c r="T199" s="7"/>
+      <c r="U199" s="7"/>
+      <c r="V199" s="7"/>
+      <c r="W199" s="7"/>
+      <c r="X199" s="7"/>
+      <c r="Y199" s="7"/>
+      <c r="Z199" s="8" t="s">
+        <v>547</v>
+      </c>
+      <c r="AA199" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB199" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="200" spans="1:28">
+      <c r="A200" s="9"/>
+      <c r="B200" s="9"/>
+      <c r="C200" s="9"/>
+      <c r="D200" s="9"/>
+      <c r="E200" s="9"/>
+      <c r="F200" s="9"/>
+      <c r="G200" s="9"/>
+      <c r="H200" s="9"/>
+      <c r="I200" s="9"/>
+      <c r="J200" s="9"/>
+      <c r="K200" s="9"/>
+      <c r="L200" s="10"/>
+      <c r="M200" s="10"/>
+      <c r="N200" s="10"/>
+      <c r="O200" s="9"/>
+      <c r="P200" s="9"/>
+      <c r="Q200" s="9"/>
+      <c r="R200" s="9"/>
+      <c r="S200" s="9"/>
+      <c r="T200" s="9"/>
+      <c r="U200" s="9"/>
+      <c r="V200" s="9"/>
+      <c r="W200" s="9"/>
+      <c r="X200" s="9"/>
+      <c r="Y200" s="9"/>
+      <c r="Z200" s="10"/>
+      <c r="AA200" s="9" t="s">
+        <v>548</v>
+      </c>
+      <c r="AB200" s="9">
+        <v>120</v>
       </c>
     </row>
   </sheetData>
